--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF87"/>
+  <dimension ref="A1:AJ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,40 +546,60 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>sample-ID</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>N_P</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLA </t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>t13C_cell</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Ci</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Ci/Ca</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>iWUE (μmol/mol)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>annual_precipitation_mm</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>elevation_m</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_annual_temperature_C</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>C:N</t>
         </is>
@@ -662,28 +682,32 @@
       <c r="X2" t="n">
         <v>0.01276762889372977</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
         <v>19.11317674246398</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AD2" t="n">
         <v>296.6970994146122</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AE2" t="n">
         <v>0.701222219552234</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AF2" t="n">
         <v>79.01070655336738</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AG2" t="n">
         <v>4500</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AH2" t="n">
         <v>3000</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AI2" t="n">
         <v>10</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -770,28 +794,32 @@
       <c r="X3" t="n">
         <v>0.0125482750406745</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
         <v>25.186292914119</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AD3" t="n">
         <v>410.3971822492604</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
         <v>0.9699441740502436</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
         <v>7.948154781712265</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AG3" t="n">
         <v>2000</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
         <v>1000</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AI3" t="n">
         <v>19</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AJ3" t="n">
         <v>25.57873717795717</v>
       </c>
     </row>
@@ -880,28 +908,32 @@
       <c r="X4" t="n">
         <v>0.008267697970525723</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
         <v>19.55357506559249</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AD4" t="n">
         <v>304.9421789429207</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
         <v>0.7207088710180973</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
         <v>73.85753184817457</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AG4" t="n">
         <v>4500</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AH4" t="n">
         <v>3000</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AI4" t="n">
         <v>10</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AJ4" t="n">
         <v>42.49161457666214</v>
       </c>
     </row>
@@ -982,28 +1014,32 @@
       <c r="X5" t="n">
         <v>0.1901166210246399</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
         <v>22.81594444937604</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
         <v>366.0198298043771</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AE5" t="n">
         <v>0.8650614986191394</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AF5" t="n">
         <v>35.68400005976433</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AG5" t="n">
         <v>2000</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AH5" t="n">
         <v>1000</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AI5" t="n">
         <v>19</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1082,28 +1118,32 @@
       <c r="X6" t="n">
         <v>0.01718012143940277</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
         <v>24.65624529971977</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AD6" t="n">
         <v>400.4737004715233</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AE6" t="n">
         <v>0.9464907397847914</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
         <v>14.15033089279794</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AG6" t="n">
         <v>2000</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AH6" t="n">
         <v>1000</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AI6" t="n">
         <v>19</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1190,28 +1230,32 @@
       <c r="X7" t="n">
         <v>0.004417864669110647</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
         <v>17.76290045603007</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AD7" t="n">
         <v>271.4174042337841</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
         <v>0.6414754812144504</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AF7" t="n">
         <v>94.81051604138494</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AG7" t="n">
         <v>4500</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="n">
         <v>3000</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AI7" t="n">
         <v>10</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AJ7" t="n">
         <v>26.51846199848626</v>
       </c>
     </row>
@@ -1292,28 +1336,32 @@
       <c r="X8" t="n">
         <v>0.03947854133799732</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
         <v>22.60483910589158</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AD8" t="n">
         <v>362.0675433072</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
         <v>0.8557205542171721</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AF8" t="n">
         <v>38.15417912050003</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AG8" t="n">
         <v>2000</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AH8" t="n">
         <v>1000</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AI8" t="n">
         <v>19</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1400,28 +1448,32 @@
       <c r="X9" t="n">
         <v>0.05995862311665734</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
         <v>22.01420747547882</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AD9" t="n">
         <v>351.0098155436303</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
         <v>0.8295864112785546</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AF9" t="n">
         <v>45.06525897273107</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AG9" t="n">
         <v>2000</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AH9" t="n">
         <v>1000</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
         <v>19</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AJ9" t="n">
         <v>28.28424514537473</v>
       </c>
     </row>
@@ -1510,28 +1562,32 @@
       <c r="X10" t="n">
         <v>0.01227184630308513</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
         <v>24.68803269978491</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AD10" t="n">
         <v>401.0688199980315</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AE10" t="n">
         <v>0.9478972619115674</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
         <v>13.77838118873034</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AG10" t="n">
         <v>2000</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AH10" t="n">
         <v>1000</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
         <v>19</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AJ10" t="n">
         <v>28.01632724421026</v>
       </c>
     </row>
@@ -1620,28 +1676,32 @@
       <c r="X11" t="n">
         <v>0.01414473817944922</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
         <v>19.59553761511313</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AD11" t="n">
         <v>305.727796280313</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AE11" t="n">
         <v>0.7225656209968867</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AF11" t="n">
         <v>73.36652101230439</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AG11" t="n">
         <v>4500</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AH11" t="n">
         <v>3000</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AI11" t="n">
         <v>10</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AJ11" t="n">
         <v>39.94038297769039</v>
       </c>
     </row>
@@ -1718,36 +1778,44 @@
       <c r="T12" t="n">
         <v>1.02</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>0.47</v>
+      </c>
       <c r="V12" t="n">
         <v>30.4822848</v>
       </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>64.85592510638298</v>
+      </c>
       <c r="X12" t="n">
         <v>0.009764266316897927</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
         <v>18.20213228729963</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AD12" t="n">
         <v>279.6406448548101</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AE12" t="n">
         <v>0.6609105179962894</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AF12" t="n">
         <v>89.67099065324369</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AG12" t="n">
         <v>4500</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AH12" t="n">
         <v>3000</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AI12" t="n">
         <v>10</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AJ12" t="n">
         <v>41.33398260330504</v>
       </c>
     </row>
@@ -1828,28 +1896,32 @@
       <c r="X13" t="n">
         <v>0.02269800692218625</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
         <v>17.90926895467806</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AD13" t="n">
         <v>274.157696029672</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AE13" t="n">
         <v>0.6479519634555122</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AF13" t="n">
         <v>93.097833668955</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AG13" t="n">
         <v>4500</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AH13" t="n">
         <v>3000</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AI13" t="n">
         <v>10</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1936,28 +2008,32 @@
       <c r="X14" t="n">
         <v>0.001963495408493621</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
         <v>17.9720111996877</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AD14" t="n">
         <v>275.3323480951343</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AE14" t="n">
         <v>0.650728168986912</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AF14" t="n">
         <v>92.36367612804105</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AG14" t="n">
         <v>4500</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AH14" t="n">
         <v>3000</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AI14" t="n">
         <v>10</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AJ14" t="n">
         <v>24.51611901423017</v>
       </c>
     </row>
@@ -2046,28 +2122,32 @@
       <c r="X15" t="n">
         <v>0.04072076634313489</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
         <v>20.803439861134</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AD15" t="n">
         <v>328.3419833873751</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AE15" t="n">
         <v>0.7760126230332086</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AF15" t="n">
         <v>59.23265407039059</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AG15" t="n">
         <v>2000</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AH15" t="n">
         <v>1000</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AI15" t="n">
         <v>19</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AJ15" t="n">
         <v>29.77748860325364</v>
       </c>
     </row>
@@ -2148,28 +2228,32 @@
       <c r="X16" t="n">
         <v>0.1237858191349084</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
         <v>19.66898038896892</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AD16" t="n">
         <v>307.1027822405658</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AE16" t="n">
         <v>0.7258153012559927</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AF16" t="n">
         <v>72.50715478714635</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AG16" t="n">
         <v>2000</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AH16" t="n">
         <v>1000</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AI16" t="n">
         <v>19</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2256,28 +2340,32 @@
       <c r="X17" t="n">
         <v>0.006807524975045357</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
         <v>22.75260369502616</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AD17" t="n">
         <v>364.833972525703</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AE17" t="n">
         <v>0.8622588103735694</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AF17" t="n">
         <v>36.42516085893565</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AG17" t="n">
         <v>2000</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AH17" t="n">
         <v>1000</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AI17" t="n">
         <v>19</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AJ17" t="n">
         <v>28.39448648615613</v>
       </c>
     </row>
@@ -2366,28 +2454,32 @@
       <c r="X18" t="n">
         <v>0.07068583470577035</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
         <v>22.59428612618935</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AD18" t="n">
         <v>361.8699718080911</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AE18" t="n">
         <v>0.8552536082126486</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AF18" t="n">
         <v>38.27766130744304</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AG18" t="n">
         <v>2000</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AH18" t="n">
         <v>1000</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AI18" t="n">
         <v>19</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AJ18" t="n">
         <v>29.17653851247548</v>
       </c>
     </row>
@@ -2476,28 +2568,32 @@
       <c r="X19" t="n">
         <v>0.01504395624468623</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
         <v>24.82580089356817</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AD19" t="n">
         <v>403.6480980164968</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AE19" t="n">
         <v>0.9539931996895877</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>12.16633242718948</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AG19" t="n">
         <v>2000</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AH19" t="n">
         <v>1000</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AI19" t="n">
         <v>19</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AJ19" t="n">
         <v>26.66776442666213</v>
       </c>
     </row>
@@ -2586,28 +2682,32 @@
       <c r="X20" t="n">
         <v>0.04614823678934805</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
         <v>17.7524471739778</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AD20" t="n">
         <v>271.2216992609755</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AE20" t="n">
         <v>0.6410129466103676</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AF20" t="n">
         <v>94.93283164939032</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AG20" t="n">
         <v>2000</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
         <v>1000</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AI20" t="n">
         <v>19</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AJ20" t="n">
         <v>30.75436275117814</v>
       </c>
     </row>
@@ -2684,36 +2784,44 @@
       <c r="T21" t="n">
         <v>13.68</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>3.6</v>
+      </c>
       <c r="V21" t="n">
         <v>250.358</v>
       </c>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>69.54388888888889</v>
+      </c>
       <c r="X21" t="n">
         <v>0.00796432222195019</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
         <v>14.64690627988655</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AD21" t="n">
         <v>213.0801707730827</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AE21" t="n">
         <v>0.5035996327125247</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AF21" t="n">
         <v>131.2712869543233</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AG21" t="n">
         <v>4500</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AH21" t="n">
         <v>3000</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AI21" t="n">
         <v>10</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AJ21" t="n">
         <v>22.9540859657499</v>
       </c>
     </row>
@@ -2802,28 +2910,32 @@
       <c r="X22" t="n">
         <v>0.02592983397076879</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
         <v>18.89312022333272</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AD22" t="n">
         <v>292.5772301833425</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AE22" t="n">
         <v>0.6914852054313819</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>81.58562482291096</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AG22" t="n">
         <v>4500</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AH22" t="n">
         <v>3000</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AI22" t="n">
         <v>10</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AJ22" t="n">
         <v>53.02578826881873</v>
       </c>
     </row>
@@ -2904,28 +3016,32 @@
       <c r="X23" t="n">
         <v>0.02208798031469382</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
         <v>19.28090266311447</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AD23" t="n">
         <v>299.8372420584309</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AE23" t="n">
         <v>0.7086437204659728</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AF23" t="n">
         <v>77.04811740098066</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AG23" t="n">
         <v>4500</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AH23" t="n">
         <v>3000</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AI23" t="n">
         <v>10</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3012,28 +3128,32 @@
       <c r="X24" t="n">
         <v>0.004071504079052372</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
         <v>16.81253028844674</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AD24" t="n">
         <v>253.6246988542728</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AE24" t="n">
         <v>0.5994237038877543</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AF24" t="n">
         <v>105.9309569035795</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AG24" t="n">
         <v>4500</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AH24" t="n">
         <v>3000</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AI24" t="n">
         <v>10</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AJ24" t="n">
         <v>30.95258432083552</v>
       </c>
     </row>
@@ -3122,28 +3242,32 @@
       <c r="X25" t="n">
         <v>0.1164156427695868</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
         <v>23.62951442295773</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AD25" t="n">
         <v>381.2513799301195</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AE25" t="n">
         <v>0.9010601700165592</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AF25" t="n">
         <v>26.16428123117529</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AG25" t="n">
         <v>2000</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AH25" t="n">
         <v>1000</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AI25" t="n">
         <v>19</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AJ25" t="n">
         <v>30.76750734875213</v>
       </c>
     </row>
@@ -3224,28 +3348,32 @@
       <c r="X26" t="n">
         <v>0.03573317384629572</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
         <v>23.68238839450821</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
         <v>382.2412794767715</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AE26" t="n">
         <v>0.9033997262798548</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AF26" t="n">
         <v>25.54559401451779</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AG26" t="n">
         <v>2000</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AH26" t="n">
         <v>1000</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AI26" t="n">
         <v>19</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3332,28 +3460,32 @@
       <c r="X27" t="n">
         <v>0.07942260387540356</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
         <v>21.9193481653363</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AD27" t="n">
         <v>349.2338720055861</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AE27" t="n">
         <v>0.8253890966704784</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AF27" t="n">
         <v>46.17522368400866</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AG27" t="n">
         <v>2000</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AH27" t="n">
         <v>1000</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AI27" t="n">
         <v>19</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AJ27" t="n">
         <v>19.36748669969131</v>
       </c>
     </row>
@@ -3442,28 +3574,32 @@
       <c r="X28" t="n">
         <v>0.004071504079052372</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
         <v>19.0293344803118</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AD28" t="n">
         <v>295.127415601179</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AE28" t="n">
         <v>0.6975123849437308</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AF28" t="n">
         <v>79.99175893676312</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AG28" t="n">
         <v>4500</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AH28" t="n">
         <v>3000</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AI28" t="n">
         <v>10</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AJ28" t="n">
         <v>31.8250079552666</v>
       </c>
     </row>
@@ -3552,28 +3688,32 @@
       <c r="X29" t="n">
         <v>0.0107145902406272</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
         <v>19.89986943123572</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AD29" t="n">
         <v>311.4254565463651</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AE29" t="n">
         <v>0.7360316305598332</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AF29" t="n">
         <v>69.80548334602179</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AG29" t="n">
         <v>2000</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AH29" t="n">
         <v>1000</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AI29" t="n">
         <v>19</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AJ29" t="n">
         <v>20.74216706763612</v>
       </c>
     </row>
@@ -3654,28 +3794,32 @@
       <c r="X30" t="n">
         <v>0.02904346644974163</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
         <v>22.28834443263765</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AD30" t="n">
         <v>356.142171628382</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AE30" t="n">
         <v>0.84171636513514</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AF30" t="n">
         <v>41.85753641976126</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AG30" t="n">
         <v>2000</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AH30" t="n">
         <v>1000</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AI30" t="n">
         <v>19</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -3762,28 +3906,32 @@
       <c r="X31" t="n">
         <v>0.008543946066537507</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
         <v>19.24944984776795</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AD31" t="n">
         <v>299.2483865830534</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AE31" t="n">
         <v>0.7072520029727636</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AF31" t="n">
         <v>77.41615207309164</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AG31" t="n">
         <v>4500</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AH31" t="n">
         <v>3000</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AI31" t="n">
         <v>10</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AJ31" t="n">
         <v>42.97256368979243</v>
       </c>
     </row>
@@ -3872,28 +4020,32 @@
       <c r="X32" t="n">
         <v>0.05603219778634775</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
         <v>22.43601756348215</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AD32" t="n">
         <v>358.9068885767976</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AE32" t="n">
         <v>0.8482505744645428</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AF32" t="n">
         <v>40.12958832700149</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AG32" t="n">
         <v>2000</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AH32" t="n">
         <v>1000</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AI32" t="n">
         <v>19</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AJ32" t="n">
         <v>20.62022678542599</v>
       </c>
     </row>
@@ -3982,28 +4134,32 @@
       <c r="X33" t="n">
         <v>0.1092716610753235</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="n">
         <v>22.54152449461855</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AD33" t="n">
         <v>360.882175475775</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AE33" t="n">
         <v>0.8529190227449143</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AF33" t="n">
         <v>38.89503401514064</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AG33" t="n">
         <v>2000</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AH33" t="n">
         <v>1000</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AI33" t="n">
         <v>19</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AJ33" t="n">
         <v>21.99115496636606</v>
       </c>
     </row>
@@ -4092,28 +4248,32 @@
       <c r="X34" t="n">
         <v>0.05674771907514772</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
         <v>20.89809210718812</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AD34" t="n">
         <v>330.1140502987685</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AE34" t="n">
         <v>0.780200775513479</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AF34" t="n">
         <v>58.12511225076972</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AG34" t="n">
         <v>4500</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AH34" t="n">
         <v>3000</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AI34" t="n">
         <v>10</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AJ34" t="n">
         <v>43.87185925469004</v>
       </c>
     </row>
@@ -4202,28 +4362,32 @@
       <c r="X35" t="n">
         <v>0.01278766440087804</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
         <v>20.61418801318365</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AD35" t="n">
         <v>324.7988351615933</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AE35" t="n">
         <v>0.7676386474601838</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AF35" t="n">
         <v>61.4471217115042</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AG35" t="n">
         <v>2000</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AH35" t="n">
         <v>1000</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AI35" t="n">
         <v>19</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AJ35" t="n">
         <v>24.17983322666046</v>
       </c>
     </row>
@@ -4312,28 +4476,32 @@
       <c r="X36" t="n">
         <v>0.01278766440087804</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
         <v>22.96377005791446</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AD36" t="n">
         <v>368.7874014201395</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AE36" t="n">
         <v>0.8716024547491579</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AF36" t="n">
         <v>33.95426779991279</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AG36" t="n">
         <v>2000</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AH36" t="n">
         <v>1000</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AI36" t="n">
         <v>19</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AJ36" t="n">
         <v>24.17983322666046</v>
       </c>
     </row>
@@ -4422,28 +4590,32 @@
       <c r="X37" t="n">
         <v>0.009764266316897927</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
         <v>20.22539061435029</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AD37" t="n">
         <v>317.5198213565269</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AE37" t="n">
         <v>0.7504352227330441</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AF37" t="n">
         <v>65.99650533967068</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AG37" t="n">
         <v>4500</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AH37" t="n">
         <v>3000</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AI37" t="n">
         <v>10</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AJ37" t="n">
         <v>45.72171601638512</v>
       </c>
     </row>
@@ -4532,28 +4704,32 @@
       <c r="X38" t="n">
         <v>0.01115943976037552</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
         <v>20.43551457876363</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AD38" t="n">
         <v>321.4537346037078</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AE38" t="n">
         <v>0.7597327432823072</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AF38" t="n">
         <v>63.53780956018262</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AG38" t="n">
         <v>4500</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AH38" t="n">
         <v>3000</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AI38" t="n">
         <v>10</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AJ38" t="n">
         <v>32.47607689365352</v>
       </c>
     </row>
@@ -4642,28 +4818,32 @@
       <c r="X39" t="n">
         <v>0.002042820622996763</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
         <v>18.33816184036092</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AD39" t="n">
         <v>282.1873722701715</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AE39" t="n">
         <v>0.6669295247689127</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AF39" t="n">
         <v>88.07928601864285</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AG39" t="n">
         <v>4500</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AH39" t="n">
         <v>3000</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AI39" t="n">
         <v>10</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AJ39" t="n">
         <v>31.24223026798137</v>
       </c>
     </row>
@@ -4752,28 +4932,32 @@
       <c r="X40" t="n">
         <v>0.07301376271606201</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
         <v>23.46035441231151</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AD40" t="n">
         <v>378.0843884418694</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AE40" t="n">
         <v>0.8935752137932749</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AF40" t="n">
         <v>28.14365091133165</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AG40" t="n">
         <v>2000</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AH40" t="n">
         <v>1000</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AI40" t="n">
         <v>19</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AJ40" t="n">
         <v>22.29074496544098</v>
       </c>
     </row>
@@ -4862,28 +5046,32 @@
       <c r="X41" t="n">
         <v>0.01615058225691323</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
         <v>19.95235879694914</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AD41" t="n">
         <v>312.4081555530808</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AE41" t="n">
         <v>0.7383541688657369</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AF41" t="n">
         <v>69.19129646682448</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AG41" t="n">
         <v>4500</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AH41" t="n">
         <v>3000</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AI41" t="n">
         <v>10</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AJ41" t="n">
         <v>40.95714602250388</v>
       </c>
     </row>
@@ -4972,28 +5160,32 @@
       <c r="X42" t="n">
         <v>0.01476266589246543</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
         <v>23.41807314508799</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AD42" t="n">
         <v>377.2928041135301</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AE42" t="n">
         <v>0.8917043612612615</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AF42" t="n">
         <v>28.63839111654372</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AG42" t="n">
         <v>2000</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AH42" t="n">
         <v>1000</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AI42" t="n">
         <v>19</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AJ42" t="n">
         <v>32.65053512949007</v>
       </c>
     </row>
@@ -5082,28 +5274,32 @@
       <c r="X43" t="n">
         <v>0.01476266589246543</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
         <v>23.69296384429431</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AD43" t="n">
         <v>382.4392716578375</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AE43" t="n">
         <v>0.9038676665358769</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AF43" t="n">
         <v>25.42184890135152</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AG43" t="n">
         <v>2000</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AH43" t="n">
         <v>1000</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AI43" t="n">
         <v>19</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AJ43" t="n">
         <v>32.65053512949007</v>
       </c>
     </row>
@@ -5192,28 +5388,32 @@
       <c r="X44" t="n">
         <v>0.01476266589246543</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="n">
         <v>23.41807314508799</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AD44" t="n">
         <v>377.2928041135301</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AE44" t="n">
         <v>0.8917043612612615</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AF44" t="n">
         <v>28.63839111654372</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AG44" t="n">
         <v>2000</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AH44" t="n">
         <v>1000</v>
       </c>
-      <c r="AE44" t="n">
+      <c r="AI44" t="n">
         <v>19</v>
       </c>
-      <c r="AF44" t="n">
+      <c r="AJ44" t="n">
         <v>32.65053512949007</v>
       </c>
     </row>
@@ -5302,28 +5502,32 @@
       <c r="X45" t="n">
         <v>0.01476266589246543</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="n">
         <v>23.69296384429431</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AD45" t="n">
         <v>382.4392716578375</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AE45" t="n">
         <v>0.9038676665358769</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AF45" t="n">
         <v>25.42184890135152</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AG45" t="n">
         <v>2000</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AH45" t="n">
         <v>1000</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AI45" t="n">
         <v>19</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AJ45" t="n">
         <v>32.65053512949007</v>
       </c>
     </row>
@@ -5412,28 +5616,32 @@
       <c r="X46" t="n">
         <v>0.008445928375745504</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
         <v>21.61381013660498</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AD46" t="n">
         <v>343.5136291855942</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AE46" t="n">
         <v>0.8118697148682075</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AF46" t="n">
         <v>49.75037544650364</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AG46" t="n">
         <v>2000</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AH46" t="n">
         <v>1000</v>
       </c>
-      <c r="AE46" t="n">
+      <c r="AI46" t="n">
         <v>19</v>
       </c>
-      <c r="AF46" t="n">
+      <c r="AJ46" t="n">
         <v>34.94837353504887</v>
       </c>
     </row>
@@ -5522,28 +5730,32 @@
       <c r="X47" t="n">
         <v>0.0166728170577011</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
         <v>21.83504356012952</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AD47" t="n">
         <v>347.6555322662459</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AE47" t="n">
         <v>0.8216588044046917</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AF47" t="n">
         <v>47.16168602109633</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AG47" t="n">
         <v>2000</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AH47" t="n">
         <v>1000</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AI47" t="n">
         <v>19</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AJ47" t="n">
         <v>27.61940167646294</v>
       </c>
     </row>
@@ -5632,28 +5844,32 @@
       <c r="X48" t="n">
         <v>0.03905706526759171</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
         <v>23.03769888705348</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AD48" t="n">
         <v>370.1714872435274</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AE48" t="n">
         <v>0.874873641879203</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AF48" t="n">
         <v>33.08921416029539</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AG48" t="n">
         <v>2000</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AH48" t="n">
         <v>1000</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AI48" t="n">
         <v>19</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AJ48" t="n">
         <v>31.61114054973259</v>
       </c>
     </row>
@@ -5742,28 +5958,32 @@
       <c r="X49" t="n">
         <v>0.009211848664690696</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
         <v>22.81594444937604</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AD49" t="n">
         <v>366.0198298043771</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AE49" t="n">
         <v>0.8650614986191394</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AF49" t="n">
         <v>35.68400005976433</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AG49" t="n">
         <v>2000</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AH49" t="n">
         <v>1000</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AI49" t="n">
         <v>19</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AJ49" t="n">
         <v>32.58259222016648</v>
       </c>
     </row>
@@ -5852,28 +6072,32 @@
       <c r="X50" t="n">
         <v>0.03401214655880617</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
         <v>19.00837607025699</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AD50" t="n">
         <v>294.7350350024944</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AE50" t="n">
         <v>0.696585021666969</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AF50" t="n">
         <v>80.23699681094099</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AG50" t="n">
         <v>4500</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AH50" t="n">
         <v>3000</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AI50" t="n">
         <v>10</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="AJ50" t="n">
         <v>37.10169593659131</v>
       </c>
     </row>
@@ -5962,28 +6186,32 @@
       <c r="X51" t="n">
         <v>0.01437756946498839</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
         <v>20.35145460742419</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AD51" t="n">
         <v>319.879974867482</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AE51" t="n">
         <v>0.7560132755239248</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AF51" t="n">
         <v>64.52140939532377</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AG51" t="n">
         <v>4500</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AH51" t="n">
         <v>3000</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AI51" t="n">
         <v>10</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AJ51" t="n">
         <v>46.62061318477368</v>
       </c>
     </row>
@@ -6072,28 +6300,32 @@
       <c r="X52" t="n">
         <v>0.003421194399759284</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="n">
         <v>18.4009569706375</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AD52" t="n">
         <v>283.3630144466514</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AE52" t="n">
         <v>0.6697080703563723</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AF52" t="n">
         <v>87.34450965834283</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AG52" t="n">
         <v>4500</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AH52" t="n">
         <v>3000</v>
       </c>
-      <c r="AE52" t="n">
+      <c r="AI52" t="n">
         <v>10</v>
       </c>
-      <c r="AF52" t="n">
+      <c r="AJ52" t="n">
         <v>27.64252745359938</v>
       </c>
     </row>
@@ -6182,28 +6414,32 @@
       <c r="X53" t="n">
         <v>0.002733971006786517</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="n">
         <v>17.05256609052653</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AD53" t="n">
         <v>258.1186175952207</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AE53" t="n">
         <v>0.6100447570771258</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AF53" t="n">
         <v>103.1222576904871</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AG53" t="n">
         <v>4500</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AH53" t="n">
         <v>3000</v>
       </c>
-      <c r="AE53" t="n">
+      <c r="AI53" t="n">
         <v>10</v>
       </c>
-      <c r="AF53" t="n">
+      <c r="AJ53" t="n">
         <v>31.43663314688067</v>
       </c>
     </row>
@@ -6292,28 +6528,32 @@
       <c r="X54" t="n">
         <v>0.009764266316897927</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="n">
         <v>22.73149185356439</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AD54" t="n">
         <v>364.4387194043813</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AE54" t="n">
         <v>0.8613246580964998</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AF54" t="n">
         <v>36.67219405976167</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AG54" t="n">
         <v>2000</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AH54" t="n">
         <v>1000</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AI54" t="n">
         <v>19</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AJ54" t="n">
         <v>16.47515809594594</v>
       </c>
     </row>
@@ -6402,28 +6642,32 @@
       <c r="X55" t="n">
         <v>0.06770207566709691</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
         <v>22.59428612618935</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AD55" t="n">
         <v>361.8699718080911</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AE55" t="n">
         <v>0.8552536082126486</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AF55" t="n">
         <v>38.27766130744304</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AG55" t="n">
         <v>2000</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AH55" t="n">
         <v>1000</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AI55" t="n">
         <v>19</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AJ55" t="n">
         <v>17.18961723916043</v>
       </c>
     </row>
@@ -6512,28 +6756,32 @@
       <c r="X56" t="n">
         <v>0.001734944542944963</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="n">
         <v>17.96155362172935</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AD56" t="n">
         <v>275.1365626949366</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AE56" t="n">
         <v>0.6502654442984893</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AF56" t="n">
         <v>92.4860420031646</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AG56" t="n">
         <v>4500</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AH56" t="n">
         <v>3000</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AI56" t="n">
         <v>10</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AJ56" t="n">
         <v>34.16916319918331</v>
       </c>
     </row>
@@ -6622,28 +6870,32 @@
       <c r="X57" t="n">
         <v>0.01435632444466849</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="n">
         <v>23.83046457818877</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AD57" t="n">
         <v>385.0135423274145</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AE57" t="n">
         <v>0.9099517698055434</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AF57" t="n">
         <v>23.8129297328659</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AG57" t="n">
         <v>2000</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AH57" t="n">
         <v>1000</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AI57" t="n">
         <v>19</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AJ57" t="n">
         <v>31.13148059335148</v>
       </c>
     </row>
@@ -6732,28 +6984,32 @@
       <c r="X58" t="n">
         <v>0.009399927962879482</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="n">
         <v>18.88264371189142</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AD58" t="n">
         <v>292.3810903129652</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AE58" t="n">
         <v>0.6910216429782269</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AF58" t="n">
         <v>81.70821224189675</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AG58" t="n">
         <v>4500</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AH58" t="n">
         <v>3000</v>
       </c>
-      <c r="AE58" t="n">
+      <c r="AI58" t="n">
         <v>10</v>
       </c>
-      <c r="AF58" t="n">
+      <c r="AJ58" t="n">
         <v>42.2826116943056</v>
       </c>
     </row>
@@ -6842,28 +7098,32 @@
       <c r="X59" t="n">
         <v>0.02153825657818705</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="n">
         <v>23.10107496024945</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AD59" t="n">
         <v>371.3580057569964</v>
       </c>
-      <c r="AA59" t="n">
+      <c r="AE59" t="n">
         <v>0.8776778929055734</v>
       </c>
-      <c r="AB59" t="n">
+      <c r="AF59" t="n">
         <v>32.34764008937727</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AG59" t="n">
         <v>2000</v>
       </c>
-      <c r="AD59" t="n">
+      <c r="AH59" t="n">
         <v>1000</v>
       </c>
-      <c r="AE59" t="n">
+      <c r="AI59" t="n">
         <v>19</v>
       </c>
-      <c r="AF59" t="n">
+      <c r="AJ59" t="n">
         <v>30.4083735401035</v>
       </c>
     </row>
@@ -6952,28 +7212,32 @@
       <c r="X60" t="n">
         <v>0.01387202437517272</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="n">
         <v>21.12953817664699</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AD60" t="n">
         <v>334.447153194453</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AE60" t="n">
         <v>0.7904417520382077</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AF60" t="n">
         <v>55.41692294096688</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AG60" t="n">
         <v>4500</v>
       </c>
-      <c r="AD60" t="n">
+      <c r="AH60" t="n">
         <v>3000</v>
       </c>
-      <c r="AE60" t="n">
+      <c r="AI60" t="n">
         <v>10</v>
       </c>
-      <c r="AF60" t="n">
+      <c r="AJ60" t="n">
         <v>41.39388452825129</v>
       </c>
     </row>
@@ -7062,28 +7326,32 @@
       <c r="X61" t="n">
         <v>0.0021237166338267</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
         <v>20.5721415762045</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AD61" t="n">
         <v>324.0116472942274</v>
       </c>
-      <c r="AA61" t="n">
+      <c r="AE61" t="n">
         <v>0.7657781856469476</v>
       </c>
-      <c r="AB61" t="n">
+      <c r="AF61" t="n">
         <v>61.93911412860785</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AG61" t="n">
         <v>4500</v>
       </c>
-      <c r="AD61" t="n">
+      <c r="AH61" t="n">
         <v>3000</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AI61" t="n">
         <v>10</v>
       </c>
-      <c r="AF61" t="n">
+      <c r="AJ61" t="n">
         <v>28.16106955669684</v>
       </c>
     </row>
@@ -7172,28 +7440,32 @@
       <c r="X62" t="n">
         <v>0.003685284532201676</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
         <v>17.00037475445168</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="AD62" t="n">
         <v>257.1414982602312</v>
       </c>
-      <c r="AA62" t="n">
+      <c r="AE62" t="n">
         <v>0.6077354059233715</v>
       </c>
-      <c r="AB62" t="n">
+      <c r="AF62" t="n">
         <v>103.7329572748555</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AG62" t="n">
         <v>4500</v>
       </c>
-      <c r="AD62" t="n">
+      <c r="AH62" t="n">
         <v>3000</v>
       </c>
-      <c r="AE62" t="n">
+      <c r="AI62" t="n">
         <v>10</v>
       </c>
-      <c r="AF62" t="n">
+      <c r="AJ62" t="n">
         <v>28.34964144442966</v>
       </c>
     </row>
@@ -7282,28 +7554,32 @@
       <c r="X63" t="n">
         <v>0.3431569509497764</v>
       </c>
-      <c r="Y63" t="n">
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
         <v>21.57168129774534</v>
       </c>
-      <c r="Z63" t="n">
+      <c r="AD63" t="n">
         <v>342.7248986010509</v>
       </c>
-      <c r="AA63" t="n">
+      <c r="AE63" t="n">
         <v>0.8100056069540642</v>
       </c>
-      <c r="AB63" t="n">
+      <c r="AF63" t="n">
         <v>50.24333206184315</v>
       </c>
-      <c r="AC63" t="n">
+      <c r="AG63" t="n">
         <v>2000</v>
       </c>
-      <c r="AD63" t="n">
+      <c r="AH63" t="n">
         <v>1000</v>
       </c>
-      <c r="AE63" t="n">
+      <c r="AI63" t="n">
         <v>19</v>
       </c>
-      <c r="AF63" t="n">
+      <c r="AJ63" t="n">
         <v>35.75055097541501</v>
       </c>
     </row>
@@ -7384,28 +7660,32 @@
       <c r="X64" t="n">
         <v>0.01583676856674615</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
         <v>22.34107993933516</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="AD64" t="n">
         <v>357.1294788542538</v>
       </c>
-      <c r="AA64" t="n">
+      <c r="AE64" t="n">
         <v>0.8440497946350297</v>
       </c>
-      <c r="AB64" t="n">
+      <c r="AF64" t="n">
         <v>41.2404694035914</v>
       </c>
-      <c r="AC64" t="n">
+      <c r="AG64" t="n">
         <v>2000</v>
       </c>
-      <c r="AD64" t="n">
+      <c r="AH64" t="n">
         <v>1000</v>
       </c>
-      <c r="AE64" t="n">
+      <c r="AI64" t="n">
         <v>19</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -7492,28 +7772,32 @@
       <c r="X65" t="n">
         <v>0.00890818231879471</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
         <v>19.74243374394122</v>
       </c>
-      <c r="Z65" t="n">
+      <c r="AD65" t="n">
         <v>308.4779662990912</v>
       </c>
-      <c r="AA65" t="n">
+      <c r="AE65" t="n">
         <v>0.7290654497060941</v>
       </c>
-      <c r="AB65" t="n">
+      <c r="AF65" t="n">
         <v>71.64766475056801</v>
       </c>
-      <c r="AC65" t="n">
+      <c r="AG65" t="n">
         <v>4500</v>
       </c>
-      <c r="AD65" t="n">
+      <c r="AH65" t="n">
         <v>3000</v>
       </c>
-      <c r="AE65" t="n">
+      <c r="AI65" t="n">
         <v>10</v>
       </c>
-      <c r="AF65" t="n">
+      <c r="AJ65" t="n">
         <v>37.77978443238764</v>
       </c>
     </row>
@@ -7602,28 +7886,32 @@
       <c r="X66" t="n">
         <v>0.01399756241761017</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
         <v>21.12953817664699</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="AD66" t="n">
         <v>334.447153194453</v>
       </c>
-      <c r="AA66" t="n">
+      <c r="AE66" t="n">
         <v>0.7904417520382077</v>
       </c>
-      <c r="AB66" t="n">
+      <c r="AF66" t="n">
         <v>55.41692294096688</v>
       </c>
-      <c r="AC66" t="n">
+      <c r="AG66" t="n">
         <v>4500</v>
       </c>
-      <c r="AD66" t="n">
+      <c r="AH66" t="n">
         <v>3000</v>
       </c>
-      <c r="AE66" t="n">
+      <c r="AI66" t="n">
         <v>10</v>
       </c>
-      <c r="AF66" t="n">
+      <c r="AJ66" t="n">
         <v>46.78990518799996</v>
       </c>
     </row>
@@ -7712,28 +8000,32 @@
       <c r="X67" t="n">
         <v>0.001963495408493621</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
         <v>20.27791349230865</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="AD67" t="n">
         <v>318.5031477750881</v>
       </c>
-      <c r="AA67" t="n">
+      <c r="AE67" t="n">
         <v>0.7527592438816441</v>
       </c>
-      <c r="AB67" t="n">
+      <c r="AF67" t="n">
         <v>65.38192632806994</v>
       </c>
-      <c r="AC67" t="n">
+      <c r="AG67" t="n">
         <v>4500</v>
       </c>
-      <c r="AD67" t="n">
+      <c r="AH67" t="n">
         <v>3000</v>
       </c>
-      <c r="AE67" t="n">
+      <c r="AI67" t="n">
         <v>10</v>
       </c>
-      <c r="AF67" t="n">
+      <c r="AJ67" t="n">
         <v>29.55848025895563</v>
       </c>
     </row>
@@ -7822,28 +8114,32 @@
       <c r="X68" t="n">
         <v>0.09820065714814662</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="n">
         <v>22.71038088367341</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="AD68" t="n">
         <v>364.0434826004935</v>
       </c>
-      <c r="AA68" t="n">
+      <c r="AE68" t="n">
         <v>0.8603905443845096</v>
       </c>
-      <c r="AB68" t="n">
+      <c r="AF68" t="n">
         <v>36.91921706219154</v>
       </c>
-      <c r="AC68" t="n">
+      <c r="AG68" t="n">
         <v>2000</v>
       </c>
-      <c r="AD68" t="n">
+      <c r="AH68" t="n">
         <v>1000</v>
       </c>
-      <c r="AE68" t="n">
+      <c r="AI68" t="n">
         <v>19</v>
       </c>
-      <c r="AF68" t="n">
+      <c r="AJ68" t="n">
         <v>24.10341074609785</v>
       </c>
     </row>
@@ -7924,28 +8220,32 @@
       <c r="X69" t="n">
         <v>0.04776128753733373</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="n">
         <v>23.27011621677441</v>
       </c>
-      <c r="Z69" t="n">
+      <c r="AD69" t="n">
         <v>374.5227739461949</v>
       </c>
-      <c r="AA69" t="n">
+      <c r="AE69" t="n">
         <v>0.885157594521722</v>
       </c>
-      <c r="AB69" t="n">
+      <c r="AF69" t="n">
         <v>30.3696599711282</v>
       </c>
-      <c r="AC69" t="n">
+      <c r="AG69" t="n">
         <v>2000</v>
       </c>
-      <c r="AD69" t="n">
+      <c r="AH69" t="n">
         <v>1000</v>
       </c>
-      <c r="AE69" t="n">
+      <c r="AI69" t="n">
         <v>19</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -8024,28 +8324,32 @@
       <c r="X70" t="n">
         <v>0.02613000840067389</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="n">
         <v>22.81594444937604</v>
       </c>
-      <c r="Z70" t="n">
+      <c r="AD70" t="n">
         <v>366.0198298043771</v>
       </c>
-      <c r="AA70" t="n">
+      <c r="AE70" t="n">
         <v>0.8650614986191394</v>
       </c>
-      <c r="AB70" t="n">
+      <c r="AF70" t="n">
         <v>35.68400005976433</v>
       </c>
-      <c r="AC70" t="n">
+      <c r="AG70" t="n">
         <v>2000</v>
       </c>
-      <c r="AD70" t="n">
+      <c r="AH70" t="n">
         <v>1000</v>
       </c>
-      <c r="AE70" t="n">
+      <c r="AI70" t="n">
         <v>19</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -8132,28 +8436,32 @@
       <c r="X71" t="n">
         <v>0.02474495088554085</v>
       </c>
-      <c r="Y71" t="n">
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="n">
         <v>20.70880516475933</v>
       </c>
-      <c r="Z71" t="n">
+      <c r="AD71" t="n">
         <v>326.5702450387737</v>
       </c>
-      <c r="AA71" t="n">
+      <c r="AE71" t="n">
         <v>0.7718252470874265</v>
       </c>
-      <c r="AB71" t="n">
+      <c r="AF71" t="n">
         <v>60.33999053826645</v>
       </c>
-      <c r="AC71" t="n">
+      <c r="AG71" t="n">
         <v>2000</v>
       </c>
-      <c r="AD71" t="n">
+      <c r="AH71" t="n">
         <v>1000</v>
       </c>
-      <c r="AE71" t="n">
+      <c r="AI71" t="n">
         <v>19</v>
       </c>
-      <c r="AF71" t="n">
+      <c r="AJ71" t="n">
         <v>27.25954615592946</v>
       </c>
     </row>
@@ -8242,28 +8550,32 @@
       <c r="X72" t="n">
         <v>0.003117245310524472</v>
       </c>
-      <c r="Y72" t="n">
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="n">
         <v>19.52210542008766</v>
       </c>
-      <c r="Z72" t="n">
+      <c r="AD72" t="n">
         <v>304.3530083755312</v>
       </c>
-      <c r="AA72" t="n">
+      <c r="AE72" t="n">
         <v>0.7193164088276182</v>
       </c>
-      <c r="AB72" t="n">
+      <c r="AF72" t="n">
         <v>74.22576345279299</v>
       </c>
-      <c r="AC72" t="n">
+      <c r="AG72" t="n">
         <v>4500</v>
       </c>
-      <c r="AD72" t="n">
+      <c r="AH72" t="n">
         <v>3000</v>
       </c>
-      <c r="AE72" t="n">
+      <c r="AI72" t="n">
         <v>10</v>
       </c>
-      <c r="AF72" t="n">
+      <c r="AJ72" t="n">
         <v>30.02082045458014</v>
       </c>
     </row>
@@ -8352,28 +8664,32 @@
       <c r="X73" t="n">
         <v>0.002733971006786517</v>
       </c>
-      <c r="Y73" t="n">
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
         <v>15.83269105354342</v>
       </c>
-      <c r="Z73" t="n">
+      <c r="AD73" t="n">
         <v>235.280277469232</v>
       </c>
-      <c r="AA73" t="n">
+      <c r="AE73" t="n">
         <v>0.5560679855292004</v>
       </c>
-      <c r="AB73" t="n">
+      <c r="AF73" t="n">
         <v>117.39622026923</v>
       </c>
-      <c r="AC73" t="n">
+      <c r="AG73" t="n">
         <v>4500</v>
       </c>
-      <c r="AD73" t="n">
+      <c r="AH73" t="n">
         <v>3000</v>
       </c>
-      <c r="AE73" t="n">
+      <c r="AI73" t="n">
         <v>10</v>
       </c>
-      <c r="AF73" t="n">
+      <c r="AJ73" t="n">
         <v>26.46707679984683</v>
       </c>
     </row>
@@ -8454,28 +8770,32 @@
       <c r="X74" t="n">
         <v>0.1121021103925018</v>
       </c>
-      <c r="Y74" t="n">
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
         <v>21.69807823935166</v>
       </c>
-      <c r="Z74" t="n">
+      <c r="AD74" t="n">
         <v>345.0912855306737</v>
       </c>
-      <c r="AA74" t="n">
+      <c r="AE74" t="n">
         <v>0.8155983919808926</v>
       </c>
-      <c r="AB74" t="n">
+      <c r="AF74" t="n">
         <v>48.76434023082894</v>
       </c>
-      <c r="AC74" t="n">
+      <c r="AG74" t="n">
         <v>2000</v>
       </c>
-      <c r="AD74" t="n">
+      <c r="AH74" t="n">
         <v>1000</v>
       </c>
-      <c r="AE74" t="n">
+      <c r="AI74" t="n">
         <v>19</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -8562,28 +8882,32 @@
       <c r="X75" t="n">
         <v>0.000855298599939821</v>
       </c>
-      <c r="Y75" t="n">
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
         <v>18.65221495523094</v>
       </c>
-      <c r="Z75" t="n">
+      <c r="AD75" t="n">
         <v>288.0670334137965</v>
       </c>
-      <c r="AA75" t="n">
+      <c r="AE75" t="n">
         <v>0.680825680294135</v>
       </c>
-      <c r="AB75" t="n">
+      <c r="AF75" t="n">
         <v>84.40449780387716</v>
       </c>
-      <c r="AC75" t="n">
+      <c r="AG75" t="n">
         <v>4500</v>
       </c>
-      <c r="AD75" t="n">
+      <c r="AH75" t="n">
         <v>3000</v>
       </c>
-      <c r="AE75" t="n">
+      <c r="AI75" t="n">
         <v>10</v>
       </c>
-      <c r="AF75" t="n">
+      <c r="AJ75" t="n">
         <v>32.73336164766602</v>
       </c>
     </row>
@@ -8672,28 +8996,32 @@
       <c r="X76" t="n">
         <v>0.00090792027688745</v>
       </c>
-      <c r="Y76" t="n">
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="n">
         <v>17.05256609052653</v>
       </c>
-      <c r="Z76" t="n">
+      <c r="AD76" t="n">
         <v>258.1186175952207</v>
       </c>
-      <c r="AA76" t="n">
+      <c r="AE76" t="n">
         <v>0.6100447570771258</v>
       </c>
-      <c r="AB76" t="n">
+      <c r="AF76" t="n">
         <v>103.1222576904871</v>
       </c>
-      <c r="AC76" t="n">
+      <c r="AG76" t="n">
         <v>4500</v>
       </c>
-      <c r="AD76" t="n">
+      <c r="AH76" t="n">
         <v>3000</v>
       </c>
-      <c r="AE76" t="n">
+      <c r="AI76" t="n">
         <v>10</v>
       </c>
-      <c r="AF76" t="n">
+      <c r="AJ76" t="n">
         <v>27.85958429127932</v>
       </c>
     </row>
@@ -8782,28 +9110,32 @@
       <c r="X77" t="n">
         <v>0.02328928607551839</v>
       </c>
-      <c r="Y77" t="n">
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
         <v>22.13017055061581</v>
       </c>
-      <c r="Z77" t="n">
+      <c r="AD77" t="n">
         <v>353.1808609964365</v>
       </c>
-      <c r="AA77" t="n">
+      <c r="AE77" t="n">
         <v>0.8347175207978901</v>
       </c>
-      <c r="AB77" t="n">
+      <c r="AF77" t="n">
         <v>43.70835556472719</v>
       </c>
-      <c r="AC77" t="n">
+      <c r="AG77" t="n">
         <v>2000</v>
       </c>
-      <c r="AD77" t="n">
+      <c r="AH77" t="n">
         <v>1000</v>
       </c>
-      <c r="AE77" t="n">
+      <c r="AI77" t="n">
         <v>19</v>
       </c>
-      <c r="AF77" t="n">
+      <c r="AJ77" t="n">
         <v>21.8162096187406</v>
       </c>
     </row>
@@ -8892,28 +9224,32 @@
       <c r="X78" t="n">
         <v>0.01020703453151324</v>
       </c>
-      <c r="Y78" t="n">
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
         <v>16.19730406719173</v>
       </c>
-      <c r="Z78" t="n">
+      <c r="AD78" t="n">
         <v>242.1065143931843</v>
       </c>
-      <c r="AA78" t="n">
+      <c r="AE78" t="n">
         <v>0.5722013047171788</v>
       </c>
-      <c r="AB78" t="n">
+      <c r="AF78" t="n">
         <v>113.1298221917598</v>
       </c>
-      <c r="AC78" t="n">
+      <c r="AG78" t="n">
         <v>4500</v>
       </c>
-      <c r="AD78" t="n">
+      <c r="AH78" t="n">
         <v>3000</v>
       </c>
-      <c r="AE78" t="n">
+      <c r="AI78" t="n">
         <v>10</v>
       </c>
-      <c r="AF78" t="n">
+      <c r="AJ78" t="n">
         <v>18.28478648070587</v>
       </c>
     </row>
@@ -9002,28 +9338,32 @@
       <c r="X79" t="n">
         <v>0.03617006728264883</v>
       </c>
-      <c r="Y79" t="n">
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
         <v>21.30845475552441</v>
       </c>
-      <c r="Z79" t="n">
+      <c r="AD79" t="n">
         <v>337.796805870916</v>
       </c>
-      <c r="AA79" t="n">
+      <c r="AE79" t="n">
         <v>0.7983584148203947</v>
       </c>
-      <c r="AB79" t="n">
+      <c r="AF79" t="n">
         <v>53.32339001817746</v>
       </c>
-      <c r="AC79" t="n">
+      <c r="AG79" t="n">
         <v>4500</v>
       </c>
-      <c r="AD79" t="n">
+      <c r="AH79" t="n">
         <v>3000</v>
       </c>
-      <c r="AE79" t="n">
+      <c r="AI79" t="n">
         <v>10</v>
       </c>
-      <c r="AF79" t="n">
+      <c r="AJ79" t="n">
         <v>22.12908955486301</v>
       </c>
     </row>
@@ -9112,28 +9452,32 @@
       <c r="X80" t="n">
         <v>0.05620014732960866</v>
       </c>
-      <c r="Y80" t="n">
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
         <v>15.13544690515705</v>
       </c>
-      <c r="Z80" t="n">
+      <c r="AD80" t="n">
         <v>222.2265641552151</v>
       </c>
-      <c r="AA80" t="n">
+      <c r="AE80" t="n">
         <v>0.5252164745386529</v>
       </c>
-      <c r="AB80" t="n">
+      <c r="AF80" t="n">
         <v>125.5547910904906</v>
       </c>
-      <c r="AC80" t="n">
+      <c r="AG80" t="n">
         <v>4500</v>
       </c>
-      <c r="AD80" t="n">
+      <c r="AH80" t="n">
         <v>3000</v>
       </c>
-      <c r="AE80" t="n">
+      <c r="AI80" t="n">
         <v>10</v>
       </c>
-      <c r="AF80" t="n">
+      <c r="AJ80" t="n">
         <v>23.88772942228289</v>
       </c>
     </row>
@@ -9222,28 +9566,32 @@
       <c r="X81" t="n">
         <v>0.01459088360616714</v>
       </c>
-      <c r="Y81" t="n">
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
         <v>22.53097282164527</v>
       </c>
-      <c r="Z81" t="n">
+      <c r="AD81" t="n">
         <v>360.6846284410738</v>
       </c>
-      <c r="AA81" t="n">
+      <c r="AE81" t="n">
         <v>0.8524521345602558</v>
       </c>
-      <c r="AB81" t="n">
+      <c r="AF81" t="n">
         <v>39.01850091182887</v>
       </c>
-      <c r="AC81" t="n">
+      <c r="AG81" t="n">
         <v>2000</v>
       </c>
-      <c r="AD81" t="n">
+      <c r="AH81" t="n">
         <v>1000</v>
       </c>
-      <c r="AE81" t="n">
+      <c r="AI81" t="n">
         <v>19</v>
       </c>
-      <c r="AF81" t="n">
+      <c r="AJ81" t="n">
         <v>29.22142888916803</v>
       </c>
     </row>
@@ -9324,28 +9672,32 @@
       <c r="X82" t="n">
         <v>0.00804360816654516</v>
       </c>
-      <c r="Y82" t="n">
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
         <v>24.38083708972119</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="AD82" t="n">
         <v>395.3175441581743</v>
       </c>
-      <c r="AA82" t="n">
+      <c r="AE82" t="n">
         <v>0.9343045358025531</v>
       </c>
-      <c r="AB82" t="n">
+      <c r="AF82" t="n">
         <v>17.3729285886411</v>
       </c>
-      <c r="AC82" t="n">
+      <c r="AG82" t="n">
         <v>2000</v>
       </c>
-      <c r="AD82" t="n">
+      <c r="AH82" t="n">
         <v>1000</v>
       </c>
-      <c r="AE82" t="n">
+      <c r="AI82" t="n">
         <v>19</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -9424,28 +9776,32 @@
       <c r="X83" t="n">
         <v>0.008413381475854314</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
         <v>23.65066335612901</v>
       </c>
-      <c r="Z83" t="n">
+      <c r="AD83" t="n">
         <v>381.6473274775519</v>
       </c>
-      <c r="AA83" t="n">
+      <c r="AE83" t="n">
         <v>0.901995963519713</v>
       </c>
-      <c r="AB83" t="n">
+      <c r="AF83" t="n">
         <v>25.91681401403009</v>
       </c>
-      <c r="AC83" t="n">
+      <c r="AG83" t="n">
         <v>2000</v>
       </c>
-      <c r="AD83" t="n">
+      <c r="AH83" t="n">
         <v>1000</v>
       </c>
-      <c r="AE83" t="n">
+      <c r="AI83" t="n">
         <v>19</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -9524,28 +9880,32 @@
       <c r="X84" t="n">
         <v>0.07655184792447974</v>
       </c>
-      <c r="Y84" t="n">
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
         <v>22.52042136643655</v>
       </c>
-      <c r="Z84" t="n">
+      <c r="AD84" t="n">
         <v>360.4870854833322</v>
       </c>
-      <c r="AA84" t="n">
+      <c r="AE84" t="n">
         <v>0.8519852560111976</v>
       </c>
-      <c r="AB84" t="n">
+      <c r="AF84" t="n">
         <v>39.14196526041737</v>
       </c>
-      <c r="AC84" t="n">
+      <c r="AG84" t="n">
         <v>2000</v>
       </c>
-      <c r="AD84" t="n">
+      <c r="AH84" t="n">
         <v>1000</v>
       </c>
-      <c r="AE84" t="n">
+      <c r="AI84" t="n">
         <v>19</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -9632,28 +9992,32 @@
       <c r="X85" t="n">
         <v>0.08434178033822919</v>
       </c>
-      <c r="Y85" t="n">
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
         <v>22.98489149021835</v>
       </c>
-      <c r="Z85" t="n">
+      <c r="AD85" t="n">
         <v>369.1828340999469</v>
       </c>
-      <c r="AA85" t="n">
+      <c r="AE85" t="n">
         <v>0.8725370313997726</v>
       </c>
-      <c r="AB85" t="n">
+      <c r="AF85" t="n">
         <v>33.70712237503319</v>
       </c>
-      <c r="AC85" t="n">
+      <c r="AG85" t="n">
         <v>2000</v>
       </c>
-      <c r="AD85" t="n">
+      <c r="AH85" t="n">
         <v>1000</v>
       </c>
-      <c r="AE85" t="n">
+      <c r="AI85" t="n">
         <v>19</v>
       </c>
-      <c r="AF85" t="n">
+      <c r="AJ85" t="n">
         <v>30.5986095096603</v>
       </c>
     </row>
@@ -9742,28 +10106,32 @@
       <c r="X86" t="n">
         <v>0.002733971006786517</v>
       </c>
-      <c r="Y86" t="n">
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="n">
         <v>16.85426750608011</v>
       </c>
-      <c r="Z86" t="n">
+      <c r="AD86" t="n">
         <v>254.4060975576848</v>
       </c>
-      <c r="AA86" t="n">
+      <c r="AE86" t="n">
         <v>0.6012704834290539</v>
       </c>
-      <c r="AB86" t="n">
+      <c r="AF86" t="n">
         <v>105.442582713947</v>
       </c>
-      <c r="AC86" t="n">
+      <c r="AG86" t="n">
         <v>4500</v>
       </c>
-      <c r="AD86" t="n">
+      <c r="AH86" t="n">
         <v>3000</v>
       </c>
-      <c r="AE86" t="n">
+      <c r="AI86" t="n">
         <v>10</v>
       </c>
-      <c r="AF86" t="n">
+      <c r="AJ86" t="n">
         <v>27.00689943428556</v>
       </c>
     </row>
@@ -9852,28 +10220,32 @@
       <c r="X87" t="n">
         <v>0.04169220176949628</v>
       </c>
-      <c r="Y87" t="n">
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="n">
         <v>22.68927078529925</v>
       </c>
-      <c r="Z87" t="n">
+      <c r="AD87" t="n">
         <v>363.6482621130292</v>
       </c>
-      <c r="AA87" t="n">
+      <c r="AE87" t="n">
         <v>0.8594564692352107</v>
       </c>
-      <c r="AB87" t="n">
+      <c r="AF87" t="n">
         <v>37.16622986685675</v>
       </c>
-      <c r="AC87" t="n">
+      <c r="AG87" t="n">
         <v>2000</v>
       </c>
-      <c r="AD87" t="n">
+      <c r="AH87" t="n">
         <v>1000</v>
       </c>
-      <c r="AE87" t="n">
+      <c r="AI87" t="n">
         <v>19</v>
       </c>
-      <c r="AF87" t="n">
+      <c r="AJ87" t="n">
         <v>20.09981608868211</v>
       </c>
     </row>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -7715,11 +7715,7 @@
       <c r="K64" t="n">
         <v>0.01461355893199637</v>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>p11-5785</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>0.4698293457032828</v>
       </c>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -10612,7 +10612,7 @@
         <v>2000</v>
       </c>
       <c r="AH89" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI89" t="n">
         <v>15</v>
@@ -10714,7 +10714,7 @@
         <v>2000</v>
       </c>
       <c r="AH90" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI90" t="n">
         <v>15</v>
@@ -10816,7 +10816,7 @@
         <v>2000</v>
       </c>
       <c r="AH91" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI91" t="n">
         <v>15</v>
@@ -10918,7 +10918,7 @@
         <v>2000</v>
       </c>
       <c r="AH92" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI92" t="n">
         <v>15</v>
@@ -11020,7 +11020,7 @@
         <v>2000</v>
       </c>
       <c r="AH93" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI93" t="n">
         <v>15</v>
@@ -11122,7 +11122,7 @@
         <v>2000</v>
       </c>
       <c r="AH94" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI94" t="n">
         <v>15</v>
@@ -11224,7 +11224,7 @@
         <v>2000</v>
       </c>
       <c r="AH95" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI95" t="n">
         <v>15</v>
@@ -11326,7 +11326,7 @@
         <v>2000</v>
       </c>
       <c r="AH96" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI96" t="n">
         <v>15</v>
@@ -11428,7 +11428,7 @@
         <v>2000</v>
       </c>
       <c r="AH97" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI97" t="n">
         <v>15</v>
@@ -11530,7 +11530,7 @@
         <v>2000</v>
       </c>
       <c r="AH98" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI98" t="n">
         <v>15</v>
@@ -11632,7 +11632,7 @@
         <v>2000</v>
       </c>
       <c r="AH99" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI99" t="n">
         <v>15</v>
@@ -11734,7 +11734,7 @@
         <v>2000</v>
       </c>
       <c r="AH100" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI100" t="n">
         <v>15</v>
@@ -11836,7 +11836,7 @@
         <v>2000</v>
       </c>
       <c r="AH101" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI101" t="n">
         <v>15</v>
@@ -11938,7 +11938,7 @@
         <v>2000</v>
       </c>
       <c r="AH102" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI102" t="n">
         <v>15</v>
@@ -12040,7 +12040,7 @@
         <v>2000</v>
       </c>
       <c r="AH103" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI103" t="n">
         <v>15</v>
@@ -12142,7 +12142,7 @@
         <v>2000</v>
       </c>
       <c r="AH104" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI104" t="n">
         <v>15</v>
@@ -12244,7 +12244,7 @@
         <v>2000</v>
       </c>
       <c r="AH105" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI105" t="n">
         <v>15</v>
@@ -12346,7 +12346,7 @@
         <v>2000</v>
       </c>
       <c r="AH106" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI106" t="n">
         <v>15</v>
@@ -12448,7 +12448,7 @@
         <v>2000</v>
       </c>
       <c r="AH107" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI107" t="n">
         <v>15</v>
@@ -12550,7 +12550,7 @@
         <v>2000</v>
       </c>
       <c r="AH108" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI108" t="n">
         <v>15</v>
@@ -12652,7 +12652,7 @@
         <v>2000</v>
       </c>
       <c r="AH109" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI109" t="n">
         <v>15</v>
@@ -12754,7 +12754,7 @@
         <v>2000</v>
       </c>
       <c r="AH110" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI110" t="n">
         <v>15</v>
@@ -12856,7 +12856,7 @@
         <v>2000</v>
       </c>
       <c r="AH111" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI111" t="n">
         <v>15</v>
@@ -12958,7 +12958,7 @@
         <v>2000</v>
       </c>
       <c r="AH112" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI112" t="n">
         <v>15</v>
@@ -13060,7 +13060,7 @@
         <v>2000</v>
       </c>
       <c r="AH113" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI113" t="n">
         <v>15</v>
@@ -13162,7 +13162,7 @@
         <v>2000</v>
       </c>
       <c r="AH114" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI114" t="n">
         <v>15</v>
@@ -13264,7 +13264,7 @@
         <v>2000</v>
       </c>
       <c r="AH115" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI115" t="n">
         <v>15</v>
@@ -13366,7 +13366,7 @@
         <v>2000</v>
       </c>
       <c r="AH116" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI116" t="n">
         <v>15</v>
@@ -13468,7 +13468,7 @@
         <v>2000</v>
       </c>
       <c r="AH117" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI117" t="n">
         <v>15</v>
@@ -13570,7 +13570,7 @@
         <v>2000</v>
       </c>
       <c r="AH118" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI118" t="n">
         <v>15</v>
@@ -13672,7 +13672,7 @@
         <v>2000</v>
       </c>
       <c r="AH119" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI119" t="n">
         <v>15</v>
@@ -13774,7 +13774,7 @@
         <v>2000</v>
       </c>
       <c r="AH120" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI120" t="n">
         <v>15</v>
@@ -13876,7 +13876,7 @@
         <v>2000</v>
       </c>
       <c r="AH121" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI121" t="n">
         <v>15</v>
@@ -13978,7 +13978,7 @@
         <v>2000</v>
       </c>
       <c r="AH122" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI122" t="n">
         <v>15</v>
@@ -14080,7 +14080,7 @@
         <v>2000</v>
       </c>
       <c r="AH123" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI123" t="n">
         <v>15</v>
@@ -14182,7 +14182,7 @@
         <v>2000</v>
       </c>
       <c r="AH124" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI124" t="n">
         <v>15</v>
@@ -14284,7 +14284,7 @@
         <v>2000</v>
       </c>
       <c r="AH125" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI125" t="n">
         <v>15</v>
@@ -14386,7 +14386,7 @@
         <v>2000</v>
       </c>
       <c r="AH126" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI126" t="n">
         <v>15</v>
@@ -14488,7 +14488,7 @@
         <v>2000</v>
       </c>
       <c r="AH127" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI127" t="n">
         <v>15</v>
@@ -14590,7 +14590,7 @@
         <v>2000</v>
       </c>
       <c r="AH128" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI128" t="n">
         <v>15</v>
@@ -14692,7 +14692,7 @@
         <v>2000</v>
       </c>
       <c r="AH129" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI129" t="n">
         <v>15</v>
@@ -14794,7 +14794,7 @@
         <v>2000</v>
       </c>
       <c r="AH130" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI130" t="n">
         <v>15</v>
@@ -14896,7 +14896,7 @@
         <v>2000</v>
       </c>
       <c r="AH131" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI131" t="n">
         <v>15</v>
@@ -14998,7 +14998,7 @@
         <v>2000</v>
       </c>
       <c r="AH132" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI132" t="n">
         <v>15</v>
@@ -15100,7 +15100,7 @@
         <v>2000</v>
       </c>
       <c r="AH133" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI133" t="n">
         <v>15</v>
@@ -15202,7 +15202,7 @@
         <v>2000</v>
       </c>
       <c r="AH134" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI134" t="n">
         <v>15</v>
@@ -15304,7 +15304,7 @@
         <v>2000</v>
       </c>
       <c r="AH135" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI135" t="n">
         <v>15</v>
@@ -15406,7 +15406,7 @@
         <v>2000</v>
       </c>
       <c r="AH136" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI136" t="n">
         <v>15</v>
@@ -15508,7 +15508,7 @@
         <v>2000</v>
       </c>
       <c r="AH137" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI137" t="n">
         <v>15</v>
@@ -15610,7 +15610,7 @@
         <v>2000</v>
       </c>
       <c r="AH138" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI138" t="n">
         <v>15</v>
@@ -15712,7 +15712,7 @@
         <v>2000</v>
       </c>
       <c r="AH139" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI139" t="n">
         <v>15</v>
@@ -15814,7 +15814,7 @@
         <v>2000</v>
       </c>
       <c r="AH140" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI140" t="n">
         <v>15</v>
@@ -15916,7 +15916,7 @@
         <v>2000</v>
       </c>
       <c r="AH141" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI141" t="n">
         <v>15</v>
@@ -16018,7 +16018,7 @@
         <v>2000</v>
       </c>
       <c r="AH142" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI142" t="n">
         <v>15</v>
@@ -16120,7 +16120,7 @@
         <v>2000</v>
       </c>
       <c r="AH143" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI143" t="n">
         <v>15</v>
@@ -16222,7 +16222,7 @@
         <v>2000</v>
       </c>
       <c r="AH144" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI144" t="n">
         <v>15</v>
@@ -16324,7 +16324,7 @@
         <v>2000</v>
       </c>
       <c r="AH145" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI145" t="n">
         <v>15</v>
@@ -16426,7 +16426,7 @@
         <v>2000</v>
       </c>
       <c r="AH146" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI146" t="n">
         <v>15</v>
@@ -16528,7 +16528,7 @@
         <v>2000</v>
       </c>
       <c r="AH147" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI147" t="n">
         <v>15</v>
@@ -16630,7 +16630,7 @@
         <v>2000</v>
       </c>
       <c r="AH148" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI148" t="n">
         <v>15</v>
@@ -16732,7 +16732,7 @@
         <v>2000</v>
       </c>
       <c r="AH149" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI149" t="n">
         <v>15</v>
@@ -16834,7 +16834,7 @@
         <v>2000</v>
       </c>
       <c r="AH150" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI150" t="n">
         <v>15</v>
@@ -16936,7 +16936,7 @@
         <v>2000</v>
       </c>
       <c r="AH151" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI151" t="n">
         <v>15</v>
@@ -17038,7 +17038,7 @@
         <v>2000</v>
       </c>
       <c r="AH152" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI152" t="n">
         <v>15</v>
@@ -17140,7 +17140,7 @@
         <v>2000</v>
       </c>
       <c r="AH153" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI153" t="n">
         <v>15</v>
@@ -17242,7 +17242,7 @@
         <v>2000</v>
       </c>
       <c r="AH154" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI154" t="n">
         <v>15</v>
@@ -17344,7 +17344,7 @@
         <v>2000</v>
       </c>
       <c r="AH155" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI155" t="n">
         <v>15</v>
@@ -17446,7 +17446,7 @@
         <v>2000</v>
       </c>
       <c r="AH156" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI156" t="n">
         <v>15</v>
@@ -17548,7 +17548,7 @@
         <v>2000</v>
       </c>
       <c r="AH157" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI157" t="n">
         <v>15</v>
@@ -17650,7 +17650,7 @@
         <v>2000</v>
       </c>
       <c r="AH158" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI158" t="n">
         <v>15</v>
@@ -17752,7 +17752,7 @@
         <v>2000</v>
       </c>
       <c r="AH159" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI159" t="n">
         <v>15</v>
@@ -17854,7 +17854,7 @@
         <v>2000</v>
       </c>
       <c r="AH160" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI160" t="n">
         <v>15</v>
@@ -17954,7 +17954,7 @@
         <v>2000</v>
       </c>
       <c r="AH161" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI161" t="n">
         <v>15</v>
@@ -18054,7 +18054,7 @@
         <v>2000</v>
       </c>
       <c r="AH162" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI162" t="n">
         <v>15</v>
@@ -18156,7 +18156,7 @@
         <v>2000</v>
       </c>
       <c r="AH163" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI163" t="n">
         <v>15</v>
@@ -18258,7 +18258,7 @@
         <v>2000</v>
       </c>
       <c r="AH164" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI164" t="n">
         <v>15</v>
@@ -18360,7 +18360,7 @@
         <v>2000</v>
       </c>
       <c r="AH165" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI165" t="n">
         <v>15</v>
@@ -18462,7 +18462,7 @@
         <v>2000</v>
       </c>
       <c r="AH166" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI166" t="n">
         <v>15</v>
@@ -18564,7 +18564,7 @@
         <v>2000</v>
       </c>
       <c r="AH167" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI167" t="n">
         <v>15</v>
@@ -18666,7 +18666,7 @@
         <v>2000</v>
       </c>
       <c r="AH168" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI168" t="n">
         <v>15</v>
@@ -18768,7 +18768,7 @@
         <v>2000</v>
       </c>
       <c r="AH169" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI169" t="n">
         <v>15</v>
@@ -18870,7 +18870,7 @@
         <v>2000</v>
       </c>
       <c r="AH170" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI170" t="n">
         <v>15</v>
@@ -18972,7 +18972,7 @@
         <v>2000</v>
       </c>
       <c r="AH171" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI171" t="n">
         <v>15</v>
@@ -19074,7 +19074,7 @@
         <v>2000</v>
       </c>
       <c r="AH172" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI172" t="n">
         <v>15</v>
@@ -19176,7 +19176,7 @@
         <v>2000</v>
       </c>
       <c r="AH173" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI173" t="n">
         <v>15</v>
@@ -19278,7 +19278,7 @@
         <v>2000</v>
       </c>
       <c r="AH174" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI174" t="n">
         <v>15</v>
@@ -19380,7 +19380,7 @@
         <v>2000</v>
       </c>
       <c r="AH175" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI175" t="n">
         <v>15</v>
@@ -19482,7 +19482,7 @@
         <v>2000</v>
       </c>
       <c r="AH176" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI176" t="n">
         <v>15</v>
@@ -19584,7 +19584,7 @@
         <v>2000</v>
       </c>
       <c r="AH177" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI177" t="n">
         <v>15</v>
@@ -19686,7 +19686,7 @@
         <v>2000</v>
       </c>
       <c r="AH178" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI178" t="n">
         <v>15</v>
@@ -19788,7 +19788,7 @@
         <v>2000</v>
       </c>
       <c r="AH179" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI179" t="n">
         <v>15</v>
@@ -19890,7 +19890,7 @@
         <v>2000</v>
       </c>
       <c r="AH180" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI180" t="n">
         <v>15</v>
@@ -19992,7 +19992,7 @@
         <v>2000</v>
       </c>
       <c r="AH181" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI181" t="n">
         <v>15</v>
@@ -20094,7 +20094,7 @@
         <v>2000</v>
       </c>
       <c r="AH182" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI182" t="n">
         <v>15</v>
@@ -20196,7 +20196,7 @@
         <v>2000</v>
       </c>
       <c r="AH183" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="AI183" t="n">
         <v>15</v>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ183"/>
+  <dimension ref="A1:AI183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,12 +511,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_toughness_(kN/m)</t>
+          <t>mean toughness (kN/m)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_thickness_(mm)</t>
+          <t>mean thickness (mm)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SLA (cm²/g)</t>
+          <t>Specific leaf area (g/cm²)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLA </t>
+          <t>code</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>C:N</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>t13C_cell</t>
+          <t>△13C_cell</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -597,11 +597,6 @@
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_annual_temperature_C</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>C:N</t>
         </is>
       </c>
     </row>
@@ -693,7 +688,9 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>39.58454796558406</v>
+      </c>
       <c r="AC2" t="n">
         <v>19.11317674246398</v>
       </c>
@@ -714,9 +711,6 @@
       </c>
       <c r="AI2" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>39.58454796558406</v>
       </c>
     </row>
     <row r="3">
@@ -807,7 +801,9 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>25.57873717795717</v>
+      </c>
       <c r="AC3" t="n">
         <v>25.186292914119</v>
       </c>
@@ -828,9 +824,6 @@
       </c>
       <c r="AI3" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>25.57873717795717</v>
       </c>
     </row>
     <row r="4">
@@ -921,7 +914,9 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>42.49161457666214</v>
+      </c>
       <c r="AC4" t="n">
         <v>19.55357506559249</v>
       </c>
@@ -942,9 +937,6 @@
       </c>
       <c r="AI4" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>42.49161457666214</v>
       </c>
     </row>
     <row r="5">
@@ -1035,7 +1027,9 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>29.47494536584171</v>
+      </c>
       <c r="AC5" t="n">
         <v>22.81594444937604</v>
       </c>
@@ -1056,9 +1050,6 @@
       </c>
       <c r="AI5" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>29.47494536584172</v>
       </c>
     </row>
     <row r="6">
@@ -1149,7 +1140,9 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>29.46857519135586</v>
+      </c>
       <c r="AC6" t="n">
         <v>24.65624529971977</v>
       </c>
@@ -1170,9 +1163,6 @@
       </c>
       <c r="AI6" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>29.46857519135586</v>
       </c>
     </row>
     <row r="7">
@@ -1263,7 +1253,9 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>26.51846199848627</v>
+      </c>
       <c r="AC7" t="n">
         <v>17.76290045603007</v>
       </c>
@@ -1284,9 +1276,6 @@
       </c>
       <c r="AI7" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>26.51846199848626</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1366,9 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>29.75015113451708</v>
+      </c>
       <c r="AC8" t="n">
         <v>22.60483910589158</v>
       </c>
@@ -1398,9 +1389,6 @@
       </c>
       <c r="AI8" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>29.75015113451709</v>
       </c>
     </row>
     <row r="9">
@@ -1491,7 +1479,9 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>28.28424514537473</v>
+      </c>
       <c r="AC9" t="n">
         <v>22.01420747547882</v>
       </c>
@@ -1512,9 +1502,6 @@
       </c>
       <c r="AI9" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>28.28424514537473</v>
       </c>
     </row>
     <row r="10">
@@ -1605,7 +1592,9 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>28.01632724421026</v>
+      </c>
       <c r="AC10" t="n">
         <v>24.68803269978491</v>
       </c>
@@ -1626,9 +1615,6 @@
       </c>
       <c r="AI10" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>28.01632724421026</v>
       </c>
     </row>
     <row r="11">
@@ -1719,7 +1705,9 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>39.94038297769038</v>
+      </c>
       <c r="AC11" t="n">
         <v>19.59553761511313</v>
       </c>
@@ -1740,9 +1728,6 @@
       </c>
       <c r="AI11" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>39.94038297769039</v>
       </c>
     </row>
     <row r="12">
@@ -1833,7 +1818,9 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>41.33398260330502</v>
+      </c>
       <c r="AC12" t="n">
         <v>18.20213228729963</v>
       </c>
@@ -1854,9 +1841,6 @@
       </c>
       <c r="AI12" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>41.33398260330504</v>
       </c>
     </row>
     <row r="13">
@@ -1947,7 +1931,9 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>33.26962395702254</v>
+      </c>
       <c r="AC13" t="n">
         <v>17.90926895467806</v>
       </c>
@@ -1968,9 +1954,6 @@
       </c>
       <c r="AI13" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>33.26962395702254</v>
       </c>
     </row>
     <row r="14">
@@ -2061,7 +2044,9 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>24.51611901423017</v>
+      </c>
       <c r="AC14" t="n">
         <v>17.9720111996877</v>
       </c>
@@ -2082,9 +2067,6 @@
       </c>
       <c r="AI14" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>24.51611901423017</v>
       </c>
     </row>
     <row r="15">
@@ -2175,7 +2157,9 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>29.77748860325364</v>
+      </c>
       <c r="AC15" t="n">
         <v>20.803439861134</v>
       </c>
@@ -2196,9 +2180,6 @@
       </c>
       <c r="AI15" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>29.77748860325364</v>
       </c>
     </row>
     <row r="16">
@@ -2289,7 +2270,9 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>32.32547486872957</v>
+      </c>
       <c r="AC16" t="n">
         <v>19.66898038896892</v>
       </c>
@@ -2310,9 +2293,6 @@
       </c>
       <c r="AI16" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>32.32547486872956</v>
       </c>
     </row>
     <row r="17">
@@ -2403,7 +2383,9 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>28.39448648615612</v>
+      </c>
       <c r="AC17" t="n">
         <v>22.75260369502616</v>
       </c>
@@ -2424,9 +2406,6 @@
       </c>
       <c r="AI17" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>28.39448648615613</v>
       </c>
     </row>
     <row r="18">
@@ -2517,7 +2496,9 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>29.17653851247548</v>
+      </c>
       <c r="AC18" t="n">
         <v>22.59428612618935</v>
       </c>
@@ -2538,9 +2519,6 @@
       </c>
       <c r="AI18" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>29.17653851247548</v>
       </c>
     </row>
     <row r="19">
@@ -2631,7 +2609,9 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>26.66776442666212</v>
+      </c>
       <c r="AC19" t="n">
         <v>24.82580089356817</v>
       </c>
@@ -2652,9 +2632,6 @@
       </c>
       <c r="AI19" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>26.66776442666213</v>
       </c>
     </row>
     <row r="20">
@@ -2745,7 +2722,9 @@
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AB20" t="n">
+        <v>30.75436275117814</v>
+      </c>
       <c r="AC20" t="n">
         <v>17.7524471739778</v>
       </c>
@@ -2766,9 +2745,6 @@
       </c>
       <c r="AI20" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>30.75436275117814</v>
       </c>
     </row>
     <row r="21">
@@ -2859,7 +2835,9 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>22.9540859657499</v>
+      </c>
       <c r="AC21" t="n">
         <v>14.64690627988655</v>
       </c>
@@ -2880,9 +2858,6 @@
       </c>
       <c r="AI21" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>22.9540859657499</v>
       </c>
     </row>
     <row r="22">
@@ -2973,7 +2948,9 @@
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>53.02578826881873</v>
+      </c>
       <c r="AC22" t="n">
         <v>18.89312022333272</v>
       </c>
@@ -2994,9 +2971,6 @@
       </c>
       <c r="AI22" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>53.02578826881873</v>
       </c>
     </row>
     <row r="23">
@@ -3087,7 +3061,9 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>38.38370176944333</v>
+      </c>
       <c r="AC23" t="n">
         <v>19.28090266311447</v>
       </c>
@@ -3108,9 +3084,6 @@
       </c>
       <c r="AI23" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>38.38370176944331</v>
       </c>
     </row>
     <row r="24">
@@ -3201,7 +3174,9 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>30.95258432083551</v>
+      </c>
       <c r="AC24" t="n">
         <v>16.81253028844674</v>
       </c>
@@ -3222,9 +3197,6 @@
       </c>
       <c r="AI24" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>30.95258432083552</v>
       </c>
     </row>
     <row r="25">
@@ -3315,7 +3287,9 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>30.76750734875213</v>
+      </c>
       <c r="AC25" t="n">
         <v>23.62951442295773</v>
       </c>
@@ -3336,9 +3310,6 @@
       </c>
       <c r="AI25" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>30.76750734875213</v>
       </c>
     </row>
     <row r="26">
@@ -3429,7 +3400,9 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>29.19160870007697</v>
+      </c>
       <c r="AC26" t="n">
         <v>23.68238839450821</v>
       </c>
@@ -3450,9 +3423,6 @@
       </c>
       <c r="AI26" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>29.19160870007696</v>
       </c>
     </row>
     <row r="27">
@@ -3543,7 +3513,9 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>19.36748669969131</v>
+      </c>
       <c r="AC27" t="n">
         <v>21.9193481653363</v>
       </c>
@@ -3564,9 +3536,6 @@
       </c>
       <c r="AI27" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>19.36748669969131</v>
       </c>
     </row>
     <row r="28">
@@ -3657,7 +3626,9 @@
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>31.82500795526659</v>
+      </c>
       <c r="AC28" t="n">
         <v>19.0293344803118</v>
       </c>
@@ -3678,9 +3649,6 @@
       </c>
       <c r="AI28" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>31.8250079552666</v>
       </c>
     </row>
     <row r="29">
@@ -3771,7 +3739,9 @@
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>20.74216706763612</v>
+      </c>
       <c r="AC29" t="n">
         <v>19.89986943123572</v>
       </c>
@@ -3792,9 +3762,6 @@
       </c>
       <c r="AI29" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>20.74216706763612</v>
       </c>
     </row>
     <row r="30">
@@ -3885,7 +3852,9 @@
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>29.19189319790335</v>
+      </c>
       <c r="AC30" t="n">
         <v>22.28834443263765</v>
       </c>
@@ -3906,9 +3875,6 @@
       </c>
       <c r="AI30" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>29.19189319790334</v>
       </c>
     </row>
     <row r="31">
@@ -3999,7 +3965,9 @@
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>42.97256368979243</v>
+      </c>
       <c r="AC31" t="n">
         <v>19.24944984776795</v>
       </c>
@@ -4020,9 +3988,6 @@
       </c>
       <c r="AI31" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>42.97256368979243</v>
       </c>
     </row>
     <row r="32">
@@ -4113,7 +4078,9 @@
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>20.62022678542598</v>
+      </c>
       <c r="AC32" t="n">
         <v>22.43601756348215</v>
       </c>
@@ -4134,9 +4101,6 @@
       </c>
       <c r="AI32" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>20.62022678542599</v>
       </c>
     </row>
     <row r="33">
@@ -4227,7 +4191,9 @@
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>21.99115496636606</v>
+      </c>
       <c r="AC33" t="n">
         <v>22.54152449461855</v>
       </c>
@@ -4248,9 +4214,6 @@
       </c>
       <c r="AI33" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>21.99115496636606</v>
       </c>
     </row>
     <row r="34">
@@ -4341,7 +4304,9 @@
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>43.87185925469005</v>
+      </c>
       <c r="AC34" t="n">
         <v>20.89809210718812</v>
       </c>
@@ -4362,9 +4327,6 @@
       </c>
       <c r="AI34" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>43.87185925469004</v>
       </c>
     </row>
     <row r="35">
@@ -4455,7 +4417,9 @@
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>24.17983322666046</v>
+      </c>
       <c r="AC35" t="n">
         <v>22.96377005791446</v>
       </c>
@@ -4476,9 +4440,6 @@
       </c>
       <c r="AI35" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>24.17983322666046</v>
       </c>
     </row>
     <row r="36">
@@ -4569,7 +4530,9 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>45.72171601638512</v>
+      </c>
       <c r="AC36" t="n">
         <v>20.22539061435029</v>
       </c>
@@ -4590,9 +4553,6 @@
       </c>
       <c r="AI36" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>45.72171601638512</v>
       </c>
     </row>
     <row r="37">
@@ -4683,7 +4643,9 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>32.47607689365352</v>
+      </c>
       <c r="AC37" t="n">
         <v>20.43551457876363</v>
       </c>
@@ -4704,9 +4666,6 @@
       </c>
       <c r="AI37" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>32.47607689365352</v>
       </c>
     </row>
     <row r="38">
@@ -4797,7 +4756,9 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>31.24223026798138</v>
+      </c>
       <c r="AC38" t="n">
         <v>18.33816184036092</v>
       </c>
@@ -4818,9 +4779,6 @@
       </c>
       <c r="AI38" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>31.24223026798137</v>
       </c>
     </row>
     <row r="39">
@@ -4911,7 +4869,9 @@
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>22.29074496544098</v>
+      </c>
       <c r="AC39" t="n">
         <v>23.46035441231151</v>
       </c>
@@ -4932,9 +4892,6 @@
       </c>
       <c r="AI39" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>22.29074496544098</v>
       </c>
     </row>
     <row r="40">
@@ -5025,7 +4982,9 @@
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>40.95714602250389</v>
+      </c>
       <c r="AC40" t="n">
         <v>19.95235879694914</v>
       </c>
@@ -5046,9 +5005,6 @@
       </c>
       <c r="AI40" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>40.95714602250388</v>
       </c>
     </row>
     <row r="41">
@@ -5139,7 +5095,9 @@
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>32.65053512949007</v>
+      </c>
       <c r="AC41" t="n">
         <v>23.41807314508799</v>
       </c>
@@ -5160,9 +5118,6 @@
       </c>
       <c r="AI41" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>32.65053512949007</v>
       </c>
     </row>
     <row r="42">
@@ -5253,7 +5208,9 @@
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>32.65053512949007</v>
+      </c>
       <c r="AC42" t="n">
         <v>23.69296384429431</v>
       </c>
@@ -5274,9 +5231,6 @@
       </c>
       <c r="AI42" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>32.65053512949007</v>
       </c>
     </row>
     <row r="43">
@@ -5367,7 +5321,9 @@
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>32.65053512949007</v>
+      </c>
       <c r="AC43" t="n">
         <v>23.41807314508799</v>
       </c>
@@ -5388,9 +5344,6 @@
       </c>
       <c r="AI43" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>32.65053512949007</v>
       </c>
     </row>
     <row r="44">
@@ -5481,7 +5434,9 @@
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
+      <c r="AB44" t="n">
+        <v>32.65053512949007</v>
+      </c>
       <c r="AC44" t="n">
         <v>23.69296384429431</v>
       </c>
@@ -5502,9 +5457,6 @@
       </c>
       <c r="AI44" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>32.65053512949007</v>
       </c>
     </row>
     <row r="45">
@@ -5595,7 +5547,9 @@
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
+      <c r="AB45" t="n">
+        <v>34.94837353504887</v>
+      </c>
       <c r="AC45" t="n">
         <v>21.61381013660498</v>
       </c>
@@ -5616,9 +5570,6 @@
       </c>
       <c r="AI45" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>34.94837353504887</v>
       </c>
     </row>
     <row r="46">
@@ -5709,7 +5660,9 @@
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+      <c r="AB46" t="n">
+        <v>27.61940167646294</v>
+      </c>
       <c r="AC46" t="n">
         <v>21.83504356012952</v>
       </c>
@@ -5730,9 +5683,6 @@
       </c>
       <c r="AI46" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>27.61940167646294</v>
       </c>
     </row>
     <row r="47">
@@ -5823,7 +5773,9 @@
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
+      <c r="AB47" t="n">
+        <v>31.61114054973259</v>
+      </c>
       <c r="AC47" t="n">
         <v>23.03769888705348</v>
       </c>
@@ -5844,9 +5796,6 @@
       </c>
       <c r="AI47" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>31.61114054973259</v>
       </c>
     </row>
     <row r="48">
@@ -5937,7 +5886,9 @@
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+      <c r="AB48" t="n">
+        <v>32.58259222016648</v>
+      </c>
       <c r="AC48" t="n">
         <v>22.81594444937604</v>
       </c>
@@ -5958,9 +5909,6 @@
       </c>
       <c r="AI48" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>32.58259222016648</v>
       </c>
     </row>
     <row r="49">
@@ -6051,7 +5999,9 @@
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
+      <c r="AB49" t="n">
+        <v>37.10169593659131</v>
+      </c>
       <c r="AC49" t="n">
         <v>19.00837607025699</v>
       </c>
@@ -6072,9 +6022,6 @@
       </c>
       <c r="AI49" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>37.10169593659131</v>
       </c>
     </row>
     <row r="50">
@@ -6165,7 +6112,9 @@
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
+      <c r="AB50" t="n">
+        <v>46.62061318477367</v>
+      </c>
       <c r="AC50" t="n">
         <v>20.35145460742419</v>
       </c>
@@ -6186,9 +6135,6 @@
       </c>
       <c r="AI50" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>46.62061318477368</v>
       </c>
     </row>
     <row r="51">
@@ -6279,7 +6225,9 @@
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>27.64252745359939</v>
+      </c>
       <c r="AC51" t="n">
         <v>18.4009569706375</v>
       </c>
@@ -6300,9 +6248,6 @@
       </c>
       <c r="AI51" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>27.64252745359938</v>
       </c>
     </row>
     <row r="52">
@@ -6393,7 +6338,9 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
+      <c r="AB52" t="n">
+        <v>31.43663314688067</v>
+      </c>
       <c r="AC52" t="n">
         <v>17.05256609052653</v>
       </c>
@@ -6414,9 +6361,6 @@
       </c>
       <c r="AI52" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>31.43663314688067</v>
       </c>
     </row>
     <row r="53">
@@ -6507,7 +6451,9 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
+      <c r="AB53" t="n">
+        <v>16.47515809594595</v>
+      </c>
       <c r="AC53" t="n">
         <v>22.73149185356439</v>
       </c>
@@ -6528,9 +6474,6 @@
       </c>
       <c r="AI53" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>16.47515809594594</v>
       </c>
     </row>
     <row r="54">
@@ -6621,7 +6564,9 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="n">
+        <v>17.18961723916043</v>
+      </c>
       <c r="AC54" t="n">
         <v>22.59428612618935</v>
       </c>
@@ -6642,9 +6587,6 @@
       </c>
       <c r="AI54" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>17.18961723916043</v>
       </c>
     </row>
     <row r="55">
@@ -6735,7 +6677,9 @@
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>34.16916319918331</v>
+      </c>
       <c r="AC55" t="n">
         <v>17.96155362172935</v>
       </c>
@@ -6756,9 +6700,6 @@
       </c>
       <c r="AI55" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>34.16916319918331</v>
       </c>
     </row>
     <row r="56">
@@ -6849,7 +6790,9 @@
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
+      <c r="AB56" t="n">
+        <v>31.13148059335148</v>
+      </c>
       <c r="AC56" t="n">
         <v>23.83046457818877</v>
       </c>
@@ -6870,9 +6813,6 @@
       </c>
       <c r="AI56" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>31.13148059335148</v>
       </c>
     </row>
     <row r="57">
@@ -6963,7 +6903,9 @@
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
+      <c r="AB57" t="n">
+        <v>42.28261169430561</v>
+      </c>
       <c r="AC57" t="n">
         <v>18.88264371189142</v>
       </c>
@@ -6984,9 +6926,6 @@
       </c>
       <c r="AI57" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>42.2826116943056</v>
       </c>
     </row>
     <row r="58">
@@ -7077,7 +7016,9 @@
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+      <c r="AB58" t="n">
+        <v>30.4083735401035</v>
+      </c>
       <c r="AC58" t="n">
         <v>23.10107496024945</v>
       </c>
@@ -7098,9 +7039,6 @@
       </c>
       <c r="AI58" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>30.4083735401035</v>
       </c>
     </row>
     <row r="59">
@@ -7191,7 +7129,9 @@
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="n">
+        <v>41.39388452825128</v>
+      </c>
       <c r="AC59" t="n">
         <v>21.12953817664699</v>
       </c>
@@ -7212,9 +7152,6 @@
       </c>
       <c r="AI59" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>41.39388452825129</v>
       </c>
     </row>
     <row r="60">
@@ -7305,7 +7242,9 @@
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AB60" t="n">
+        <v>28.16106955669685</v>
+      </c>
       <c r="AC60" t="n">
         <v>20.5721415762045</v>
       </c>
@@ -7326,9 +7265,6 @@
       </c>
       <c r="AI60" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>28.16106955669684</v>
       </c>
     </row>
     <row r="61">
@@ -7419,7 +7355,9 @@
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>28.34964144442967</v>
+      </c>
       <c r="AC61" t="n">
         <v>17.00037475445168</v>
       </c>
@@ -7440,9 +7378,6 @@
       </c>
       <c r="AI61" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>28.34964144442966</v>
       </c>
     </row>
     <row r="62">
@@ -7533,7 +7468,9 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+      <c r="AB62" t="n">
+        <v>35.750550975415</v>
+      </c>
       <c r="AC62" t="n">
         <v>21.57168129774534</v>
       </c>
@@ -7554,9 +7491,6 @@
       </c>
       <c r="AI62" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>35.75055097541501</v>
       </c>
     </row>
     <row r="63">
@@ -7647,7 +7581,9 @@
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+      <c r="AB63" t="n">
+        <v>31.74524498440573</v>
+      </c>
       <c r="AC63" t="n">
         <v>22.34107993933516</v>
       </c>
@@ -7668,9 +7604,6 @@
       </c>
       <c r="AI63" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>31.74524498440575</v>
       </c>
     </row>
     <row r="64">
@@ -7757,7 +7690,9 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+      <c r="AB64" t="n">
+        <v>32.75482157518042</v>
+      </c>
       <c r="AC64" t="n">
         <v>22.34107993933516</v>
       </c>
@@ -7778,9 +7713,6 @@
       </c>
       <c r="AI64" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>32.75482157518042</v>
       </c>
     </row>
     <row r="65">
@@ -7871,7 +7803,9 @@
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AB65" t="n">
+        <v>37.77978443238764</v>
+      </c>
       <c r="AC65" t="n">
         <v>19.74243374394122</v>
       </c>
@@ -7892,9 +7826,6 @@
       </c>
       <c r="AI65" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>37.77978443238764</v>
       </c>
     </row>
     <row r="66">
@@ -7985,7 +7916,9 @@
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+      <c r="AB66" t="n">
+        <v>46.78990518799996</v>
+      </c>
       <c r="AC66" t="n">
         <v>21.12953817664699</v>
       </c>
@@ -8006,9 +7939,6 @@
       </c>
       <c r="AI66" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>46.78990518799996</v>
       </c>
     </row>
     <row r="67">
@@ -8099,7 +8029,9 @@
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+      <c r="AB67" t="n">
+        <v>29.55848025895564</v>
+      </c>
       <c r="AC67" t="n">
         <v>20.27791349230865</v>
       </c>
@@ -8120,9 +8052,6 @@
       </c>
       <c r="AI67" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>29.55848025895563</v>
       </c>
     </row>
     <row r="68">
@@ -8213,7 +8142,9 @@
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
-      <c r="AB68" t="inlineStr"/>
+      <c r="AB68" t="n">
+        <v>27.95108301698842</v>
+      </c>
       <c r="AC68" t="n">
         <v>20.61418801318365</v>
       </c>
@@ -8234,9 +8165,6 @@
       </c>
       <c r="AI68" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>27.95108301698842</v>
       </c>
     </row>
     <row r="69">
@@ -8327,7 +8255,9 @@
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
+      <c r="AB69" t="n">
+        <v>24.10341074609785</v>
+      </c>
       <c r="AC69" t="n">
         <v>22.71038088367341</v>
       </c>
@@ -8348,9 +8278,6 @@
       </c>
       <c r="AI69" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>24.10341074609785</v>
       </c>
     </row>
     <row r="70">
@@ -8441,7 +8368,9 @@
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
+      <c r="AB70" t="n">
+        <v>33.07869485466203</v>
+      </c>
       <c r="AC70" t="n">
         <v>23.27011621677441</v>
       </c>
@@ -8462,9 +8391,6 @@
       </c>
       <c r="AI70" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>33.07869485466202</v>
       </c>
     </row>
     <row r="71">
@@ -8555,7 +8481,9 @@
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
+      <c r="AB71" t="n">
+        <v>28.43772466129882</v>
+      </c>
       <c r="AC71" t="n">
         <v>22.81594444937604</v>
       </c>
@@ -8576,9 +8504,6 @@
       </c>
       <c r="AI71" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>28.43772466129882</v>
       </c>
     </row>
     <row r="72">
@@ -8669,7 +8594,9 @@
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
+      <c r="AB72" t="n">
+        <v>27.25954615592946</v>
+      </c>
       <c r="AC72" t="n">
         <v>20.70880516475933</v>
       </c>
@@ -8690,9 +8617,6 @@
       </c>
       <c r="AI72" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>27.25954615592946</v>
       </c>
     </row>
     <row r="73">
@@ -8783,7 +8707,9 @@
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
+      <c r="AB73" t="n">
+        <v>30.02082045458015</v>
+      </c>
       <c r="AC73" t="n">
         <v>19.52210542008766</v>
       </c>
@@ -8804,9 +8730,6 @@
       </c>
       <c r="AI73" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>30.02082045458014</v>
       </c>
     </row>
     <row r="74">
@@ -8897,7 +8820,9 @@
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
-      <c r="AB74" t="inlineStr"/>
+      <c r="AB74" t="n">
+        <v>26.46707679984683</v>
+      </c>
       <c r="AC74" t="n">
         <v>15.83269105354342</v>
       </c>
@@ -8918,9 +8843,6 @@
       </c>
       <c r="AI74" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>26.46707679984683</v>
       </c>
     </row>
     <row r="75">
@@ -9011,7 +8933,9 @@
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
+      <c r="AB75" t="n">
+        <v>30.22124201621856</v>
+      </c>
       <c r="AC75" t="n">
         <v>21.69807823935166</v>
       </c>
@@ -9032,9 +8956,6 @@
       </c>
       <c r="AI75" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>30.22124201621855</v>
       </c>
     </row>
     <row r="76">
@@ -9125,7 +9046,9 @@
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
+      <c r="AB76" t="n">
+        <v>32.73336164766602</v>
+      </c>
       <c r="AC76" t="n">
         <v>18.65221495523094</v>
       </c>
@@ -9146,9 +9069,6 @@
       </c>
       <c r="AI76" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>32.73336164766602</v>
       </c>
     </row>
     <row r="77">
@@ -9239,7 +9159,9 @@
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
+      <c r="AB77" t="n">
+        <v>27.85958429127932</v>
+      </c>
       <c r="AC77" t="n">
         <v>17.05256609052653</v>
       </c>
@@ -9260,9 +9182,6 @@
       </c>
       <c r="AI77" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>27.85958429127932</v>
       </c>
     </row>
     <row r="78">
@@ -9353,7 +9272,9 @@
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
+      <c r="AB78" t="n">
+        <v>21.8162096187406</v>
+      </c>
       <c r="AC78" t="n">
         <v>22.13017055061581</v>
       </c>
@@ -9374,9 +9295,6 @@
       </c>
       <c r="AI78" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>21.8162096187406</v>
       </c>
     </row>
     <row r="79">
@@ -9467,7 +9385,9 @@
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+      <c r="AB79" t="n">
+        <v>18.28478648070588</v>
+      </c>
       <c r="AC79" t="n">
         <v>16.19730406719173</v>
       </c>
@@ -9488,9 +9408,6 @@
       </c>
       <c r="AI79" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>18.28478648070587</v>
       </c>
     </row>
     <row r="80">
@@ -9581,7 +9498,9 @@
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+      <c r="AB80" t="n">
+        <v>22.12908955486301</v>
+      </c>
       <c r="AC80" t="n">
         <v>21.30845475552441</v>
       </c>
@@ -9602,9 +9521,6 @@
       </c>
       <c r="AI80" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ80" t="n">
-        <v>22.12908955486301</v>
       </c>
     </row>
     <row r="81">
@@ -9695,7 +9611,9 @@
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
+      <c r="AB81" t="n">
+        <v>23.88772942228289</v>
+      </c>
       <c r="AC81" t="n">
         <v>15.13544690515705</v>
       </c>
@@ -9716,9 +9634,6 @@
       </c>
       <c r="AI81" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>23.88772942228289</v>
       </c>
     </row>
     <row r="82">
@@ -9809,7 +9724,9 @@
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
+      <c r="AB82" t="n">
+        <v>29.22142888916803</v>
+      </c>
       <c r="AC82" t="n">
         <v>22.53097282164527</v>
       </c>
@@ -9830,9 +9747,6 @@
       </c>
       <c r="AI82" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>29.22142888916803</v>
       </c>
     </row>
     <row r="83">
@@ -9923,7 +9837,9 @@
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
+      <c r="AB83" t="n">
+        <v>26.31625012037236</v>
+      </c>
       <c r="AC83" t="n">
         <v>24.38083708972119</v>
       </c>
@@ -9944,9 +9860,6 @@
       </c>
       <c r="AI83" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>26.31625012037235</v>
       </c>
     </row>
     <row r="84">
@@ -10037,7 +9950,9 @@
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
+      <c r="AB84" t="n">
+        <v>30.20416467837983</v>
+      </c>
       <c r="AC84" t="n">
         <v>23.65066335612901</v>
       </c>
@@ -10058,9 +9973,6 @@
       </c>
       <c r="AI84" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>30.20416467837984</v>
       </c>
     </row>
     <row r="85">
@@ -10151,7 +10063,9 @@
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
+      <c r="AB85" t="n">
+        <v>27.98331631734705</v>
+      </c>
       <c r="AC85" t="n">
         <v>22.52042136643655</v>
       </c>
@@ -10172,9 +10086,6 @@
       </c>
       <c r="AI85" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>27.98331631734705</v>
       </c>
     </row>
     <row r="86">
@@ -10265,7 +10176,9 @@
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
+      <c r="AB86" t="n">
+        <v>30.59860950966031</v>
+      </c>
       <c r="AC86" t="n">
         <v>22.98489149021835</v>
       </c>
@@ -10286,9 +10199,6 @@
       </c>
       <c r="AI86" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>30.5986095096603</v>
       </c>
     </row>
     <row r="87">
@@ -10379,7 +10289,9 @@
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
+      <c r="AB87" t="n">
+        <v>27.00689943428555</v>
+      </c>
       <c r="AC87" t="n">
         <v>16.85426750608011</v>
       </c>
@@ -10400,9 +10312,6 @@
       </c>
       <c r="AI87" t="n">
         <v>10</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>27.00689943428556</v>
       </c>
     </row>
     <row r="88">
@@ -10493,7 +10402,9 @@
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AB88" t="n">
+        <v>20.09981608868212</v>
+      </c>
       <c r="AC88" t="n">
         <v>22.68927078529925</v>
       </c>
@@ -10514,9 +10425,6 @@
       </c>
       <c r="AI88" t="n">
         <v>19</v>
-      </c>
-      <c r="AJ88" t="n">
-        <v>20.09981608868211</v>
       </c>
     </row>
     <row r="89">
@@ -10592,9 +10500,11 @@
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+      <c r="AA89" t="n">
+        <v>592012</v>
+      </c>
       <c r="AB89" t="n">
-        <v>592012</v>
+        <v>59.38716473519461</v>
       </c>
       <c r="AC89" t="n">
         <v>18.95598381663376</v>
@@ -10616,9 +10526,6 @@
       </c>
       <c r="AI89" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>59.38716473519461</v>
       </c>
     </row>
     <row r="90">
@@ -10694,9 +10601,11 @@
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
+      <c r="AA90" t="n">
+        <v>592033</v>
+      </c>
       <c r="AB90" t="n">
-        <v>592033</v>
+        <v>55.07549417735655</v>
       </c>
       <c r="AC90" t="n">
         <v>19.6375036189457</v>
@@ -10718,9 +10627,6 @@
       </c>
       <c r="AI90" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ90" t="n">
-        <v>55.07549417735656</v>
       </c>
     </row>
     <row r="91">
@@ -10796,9 +10702,11 @@
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
+      <c r="AA91" t="n">
+        <v>592031</v>
+      </c>
       <c r="AB91" t="n">
-        <v>592031</v>
+        <v>45.17757835768303</v>
       </c>
       <c r="AC91" t="n">
         <v>19.73193975960648</v>
@@ -10820,9 +10728,6 @@
       </c>
       <c r="AI91" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ91" t="n">
-        <v>45.17757835768303</v>
       </c>
     </row>
     <row r="92">
@@ -10898,9 +10803,11 @@
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
+      <c r="AA92" t="n">
+        <v>592251</v>
+      </c>
       <c r="AB92" t="n">
-        <v>592251</v>
+        <v>43.38637434690112</v>
       </c>
       <c r="AC92" t="n">
         <v>21.23477563046862</v>
@@ -10922,9 +10829,6 @@
       </c>
       <c r="AI92" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ92" t="n">
-        <v>43.38637434690111</v>
       </c>
     </row>
     <row r="93">
@@ -11000,9 +10904,11 @@
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
+      <c r="AA93" t="n">
+        <v>592151</v>
+      </c>
       <c r="AB93" t="n">
-        <v>592151</v>
+        <v>61.02294354014969</v>
       </c>
       <c r="AC93" t="n">
         <v>18.34862715762646</v>
@@ -11024,9 +10930,6 @@
       </c>
       <c r="AI93" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>61.02294354014969</v>
       </c>
     </row>
     <row r="94">
@@ -11102,9 +11005,11 @@
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
+      <c r="AA94" t="n">
+        <v>592379</v>
+      </c>
       <c r="AB94" t="n">
-        <v>592379</v>
+        <v>50.18888849181604</v>
       </c>
       <c r="AC94" t="n">
         <v>17.41805548744802</v>
@@ -11126,9 +11031,6 @@
       </c>
       <c r="AI94" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>50.18888849181604</v>
       </c>
     </row>
     <row r="95">
@@ -11204,9 +11106,11 @@
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+      <c r="AA95" t="n">
+        <v>592333</v>
+      </c>
       <c r="AB95" t="n">
-        <v>592333</v>
+        <v>44.53537356895627</v>
       </c>
       <c r="AC95" t="n">
         <v>18.87216741589208</v>
@@ -11228,9 +11132,6 @@
       </c>
       <c r="AI95" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ95" t="n">
-        <v>44.53537356895627</v>
       </c>
     </row>
     <row r="96">
@@ -11306,9 +11207,11 @@
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
+      <c r="AA96" t="n">
+        <v>592305</v>
+      </c>
       <c r="AB96" t="n">
-        <v>592305</v>
+        <v>41.91201493351629</v>
       </c>
       <c r="AC96" t="n">
         <v>18.93502842365038</v>
@@ -11330,9 +11233,6 @@
       </c>
       <c r="AI96" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>41.91201493351629</v>
       </c>
     </row>
     <row r="97">
@@ -11408,9 +11308,11 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
+      <c r="AA97" t="n">
+        <v>592315</v>
+      </c>
       <c r="AB97" t="n">
-        <v>592315</v>
+        <v>70.70612613426273</v>
       </c>
       <c r="AC97" t="n">
         <v>18.25444704516262</v>
@@ -11432,9 +11334,6 @@
       </c>
       <c r="AI97" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ97" t="n">
-        <v>70.70612613426273</v>
       </c>
     </row>
     <row r="98">
@@ -11510,9 +11409,11 @@
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
+      <c r="AA98" t="n">
+        <v>592052</v>
+      </c>
       <c r="AB98" t="n">
-        <v>592052</v>
+        <v>56.15700798713841</v>
       </c>
       <c r="AC98" t="n">
         <v>18.57891857037128</v>
@@ -11534,9 +11435,6 @@
       </c>
       <c r="AI98" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ98" t="n">
-        <v>56.15700798713841</v>
       </c>
     </row>
     <row r="99">
@@ -11612,9 +11510,11 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
+      <c r="AA99" t="n">
+        <v>592353</v>
+      </c>
       <c r="AB99" t="n">
-        <v>592353</v>
+        <v>55.79246449666994</v>
       </c>
       <c r="AC99" t="n">
         <v>20.42500632491659</v>
@@ -11636,9 +11536,6 @@
       </c>
       <c r="AI99" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>55.79246449666994</v>
       </c>
     </row>
     <row r="100">
@@ -11714,9 +11611,11 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
+      <c r="AA100" t="n">
+        <v>592324</v>
+      </c>
       <c r="AB100" t="n">
-        <v>592324</v>
+        <v>65.93475017680478</v>
       </c>
       <c r="AC100" t="n">
         <v>19.09221488352959</v>
@@ -11738,9 +11637,6 @@
       </c>
       <c r="AI100" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>65.93475017680478</v>
       </c>
     </row>
     <row r="101">
@@ -11816,9 +11712,11 @@
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
+      <c r="AA101" t="n">
+        <v>592378</v>
+      </c>
       <c r="AB101" t="n">
-        <v>592378</v>
+        <v>35.49376434405512</v>
       </c>
       <c r="AC101" t="n">
         <v>16.33279843075314</v>
@@ -11840,9 +11738,6 @@
       </c>
       <c r="AI101" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>35.49376434405513</v>
       </c>
     </row>
     <row r="102">
@@ -11918,9 +11813,11 @@
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
+      <c r="AA102" t="n">
+        <v>592339</v>
+      </c>
       <c r="AB102" t="n">
-        <v>592339</v>
+        <v>62.55686848770559</v>
       </c>
       <c r="AC102" t="n">
         <v>16.76036358431324</v>
@@ -11942,9 +11839,6 @@
       </c>
       <c r="AI102" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>62.55686848770559</v>
       </c>
     </row>
     <row r="103">
@@ -12020,9 +11914,11 @@
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
+      <c r="AA103" t="n">
+        <v>592129</v>
+      </c>
       <c r="AB103" t="n">
-        <v>592129</v>
+        <v>48.18483993222593</v>
       </c>
       <c r="AC103" t="n">
         <v>18.79883937571327</v>
@@ -12044,9 +11940,6 @@
       </c>
       <c r="AI103" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ103" t="n">
-        <v>48.18483993222593</v>
       </c>
     </row>
     <row r="104">
@@ -12122,9 +12015,11 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
+      <c r="AA104" t="n">
+        <v>592101</v>
+      </c>
       <c r="AB104" t="n">
-        <v>592101</v>
+        <v>48.50036505453044</v>
       </c>
       <c r="AC104" t="n">
         <v>18.64174339727379</v>
@@ -12146,9 +12041,6 @@
       </c>
       <c r="AI104" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>48.50036505453044</v>
       </c>
     </row>
     <row r="105">
@@ -12224,9 +12116,11 @@
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
+      <c r="AA105" t="n">
+        <v>592222</v>
+      </c>
       <c r="AB105" t="n">
-        <v>592222</v>
+        <v>48.82405714366423</v>
       </c>
       <c r="AC105" t="n">
         <v>18.67315871703932</v>
@@ -12248,9 +12142,6 @@
       </c>
       <c r="AI105" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ105" t="n">
-        <v>48.82405714366423</v>
       </c>
     </row>
     <row r="106">
@@ -12326,9 +12217,11 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
+      <c r="AA106" t="n">
+        <v>592115</v>
+      </c>
       <c r="AB106" t="n">
-        <v>592115</v>
+        <v>42.08566962870098</v>
       </c>
       <c r="AC106" t="n">
         <v>18.09751889653755</v>
@@ -12350,9 +12243,6 @@
       </c>
       <c r="AI106" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ106" t="n">
-        <v>42.08566962870098</v>
       </c>
     </row>
     <row r="107">
@@ -12428,9 +12318,11 @@
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
+      <c r="AA107" t="n">
+        <v>592065</v>
+      </c>
       <c r="AB107" t="n">
-        <v>592065</v>
+        <v>51.94526295590641</v>
       </c>
       <c r="AC107" t="n">
         <v>19.52210542008766</v>
@@ -12452,9 +12344,6 @@
       </c>
       <c r="AI107" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ107" t="n">
-        <v>51.94526295590641</v>
       </c>
     </row>
     <row r="108">
@@ -12530,9 +12419,11 @@
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
+      <c r="AA108" t="n">
+        <v>592180</v>
+      </c>
       <c r="AB108" t="n">
-        <v>592180</v>
+        <v>55.62393534386633</v>
       </c>
       <c r="AC108" t="n">
         <v>19.81589768231686</v>
@@ -12554,9 +12445,6 @@
       </c>
       <c r="AI108" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ108" t="n">
-        <v>55.62393534386634</v>
       </c>
     </row>
     <row r="109">
@@ -12632,9 +12520,11 @@
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
+      <c r="AA109" t="n">
+        <v>592225</v>
+      </c>
       <c r="AB109" t="n">
-        <v>592225</v>
+        <v>58.95157666997726</v>
       </c>
       <c r="AC109" t="n">
         <v>17.58522385935366</v>
@@ -12656,9 +12546,6 @@
       </c>
       <c r="AI109" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ109" t="n">
-        <v>58.95157666997726</v>
       </c>
     </row>
     <row r="110">
@@ -12734,9 +12621,11 @@
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
+      <c r="AA110" t="n">
+        <v>592156</v>
+      </c>
       <c r="AB110" t="n">
-        <v>592156</v>
+        <v>61.68991897543837</v>
       </c>
       <c r="AC110" t="n">
         <v>19.60602879221287</v>
@@ -12758,9 +12647,6 @@
       </c>
       <c r="AI110" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>61.68991897543837</v>
       </c>
     </row>
     <row r="111">
@@ -12836,9 +12722,11 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
+      <c r="AA111" t="n">
+        <v>592293</v>
+      </c>
       <c r="AB111" t="n">
-        <v>592293</v>
+        <v>42.51564615776595</v>
       </c>
       <c r="AC111" t="n">
         <v>17.86744508792834</v>
@@ -12860,9 +12748,6 @@
       </c>
       <c r="AI111" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>42.51564615776597</v>
       </c>
     </row>
     <row r="112">
@@ -12938,9 +12823,11 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
+      <c r="AA112" t="n">
+        <v>592141</v>
+      </c>
       <c r="AB112" t="n">
-        <v>592141</v>
+        <v>43.63977691743113</v>
       </c>
       <c r="AC112" t="n">
         <v>17.36582663449692</v>
@@ -12962,9 +12849,6 @@
       </c>
       <c r="AI112" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>43.63977691743113</v>
       </c>
     </row>
     <row r="113">
@@ -13040,9 +12924,11 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
+      <c r="AA113" t="n">
+        <v>592087</v>
+      </c>
       <c r="AB113" t="n">
-        <v>592087</v>
+        <v>48.27107341587141</v>
       </c>
       <c r="AC113" t="n">
         <v>20.38297547367987</v>
@@ -13064,9 +12950,6 @@
       </c>
       <c r="AI113" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>48.27107341587141</v>
       </c>
     </row>
     <row r="114">
@@ -13142,9 +13025,11 @@
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
+      <c r="AA114" t="n">
+        <v>592041</v>
+      </c>
       <c r="AB114" t="n">
-        <v>592041</v>
+        <v>55.68533253151493</v>
       </c>
       <c r="AC114" t="n">
         <v>18.93502842365038</v>
@@ -13166,9 +13051,6 @@
       </c>
       <c r="AI114" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ114" t="n">
-        <v>55.68533253151494</v>
       </c>
     </row>
     <row r="115">
@@ -13244,9 +13126,11 @@
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
+      <c r="AA115" t="n">
+        <v>592043</v>
+      </c>
       <c r="AB115" t="n">
-        <v>592043</v>
+        <v>46.55285938373989</v>
       </c>
       <c r="AC115" t="n">
         <v>17.6165740449392</v>
@@ -13268,9 +13152,6 @@
       </c>
       <c r="AI115" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>46.5528593837399</v>
       </c>
     </row>
     <row r="116">
@@ -13346,9 +13227,11 @@
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr"/>
+      <c r="AA116" t="n">
+        <v>592064</v>
+      </c>
       <c r="AB116" t="n">
-        <v>592064</v>
+        <v>28.78285344011537</v>
       </c>
       <c r="AC116" t="n">
         <v>16.38492126900117</v>
@@ -13370,9 +13253,6 @@
       </c>
       <c r="AI116" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ116" t="n">
-        <v>28.78285344011539</v>
       </c>
     </row>
     <row r="117">
@@ -13448,9 +13328,11 @@
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
+      <c r="AA117" t="n">
+        <v>592046</v>
+      </c>
       <c r="AB117" t="n">
-        <v>592046</v>
+        <v>40.26096003557048</v>
       </c>
       <c r="AC117" t="n">
         <v>20.6352125308998</v>
@@ -13472,9 +13354,6 @@
       </c>
       <c r="AI117" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>40.26096003557048</v>
       </c>
     </row>
     <row r="118">
@@ -13550,9 +13429,11 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
+      <c r="AA118" t="n">
+        <v>592046</v>
+      </c>
       <c r="AB118" t="n">
-        <v>592046</v>
+        <v>40.26096003557048</v>
       </c>
       <c r="AC118" t="n">
         <v>20.6352125308998</v>
@@ -13574,9 +13455,6 @@
       </c>
       <c r="AI118" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ118" t="n">
-        <v>40.26096003557048</v>
       </c>
     </row>
     <row r="119">
@@ -13652,9 +13530,11 @@
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr"/>
+      <c r="AA119" t="n">
+        <v>592004</v>
+      </c>
       <c r="AB119" t="n">
-        <v>592004</v>
+        <v>38.62830546324884</v>
       </c>
       <c r="AC119" t="n">
         <v>19.45917195679012</v>
@@ -13676,9 +13556,6 @@
       </c>
       <c r="AI119" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>38.62830546324885</v>
       </c>
     </row>
     <row r="120">
@@ -13754,9 +13631,11 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr"/>
+      <c r="AA120" t="n">
+        <v>592037</v>
+      </c>
       <c r="AB120" t="n">
-        <v>592037</v>
+        <v>47.60443554531614</v>
       </c>
       <c r="AC120" t="n">
         <v>17.52252928274375</v>
@@ -13778,9 +13657,6 @@
       </c>
       <c r="AI120" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ120" t="n">
-        <v>47.60443554531616</v>
       </c>
     </row>
     <row r="121">
@@ -13856,9 +13732,11 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
+      <c r="AA121" t="n">
+        <v>592037</v>
+      </c>
       <c r="AB121" t="n">
-        <v>592037</v>
+        <v>47.60443554531614</v>
       </c>
       <c r="AC121" t="n">
         <v>17.52252928274375</v>
@@ -13880,9 +13758,6 @@
       </c>
       <c r="AI121" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>47.60443554531616</v>
       </c>
     </row>
     <row r="122">
@@ -13958,9 +13833,11 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr"/>
+      <c r="AA122" t="n">
+        <v>592073</v>
+      </c>
       <c r="AB122" t="n">
-        <v>592073</v>
+        <v>38.09610849251812</v>
       </c>
       <c r="AC122" t="n">
         <v>17.58522385935366</v>
@@ -13982,9 +13859,6 @@
       </c>
       <c r="AI122" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>38.09610849251811</v>
       </c>
     </row>
     <row r="123">
@@ -14060,9 +13934,11 @@
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
+      <c r="AA123" t="n">
+        <v>592227</v>
+      </c>
       <c r="AB123" t="n">
-        <v>592227</v>
+        <v>35.84967061566433</v>
       </c>
       <c r="AC123" t="n">
         <v>17.36582663449692</v>
@@ -14084,9 +13960,6 @@
       </c>
       <c r="AI123" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>35.84967061566434</v>
       </c>
     </row>
     <row r="124">
@@ -14162,9 +14035,11 @@
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
+      <c r="AA124" t="n">
+        <v>592223</v>
+      </c>
       <c r="AB124" t="n">
-        <v>592223</v>
+        <v>46.88581586268426</v>
       </c>
       <c r="AC124" t="n">
         <v>17.26138501385894</v>
@@ -14186,9 +14061,6 @@
       </c>
       <c r="AI124" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>46.88581586268425</v>
       </c>
     </row>
     <row r="125">
@@ -14264,9 +14136,11 @@
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
+      <c r="AA125" t="n">
+        <v>592231</v>
+      </c>
       <c r="AB125" t="n">
-        <v>592231</v>
+        <v>51.2080861390158</v>
       </c>
       <c r="AC125" t="n">
         <v>19.50112673566813</v>
@@ -14288,9 +14162,6 @@
       </c>
       <c r="AI125" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>51.2080861390158</v>
       </c>
     </row>
     <row r="126">
@@ -14366,9 +14237,11 @@
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
+      <c r="AA126" t="n">
+        <v>592273</v>
+      </c>
       <c r="AB126" t="n">
-        <v>592273</v>
+        <v>44.75623909743305</v>
       </c>
       <c r="AC126" t="n">
         <v>18.26491064183982</v>
@@ -14390,9 +14263,6 @@
       </c>
       <c r="AI126" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>44.75623909743306</v>
       </c>
     </row>
     <row r="127">
@@ -14468,9 +14338,11 @@
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
+      <c r="AA127" t="n">
+        <v>592269</v>
+      </c>
       <c r="AB127" t="n">
-        <v>592269</v>
+        <v>38.4857211629195</v>
       </c>
       <c r="AC127" t="n">
         <v>19.35430011521448</v>
@@ -14492,9 +14364,6 @@
       </c>
       <c r="AI127" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>38.48572116291952</v>
       </c>
     </row>
     <row r="128">
@@ -14570,9 +14439,11 @@
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr"/>
+      <c r="AA128" t="n">
+        <v>592299</v>
+      </c>
       <c r="AB128" t="n">
-        <v>592299</v>
+        <v>38.02881287743782</v>
       </c>
       <c r="AC128" t="n">
         <v>17.29271524839077</v>
@@ -14594,9 +14465,6 @@
       </c>
       <c r="AI128" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>38.02881287743784</v>
       </c>
     </row>
     <row r="129">
@@ -14672,9 +14540,11 @@
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
+      <c r="AA129" t="n">
+        <v>592105</v>
+      </c>
       <c r="AB129" t="n">
-        <v>592105</v>
+        <v>42.69161633319679</v>
       </c>
       <c r="AC129" t="n">
         <v>16.1139408757178</v>
@@ -14696,9 +14566,6 @@
       </c>
       <c r="AI129" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>42.69161633319681</v>
       </c>
     </row>
     <row r="130">
@@ -14774,9 +14641,11 @@
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr"/>
+      <c r="AA130" t="n">
+        <v>592220</v>
+      </c>
       <c r="AB130" t="n">
-        <v>592220</v>
+        <v>42.92451945516472</v>
       </c>
       <c r="AC130" t="n">
         <v>17.41805548744802</v>
@@ -14798,9 +14667,6 @@
       </c>
       <c r="AI130" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>42.92451945516469</v>
       </c>
     </row>
     <row r="131">
@@ -14876,9 +14742,11 @@
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
-      <c r="AA131" t="inlineStr"/>
+      <c r="AA131" t="n">
+        <v>592198</v>
+      </c>
       <c r="AB131" t="n">
-        <v>592198</v>
+        <v>40.16479905872414</v>
       </c>
       <c r="AC131" t="n">
         <v>19.8473854677192</v>
@@ -14900,9 +14768,6 @@
       </c>
       <c r="AI131" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>40.16479905872412</v>
       </c>
     </row>
     <row r="132">
@@ -14978,9 +14843,11 @@
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
+      <c r="AA132" t="n">
+        <v>592092</v>
+      </c>
       <c r="AB132" t="n">
-        <v>592092</v>
+        <v>54.14554217891045</v>
       </c>
       <c r="AC132" t="n">
         <v>17.29271524839077</v>
@@ -15002,9 +14869,6 @@
       </c>
       <c r="AI132" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>54.14554217891045</v>
       </c>
     </row>
     <row r="133">
@@ -15080,9 +14944,11 @@
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
+      <c r="AA133" t="n">
+        <v>592092</v>
+      </c>
       <c r="AB133" t="n">
-        <v>592092</v>
+        <v>54.14554217891045</v>
       </c>
       <c r="AC133" t="n">
         <v>17.17784715555647</v>
@@ -15104,9 +14970,6 @@
       </c>
       <c r="AI133" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>54.14554217891045</v>
       </c>
     </row>
     <row r="134">
@@ -15182,9 +15045,11 @@
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr"/>
+      <c r="AA134" t="n">
+        <v>592206</v>
+      </c>
       <c r="AB134" t="n">
-        <v>592206</v>
+        <v>34.63030631687734</v>
       </c>
       <c r="AC134" t="n">
         <v>19.91036687217596</v>
@@ -15206,9 +15071,6 @@
       </c>
       <c r="AI134" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>34.63030631687735</v>
       </c>
     </row>
     <row r="135">
@@ -15284,9 +15146,11 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
+      <c r="AA135" t="n">
+        <v>592249</v>
+      </c>
       <c r="AB135" t="n">
-        <v>592249</v>
+        <v>44.89996935838486</v>
       </c>
       <c r="AC135" t="n">
         <v>17.60612376844635</v>
@@ -15308,9 +15172,6 @@
       </c>
       <c r="AI135" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>44.89996935838485</v>
       </c>
     </row>
     <row r="136">
@@ -15386,9 +15247,11 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
+      <c r="AA136" t="n">
+        <v>592162</v>
+      </c>
       <c r="AB136" t="n">
-        <v>592162</v>
+        <v>43.93419906095097</v>
       </c>
       <c r="AC136" t="n">
         <v>18.78836480301036</v>
@@ -15410,9 +15273,6 @@
       </c>
       <c r="AI136" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>43.93419906095096</v>
       </c>
     </row>
     <row r="137">
@@ -15488,9 +15348,11 @@
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr"/>
+      <c r="AA137" t="n">
+        <v>592317</v>
+      </c>
       <c r="AB137" t="n">
-        <v>592317</v>
+        <v>62.73974732172039</v>
       </c>
       <c r="AC137" t="n">
         <v>18.63127205460582</v>
@@ -15512,9 +15374,6 @@
       </c>
       <c r="AI137" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ137" t="n">
-        <v>62.73974732172039</v>
       </c>
     </row>
     <row r="138">
@@ -15590,9 +15449,11 @@
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
+      <c r="AA138" t="n">
+        <v>592323</v>
+      </c>
       <c r="AB138" t="n">
-        <v>592323</v>
+        <v>56.82593529734338</v>
       </c>
       <c r="AC138" t="n">
         <v>18.11843985492355</v>
@@ -15614,9 +15475,6 @@
       </c>
       <c r="AI138" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ138" t="n">
-        <v>56.82593529734339</v>
       </c>
     </row>
     <row r="139">
@@ -15692,9 +15550,11 @@
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
+      <c r="AA139" t="n">
+        <v>592325</v>
+      </c>
       <c r="AB139" t="n">
-        <v>592325</v>
+        <v>51.97156457320585</v>
       </c>
       <c r="AC139" t="n">
         <v>17.86744508792834</v>
@@ -15716,9 +15576,6 @@
       </c>
       <c r="AI139" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ139" t="n">
-        <v>51.97156457320585</v>
       </c>
     </row>
     <row r="140">
@@ -15794,9 +15651,11 @@
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
+      <c r="AA140" t="n">
+        <v>592365</v>
+      </c>
       <c r="AB140" t="n">
-        <v>592365</v>
+        <v>34.71279366258031</v>
       </c>
       <c r="AC140" t="n">
         <v>19.102695705206</v>
@@ -15818,9 +15677,6 @@
       </c>
       <c r="AI140" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ140" t="n">
-        <v>34.71279366258031</v>
       </c>
     </row>
     <row r="141">
@@ -15896,9 +15752,11 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
+      <c r="AA141" t="n">
+        <v>592344</v>
+      </c>
       <c r="AB141" t="n">
-        <v>592344</v>
+        <v>16.82978356315537</v>
       </c>
       <c r="AC141" t="n">
         <v>17.53297784235603</v>
@@ -15920,9 +15778,6 @@
       </c>
       <c r="AI141" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ141" t="n">
-        <v>16.82978356315537</v>
       </c>
     </row>
     <row r="142">
@@ -15998,9 +15853,11 @@
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
+      <c r="AA142" t="n">
+        <v>592359</v>
+      </c>
       <c r="AB142" t="n">
-        <v>592359</v>
+        <v>48.86662529556703</v>
       </c>
       <c r="AC142" t="n">
         <v>20.08885643607165</v>
@@ -16022,9 +15879,6 @@
       </c>
       <c r="AI142" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ142" t="n">
-        <v>48.86662529556703</v>
       </c>
     </row>
     <row r="143">
@@ -16100,9 +15954,11 @@
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
+      <c r="AA143" t="n">
+        <v>592246</v>
+      </c>
       <c r="AB143" t="n">
-        <v>592246</v>
+        <v>48.48989580379418</v>
       </c>
       <c r="AC143" t="n">
         <v>19.102695705206</v>
@@ -16124,9 +15980,6 @@
       </c>
       <c r="AI143" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ143" t="n">
-        <v>48.48989580379418</v>
       </c>
     </row>
     <row r="144">
@@ -16202,9 +16055,11 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
+      <c r="AA144" t="n">
+        <v>592005</v>
+      </c>
       <c r="AB144" t="n">
-        <v>592005</v>
+        <v>52.45513538310598</v>
       </c>
       <c r="AC144" t="n">
         <v>18.10797926825509</v>
@@ -16226,9 +16081,6 @@
       </c>
       <c r="AI144" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>52.45513538310598</v>
       </c>
     </row>
     <row r="145">
@@ -16304,9 +16156,11 @@
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
+      <c r="AA145" t="n">
+        <v>592132</v>
+      </c>
       <c r="AB145" t="n">
-        <v>592132</v>
+        <v>50.12173210626537</v>
       </c>
       <c r="AC145" t="n">
         <v>18.83026438618137</v>
@@ -16328,9 +16182,6 @@
       </c>
       <c r="AI145" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>50.12173210626536</v>
       </c>
     </row>
     <row r="146">
@@ -16406,9 +16257,11 @@
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr"/>
+      <c r="AA146" t="n">
+        <v>592361</v>
+      </c>
       <c r="AB146" t="n">
-        <v>592361</v>
+        <v>51.64905585832408</v>
       </c>
       <c r="AC146" t="n">
         <v>17.81517008741025</v>
@@ -16430,9 +16283,6 @@
       </c>
       <c r="AI146" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ146" t="n">
-        <v>51.64905585832408</v>
       </c>
     </row>
     <row r="147">
@@ -16508,9 +16358,11 @@
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
+      <c r="AA147" t="n">
+        <v>592074</v>
+      </c>
       <c r="AB147" t="n">
-        <v>592074</v>
+        <v>40.84573233660999</v>
       </c>
       <c r="AC147" t="n">
         <v>18.86169133532805</v>
@@ -16532,9 +16384,6 @@
       </c>
       <c r="AI147" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ147" t="n">
-        <v>40.84573233661</v>
       </c>
     </row>
     <row r="148">
@@ -16610,9 +16459,11 @@
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr"/>
+      <c r="AA148" t="n">
+        <v>592334</v>
+      </c>
       <c r="AB148" t="n">
-        <v>592334</v>
+        <v>37.41961875184389</v>
       </c>
       <c r="AC148" t="n">
         <v>17.70018398447128</v>
@@ -16634,9 +16485,6 @@
       </c>
       <c r="AI148" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ148" t="n">
-        <v>37.41961875184389</v>
       </c>
     </row>
     <row r="149">
@@ -16712,9 +16560,11 @@
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr"/>
+      <c r="AA149" t="n">
+        <v>592016</v>
+      </c>
       <c r="AB149" t="n">
-        <v>592016</v>
+        <v>44.98594091218243</v>
       </c>
       <c r="AC149" t="n">
         <v>21.82450646249033</v>
@@ -16736,9 +16586,6 @@
       </c>
       <c r="AI149" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ149" t="n">
-        <v>44.98594091218241</v>
       </c>
     </row>
     <row r="150">
@@ -16814,9 +16661,11 @@
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
-      <c r="AA150" t="inlineStr"/>
+      <c r="AA150" t="n">
+        <v>592253</v>
+      </c>
       <c r="AB150" t="n">
-        <v>592253</v>
+        <v>62.3287590104805</v>
       </c>
       <c r="AC150" t="n">
         <v>18.49516418821691</v>
@@ -16838,9 +16687,6 @@
       </c>
       <c r="AI150" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ150" t="n">
-        <v>62.3287590104805</v>
       </c>
     </row>
     <row r="151">
@@ -16916,9 +16762,11 @@
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
-      <c r="AA151" t="inlineStr"/>
+      <c r="AA151" t="n">
+        <v>592139</v>
+      </c>
       <c r="AB151" t="n">
-        <v>592139</v>
+        <v>63.04106431069755</v>
       </c>
       <c r="AC151" t="n">
         <v>19.87887519761219</v>
@@ -16940,9 +16788,6 @@
       </c>
       <c r="AI151" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ151" t="n">
-        <v>63.04106431069756</v>
       </c>
     </row>
     <row r="152">
@@ -17018,9 +16863,11 @@
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
-      <c r="AA152" t="inlineStr"/>
+      <c r="AA152" t="n">
+        <v>592014</v>
+      </c>
       <c r="AB152" t="n">
-        <v>592014</v>
+        <v>55.56667726163774</v>
       </c>
       <c r="AC152" t="n">
         <v>18.94550601240116</v>
@@ -17042,9 +16889,6 @@
       </c>
       <c r="AI152" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ152" t="n">
-        <v>55.56667726163774</v>
       </c>
     </row>
     <row r="153">
@@ -17120,9 +16964,11 @@
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
-      <c r="AA153" t="inlineStr"/>
+      <c r="AA153" t="n">
+        <v>592136</v>
+      </c>
       <c r="AB153" t="n">
-        <v>592136</v>
+        <v>61.70799806962501</v>
       </c>
       <c r="AC153" t="n">
         <v>19.35430011521448</v>
@@ -17144,9 +16990,6 @@
       </c>
       <c r="AI153" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ153" t="n">
-        <v>61.70799806962501</v>
       </c>
     </row>
     <row r="154">
@@ -17222,9 +17065,11 @@
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr"/>
+      <c r="AA154" t="n">
+        <v>592377</v>
+      </c>
       <c r="AB154" t="n">
-        <v>592377</v>
+        <v>47.27323855607655</v>
       </c>
       <c r="AC154" t="n">
         <v>17.99292700020547</v>
@@ -17246,9 +17091,6 @@
       </c>
       <c r="AI154" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ154" t="n">
-        <v>47.27323855607658</v>
       </c>
     </row>
     <row r="155">
@@ -17324,9 +17166,11 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
-      <c r="AA155" t="inlineStr"/>
+      <c r="AA155" t="n">
+        <v>592368</v>
+      </c>
       <c r="AB155" t="n">
-        <v>592368</v>
+        <v>46.60021045219221</v>
       </c>
       <c r="AC155" t="n">
         <v>20.07835532061642</v>
@@ -17348,9 +17192,6 @@
       </c>
       <c r="AI155" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>46.60021045219221</v>
       </c>
     </row>
     <row r="156">
@@ -17426,9 +17267,11 @@
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="inlineStr"/>
-      <c r="AA156" t="inlineStr"/>
+      <c r="AA156" t="n">
+        <v>592320</v>
+      </c>
       <c r="AB156" t="n">
-        <v>592320</v>
+        <v>36.4008599384631</v>
       </c>
       <c r="AC156" t="n">
         <v>16.3432225707194</v>
@@ -17450,9 +17293,6 @@
       </c>
       <c r="AI156" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ156" t="n">
-        <v>36.40085993846309</v>
       </c>
     </row>
     <row r="157">
@@ -17528,9 +17368,11 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr"/>
-      <c r="AA157" t="inlineStr"/>
+      <c r="AA157" t="n">
+        <v>592351</v>
+      </c>
       <c r="AB157" t="n">
-        <v>592351</v>
+        <v>55.60819532627404</v>
       </c>
       <c r="AC157" t="n">
         <v>17.89881266576955</v>
@@ -17552,9 +17394,6 @@
       </c>
       <c r="AI157" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ157" t="n">
-        <v>55.60819532627404</v>
       </c>
     </row>
     <row r="158">
@@ -17630,9 +17469,11 @@
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
       <c r="Z158" t="inlineStr"/>
-      <c r="AA158" t="inlineStr"/>
+      <c r="AA158" t="n">
+        <v>592172</v>
+      </c>
       <c r="AB158" t="n">
-        <v>592172</v>
+        <v>43.12164298019695</v>
       </c>
       <c r="AC158" t="n">
         <v>20.77189301261911</v>
@@ -17654,9 +17495,6 @@
       </c>
       <c r="AI158" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ158" t="n">
-        <v>43.12164298019695</v>
       </c>
     </row>
     <row r="159">
@@ -17732,9 +17570,11 @@
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="inlineStr"/>
-      <c r="AA159" t="inlineStr"/>
+      <c r="AA159" t="n">
+        <v>592172</v>
+      </c>
       <c r="AB159" t="n">
-        <v>592172</v>
+        <v>43.12164298019695</v>
       </c>
       <c r="AC159" t="n">
         <v>20.77189301261911</v>
@@ -17756,9 +17596,6 @@
       </c>
       <c r="AI159" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ159" t="n">
-        <v>43.12164298019695</v>
       </c>
     </row>
     <row r="160">
@@ -17834,9 +17671,11 @@
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="inlineStr"/>
-      <c r="AA160" t="inlineStr"/>
+      <c r="AA160" t="n">
+        <v>592124</v>
+      </c>
       <c r="AB160" t="n">
-        <v>592124</v>
+        <v>40.64145553340282</v>
       </c>
       <c r="AC160" t="n">
         <v>18.83026438618137</v>
@@ -17858,9 +17697,6 @@
       </c>
       <c r="AI160" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ160" t="n">
-        <v>40.64145553340281</v>
       </c>
     </row>
     <row r="161">
@@ -17934,9 +17770,11 @@
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr"/>
       <c r="Z161" t="inlineStr"/>
-      <c r="AA161" t="inlineStr"/>
+      <c r="AA161" t="n">
+        <v>592118</v>
+      </c>
       <c r="AB161" t="n">
-        <v>592118</v>
+        <v>39.86388713858987</v>
       </c>
       <c r="AC161" t="n">
         <v>18.89312022333272</v>
@@ -17958,9 +17796,6 @@
       </c>
       <c r="AI161" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ161" t="n">
-        <v>39.86388713858986</v>
       </c>
     </row>
     <row r="162">
@@ -18034,9 +17869,11 @@
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="inlineStr"/>
-      <c r="AA162" t="inlineStr"/>
+      <c r="AA162" t="n">
+        <v>592097</v>
+      </c>
       <c r="AB162" t="n">
-        <v>592097</v>
+        <v>50.48954256485062</v>
       </c>
       <c r="AC162" t="n">
         <v>19.5116159699573</v>
@@ -18058,9 +17895,6 @@
       </c>
       <c r="AI162" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ162" t="n">
-        <v>50.48954256485061</v>
       </c>
     </row>
     <row r="163">
@@ -18136,9 +17970,11 @@
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="inlineStr"/>
-      <c r="AA163" t="inlineStr"/>
+      <c r="AA163" t="n">
+        <v>592235</v>
+      </c>
       <c r="AB163" t="n">
-        <v>592235</v>
+        <v>53.08725031617568</v>
       </c>
       <c r="AC163" t="n">
         <v>18.49516418821691</v>
@@ -18160,9 +17996,6 @@
       </c>
       <c r="AI163" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ163" t="n">
-        <v>53.08725031617568</v>
       </c>
     </row>
     <row r="164">
@@ -18238,9 +18071,11 @@
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr"/>
       <c r="Z164" t="inlineStr"/>
-      <c r="AA164" t="inlineStr"/>
+      <c r="AA164" t="n">
+        <v>592123</v>
+      </c>
       <c r="AB164" t="n">
-        <v>592123</v>
+        <v>45.2001414226272</v>
       </c>
       <c r="AC164" t="n">
         <v>19.75292794426378</v>
@@ -18262,9 +18097,6 @@
       </c>
       <c r="AI164" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ164" t="n">
-        <v>45.20014142262722</v>
       </c>
     </row>
     <row r="165">
@@ -18340,9 +18172,11 @@
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr"/>
       <c r="Z165" t="inlineStr"/>
-      <c r="AA165" t="inlineStr"/>
+      <c r="AA165" t="n">
+        <v>592107</v>
+      </c>
       <c r="AB165" t="n">
-        <v>592107</v>
+        <v>48.16685335643782</v>
       </c>
       <c r="AC165" t="n">
         <v>18.93502842365038</v>
@@ -18364,9 +18198,6 @@
       </c>
       <c r="AI165" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ165" t="n">
-        <v>48.16685335643782</v>
       </c>
     </row>
     <row r="166">
@@ -18442,9 +18273,11 @@
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr"/>
       <c r="Z166" t="inlineStr"/>
-      <c r="AA166" t="inlineStr"/>
+      <c r="AA166" t="n">
+        <v>592108</v>
+      </c>
       <c r="AB166" t="n">
-        <v>592108</v>
+        <v>42.61425540516829</v>
       </c>
       <c r="AC166" t="n">
         <v>17.2718282109456</v>
@@ -18466,9 +18299,6 @@
       </c>
       <c r="AI166" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ166" t="n">
-        <v>42.61425540516829</v>
       </c>
     </row>
     <row r="167">
@@ -18544,9 +18374,11 @@
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr"/>
       <c r="Z167" t="inlineStr"/>
-      <c r="AA167" t="inlineStr"/>
+      <c r="AA167" t="n">
+        <v>592055</v>
+      </c>
       <c r="AB167" t="n">
-        <v>592055</v>
+        <v>42.46993249100026</v>
       </c>
       <c r="AC167" t="n">
         <v>16.82296427164142</v>
@@ -18568,9 +18400,6 @@
       </c>
       <c r="AI167" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ167" t="n">
-        <v>42.46993249100028</v>
       </c>
     </row>
     <row r="168">
@@ -18646,9 +18475,11 @@
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" t="inlineStr"/>
-      <c r="AA168" t="inlineStr"/>
+      <c r="AA168" t="n">
+        <v>592277</v>
+      </c>
       <c r="AB168" t="n">
-        <v>592277</v>
+        <v>38.40701417106357</v>
       </c>
       <c r="AC168" t="n">
         <v>17.73154125404406</v>
@@ -18670,9 +18501,6 @@
       </c>
       <c r="AI168" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ168" t="n">
-        <v>38.40701417106358</v>
       </c>
     </row>
     <row r="169">
@@ -18748,9 +18576,11 @@
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
-      <c r="AA169" t="inlineStr"/>
+      <c r="AA169" t="n">
+        <v>592117</v>
+      </c>
       <c r="AB169" t="n">
-        <v>592117</v>
+        <v>41.27967137504851</v>
       </c>
       <c r="AC169" t="n">
         <v>19.46966032778115</v>
@@ -18772,9 +18602,6 @@
       </c>
       <c r="AI169" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ169" t="n">
-        <v>41.27967137504851</v>
       </c>
     </row>
     <row r="170">
@@ -18850,9 +18677,11 @@
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr"/>
       <c r="Z170" t="inlineStr"/>
-      <c r="AA170" t="inlineStr"/>
+      <c r="AA170" t="n">
+        <v>592250</v>
+      </c>
       <c r="AB170" t="n">
-        <v>592250</v>
+        <v>40.6374878617617</v>
       </c>
       <c r="AC170" t="n">
         <v>16.55175028416668</v>
@@ -18874,9 +18703,6 @@
       </c>
       <c r="AI170" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ170" t="n">
-        <v>40.63748786176171</v>
       </c>
     </row>
     <row r="171">
@@ -18952,9 +18778,11 @@
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr"/>
       <c r="Z171" t="inlineStr"/>
-      <c r="AA171" t="inlineStr"/>
+      <c r="AA171" t="n">
+        <v>592148</v>
+      </c>
       <c r="AB171" t="n">
-        <v>592148</v>
+        <v>38.08684472600527</v>
       </c>
       <c r="AC171" t="n">
         <v>17.71063619296065</v>
@@ -18976,9 +18804,6 @@
       </c>
       <c r="AI171" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ171" t="n">
-        <v>38.08684472600529</v>
       </c>
     </row>
     <row r="172">
@@ -19054,9 +18879,11 @@
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr"/>
       <c r="Z172" t="inlineStr"/>
-      <c r="AA172" t="inlineStr"/>
+      <c r="AA172" t="n">
+        <v>592015</v>
+      </c>
       <c r="AB172" t="n">
-        <v>592015</v>
+        <v>43.33108356621307</v>
       </c>
       <c r="AC172" t="n">
         <v>16.95862554213405</v>
@@ -19078,9 +18905,6 @@
       </c>
       <c r="AI172" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ172" t="n">
-        <v>43.33108356621308</v>
       </c>
     </row>
     <row r="173">
@@ -19156,9 +18980,11 @@
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr"/>
       <c r="Z173" t="inlineStr"/>
-      <c r="AA173" t="inlineStr"/>
+      <c r="AA173" t="n">
+        <v>592133</v>
+      </c>
       <c r="AB173" t="n">
-        <v>592133</v>
+        <v>45.59782712484886</v>
       </c>
       <c r="AC173" t="n">
         <v>18.69410334008409</v>
@@ -19180,9 +19006,6 @@
       </c>
       <c r="AI173" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ173" t="n">
-        <v>45.59782712484888</v>
       </c>
     </row>
     <row r="174">
@@ -19258,9 +19081,11 @@
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="inlineStr"/>
-      <c r="AA174" t="inlineStr"/>
+      <c r="AA174" t="n">
+        <v>592286</v>
+      </c>
       <c r="AB174" t="n">
-        <v>592286</v>
+        <v>46.08862851636469</v>
       </c>
       <c r="AC174" t="n">
         <v>17.89881266576955</v>
@@ -19282,9 +19107,6 @@
       </c>
       <c r="AI174" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ174" t="n">
-        <v>46.0886285163647</v>
       </c>
     </row>
     <row r="175">
@@ -19360,9 +19182,11 @@
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr"/>
-      <c r="AA175" t="inlineStr"/>
+      <c r="AA175" t="n">
+        <v>592079</v>
+      </c>
       <c r="AB175" t="n">
-        <v>592079</v>
+        <v>31.20218338168698</v>
       </c>
       <c r="AC175" t="n">
         <v>16.78122962362502</v>
@@ -19384,9 +19208,6 @@
       </c>
       <c r="AI175" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ175" t="n">
-        <v>31.20218338168698</v>
       </c>
     </row>
     <row r="176">
@@ -19462,9 +19283,11 @@
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="inlineStr"/>
-      <c r="AA176" t="inlineStr"/>
+      <c r="AA176" t="n">
+        <v>592019</v>
+      </c>
       <c r="AB176" t="n">
-        <v>592019</v>
+        <v>37.47652040214079</v>
       </c>
       <c r="AC176" t="n">
         <v>18.4323574400296</v>
@@ -19486,9 +19309,6 @@
       </c>
       <c r="AI176" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ176" t="n">
-        <v>37.47652040214078</v>
       </c>
     </row>
     <row r="177">
@@ -19564,9 +19384,11 @@
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr"/>
-      <c r="AA177" t="inlineStr"/>
+      <c r="AA177" t="n">
+        <v>592103</v>
+      </c>
       <c r="AB177" t="n">
-        <v>592103</v>
+        <v>45.90057484261069</v>
       </c>
       <c r="AC177" t="n">
         <v>16.61432528521011</v>
@@ -19588,9 +19410,6 @@
       </c>
       <c r="AI177" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ177" t="n">
-        <v>45.90057484261067</v>
       </c>
     </row>
     <row r="178">
@@ -19666,9 +19485,11 @@
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="inlineStr"/>
-      <c r="AA178" t="inlineStr"/>
+      <c r="AA178" t="n">
+        <v>592294</v>
+      </c>
       <c r="AB178" t="n">
-        <v>592294</v>
+        <v>47.40155652187085</v>
       </c>
       <c r="AC178" t="n">
         <v>17.83607944327461</v>
@@ -19690,9 +19511,6 @@
       </c>
       <c r="AI178" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ178" t="n">
-        <v>47.40155652187085</v>
       </c>
     </row>
     <row r="179">
@@ -19768,9 +19586,11 @@
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="inlineStr"/>
-      <c r="AA179" t="inlineStr"/>
+      <c r="AA179" t="n">
+        <v>592091</v>
+      </c>
       <c r="AB179" t="n">
-        <v>592091</v>
+        <v>44.74207179927146</v>
       </c>
       <c r="AC179" t="n">
         <v>19.23896600734409</v>
@@ -19792,9 +19612,6 @@
       </c>
       <c r="AI179" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ179" t="n">
-        <v>44.74207179927147</v>
       </c>
     </row>
     <row r="180">
@@ -19870,9 +19687,11 @@
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="inlineStr"/>
-      <c r="AA180" t="inlineStr"/>
+      <c r="AA180" t="n">
+        <v>592302</v>
+      </c>
       <c r="AB180" t="n">
-        <v>592302</v>
+        <v>44.0343228797727</v>
       </c>
       <c r="AC180" t="n">
         <v>18.76741630374437</v>
@@ -19894,9 +19713,6 @@
       </c>
       <c r="AI180" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>44.03432287977269</v>
       </c>
     </row>
     <row r="181">
@@ -19972,9 +19788,11 @@
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="inlineStr"/>
-      <c r="AA181" t="inlineStr"/>
+      <c r="AA181" t="n">
+        <v>592272</v>
+      </c>
       <c r="AB181" t="n">
-        <v>592272</v>
+        <v>54.20072825178515</v>
       </c>
       <c r="AC181" t="n">
         <v>17.94063911038061</v>
@@ -19996,9 +19814,6 @@
       </c>
       <c r="AI181" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>54.20072825178514</v>
       </c>
     </row>
     <row r="182">
@@ -20074,9 +19889,11 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr"/>
-      <c r="AA182" t="inlineStr"/>
+      <c r="AA182" t="n">
+        <v>592029</v>
+      </c>
       <c r="AB182" t="n">
-        <v>592029</v>
+        <v>39.38800376216415</v>
       </c>
       <c r="AC182" t="n">
         <v>18.7359951700953</v>
@@ -20098,9 +19915,6 @@
       </c>
       <c r="AI182" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ182" t="n">
-        <v>39.38800376216417</v>
       </c>
     </row>
     <row r="183">
@@ -20176,9 +19990,11 @@
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="inlineStr"/>
-      <c r="AA183" t="inlineStr"/>
+      <c r="AA183" t="n">
+        <v>592291</v>
+      </c>
       <c r="AB183" t="n">
-        <v>592291</v>
+        <v>42.7829066706362</v>
       </c>
       <c r="AC183" t="n">
         <v>20.10985931561284</v>
@@ -20200,9 +20016,6 @@
       </c>
       <c r="AI183" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ183" t="n">
-        <v>42.78290667063618</v>
       </c>
     </row>
   </sheetData>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -7644,11 +7644,15 @@
       <c r="I64" t="n">
         <v>0.4786645153959252</v>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>-33.6</v>
+      </c>
       <c r="K64" t="n">
         <v>0.01461355893199637</v>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>1.37</v>
+      </c>
       <c r="M64" t="n">
         <v>0.4698293457032828</v>
       </c>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>[C_b]%</t>
+          <t>[C_b]</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>[C]%</t>
+          <t>[C]</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -755,7 +755,9 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>492.7536231884059</v>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -883,7 +885,9 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>518.4560219363003</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
@@ -1011,7 +1015,9 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>473.6842105263158</v>
+      </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -1139,7 +1145,9 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>545.2314165497896</v>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1267,7 +1275,9 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>508.6805555555556</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1395,7 +1405,9 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>263.877381938691</v>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1523,7 +1535,9 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>513.036809815951</v>
+      </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
@@ -1651,7 +1665,9 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>570.3001579778831</v>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -1779,7 +1795,9 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>431.0411064156742</v>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -1907,7 +1925,9 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>493.8271604938271</v>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -2035,7 +2055,9 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>460.7843137254902</v>
+      </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
@@ -2163,7 +2185,9 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>427.3504273504274</v>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -2291,7 +2315,9 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>243.3132010353753</v>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
@@ -2419,7 +2445,9 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>506.4848686398404</v>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
@@ -2547,7 +2575,9 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>556.1418938727646</v>
+      </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
@@ -2675,7 +2705,9 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>514.4526445264453</v>
+      </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
@@ -2803,7 +2835,9 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>518.3496199782845</v>
+      </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
@@ -2931,7 +2965,9 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>469.5481335952849</v>
+      </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
@@ -3059,7 +3095,9 @@
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AB20" t="n">
+        <v>481.6525532460868</v>
+      </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
@@ -3187,7 +3225,9 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>263.1578947368421</v>
+      </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
@@ -3315,7 +3355,9 @@
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>444.4444444444445</v>
+      </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
@@ -3443,7 +3485,9 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>446.6019417475728</v>
+      </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
@@ -3571,7 +3615,9 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>248.4619025082821</v>
+      </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
@@ -3699,7 +3745,9 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>391.0652920962199</v>
+      </c>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
@@ -3827,7 +3875,9 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>508.258612553091</v>
+      </c>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
@@ -3955,7 +4005,9 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>556.3333333333334</v>
+      </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
@@ -4083,7 +4135,9 @@
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>251.5765018254232</v>
+      </c>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
@@ -4211,7 +4265,9 @@
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>442.622950819672</v>
+      </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
@@ -4339,7 +4395,9 @@
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>477.7251184834123</v>
+      </c>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
@@ -4467,7 +4525,9 @@
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>446.6019417475728</v>
+      </c>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
@@ -4595,7 +4655,9 @@
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>442.0572916666667</v>
+      </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
@@ -4723,7 +4785,9 @@
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>476.1255115961801</v>
+      </c>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
@@ -4851,7 +4915,9 @@
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>415.929203539823</v>
+      </c>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
@@ -4979,7 +5045,9 @@
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>503.7688442211054</v>
+      </c>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
@@ -5107,7 +5175,9 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>500</v>
+      </c>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
@@ -5235,7 +5305,9 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>436.6197183098592</v>
+      </c>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
@@ -5363,7 +5435,9 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>339.21302578019</v>
+      </c>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
@@ -5491,7 +5565,9 @@
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>444.578313253012</v>
+      </c>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
@@ -5619,7 +5695,9 @@
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>455.2238805970149</v>
+      </c>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
@@ -5747,7 +5825,9 @@
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>549.93625159371</v>
+      </c>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
@@ -5875,7 +5955,9 @@
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>549.93625159371</v>
+      </c>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
@@ -6003,7 +6085,9 @@
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>549.93625159371</v>
+      </c>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
@@ -6131,7 +6215,9 @@
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
+      <c r="AB44" t="n">
+        <v>549.93625159371</v>
+      </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
@@ -6259,7 +6345,9 @@
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
+      <c r="AB45" t="n">
+        <v>564.5110902842863</v>
+      </c>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
@@ -6387,7 +6475,9 @@
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+      <c r="AB46" t="n">
+        <v>489.9193548387096</v>
+      </c>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
@@ -6515,7 +6605,9 @@
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
+      <c r="AB47" t="n">
+        <v>483.4977883633889</v>
+      </c>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
@@ -6643,7 +6735,9 @@
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+      <c r="AB48" t="n">
+        <v>495.6962025316456</v>
+      </c>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
@@ -6771,7 +6865,9 @@
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
+      <c r="AB49" t="n">
+        <v>591.8367346938776</v>
+      </c>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
@@ -6899,7 +6995,9 @@
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
+      <c r="AB50" t="n">
+        <v>441.4893617021277</v>
+      </c>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
@@ -7027,7 +7125,9 @@
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>314.5665773011618</v>
+      </c>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
@@ -7155,7 +7255,9 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
+      <c r="AB52" t="n">
+        <v>304.0178571428571</v>
+      </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
@@ -7283,7 +7385,9 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
+      <c r="AB53" t="n">
+        <v>443.8573315719947</v>
+      </c>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
@@ -7411,7 +7515,9 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="n">
+        <v>443.1664411366712</v>
+      </c>
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
@@ -7539,7 +7645,9 @@
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>349.8380379453956</v>
+      </c>
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
@@ -7667,7 +7775,9 @@
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
+      <c r="AB56" t="n">
+        <v>483.5833876929767</v>
+      </c>
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr"/>
@@ -7795,7 +7905,9 @@
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
+      <c r="AB57" t="n">
+        <v>434.3434343434344</v>
+      </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr"/>
@@ -7923,7 +8035,9 @@
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+      <c r="AB58" t="n">
+        <v>451.0218463706835</v>
+      </c>
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr"/>
@@ -8051,7 +8165,9 @@
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="n">
+        <v>439.252336448598</v>
+      </c>
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr"/>
@@ -8179,7 +8295,9 @@
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AB60" t="n">
+        <v>230.1545018646777</v>
+      </c>
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
@@ -8307,7 +8425,9 @@
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>259.0775269872424</v>
+      </c>
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
@@ -8435,7 +8555,9 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+      <c r="AB62" t="n">
+        <v>680.2507836990595</v>
+      </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
@@ -8563,7 +8685,9 @@
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+      <c r="AB63" t="n">
+        <v>723.6580516898608</v>
+      </c>
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
@@ -8691,7 +8815,9 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+      <c r="AB64" t="n">
+        <v>723.6580516898608</v>
+      </c>
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
@@ -8819,7 +8945,9 @@
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AB65" t="n">
+        <v>452.9914529914531</v>
+      </c>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
@@ -8947,7 +9075,9 @@
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+      <c r="AB66" t="n">
+        <v>458.3333333333334</v>
+      </c>
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr"/>
@@ -9075,7 +9205,9 @@
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+      <c r="AB67" t="n">
+        <v>234.0425531914894</v>
+      </c>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
@@ -9203,7 +9335,9 @@
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
-      <c r="AB68" t="inlineStr"/>
+      <c r="AB68" t="n">
+        <v>232.7044025157233</v>
+      </c>
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
@@ -9331,7 +9465,9 @@
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
+      <c r="AB69" t="n">
+        <v>439.4329896907217</v>
+      </c>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
@@ -9459,7 +9595,9 @@
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
+      <c r="AB70" t="n">
+        <v>471.5964740450539</v>
+      </c>
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
@@ -9587,7 +9725,9 @@
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
+      <c r="AB71" t="n">
+        <v>486.2813776999417</v>
+      </c>
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr"/>
@@ -9715,7 +9855,9 @@
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
+      <c r="AB72" t="n">
+        <v>448.7041036717063</v>
+      </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr"/>
@@ -9843,7 +9985,9 @@
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
+      <c r="AB73" t="n">
+        <v>256.2613430127042</v>
+      </c>
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
@@ -9971,7 +10115,9 @@
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
-      <c r="AB74" t="inlineStr"/>
+      <c r="AB74" t="n">
+        <v>256.5853658536585</v>
+      </c>
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="inlineStr"/>
@@ -10099,7 +10245,9 @@
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
+      <c r="AB75" t="n">
+        <v>550.1138952164009</v>
+      </c>
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
@@ -10227,7 +10375,9 @@
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
+      <c r="AB76" t="n">
+        <v>285.7142857142857</v>
+      </c>
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
@@ -10355,7 +10505,9 @@
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
+      <c r="AB77" t="n">
+        <v>268.8346883468835</v>
+      </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
@@ -10483,7 +10635,9 @@
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
+      <c r="AB78" t="n">
+        <v>457.2884012539185</v>
+      </c>
       <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr"/>
@@ -10611,7 +10765,9 @@
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+      <c r="AB79" t="n">
+        <v>280.4171494785631</v>
+      </c>
       <c r="AC79" t="inlineStr"/>
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr"/>
@@ -10739,7 +10895,9 @@
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+      <c r="AB80" t="n">
+        <v>290.6066536203523</v>
+      </c>
       <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="inlineStr"/>
@@ -10867,7 +11025,9 @@
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
+      <c r="AB81" t="n">
+        <v>292.6186291739895</v>
+      </c>
       <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
@@ -10995,7 +11155,9 @@
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
+      <c r="AB82" t="n">
+        <v>509.7316123745134</v>
+      </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr"/>
@@ -11123,7 +11285,9 @@
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
+      <c r="AB83" t="n">
+        <v>440.4479131319986</v>
+      </c>
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr"/>
@@ -11251,7 +11415,9 @@
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
+      <c r="AB84" t="n">
+        <v>501.0974539069358</v>
+      </c>
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr"/>
@@ -11379,7 +11545,9 @@
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
+      <c r="AB85" t="n">
+        <v>545.4545454545454</v>
+      </c>
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
@@ -11507,7 +11675,9 @@
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
+      <c r="AB86" t="n">
+        <v>509.907120743034</v>
+      </c>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr"/>
       <c r="AE86" t="inlineStr"/>
@@ -11635,7 +11805,9 @@
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
+      <c r="AB87" t="n">
+        <v>268.1818181818181</v>
+      </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr"/>
@@ -11763,7 +11935,9 @@
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AB88" t="n">
+        <v>403.8790644609241</v>
+      </c>
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="inlineStr"/>
       <c r="AE88" t="inlineStr"/>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV183"/>
+  <dimension ref="A1:AX183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,6 +666,16 @@
       <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>13dC/18dO</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Narea</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Carea</t>
         </is>
       </c>
     </row>
@@ -798,6 +808,12 @@
       <c r="AV2" t="n">
         <v>-1.069204566063425</v>
       </c>
+      <c r="AW2" t="n">
+        <v>0.1583411527786951</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.267862957094129</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -928,6 +944,12 @@
       <c r="AV3" t="n">
         <v>-1.162714378482783</v>
       </c>
+      <c r="AW3" t="n">
+        <v>0.1927929018543231</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.931398966307422</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1058,6 +1080,12 @@
       <c r="AV4" t="n">
         <v>-1.083217188451016</v>
       </c>
+      <c r="AW4" t="n">
+        <v>0.1459443363957555</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.201410491775166</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1188,6 +1216,12 @@
       <c r="AV5" t="n">
         <v>-1.173469655199274</v>
       </c>
+      <c r="AW5" t="n">
+        <v>0.2308390026071944</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.803966990152447</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1318,6 +1352,12 @@
       <c r="AV6" t="n">
         <v>-1.152717050430573</v>
       </c>
+      <c r="AW6" t="n">
+        <v>0.1972952651382424</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.814010355624786</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1448,6 +1488,12 @@
       <c r="AV7" t="n">
         <v>-0.9757692279498354</v>
       </c>
+      <c r="AW7" t="n">
+        <v>0.2411024955423218</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.393667365779264</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1578,6 +1624,12 @@
       <c r="AV8" t="n">
         <v>-1.066817746219274</v>
       </c>
+      <c r="AW8" t="n">
+        <v>0.2212734935521185</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.582919875238116</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1708,6 +1760,12 @@
       <c r="AV9" t="n">
         <v>-1.120257664680253</v>
       </c>
+      <c r="AW9" t="n">
+        <v>0.2491330280495736</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.04653963916366</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1838,6 +1896,12 @@
       <c r="AV10" t="n">
         <v>-1.176763154946914</v>
       </c>
+      <c r="AW10" t="n">
+        <v>0.1922442143630735</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.385976820401974</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1968,6 +2032,12 @@
       <c r="AV11" t="n">
         <v>-1.083133704760353</v>
       </c>
+      <c r="AW11" t="n">
+        <v>0.1541538771183675</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.156964889603419</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -2098,6 +2168,12 @@
       <c r="AV12" t="n">
         <v>-0.9693632665794485</v>
       </c>
+      <c r="AW12" t="n">
+        <v>0.1704503359635594</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.04539122144526</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2228,6 +2304,12 @@
       <c r="AV13" t="n">
         <v>-1.01178671221848</v>
       </c>
+      <c r="AW13" t="n">
+        <v>0.1893086604314295</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.298227944361334</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2358,6 +2440,12 @@
       <c r="AV14" t="n">
         <v>-0.9086318732906992</v>
       </c>
+      <c r="AW14" t="n">
+        <v>0.2420263723581012</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.933547349313596</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2488,6 +2576,12 @@
       <c r="AV15" t="n">
         <v>-0.9710658232898745</v>
       </c>
+      <c r="AW15" t="n">
+        <v>0.1835954858483998</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.467012487459539</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2618,6 +2712,12 @@
       <c r="AV16" t="n">
         <v>-0.9202190103021481</v>
       </c>
+      <c r="AW16" t="n">
+        <v>0.2667160375811695</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.621722569917226</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2748,6 +2848,12 @@
       <c r="AV17" t="n">
         <v>-1.137930339273472</v>
       </c>
+      <c r="AW17" t="n">
+        <v>0.2040293659175826</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.793309073325802</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2878,6 +2984,12 @@
       <c r="AV18" t="n">
         <v>-0.9983195512068304</v>
       </c>
+      <c r="AW18" t="n">
+        <v>0.2199748552043699</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.418104834646514</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -3008,6 +3120,12 @@
       <c r="AV19" t="n">
         <v>-1.159881181147376</v>
       </c>
+      <c r="AW19" t="n">
+        <v>0.1804095984933663</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.811120672929789</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -3138,6 +3256,12 @@
       <c r="AV20" t="n">
         <v>-0.9251081452731393</v>
       </c>
+      <c r="AW20" t="n">
+        <v>0.2193069154530283</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.744644431684386</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -3268,6 +3392,12 @@
       <c r="AV21" t="n">
         <v>-0.8250529055541557</v>
       </c>
+      <c r="AW21" t="n">
+        <v>0.2731252805030631</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.269341168086865</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3398,6 +3528,12 @@
       <c r="AV22" t="n">
         <v>-0.9307778716019919</v>
       </c>
+      <c r="AW22" t="n">
+        <v>0.1359691165823957</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.209869586996444</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -3528,6 +3664,12 @@
       <c r="AV23" t="n">
         <v>-1.076624094600751</v>
       </c>
+      <c r="AW23" t="n">
+        <v>0.1532285064088778</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.8814772925756</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3658,6 +3800,12 @@
       <c r="AV24" t="n">
         <v>-0.9531215121310557</v>
       </c>
+      <c r="AW24" t="n">
+        <v>0.2083919474390169</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.450269324889292</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3788,6 +3936,12 @@
       <c r="AV25" t="n">
         <v>-1.127672428671739</v>
       </c>
+      <c r="AW25" t="n">
+        <v>0.07191749109464135</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2.212721935758194</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3918,6 +4072,12 @@
       <c r="AV26" t="n">
         <v>-1.093730835683608</v>
       </c>
+      <c r="AW26" t="n">
+        <v>0.1993680458705612</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.819873982352418</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -4048,6 +4208,12 @@
       <c r="AV27" t="n">
         <v>-0.9251981278059437</v>
       </c>
+      <c r="AW27" t="n">
+        <v>0.6593596761464461</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12.77013975807906</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -4178,6 +4344,12 @@
       <c r="AV28" t="n">
         <v>-1.110646754176239</v>
       </c>
+      <c r="AW28" t="n">
+        <v>0.1941969337398241</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.180318961158282</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -4308,6 +4480,12 @@
       <c r="AV29" t="n">
         <v>-0.8721981465115956</v>
       </c>
+      <c r="AW29" t="n">
+        <v>0.2299853817964811</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>4.77039521233669</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -4438,6 +4616,12 @@
       <c r="AV30" t="n">
         <v>-1.026018023099852</v>
       </c>
+      <c r="AW30" t="n">
+        <v>0.2056480718564838</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>6.003256549989229</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -4568,6 +4752,12 @@
       <c r="AV31" t="n">
         <v>-1.081725628636109</v>
       </c>
+      <c r="AW31" t="n">
+        <v>0.136631885562437</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>5.871422404388254</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -4698,6 +4888,12 @@
       <c r="AV32" t="n">
         <v>-0.9757257325131097</v>
       </c>
+      <c r="AW32" t="n">
+        <v>0.2060536274187499</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4.248872527334292</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -4828,6 +5024,12 @@
       <c r="AV33" t="n">
         <v>-1.108000186694067</v>
       </c>
+      <c r="AW33" t="n">
+        <v>0.2140487849336566</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4.707179999838402</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -4958,6 +5160,12 @@
       <c r="AV34" t="n">
         <v>-1.1317622997201</v>
       </c>
+      <c r="AW34" t="n">
+        <v>0.1262484116656832</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>5.538752547725021</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -5088,6 +5296,12 @@
       <c r="AV35" t="n">
         <v>-1.097985206987246</v>
       </c>
+      <c r="AW35" t="n">
+        <v>0.236853606683806</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>5.72708070874746</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -5218,6 +5432,12 @@
       <c r="AV36" t="n">
         <v>-1.041003254864917</v>
       </c>
+      <c r="AW36" t="n">
+        <v>0.1404492354378129</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>6.421580057406096</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -5348,6 +5568,12 @@
       <c r="AV37" t="n">
         <v>-1.128326182974303</v>
       </c>
+      <c r="AW37" t="n">
+        <v>0.165736668134432</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>5.382476778431748</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -5478,6 +5704,12 @@
       <c r="AV38" t="n">
         <v>-1.052221717593601</v>
       </c>
+      <c r="AW38" t="n">
+        <v>0.25370946862891</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>7.926449640071605</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -5608,6 +5840,12 @@
       <c r="AV39" t="n">
         <v>-1.018263130425242</v>
       </c>
+      <c r="AW39" t="n">
+        <v>0.1790085898974969</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>3.990234824028318</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -5738,6 +5976,12 @@
       <c r="AV40" t="n">
         <v>-1.134852638614013</v>
       </c>
+      <c r="AW40" t="n">
+        <v>0.1636334848571583</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>6.701960533465813</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -5868,6 +6112,12 @@
       <c r="AV41" t="n">
         <v>-1.046794083447492</v>
       </c>
+      <c r="AW41" t="n">
+        <v>0.1962293560349081</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>6.406993482654983</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -5998,6 +6248,12 @@
       <c r="AV42" t="n">
         <v>-1.055363556422817</v>
       </c>
+      <c r="AW42" t="n">
+        <v>0.1962293560349081</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>6.406993482654983</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -6128,6 +6384,12 @@
       <c r="AV43" t="n">
         <v>-1.027478472194354</v>
       </c>
+      <c r="AW43" t="n">
+        <v>0.1962293560349081</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>6.406993482654983</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -6258,6 +6520,12 @@
       <c r="AV44" t="n">
         <v>-1.035889819888641</v>
       </c>
+      <c r="AW44" t="n">
+        <v>0.1962293560349081</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>6.406993482654983</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -6388,6 +6656,12 @@
       <c r="AV45" t="n">
         <v>-1.016944806660762</v>
       </c>
+      <c r="AW45" t="n">
+        <v>0.2080347916779913</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>7.270477607848516</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -6518,6 +6792,12 @@
       <c r="AV46" t="n">
         <v>-1.168428613749502</v>
       </c>
+      <c r="AW46" t="n">
+        <v>0.1803572361821152</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>4.981358951370535</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -6648,6 +6928,12 @@
       <c r="AV47" t="n">
         <v>-1.006406074511895</v>
       </c>
+      <c r="AW47" t="n">
+        <v>0.1563233988308393</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>4.941560931653564</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -6778,6 +7064,12 @@
       <c r="AV48" t="n">
         <v>-1.002974473340656</v>
       </c>
+      <c r="AW48" t="n">
+        <v>0.1727182447385554</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>5.627608137299266</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -6908,6 +7200,12 @@
       <c r="AV49" t="n">
         <v>-1.033343565098957</v>
       </c>
+      <c r="AW49" t="n">
+        <v>0.2118768969038876</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>7.860992204916545</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -7038,6 +7336,12 @@
       <c r="AV50" t="n">
         <v>-1.094831536193773</v>
       </c>
+      <c r="AW50" t="n">
+        <v>0.1305405133948935</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>6.085878779925097</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -7168,6 +7472,12 @@
       <c r="AV51" t="n">
         <v>-1.034130614924995</v>
       </c>
+      <c r="AW51" t="n">
+        <v>0.2749705279828398</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>7.600880368696366</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -7298,6 +7608,12 @@
       <c r="AV52" t="n">
         <v>-0.9330413776996519</v>
       </c>
+      <c r="AW52" t="n">
+        <v>0.2554237568151246</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>8.029662939995131</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -7428,6 +7744,12 @@
       <c r="AV53" t="n">
         <v>-1.059704205037399</v>
       </c>
+      <c r="AW53" t="n">
+        <v>0.2105696461538427</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>3.469168210591955</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -7558,6 +7880,12 @@
       <c r="AV54" t="n">
         <v>-1.09799079624996</v>
       </c>
+      <c r="AW54" t="n">
+        <v>0.2230482700063978</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>3.834114387266885</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -7688,6 +8016,12 @@
       <c r="AV55" t="n">
         <v>-1.013558134662488</v>
       </c>
+      <c r="AW55" t="n">
+        <v>0.2700331914670088</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>9.226808188432537</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -7818,6 +8152,12 @@
       <c r="AV56" t="n">
         <v>-1.029758709416929</v>
       </c>
+      <c r="AW56" t="n">
+        <v>0.1811914954031918</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>5.640759522824799</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -7948,6 +8288,12 @@
       <c r="AV57" t="n">
         <v>-1.071407723597514</v>
       </c>
+      <c r="AW57" t="n">
+        <v>0.1485071659290358</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>6.279270830799232</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -8078,6 +8424,12 @@
       <c r="AV58" t="n">
         <v>-1.076020463092165</v>
       </c>
+      <c r="AW58" t="n">
+        <v>0.181805467668072</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>5.528408572483942</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -8208,6 +8560,12 @@
       <c r="AV59" t="n">
         <v>-1.131721301339614</v>
       </c>
+      <c r="AW59" t="n">
+        <v>0.1468960643433882</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>6.080598725084783</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -8338,6 +8696,12 @@
       <c r="AV60" t="n">
         <v>-1.148906986345209</v>
       </c>
+      <c r="AW60" t="n">
+        <v>0.1640718941643498</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>4.620440023861259</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -8468,6 +8832,12 @@
       <c r="AV61" t="n">
         <v>-0.9802187884414533</v>
       </c>
+      <c r="AW61" t="n">
+        <v>0.2324436326842925</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>6.589693642640406</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -8598,6 +8968,12 @@
       <c r="AV62" t="n">
         <v>-1.059967417806882</v>
       </c>
+      <c r="AW62" t="n">
+        <v>0.2271852849396293</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>8.1219991100984</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -8728,6 +9104,12 @@
       <c r="AV63" t="n">
         <v>-1.07072599241777</v>
       </c>
+      <c r="AW63" t="n">
+        <v>0.2097736888129386</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>6.659317142649229</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -8858,6 +9240,12 @@
       <c r="AV64" t="n">
         <v>-1.07072599241777</v>
       </c>
+      <c r="AW64" t="n">
+        <v>0.2051731480905204</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>6.720409857723063</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -8988,6 +9376,12 @@
       <c r="AV65" t="n">
         <v>-1.072717162486702</v>
       </c>
+      <c r="AW65" t="n">
+        <v>0.1711270057226029</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>6.465141386759904</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -9118,6 +9512,12 @@
       <c r="AV66" t="n">
         <v>-1.186907968195777</v>
       </c>
+      <c r="AW66" t="n">
+        <v>0.1264668813853405</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>5.917373389442116</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -9248,6 +9648,12 @@
       <c r="AV67" t="n">
         <v>-1.05716724908219</v>
       </c>
+      <c r="AW67" t="n">
+        <v>0.1735620252135451</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>5.130229695978934</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -9378,6 +9784,12 @@
       <c r="AV68" t="n">
         <v>-1.062612342442872</v>
       </c>
+      <c r="AW68" t="n">
+        <v>0.1651892043876882</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>4.61721716535054</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -9508,6 +9920,12 @@
       <c r="AV69" t="n">
         <v>-1.162202419950019</v>
       </c>
+      <c r="AW69" t="n">
+        <v>0.1729739026459769</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>4.169261023831525</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -9638,6 +10056,12 @@
       <c r="AV70" t="n">
         <v>-0.9735100220183867</v>
       </c>
+      <c r="AW70" t="n">
+        <v>0.1653302877966243</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>5.468910140257988</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -9768,6 +10192,12 @@
       <c r="AV71" t="n">
         <v>-1.151540486656524</v>
       </c>
+      <c r="AW71" t="n">
+        <v>0.224534879706159</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>6.385261085941602</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -9898,6 +10328,12 @@
       <c r="AV72" t="n">
         <v>-1.081507885923864</v>
       </c>
+      <c r="AW72" t="n">
+        <v>0.1704181532420173</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>4.64552151410903</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -10028,6 +10464,12 @@
       <c r="AV73" t="n">
         <v>-1.008164398010397</v>
       </c>
+      <c r="AW73" t="n">
+        <v>0.1771344004138958</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>5.317720031155273</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -10158,6 +10600,12 @@
       <c r="AV74" t="n">
         <v>-0.9019527661726316</v>
       </c>
+      <c r="AW74" t="n">
+        <v>0.2890653446677475</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>7.650714677495467</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -10288,6 +10736,12 @@
       <c r="AV75" t="n">
         <v>-1.064321440481539</v>
       </c>
+      <c r="AW75" t="n">
+        <v>0.2678379030470969</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>8.094394089102797</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -10418,6 +10872,12 @@
       <c r="AV76" t="n">
         <v>-1.036430349351861</v>
       </c>
+      <c r="AW76" t="n">
+        <v>0.2020516390549202</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>6.613829372688381</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -10548,6 +11008,12 @@
       <c r="AV77" t="n">
         <v>-0.9447135609596995</v>
       </c>
+      <c r="AW77" t="n">
+        <v>0.2290004233178914</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>6.379856596163442</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -10678,6 +11144,12 @@
       <c r="AV78" t="n">
         <v>-1.136069687512091</v>
       </c>
+      <c r="AW78" t="n">
+        <v>0.2143935207599353</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>4.677253989798563</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -10808,6 +11280,12 @@
       <c r="AV79" t="n">
         <v>-0.7957323640055816</v>
       </c>
+      <c r="AW79" t="n">
+        <v>0.3250436485054538</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>5.943353709831833</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -10938,6 +11416,12 @@
       <c r="AV80" t="n">
         <v>-1.083830924468203</v>
       </c>
+      <c r="AW80" t="n">
+        <v>0.2998648154876037</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>6.635735356277657</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -11068,6 +11552,12 @@
       <c r="AV81" t="n">
         <v>-0.852490835998494</v>
       </c>
+      <c r="AW81" t="n">
+        <v>0.2994186256562353</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>7.152431113667959</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -11198,6 +11688,12 @@
       <c r="AV82" t="n">
         <v>-1.073512489772441</v>
       </c>
+      <c r="AW82" t="n">
+        <v>0.1986099449474032</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>5.80366638296212</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -11328,6 +11824,12 @@
       <c r="AV83" t="n">
         <v>-1.045162407612312</v>
       </c>
+      <c r="AW83" t="n">
+        <v>0.1574768288150041</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>4.144199615258708</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -11458,6 +11960,12 @@
       <c r="AV84" t="n">
         <v>-1.011763599487811</v>
       </c>
+      <c r="AW84" t="n">
+        <v>0.1625698637855855</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>4.910286937521602</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -11588,6 +12096,12 @@
       <c r="AV85" t="n">
         <v>-1.056436243301099</v>
       </c>
+      <c r="AW85" t="n">
+        <v>0.2261410104794487</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>6.328175428570905</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -11718,6 +12232,12 @@
       <c r="AV86" t="n">
         <v>-1.139184969499528</v>
       </c>
+      <c r="AW86" t="n">
+        <v>0.2131678007547578</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>6.522638295327906</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -11848,6 +12368,12 @@
       <c r="AV87" t="n">
         <v>-0.9994064701242487</v>
       </c>
+      <c r="AW87" t="n">
+        <v>0.2723142473493239</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>7.354363492686352</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -11978,6 +12504,12 @@
       <c r="AV88" t="n">
         <v>-0.9530514877786842</v>
       </c>
+      <c r="AW88" t="n">
+        <v>0.2165437559626953</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>4.352489670002637</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -12118,6 +12650,8 @@
       <c r="AV89" t="n">
         <v>-0.921325744894543</v>
       </c>
+      <c r="AW89" t="inlineStr"/>
+      <c r="AX89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -12258,6 +12792,8 @@
       <c r="AV90" t="n">
         <v>-0.9396264176117411</v>
       </c>
+      <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -12398,6 +12934,8 @@
       <c r="AV91" t="n">
         <v>-0.9000000000000001</v>
       </c>
+      <c r="AW91" t="inlineStr"/>
+      <c r="AX91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -12538,6 +13076,8 @@
       <c r="AV92" t="n">
         <v>-0.9772876892692561</v>
       </c>
+      <c r="AW92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -12678,6 +13218,8 @@
       <c r="AV93" t="n">
         <v>-0.8726919339164237</v>
       </c>
+      <c r="AW93" t="inlineStr"/>
+      <c r="AX93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -12818,6 +13360,8 @@
       <c r="AV94" t="n">
         <v>-0.8030209617755858</v>
       </c>
+      <c r="AW94" t="inlineStr"/>
+      <c r="AX94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -12958,6 +13502,8 @@
       <c r="AV95" t="n">
         <v>-0.9410150891632374</v>
       </c>
+      <c r="AW95" t="inlineStr"/>
+      <c r="AX95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -13098,6 +13644,8 @@
       <c r="AV96" t="n">
         <v>-0.8697027197975964</v>
       </c>
+      <c r="AW96" t="inlineStr"/>
+      <c r="AX96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -13238,6 +13786,8 @@
       <c r="AV97" t="n">
         <v>-0.8926196808510639</v>
       </c>
+      <c r="AW97" t="inlineStr"/>
+      <c r="AX97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -13378,6 +13928,8 @@
       <c r="AV98" t="n">
         <v>-0.9120214909335124</v>
       </c>
+      <c r="AW98" t="inlineStr"/>
+      <c r="AX98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -13518,6 +14070,8 @@
       <c r="AV99" t="n">
         <v>-0.9579330904272938</v>
       </c>
+      <c r="AW99" t="inlineStr"/>
+      <c r="AX99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -13658,6 +14212,8 @@
       <c r="AV100" t="n">
         <v>-0.8845169545745361</v>
       </c>
+      <c r="AW100" t="inlineStr"/>
+      <c r="AX100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -13798,6 +14354,8 @@
       <c r="AV101" t="n">
         <v>-0.8375753516409914</v>
       </c>
+      <c r="AW101" t="inlineStr"/>
+      <c r="AX101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -13938,6 +14496,8 @@
       <c r="AV102" t="n">
         <v>-0.8345370978332239</v>
       </c>
+      <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -14078,6 +14638,8 @@
       <c r="AV103" t="n">
         <v>-0.8655913978494624</v>
       </c>
+      <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -14218,6 +14780,8 @@
       <c r="AV104" t="n">
         <v>-0.8713188220230473</v>
       </c>
+      <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -14358,6 +14922,8 @@
       <c r="AV105" t="n">
         <v>-0.8558417085427136</v>
       </c>
+      <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -14498,6 +15064,8 @@
       <c r="AV106" t="n">
         <v>-0.873405299313052</v>
       </c>
+      <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -14638,6 +15206,8 @@
       <c r="AV107" t="n">
         <v>-0.7809629835791817</v>
       </c>
+      <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -14778,6 +15348,8 @@
       <c r="AV108" t="n">
         <v>-0.9106683804627249</v>
       </c>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -14918,6 +15490,8 @@
       <c r="AV109" t="n">
         <v>-0.840602950609365</v>
       </c>
+      <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -15058,6 +15632,8 @@
       <c r="AV110" t="n">
         <v>-0.9048231511254019</v>
       </c>
+      <c r="AW110" t="inlineStr"/>
+      <c r="AX110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -15198,6 +15774,8 @@
       <c r="AV111" t="n">
         <v>-0.8401015228426396</v>
       </c>
+      <c r="AW111" t="inlineStr"/>
+      <c r="AX111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -15338,6 +15916,8 @@
       <c r="AV112" t="n">
         <v>-0.9122807017543859</v>
       </c>
+      <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -15478,6 +16058,8 @@
       <c r="AV113" t="n">
         <v>-0.9649181423321083</v>
       </c>
+      <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -15618,6 +16200,8 @@
       <c r="AV114" t="n">
         <v>-0.9372869802317655</v>
       </c>
+      <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -15758,6 +16342,8 @@
       <c r="AV115" t="n">
         <v>-0.8688741721854304</v>
       </c>
+      <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -15898,6 +16484,8 @@
       <c r="AV116" t="n">
         <v>-0.821639344262295</v>
       </c>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -16038,6 +16626,8 @@
       <c r="AV117" t="n">
         <v>-1.043353636689359</v>
       </c>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -16178,6 +16768,8 @@
       <c r="AV118" t="n">
         <v>-1.023550087873462</v>
       </c>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -16318,6 +16910,8 @@
       <c r="AV119" t="n">
         <v>-0.9992862241256246</v>
       </c>
+      <c r="AW119" t="inlineStr"/>
+      <c r="AX119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -16458,6 +17052,8 @@
       <c r="AV120" t="n">
         <v>-0.9220733427362482</v>
       </c>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -16598,6 +17194,8 @@
       <c r="AV121" t="n">
         <v>-0.9540313754104341</v>
       </c>
+      <c r="AW121" t="inlineStr"/>
+      <c r="AX121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -16738,6 +17336,8 @@
       <c r="AV122" t="n">
         <v>-0.8568159529257928</v>
       </c>
+      <c r="AW122" t="inlineStr"/>
+      <c r="AX122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -16878,6 +17478,8 @@
       <c r="AV123" t="n">
         <v>-0.8646491519787163</v>
       </c>
+      <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -17018,6 +17620,8 @@
       <c r="AV124" t="n">
         <v>-0.8040981061782054</v>
       </c>
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -17158,6 +17762,8 @@
       <c r="AV125" t="n">
         <v>-0.9652323580034423</v>
       </c>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -17298,6 +17904,8 @@
       <c r="AV126" t="n">
         <v>-0.9461077844311376</v>
       </c>
+      <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -17438,6 +18046,8 @@
       <c r="AV127" t="n">
         <v>-0.9985683607730851</v>
       </c>
+      <c r="AW127" t="inlineStr"/>
+      <c r="AX127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -17578,6 +18188,8 @@
       <c r="AV128" t="n">
         <v>-0.8554932365555923</v>
       </c>
+      <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -17718,6 +18330,8 @@
       <c r="AV129" t="n">
         <v>-0.8341742347796839</v>
       </c>
+      <c r="AW129" t="inlineStr"/>
+      <c r="AX129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -17858,6 +18472,8 @@
       <c r="AV130" t="n">
         <v>-0.8899897505978819</v>
       </c>
+      <c r="AW130" t="inlineStr"/>
+      <c r="AX130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -17998,6 +18614,8 @@
       <c r="AV131" t="n">
         <v>-0.9594183293878932</v>
       </c>
+      <c r="AW131" t="inlineStr"/>
+      <c r="AX131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -18138,6 +18756,8 @@
       <c r="AV132" t="n">
         <v>-0.8095535435529191</v>
       </c>
+      <c r="AW132" t="inlineStr"/>
+      <c r="AX132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -18278,6 +18898,8 @@
       <c r="AV133" t="n">
         <v>-0.8061192631907587</v>
       </c>
+      <c r="AW133" t="inlineStr"/>
+      <c r="AX133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -18418,6 +19040,8 @@
       <c r="AV134" t="n">
         <v>-0.9432647644326476</v>
       </c>
+      <c r="AW134" t="inlineStr"/>
+      <c r="AX134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -18558,6 +19182,8 @@
       <c r="AV135" t="n">
         <v>-0.9047947568126941</v>
       </c>
+      <c r="AW135" t="inlineStr"/>
+      <c r="AX135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -18698,6 +19324,8 @@
       <c r="AV136" t="n">
         <v>-0.925575101488498</v>
       </c>
+      <c r="AW136" t="inlineStr"/>
+      <c r="AX136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -18838,6 +19466,8 @@
       <c r="AV137" t="n">
         <v>-0.8729547641963427</v>
       </c>
+      <c r="AW137" t="inlineStr"/>
+      <c r="AX137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -18978,6 +19608,8 @@
       <c r="AV138" t="n">
         <v>-0.8111718275652702</v>
       </c>
+      <c r="AW138" t="inlineStr"/>
+      <c r="AX138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -19118,6 +19750,8 @@
       <c r="AV139" t="n">
         <v>-0.9191253037139883</v>
       </c>
+      <c r="AW139" t="inlineStr"/>
+      <c r="AX139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -19258,6 +19892,8 @@
       <c r="AV140" t="n">
         <v>-0.983991462113127</v>
       </c>
+      <c r="AW140" t="inlineStr"/>
+      <c r="AX140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -19398,6 +20034,8 @@
       <c r="AV141" t="n">
         <v>-0.8676616915422886</v>
       </c>
+      <c r="AW141" t="inlineStr"/>
+      <c r="AX141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -19538,6 +20176,8 @@
       <c r="AV142" t="n">
         <v>-0.9794520547945206</v>
       </c>
+      <c r="AW142" t="inlineStr"/>
+      <c r="AX142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -19678,6 +20318,8 @@
       <c r="AV143" t="n">
         <v>-0.8755935422602089</v>
       </c>
+      <c r="AW143" t="inlineStr"/>
+      <c r="AX143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -19818,6 +20460,8 @@
       <c r="AV144" t="n">
         <v>-0.8558154437680231</v>
       </c>
+      <c r="AW144" t="inlineStr"/>
+      <c r="AX144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -19958,6 +20602,8 @@
       <c r="AV145" t="n">
         <v>-0.910299003322259</v>
       </c>
+      <c r="AW145" t="inlineStr"/>
+      <c r="AX145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -20098,6 +20744,8 @@
       <c r="AV146" t="n">
         <v>-0.8479307025986524</v>
       </c>
+      <c r="AW146" t="inlineStr"/>
+      <c r="AX146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -20238,6 +20886,8 @@
       <c r="AV147" t="n">
         <v>-0.9031939413895291</v>
       </c>
+      <c r="AW147" t="inlineStr"/>
+      <c r="AX147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -20378,6 +21028,8 @@
       <c r="AV148" t="n">
         <v>-0.8867924528301887</v>
       </c>
+      <c r="AW148" t="inlineStr"/>
+      <c r="AX148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -20518,6 +21170,8 @@
       <c r="AV149" t="n">
         <v>-0.9927797833935018</v>
       </c>
+      <c r="AW149" t="inlineStr"/>
+      <c r="AX149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -20658,6 +21312,8 @@
       <c r="AV150" t="n">
         <v>-0.8752424046541692</v>
       </c>
+      <c r="AW150" t="inlineStr"/>
+      <c r="AX150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -20798,6 +21454,8 @@
       <c r="AV151" t="n">
         <v>-0.9457209457209457</v>
       </c>
+      <c r="AW151" t="inlineStr"/>
+      <c r="AX151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -20938,6 +21596,8 @@
       <c r="AV152" t="n">
         <v>-0.8900032351989647</v>
       </c>
+      <c r="AW152" t="inlineStr"/>
+      <c r="AX152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -21078,6 +21738,8 @@
       <c r="AV153" t="n">
         <v>-0.9144542772861356</v>
       </c>
+      <c r="AW153" t="inlineStr"/>
+      <c r="AX153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -21218,6 +21880,8 @@
       <c r="AV154" t="n">
         <v>-0.870988867059594</v>
       </c>
+      <c r="AW154" t="inlineStr"/>
+      <c r="AX154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -21358,6 +22022,8 @@
       <c r="AV155" t="n">
         <v>-0.9734422880490295</v>
       </c>
+      <c r="AW155" t="inlineStr"/>
+      <c r="AX155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -21498,6 +22164,8 @@
       <c r="AV156" t="n">
         <v>-0.8216748768472907</v>
       </c>
+      <c r="AW156" t="inlineStr"/>
+      <c r="AX156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -21638,6 +22306,8 @@
       <c r="AV157" t="n">
         <v>-0.8612735542560104</v>
       </c>
+      <c r="AW157" t="inlineStr"/>
+      <c r="AX157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -21778,6 +22448,8 @@
       <c r="AV158" t="n">
         <v>-1.018099547511312</v>
       </c>
+      <c r="AW158" t="inlineStr"/>
+      <c r="AX158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -21918,6 +22590,8 @@
       <c r="AV159" t="n">
         <v>-1.04876299749014</v>
       </c>
+      <c r="AW159" t="inlineStr"/>
+      <c r="AX159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -22058,6 +22732,8 @@
       <c r="AV160" t="n">
         <v>-0.8695652173913042</v>
       </c>
+      <c r="AW160" t="inlineStr"/>
+      <c r="AX160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -22194,6 +22870,8 @@
         <v>39.86388713858987</v>
       </c>
       <c r="AV161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr"/>
+      <c r="AX161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -22330,6 +23008,8 @@
         <v>50.48954256485062</v>
       </c>
       <c r="AV162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr"/>
+      <c r="AX162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -22470,6 +23150,8 @@
       <c r="AV163" t="n">
         <v>-0.9148648648648647</v>
       </c>
+      <c r="AW163" t="inlineStr"/>
+      <c r="AX163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -22610,6 +23292,8 @@
       <c r="AV164" t="n">
         <v>-0.875</v>
       </c>
+      <c r="AW164" t="inlineStr"/>
+      <c r="AX164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -22750,6 +23434,8 @@
       <c r="AV165" t="n">
         <v>-0.9019350606756315</v>
       </c>
+      <c r="AW165" t="inlineStr"/>
+      <c r="AX165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -22890,6 +23576,8 @@
       <c r="AV166" t="n">
         <v>-0.8602257636122178</v>
       </c>
+      <c r="AW166" t="inlineStr"/>
+      <c r="AX166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -23030,6 +23718,8 @@
       <c r="AV167" t="n">
         <v>-0.8340425531914893</v>
       </c>
+      <c r="AW167" t="inlineStr"/>
+      <c r="AX167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -23170,6 +23860,8 @@
       <c r="AV168" t="n">
         <v>-0.9123961218836566</v>
       </c>
+      <c r="AW168" t="inlineStr"/>
+      <c r="AX168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -23310,6 +24002,8 @@
       <c r="AV169" t="n">
         <v>-0.9287135278514589</v>
       </c>
+      <c r="AW169" t="inlineStr"/>
+      <c r="AX169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -23450,6 +24144,8 @@
       <c r="AV170" t="n">
         <v>-0.794580970384373</v>
       </c>
+      <c r="AW170" t="inlineStr"/>
+      <c r="AX170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -23590,6 +24286,8 @@
       <c r="AV171" t="n">
         <v>-0.8666886109282422</v>
       </c>
+      <c r="AW171" t="inlineStr"/>
+      <c r="AX171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -23730,6 +24428,8 @@
       <c r="AV172" t="n">
         <v>-0.8734652114597544</v>
       </c>
+      <c r="AW172" t="inlineStr"/>
+      <c r="AX172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -23870,6 +24570,8 @@
       <c r="AV173" t="n">
         <v>-0.9163306451612903</v>
       </c>
+      <c r="AW173" t="inlineStr"/>
+      <c r="AX173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -24010,6 +24712,8 @@
       <c r="AV174" t="n">
         <v>-0.8450749123366273</v>
       </c>
+      <c r="AW174" t="inlineStr"/>
+      <c r="AX174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -24150,6 +24854,8 @@
       <c r="AV175" t="n">
         <v>-0.8522613065326633</v>
       </c>
+      <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -24290,6 +24996,8 @@
       <c r="AV176" t="n">
         <v>-0.9190476190476191</v>
       </c>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -24430,6 +25138,8 @@
       <c r="AV177" t="n">
         <v>-0.8253346392425727</v>
       </c>
+      <c r="AW177" t="inlineStr"/>
+      <c r="AX177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -24570,6 +25280,8 @@
       <c r="AV178" t="n">
         <v>-0.8593242365172189</v>
       </c>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -24710,6 +25422,8 @@
       <c r="AV179" t="n">
         <v>-1.011280931586608</v>
       </c>
+      <c r="AW179" t="inlineStr"/>
+      <c r="AX179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -24850,6 +25564,8 @@
       <c r="AV180" t="n">
         <v>-0.8638230647709321</v>
       </c>
+      <c r="AW180" t="inlineStr"/>
+      <c r="AX180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -24990,6 +25706,8 @@
       <c r="AV181" t="n">
         <v>-0.8194444444444445</v>
       </c>
+      <c r="AW181" t="inlineStr"/>
+      <c r="AX181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -25130,6 +25848,8 @@
       <c r="AV182" t="n">
         <v>-0.8907371167645139</v>
       </c>
+      <c r="AW182" t="inlineStr"/>
+      <c r="AX182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -25270,6 +25990,8 @@
       <c r="AV183" t="n">
         <v>-0.9359058207979072</v>
       </c>
+      <c r="AW183" t="inlineStr"/>
+      <c r="AX183" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -12955,7 +12955,9 @@
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
       <c r="C89" t="n">
         <v>88</v>
       </c>
@@ -13114,7 +13116,9 @@
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
       <c r="C90" t="n">
         <v>8386</v>
       </c>
@@ -13273,7 +13277,9 @@
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
       <c r="C91" t="n">
         <v>9096</v>
       </c>
@@ -13432,7 +13438,9 @@
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>12</v>
+      </c>
       <c r="C92" t="n">
         <v>721</v>
       </c>
@@ -13591,7 +13599,9 @@
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>7</v>
+      </c>
       <c r="C93" t="n">
         <v>7994</v>
       </c>
@@ -13750,7 +13760,9 @@
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>19</v>
+      </c>
       <c r="C94" t="n">
         <v>795</v>
       </c>
@@ -13909,7 +13921,9 @@
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>17</v>
+      </c>
       <c r="C95" t="n">
         <v>881</v>
       </c>
@@ -14068,7 +14082,9 @@
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>14</v>
+      </c>
       <c r="C96" t="n">
         <v>693</v>
       </c>
@@ -14227,7 +14243,9 @@
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>16</v>
+      </c>
       <c r="C97" t="n">
         <v>740</v>
       </c>
@@ -14386,7 +14404,9 @@
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
       <c r="C98" t="n">
         <v>8384</v>
       </c>
@@ -14545,7 +14565,9 @@
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>17</v>
+      </c>
       <c r="C99" t="n">
         <v>8954</v>
       </c>
@@ -14704,7 +14726,9 @@
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>16</v>
+      </c>
       <c r="C100" t="n">
         <v>764</v>
       </c>
@@ -14863,7 +14887,9 @@
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>17</v>
+      </c>
       <c r="C101" t="n">
         <v>4955</v>
       </c>
@@ -15022,7 +15048,9 @@
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>6</v>
+      </c>
       <c r="C102" t="n">
         <v>7645</v>
       </c>
@@ -15181,7 +15209,9 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
       <c r="C103" t="n">
         <v>6021</v>
       </c>
@@ -15340,7 +15370,9 @@
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>6</v>
+      </c>
       <c r="C104" t="n">
         <v>205</v>
       </c>
@@ -15499,7 +15531,9 @@
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
       <c r="C105" t="n">
         <v>4898</v>
       </c>
@@ -15658,7 +15692,9 @@
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>8</v>
+      </c>
       <c r="C106" t="n">
         <v>8381</v>
       </c>
@@ -15817,7 +15853,9 @@
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>11</v>
+      </c>
       <c r="C107" t="n">
         <v>9090</v>
       </c>
@@ -15976,7 +16014,9 @@
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>8</v>
+      </c>
       <c r="C108" t="n">
         <v>9080</v>
       </c>
@@ -16135,7 +16175,9 @@
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>14</v>
+      </c>
       <c r="C109" t="n">
         <v>580</v>
       </c>
@@ -16294,7 +16336,9 @@
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>7</v>
+      </c>
       <c r="C110" t="n">
         <v>378</v>
       </c>
@@ -16453,7 +16497,9 @@
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>3</v>
+      </c>
       <c r="C111" t="n">
         <v>9738</v>
       </c>
@@ -16612,7 +16658,9 @@
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="n">
+        <v>2</v>
+      </c>
       <c r="C112" t="n">
         <v>356</v>
       </c>
@@ -16771,7 +16819,9 @@
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="n">
+        <v>2</v>
+      </c>
       <c r="C113" t="n">
         <v>172</v>
       </c>
@@ -16930,7 +16980,9 @@
       <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
       <c r="C114" t="n">
         <v>9084</v>
       </c>
@@ -17089,7 +17141,9 @@
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
       <c r="C115" t="n">
         <v>254</v>
       </c>
@@ -17248,7 +17302,9 @@
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="n">
+        <v>2</v>
+      </c>
       <c r="C116" t="n">
         <v>8396</v>
       </c>
@@ -17407,7 +17463,9 @@
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
       <c r="C117" t="n">
         <v>7924</v>
       </c>
@@ -17566,7 +17624,9 @@
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
       <c r="C118" t="n">
         <v>7924</v>
       </c>
@@ -17725,7 +17785,9 @@
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
       <c r="C119" t="n">
         <v>69</v>
       </c>
@@ -17884,7 +17946,9 @@
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>3</v>
+      </c>
       <c r="C120" t="n">
         <v>7922</v>
       </c>
@@ -18043,7 +18107,9 @@
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>11</v>
+      </c>
       <c r="C121" t="n">
         <v>7922</v>
       </c>
@@ -18202,7 +18268,9 @@
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>11</v>
+      </c>
       <c r="C122" t="n">
         <v>141</v>
       </c>
@@ -18361,7 +18429,9 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>11</v>
+      </c>
       <c r="C123" t="n">
         <v>587</v>
       </c>
@@ -18520,7 +18590,9 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>13</v>
+      </c>
       <c r="C124" t="n">
         <v>575</v>
       </c>
@@ -18679,7 +18751,9 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>13</v>
+      </c>
       <c r="C125" t="n">
         <v>596</v>
       </c>
@@ -18838,7 +18912,9 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>14</v>
+      </c>
       <c r="C126" t="n">
         <v>631</v>
       </c>
@@ -18997,7 +19073,9 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>4</v>
+      </c>
       <c r="C127" t="n">
         <v>4445</v>
       </c>
@@ -19156,7 +19234,9 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>11</v>
+      </c>
       <c r="C128" t="n">
         <v>6976</v>
       </c>
@@ -19315,7 +19395,9 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>9</v>
+      </c>
       <c r="C129" t="n">
         <v>213</v>
       </c>
@@ -19474,7 +19556,9 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="n">
+        <v>4</v>
+      </c>
       <c r="C130" t="n">
         <v>569</v>
       </c>
@@ -19633,7 +19717,9 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
       <c r="C131" t="n">
         <v>8361</v>
       </c>
@@ -19792,7 +19878,9 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>9</v>
+      </c>
       <c r="C132" t="n">
         <v>191</v>
       </c>
@@ -19951,7 +20039,9 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="n">
+        <v>12</v>
+      </c>
       <c r="C133" t="n">
         <v>191</v>
       </c>
@@ -20110,7 +20200,9 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>8</v>
+      </c>
       <c r="C134" t="n">
         <v>4469</v>
       </c>
@@ -20269,7 +20361,9 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>16</v>
+      </c>
       <c r="C135" t="n">
         <v>4894</v>
       </c>
@@ -20428,7 +20522,9 @@
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>16</v>
+      </c>
       <c r="C136" t="n">
         <v>389</v>
       </c>
@@ -20587,7 +20683,9 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="n">
+        <v>16</v>
+      </c>
       <c r="C137" t="n">
         <v>746</v>
       </c>
@@ -20746,7 +20844,9 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>18</v>
+      </c>
       <c r="C138" t="n">
         <v>763</v>
       </c>
@@ -20905,7 +21005,9 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>17</v>
+      </c>
       <c r="C139" t="n">
         <v>768</v>
       </c>
@@ -21064,7 +21166,9 @@
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>18</v>
+      </c>
       <c r="C140" t="n">
         <v>4940</v>
       </c>
@@ -21223,7 +21327,9 @@
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>12</v>
+      </c>
       <c r="C141" t="n">
         <v>902</v>
       </c>
@@ -21382,7 +21488,9 @@
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
       <c r="C142" t="n">
         <v>5880</v>
       </c>
@@ -21541,7 +21649,9 @@
       <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>7</v>
+      </c>
       <c r="C143" t="n">
         <v>708</v>
       </c>
@@ -21700,7 +21810,9 @@
       <c r="A144" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>18</v>
+      </c>
       <c r="C144" t="n">
         <v>5812</v>
       </c>
@@ -21859,7 +21971,9 @@
       <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
       <c r="C145" t="n">
         <v>333</v>
       </c>
@@ -22018,7 +22132,9 @@
       <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>17</v>
+      </c>
       <c r="C146" t="n">
         <v>816</v>
       </c>
@@ -22177,7 +22293,9 @@
       <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
       <c r="C147" t="n">
         <v>143</v>
       </c>
@@ -22336,7 +22454,9 @@
       <c r="A148" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>12</v>
+      </c>
       <c r="C148" t="n">
         <v>4932</v>
       </c>
@@ -22495,7 +22615,9 @@
       <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>7</v>
+      </c>
       <c r="C149" t="n">
         <v>96</v>
       </c>
@@ -22654,7 +22776,9 @@
       <c r="A150" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
       <c r="C150" t="n">
         <v>729</v>
       </c>
@@ -22813,7 +22937,9 @@
       <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>7</v>
+      </c>
       <c r="C151" t="n">
         <v>6992</v>
       </c>
@@ -22972,7 +23098,9 @@
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="n">
+        <v>19</v>
+      </c>
       <c r="C152" t="n">
         <v>90</v>
       </c>
@@ -23131,7 +23259,9 @@
       <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="n">
+        <v>18</v>
+      </c>
       <c r="C153" t="n">
         <v>341</v>
       </c>
@@ -23290,7 +23420,9 @@
       <c r="A154" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>16</v>
+      </c>
       <c r="C154" t="n">
         <v>4952</v>
       </c>
@@ -23449,7 +23581,9 @@
       <c r="A155" s="1" t="n">
         <v>153</v>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>17</v>
+      </c>
       <c r="C155" t="n">
         <v>7578</v>
       </c>
@@ -23608,7 +23742,9 @@
       <c r="A156" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>8</v>
+      </c>
       <c r="C156" t="n">
         <v>755</v>
       </c>
@@ -23767,7 +23903,9 @@
       <c r="A157" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>8</v>
+      </c>
       <c r="C157" t="n">
         <v>4933</v>
       </c>
@@ -23926,7 +24064,9 @@
       <c r="A158" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>6</v>
+      </c>
       <c r="C158" t="n">
         <v>410</v>
       </c>
@@ -24085,7 +24225,9 @@
       <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>6</v>
+      </c>
       <c r="C159" t="n">
         <v>410</v>
       </c>
@@ -24240,7 +24382,9 @@
       <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="n">
+        <v>4</v>
+      </c>
       <c r="C160" t="n">
         <v>310</v>
       </c>
@@ -24395,7 +24539,9 @@
       <c r="A161" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>11</v>
+      </c>
       <c r="C161" t="n">
         <v>290</v>
       </c>
@@ -24554,7 +24700,9 @@
       <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>6</v>
+      </c>
       <c r="C162" t="n">
         <v>200</v>
       </c>
@@ -24713,7 +24861,9 @@
       <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>4</v>
+      </c>
       <c r="C163" t="n">
         <v>915</v>
       </c>
@@ -24872,7 +25022,9 @@
       <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>4</v>
+      </c>
       <c r="C164" t="n">
         <v>4905</v>
       </c>
@@ -25031,7 +25183,9 @@
       <c r="A165" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>2</v>
+      </c>
       <c r="C165" t="n">
         <v>5807</v>
       </c>
@@ -25190,7 +25344,9 @@
       <c r="A166" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>13</v>
+      </c>
       <c r="C166" t="n">
         <v>219</v>
       </c>
@@ -25349,7 +25505,9 @@
       <c r="A167" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
       <c r="C167" t="n">
         <v>267</v>
       </c>
@@ -25508,7 +25666,9 @@
       <c r="A168" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>12</v>
+      </c>
       <c r="C168" t="n">
         <v>642</v>
       </c>
@@ -25667,7 +25827,9 @@
       <c r="A169" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>7</v>
+      </c>
       <c r="C169" t="n">
         <v>286</v>
       </c>
@@ -25826,7 +25988,9 @@
       <c r="A170" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
       <c r="C170" t="n">
         <v>7594</v>
       </c>
@@ -25985,7 +26149,9 @@
       <c r="A171" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="n">
+        <v>7</v>
+      </c>
       <c r="C171" t="n">
         <v>6994</v>
       </c>
@@ -26144,7 +26310,9 @@
       <c r="A172" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>13</v>
+      </c>
       <c r="C172" t="n">
         <v>92</v>
       </c>
@@ -26303,7 +26471,9 @@
       <c r="A173" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>3</v>
+      </c>
       <c r="C173" t="n">
         <v>335</v>
       </c>
@@ -26462,7 +26632,9 @@
       <c r="A174" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
       <c r="C174" t="n">
         <v>9742</v>
       </c>
@@ -26621,7 +26793,9 @@
       <c r="A175" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
       <c r="C175" t="n">
         <v>155</v>
       </c>
@@ -26780,7 +26954,9 @@
       <c r="A176" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="n">
+        <v>14</v>
+      </c>
       <c r="C176" t="n">
         <v>101</v>
       </c>
@@ -26939,7 +27115,9 @@
       <c r="A177" s="1" t="n">
         <v>175</v>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>4</v>
+      </c>
       <c r="C177" t="n">
         <v>209</v>
       </c>
@@ -27098,7 +27276,9 @@
       <c r="A178" s="1" t="n">
         <v>176</v>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="n">
+        <v>14</v>
+      </c>
       <c r="C178" t="n">
         <v>666</v>
       </c>
@@ -27257,7 +27437,9 @@
       <c r="A179" s="1" t="n">
         <v>177</v>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>13</v>
+      </c>
       <c r="C179" t="n">
         <v>188</v>
       </c>
@@ -27416,7 +27598,9 @@
       <c r="A180" s="1" t="n">
         <v>178</v>
       </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
       <c r="C180" t="n">
         <v>685</v>
       </c>
@@ -27575,7 +27759,9 @@
       <c r="A181" s="1" t="n">
         <v>179</v>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>14</v>
+      </c>
       <c r="C181" t="n">
         <v>627</v>
       </c>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:BA181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,30 +655,40 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (g/cm²)</t>
+          <t>Bloque</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>Specific leaf area (cm²/g)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>LMA g/m2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
           <t>leaf water content</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>C:N</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>13dC/18dO</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Narea</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Carea</t>
         </is>
@@ -807,21 +817,27 @@
         <v>0.536</v>
       </c>
       <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
         <v>71.47877382352941</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
+        <v>13.99016724138068</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0.5072463768115941</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AX2" t="n">
         <v>39.58454796558406</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AY2" t="n">
         <v>-1.069204566063425</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AZ2" t="n">
         <v>0.1583411527786951</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BA2" t="n">
         <v>6.267862957094129</v>
       </c>
     </row>
@@ -948,21 +964,27 @@
         <v>0.788</v>
       </c>
       <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
         <v>96.28079739625713</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
+        <v>10.38628705872013</v>
+      </c>
+      <c r="AW3" t="n">
         <v>0.4815439780636996</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AX3" t="n">
         <v>25.57873717795717</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AY3" t="n">
         <v>-1.162714378482783</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AZ3" t="n">
         <v>0.1927929018543231</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BA3" t="n">
         <v>4.931398966307422</v>
       </c>
     </row>
@@ -1089,21 +1111,27 @@
         <v>0.536</v>
       </c>
       <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
         <v>73.13888888888889</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
+        <v>13.67261678693506</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AX4" t="n">
         <v>42.49161457666214</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AY4" t="n">
         <v>-1.083217188451016</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AZ4" t="n">
         <v>0.1459443363957555</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BA4" t="n">
         <v>6.201410491775166</v>
       </c>
     </row>
@@ -1230,21 +1258,27 @@
         <v>0.788</v>
       </c>
       <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
         <v>69.1300964630225</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>14.46547959809223</v>
+      </c>
+      <c r="AW5" t="n">
         <v>0.4547685834502104</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AX5" t="n">
         <v>29.47494536584171</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AY5" t="n">
         <v>-1.173469655199274</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AZ5" t="n">
         <v>0.2308390026071944</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BA5" t="n">
         <v>6.803966990152447</v>
       </c>
     </row>
@@ -1371,21 +1405,27 @@
         <v>0.788</v>
       </c>
       <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
         <v>82.4059385665529</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
+        <v>12.13504775741832</v>
+      </c>
+      <c r="AW6" t="n">
         <v>0.4913194444444444</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AX6" t="n">
         <v>29.46857519135586</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AY6" t="n">
         <v>-1.152717050430573</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AZ6" t="n">
         <v>0.1972952651382424</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BA6" t="n">
         <v>5.814010355624786</v>
       </c>
     </row>
@@ -1512,21 +1552,27 @@
         <v>0.585</v>
       </c>
       <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
         <v>67.8012654945055</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
+        <v>14.7489872453935</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0.736122618061309</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AX7" t="n">
         <v>26.51846199848627</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AY7" t="n">
         <v>-0.9757692279498354</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AZ7" t="n">
         <v>0.2411024955423218</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BA7" t="n">
         <v>6.393667365779264</v>
       </c>
     </row>
@@ -1653,21 +1699,27 @@
         <v>0.788</v>
       </c>
       <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
         <v>71.94738415545589</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
+        <v>13.89904597280856</v>
+      </c>
+      <c r="AW8" t="n">
         <v>0.486963190184049</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AX8" t="n">
         <v>29.75015113451708</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AY8" t="n">
         <v>-1.066817746219274</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AZ8" t="n">
         <v>0.2212734935521185</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BA8" t="n">
         <v>6.582919875238116</v>
       </c>
     </row>
@@ -1794,21 +1846,27 @@
         <v>0.788</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
         <v>69.39019390581717</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
+        <v>14.4112581866725</v>
+      </c>
+      <c r="AW9" t="n">
         <v>0.4296998420221169</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AX9" t="n">
         <v>28.28424514537473</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AY9" t="n">
         <v>-1.120257664680253</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AZ9" t="n">
         <v>0.2491330280495736</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BA9" t="n">
         <v>7.04653963916366</v>
       </c>
     </row>
@@ -1935,21 +1993,27 @@
         <v>0.788</v>
       </c>
       <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
         <v>89.16889483065954</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
+        <v>11.2146730303106</v>
+      </c>
+      <c r="AW10" t="n">
         <v>0.5689588935843257</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
         <v>28.01632724421026</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AY10" t="n">
         <v>-1.176763154946914</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AZ10" t="n">
         <v>0.1922442143630735</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
         <v>5.385976820401974</v>
       </c>
     </row>
@@ -2076,21 +2140,27 @@
         <v>0.536</v>
       </c>
       <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
         <v>72.18481374999999</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
+        <v>13.85332936458536</v>
+      </c>
+      <c r="AW11" t="n">
         <v>0.5061728395061729</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AX11" t="n">
         <v>39.94038297769038</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AY11" t="n">
         <v>-1.083133704760353</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AZ11" t="n">
         <v>0.1541538771183675</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BA11" t="n">
         <v>6.156964889603419</v>
       </c>
     </row>
@@ -2217,21 +2287,27 @@
         <v>0.536</v>
       </c>
       <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
         <v>64.85592510638298</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
+        <v>15.41879170422291</v>
+      </c>
+      <c r="AW12" t="n">
         <v>0.5392156862745099</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AX12" t="n">
         <v>41.33398260330502</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AY12" t="n">
         <v>-0.9693632665794485</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AZ12" t="n">
         <v>0.1704503359635594</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BA12" t="n">
         <v>7.04539122144526</v>
       </c>
     </row>
@@ -2358,21 +2434,27 @@
         <v>0.536</v>
       </c>
       <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
         <v>71.358</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
+        <v>14.01384567953138</v>
+      </c>
+      <c r="AW13" t="n">
         <v>0.5726495726495726</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AX13" t="n">
         <v>33.26962395702254</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
         <v>-1.01178671221848</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AZ13" t="n">
         <v>0.1893086604314295</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BA13" t="n">
         <v>6.298227944361334</v>
       </c>
     </row>
@@ -2499,21 +2581,27 @@
         <v>0.585</v>
       </c>
       <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
         <v>74.18300281914894</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
+        <v>13.48017688685243</v>
+      </c>
+      <c r="AW14" t="n">
         <v>0.7566867989646247</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AX14" t="n">
         <v>24.51611901423017</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AY14" t="n">
         <v>-0.9086318732906992</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AZ14" t="n">
         <v>0.2420263723581012</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BA14" t="n">
         <v>5.933547349313596</v>
       </c>
     </row>
@@ -2586,10 +2674,10 @@
         <v>0.1961666666666667</v>
       </c>
       <c r="T15" t="n">
-        <v>30.07</v>
+        <v>38.97</v>
       </c>
       <c r="U15" t="n">
-        <v>15.23</v>
+        <v>18.77</v>
       </c>
       <c r="V15" t="n">
         <v>1332.582</v>
@@ -2603,7 +2691,7 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
-        <v>506.4848686398404</v>
+        <v>481.6525532460868</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2640,22 +2728,28 @@
         <v>0.788</v>
       </c>
       <c r="AT15" t="n">
-        <v>87.49717662508208</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4935151313601596</v>
+        <v>70.99531166755462</v>
       </c>
       <c r="AV15" t="n">
+        <v>14.08543714383055</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.5183474467539133</v>
+      </c>
+      <c r="AX15" t="n">
         <v>29.77748860325364</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AY15" t="n">
         <v>-0.9710658232898745</v>
       </c>
-      <c r="AX15" t="n">
-        <v>0.1835954858483998</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.467012487459539</v>
+      <c r="AZ15" t="n">
+        <v>0.2262696828216982</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.737742901484933</v>
       </c>
     </row>
     <row r="16">
@@ -2727,10 +2821,10 @@
         <v>0.239</v>
       </c>
       <c r="T16" t="n">
-        <v>34.11</v>
+        <v>30</v>
       </c>
       <c r="U16" t="n">
-        <v>18.97</v>
+        <v>16.69</v>
       </c>
       <c r="V16" t="n">
         <v>1047.219</v>
@@ -2744,7 +2838,7 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
-        <v>556.1418938727646</v>
+        <v>556.3333333333334</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2781,22 +2875,28 @@
         <v>0.788</v>
       </c>
       <c r="AT16" t="n">
-        <v>55.20395361096469</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4438581061272354</v>
+        <v>62.74529658478131</v>
       </c>
       <c r="AV16" t="n">
+        <v>15.93744956881035</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.4436666666666666</v>
+      </c>
+      <c r="AX16" t="n">
         <v>32.32547486872957</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AY16" t="n">
         <v>-0.9202190103021481</v>
       </c>
-      <c r="AX16" t="n">
-        <v>0.2667160375811695</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.621722569917226</v>
+      <c r="AZ16" t="n">
+        <v>0.2346594974817987</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.585479688556592</v>
       </c>
     </row>
     <row r="17">
@@ -2922,21 +3022,27 @@
         <v>0.788</v>
       </c>
       <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
         <v>83.15552898983861</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
+        <v>12.02565857192968</v>
+      </c>
+      <c r="AW17" t="n">
         <v>0.4855473554735548</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AX17" t="n">
         <v>28.39448648615612</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AY17" t="n">
         <v>-1.137930339273472</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
         <v>0.2040293659175826</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BA17" t="n">
         <v>5.793309073325802</v>
       </c>
     </row>
@@ -3063,21 +3169,27 @@
         <v>0.788</v>
       </c>
       <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
         <v>75.3908671973188</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
+        <v>13.2642060925327</v>
+      </c>
+      <c r="AW18" t="n">
         <v>0.4816503800217155</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AX18" t="n">
         <v>29.17653851247548</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AY18" t="n">
         <v>-0.9983195512068304</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AZ18" t="n">
         <v>0.2199748552043699</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BA18" t="n">
         <v>6.418104834646514</v>
       </c>
     </row>
@@ -3204,21 +3316,27 @@
         <v>0.788</v>
       </c>
       <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
         <v>97.0510460251046</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
+        <v>10.30385597020073</v>
+      </c>
+      <c r="AW19" t="n">
         <v>0.5304518664047152</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AX19" t="n">
         <v>26.66776442666212</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AY19" t="n">
         <v>-1.159881181147376</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AZ19" t="n">
         <v>0.1804095984933663</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BA19" t="n">
         <v>4.811120672929789</v>
       </c>
     </row>
@@ -3291,10 +3409,10 @@
         <v>0.2016666666666667</v>
       </c>
       <c r="T20" t="n">
-        <v>38.97</v>
+        <v>34.11</v>
       </c>
       <c r="U20" t="n">
-        <v>18.77</v>
+        <v>18.97</v>
       </c>
       <c r="V20" t="n">
         <v>1362.462</v>
@@ -3308,7 +3426,7 @@
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
-        <v>481.6525532460868</v>
+        <v>556.1418938727646</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -3345,22 +3463,28 @@
         <v>0.788</v>
       </c>
       <c r="AT20" t="n">
-        <v>72.5872136387853</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.5183474467539133</v>
+        <v>71.82192936215077</v>
       </c>
       <c r="AV20" t="n">
+        <v>13.92332410004829</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.4438581061272354</v>
+      </c>
+      <c r="AX20" t="n">
         <v>30.75436275117814</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AY20" t="n">
         <v>-0.9251081452731393</v>
       </c>
-      <c r="AX20" t="n">
-        <v>0.2193069154530283</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>6.744644431684386</v>
+      <c r="AZ20" t="n">
+        <v>0.2216436966512492</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>6.816510648324604</v>
       </c>
     </row>
     <row r="21">
@@ -3486,21 +3610,27 @@
         <v>0.585</v>
       </c>
       <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
         <v>69.54388888888889</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
+        <v>14.37940868676056</v>
+      </c>
+      <c r="AW21" t="n">
         <v>0.736842105263158</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AX21" t="n">
         <v>22.9540859657499</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AY21" t="n">
         <v>-0.8250529055541557</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AZ21" t="n">
         <v>0.2731252805030631</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BA21" t="n">
         <v>6.269341168086865</v>
       </c>
     </row>
@@ -3627,21 +3757,27 @@
         <v>0.536</v>
       </c>
       <c r="AT22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU22" t="n">
         <v>59.98653846153847</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
+        <v>16.67040682204341</v>
+      </c>
+      <c r="AW22" t="n">
         <v>0.5555555555555555</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AX22" t="n">
         <v>53.02578826881873</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AY22" t="n">
         <v>-0.9307778716019919</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AZ22" t="n">
         <v>0.1359691165823957</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BA22" t="n">
         <v>7.209869586996444</v>
       </c>
     </row>
@@ -3768,21 +3904,27 @@
         <v>0.536</v>
       </c>
       <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>75.1049597826087</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
+        <v>13.31469989324939</v>
+      </c>
+      <c r="AW23" t="n">
         <v>0.5533980582524273</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AX23" t="n">
         <v>38.38370176944333</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AY23" t="n">
         <v>-1.076624094600751</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AZ23" t="n">
         <v>0.1532285064088778</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
         <v>5.8814772925756</v>
       </c>
     </row>
@@ -3909,21 +4051,27 @@
         <v>0.585</v>
       </c>
       <c r="AT24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU24" t="n">
         <v>67.90667645714286</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
+        <v>14.72609251656011</v>
+      </c>
+      <c r="AW24" t="n">
         <v>0.751538097491718</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AX24" t="n">
         <v>30.95258432083551</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AY24" t="n">
         <v>-0.9531215121310557</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AZ24" t="n">
         <v>0.2083919474390169</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BA24" t="n">
         <v>6.450269324889292</v>
       </c>
     </row>
@@ -3996,10 +4144,10 @@
         <v>0.1948333333333333</v>
       </c>
       <c r="T25" t="n">
-        <v>14.55</v>
+        <v>30.07</v>
       </c>
       <c r="U25" t="n">
-        <v>5.69</v>
+        <v>15.23</v>
       </c>
       <c r="V25" t="n">
         <v>1248.499</v>
@@ -4013,7 +4161,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>391.0652920962199</v>
+        <v>506.4848686398404</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -4050,22 +4198,28 @@
         <v>0.788</v>
       </c>
       <c r="AT25" t="n">
-        <v>219.4198594024604</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.60893470790378</v>
+        <v>81.97629678266578</v>
       </c>
       <c r="AV25" t="n">
+        <v>12.19864813668253</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.4935151313601596</v>
+      </c>
+      <c r="AX25" t="n">
         <v>30.76750734875213</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AY25" t="n">
         <v>-1.127672428671739</v>
       </c>
-      <c r="AX25" t="n">
-        <v>0.07191749109464135</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>2.212721935758194</v>
+      <c r="AZ25" t="n">
+        <v>0.1924962019984864</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.922628309595306</v>
       </c>
     </row>
     <row r="26">
@@ -4191,21 +4345,27 @@
         <v>0.788</v>
       </c>
       <c r="AT26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU26" t="n">
         <v>81.5699164345404</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
+        <v>12.25942165580735</v>
+      </c>
+      <c r="AW26" t="n">
         <v>0.491741387446909</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AX26" t="n">
         <v>29.19160870007697</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AY26" t="n">
         <v>-1.093730835683608</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AZ26" t="n">
         <v>0.1993680458705612</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BA26" t="n">
         <v>5.819873982352418</v>
       </c>
     </row>
@@ -4278,10 +4438,10 @@
         <v>0.2273333333333334</v>
       </c>
       <c r="T27" t="n">
-        <v>30</v>
+        <v>14.55</v>
       </c>
       <c r="U27" t="n">
-        <v>16.69</v>
+        <v>5.69</v>
       </c>
       <c r="V27" t="n">
         <v>579.081</v>
@@ -4295,7 +4455,7 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
-        <v>556.3333333333334</v>
+        <v>391.0652920962199</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -4332,22 +4492,28 @@
         <v>0.585</v>
       </c>
       <c r="AT27" t="n">
-        <v>34.69628520071899</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.4436666666666666</v>
+        <v>101.771704745167</v>
       </c>
       <c r="AV27" t="n">
+        <v>9.825913818619503</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.60893470790378</v>
+      </c>
+      <c r="AX27" t="n">
         <v>19.36748669969131</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AY27" t="n">
         <v>-0.9251981278059437</v>
       </c>
-      <c r="AX27" t="n">
-        <v>0.6593596761464461</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>12.77013975807906</v>
+      <c r="AZ27" t="n">
+        <v>0.2247906864753312</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.353630630525455</v>
       </c>
     </row>
     <row r="28">
@@ -4473,21 +4639,27 @@
         <v>0.585</v>
       </c>
       <c r="AT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU28" t="n">
         <v>69.6693247757256</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
+        <v>14.35351933177373</v>
+      </c>
+      <c r="AW28" t="n">
         <v>0.7484234981745768</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AX28" t="n">
         <v>31.82500795526659</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AY28" t="n">
         <v>-1.110646754176239</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AZ28" t="n">
         <v>0.1941969337398241</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BA28" t="n">
         <v>6.180318961158282</v>
       </c>
     </row>
@@ -4614,21 +4786,27 @@
         <v>0.585</v>
       </c>
       <c r="AT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU29" t="n">
         <v>94.70271604938272</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
+        <v>10.55935924243767</v>
+      </c>
+      <c r="AW29" t="n">
         <v>0.5573770491803279</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AX29" t="n">
         <v>20.74216706763612</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AY29" t="n">
         <v>-0.8721981465115956</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AZ29" t="n">
         <v>0.2299853817964811</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BA29" t="n">
         <v>4.77039521233669</v>
       </c>
     </row>
@@ -4755,21 +4933,27 @@
         <v>0.788</v>
       </c>
       <c r="AT30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU30" t="n">
         <v>78.94186507936509</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
+        <v>12.66754970882229</v>
+      </c>
+      <c r="AW30" t="n">
         <v>0.5222748815165877</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AX30" t="n">
         <v>29.19189319790335</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AY30" t="n">
         <v>-1.026018023099852</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AZ30" t="n">
         <v>0.2056480718564838</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BA30" t="n">
         <v>6.003256549989229</v>
       </c>
     </row>
@@ -4896,21 +5080,27 @@
         <v>0.536</v>
       </c>
       <c r="AT31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU31" t="n">
         <v>73.10914565217391</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
+        <v>13.67817926306549</v>
+      </c>
+      <c r="AW31" t="n">
         <v>0.5533980582524273</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AX31" t="n">
         <v>42.97256368979243</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AY31" t="n">
         <v>-1.081725628636109</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AZ31" t="n">
         <v>0.136631885562437</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BA31" t="n">
         <v>5.871422404388254</v>
       </c>
     </row>
@@ -5037,21 +5227,27 @@
         <v>0.585</v>
       </c>
       <c r="AT32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU32" t="n">
         <v>104.4525773195876</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
+        <v>9.573722598920243</v>
+      </c>
+      <c r="AW32" t="n">
         <v>0.5579427083333334</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AX32" t="n">
         <v>20.62022678542598</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AY32" t="n">
         <v>-0.9757257325131097</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AZ32" t="n">
         <v>0.2060536274187499</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BA32" t="n">
         <v>4.248872527334292</v>
       </c>
     </row>
@@ -5178,21 +5374,27 @@
         <v>0.585</v>
       </c>
       <c r="AT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU33" t="n">
         <v>89.62449856733524</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
+        <v>11.15766354049608</v>
+      </c>
+      <c r="AW33" t="n">
         <v>0.5238744884038199</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AX33" t="n">
         <v>21.99115496636606</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AY33" t="n">
         <v>-1.108000186694067</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AZ33" t="n">
         <v>0.2140487849336566</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BA33" t="n">
         <v>4.707179999838402</v>
       </c>
     </row>
@@ -5319,21 +5521,27 @@
         <v>0.536</v>
       </c>
       <c r="AT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU34" t="n">
         <v>79.74831617021276</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
+        <v>12.53944970907756</v>
+      </c>
+      <c r="AW34" t="n">
         <v>0.584070796460177</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AX34" t="n">
         <v>43.87185925469005</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AY34" t="n">
         <v>-1.1317622997201</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AZ34" t="n">
         <v>0.1262484116656832</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="BA34" t="n">
         <v>5.538752547725021</v>
       </c>
     </row>
@@ -5460,21 +5668,27 @@
         <v>0.788</v>
       </c>
       <c r="AT35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU35" t="n">
         <v>84.60972568578555</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
+        <v>11.81897225046789</v>
+      </c>
+      <c r="AW35" t="n">
         <v>0.4962311557788945</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AX35" t="n">
         <v>24.17983322666046</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AY35" t="n">
         <v>-1.097985206987246</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AZ35" t="n">
         <v>0.236853606683806</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="BA35" t="n">
         <v>5.72708070874746</v>
       </c>
     </row>
@@ -5601,21 +5815,27 @@
         <v>0.536</v>
       </c>
       <c r="AT36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU36" t="n">
         <v>67.44528301886793</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
+        <v>14.82683377161081</v>
+      </c>
+      <c r="AW36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AX36" t="n">
         <v>45.72171601638512</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AY36" t="n">
         <v>-1.041003254864917</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AZ36" t="n">
         <v>0.1404492354378129</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="BA36" t="n">
         <v>6.421580057406096</v>
       </c>
     </row>
@@ -5742,21 +5962,27 @@
         <v>0.536</v>
       </c>
       <c r="AT37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU37" t="n">
         <v>83.75136225806452</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
+        <v>11.94010429249715</v>
+      </c>
+      <c r="AW37" t="n">
         <v>0.5633802816901409</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AX37" t="n">
         <v>32.47607689365352</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AY37" t="n">
         <v>-1.128326182974303</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AZ37" t="n">
         <v>0.165736668134432</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="BA37" t="n">
         <v>5.382476778431748</v>
       </c>
     </row>
@@ -5883,21 +6109,27 @@
         <v>0.585</v>
       </c>
       <c r="AT38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU38" t="n">
         <v>56.4139702</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
+        <v>17.72610572265662</v>
+      </c>
+      <c r="AW38" t="n">
         <v>0.66078697421981</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AX38" t="n">
         <v>31.24223026798138</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AY38" t="n">
         <v>-1.052221717593601</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AZ38" t="n">
         <v>0.25370946862891</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="BA38" t="n">
         <v>7.926449640071605</v>
       </c>
     </row>
@@ -6024,21 +6256,27 @@
         <v>0.585</v>
       </c>
       <c r="AT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU39" t="n">
         <v>112.059891598916</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
+        <v>8.923799458767936</v>
+      </c>
+      <c r="AW39" t="n">
         <v>0.555421686746988</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AX39" t="n">
         <v>22.29074496544098</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AY39" t="n">
         <v>-1.018263130425242</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AZ39" t="n">
         <v>0.1790085898974969</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="BA39" t="n">
         <v>3.990234824028318</v>
       </c>
     </row>
@@ -6165,21 +6403,27 @@
         <v>0.536</v>
       </c>
       <c r="AT40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU40" t="n">
         <v>67.68852459016394</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
+        <v>14.77355291838217</v>
+      </c>
+      <c r="AW40" t="n">
         <v>0.5447761194029851</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AX40" t="n">
         <v>40.95714602250389</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AY40" t="n">
         <v>-1.134852638614013</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AZ40" t="n">
         <v>0.1636334848571583</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="BA40" t="n">
         <v>6.701960533465813</v>
       </c>
     </row>
@@ -6306,21 +6550,27 @@
         <v>0.788</v>
       </c>
       <c r="AT41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU41" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW41" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AX41" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AY41" t="n">
         <v>-1.046794083447492</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AZ41" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="BA41" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6447,21 +6697,27 @@
         <v>0.788</v>
       </c>
       <c r="AT42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU42" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW42" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AX42" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AY42" t="n">
         <v>-1.055363556422817</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AZ42" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="BA42" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6588,21 +6844,27 @@
         <v>0.788</v>
       </c>
       <c r="AT43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU43" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW43" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AX43" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AY43" t="n">
         <v>-1.027478472194354</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AZ43" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="BA43" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6729,21 +6991,27 @@
         <v>0.788</v>
       </c>
       <c r="AT44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU44" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW44" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AX44" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AY44" t="n">
         <v>-1.035889819888641</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AZ44" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="BA44" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6870,21 +7138,27 @@
         <v>0.788</v>
       </c>
       <c r="AT45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU45" t="n">
         <v>76.05677919203099</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
+        <v>13.1480718829174</v>
+      </c>
+      <c r="AW45" t="n">
         <v>0.4354889097157138</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AX45" t="n">
         <v>34.94837353504887</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AY45" t="n">
         <v>-1.016944806660762</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AZ45" t="n">
         <v>0.2080347916779913</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="BA45" t="n">
         <v>7.270477607848516</v>
       </c>
     </row>
@@ -7011,21 +7285,27 @@
         <v>0.585</v>
       </c>
       <c r="AT46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU46" t="n">
         <v>81.26364883401921</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
+        <v>12.30562513926119</v>
+      </c>
+      <c r="AW46" t="n">
         <v>0.5100806451612904</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AX46" t="n">
         <v>27.61940167646294</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AY46" t="n">
         <v>-1.168428613749502</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AZ46" t="n">
         <v>0.1803572361821152</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="BA46" t="n">
         <v>4.981358951370535</v>
       </c>
     </row>
@@ -7152,21 +7432,27 @@
         <v>0.788</v>
       </c>
       <c r="AT47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU47" t="n">
         <v>97.08402533427164</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
+        <v>10.3003557645749</v>
+      </c>
+      <c r="AW47" t="n">
         <v>0.516502211636611</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AX47" t="n">
         <v>31.61114054973259</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AY47" t="n">
         <v>-1.006406074511895</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AZ47" t="n">
         <v>0.1563233988308393</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="BA47" t="n">
         <v>4.941560931653564</v>
       </c>
     </row>
@@ -7293,21 +7579,27 @@
         <v>0.788</v>
       </c>
       <c r="AT48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU48" t="n">
         <v>84.03498467824311</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
+        <v>11.89980582288251</v>
+      </c>
+      <c r="AW48" t="n">
         <v>0.5043037974683545</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AX48" t="n">
         <v>32.58259222016648</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AY48" t="n">
         <v>-1.002974473340656</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AZ48" t="n">
         <v>0.1727182447385554</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="BA48" t="n">
         <v>5.627608137299266</v>
       </c>
     </row>
@@ -7434,21 +7726,27 @@
         <v>0.536</v>
       </c>
       <c r="AT49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU49" t="n">
         <v>57.71341344827587</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
+        <v>17.32699454514545</v>
+      </c>
+      <c r="AW49" t="n">
         <v>0.4081632653061225</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AX49" t="n">
         <v>37.10169593659131</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AY49" t="n">
         <v>-1.033343565098957</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AZ49" t="n">
         <v>0.2118768969038876</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="BA49" t="n">
         <v>7.860992204916545</v>
       </c>
     </row>
@@ -7575,21 +7873,27 @@
         <v>0.536</v>
       </c>
       <c r="AT50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU50" t="n">
         <v>69.24775590361446</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
+        <v>14.44090118085406</v>
+      </c>
+      <c r="AW50" t="n">
         <v>0.5585106382978723</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AX50" t="n">
         <v>46.62061318477367</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AY50" t="n">
         <v>-1.094831536193773</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AZ50" t="n">
         <v>0.1305405133948935</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="BA50" t="n">
         <v>6.085878779925097</v>
       </c>
     </row>
@@ -7716,21 +8020,27 @@
         <v>0.585</v>
       </c>
       <c r="AT51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU51" t="n">
         <v>56.8577403125</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
+        <v>17.58775488620945</v>
+      </c>
+      <c r="AW51" t="n">
         <v>0.6854334226988382</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AX51" t="n">
         <v>27.64252745359939</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AY51" t="n">
         <v>-1.034130614924995</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AZ51" t="n">
         <v>0.2749705279828398</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="BA51" t="n">
         <v>7.600880368696366</v>
       </c>
     </row>
@@ -7857,21 +8167,27 @@
         <v>0.585</v>
       </c>
       <c r="AT52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU52" t="n">
         <v>55.35752960352423</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
+        <v>18.06438992422698</v>
+      </c>
+      <c r="AW52" t="n">
         <v>0.6959821428571429</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AX52" t="n">
         <v>31.43663314688067</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AY52" t="n">
         <v>-0.9330413776996519</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AZ52" t="n">
         <v>0.2554237568151246</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="BA52" t="n">
         <v>8.029662939995131</v>
       </c>
     </row>
@@ -7998,21 +8314,27 @@
         <v>0.585</v>
       </c>
       <c r="AT53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU53" t="n">
         <v>120.4613095238095</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
+        <v>8.301420630018528</v>
+      </c>
+      <c r="AW53" t="n">
         <v>0.5561426684280054</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AX53" t="n">
         <v>16.47515809594595</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AY53" t="n">
         <v>-1.059704205037399</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AZ53" t="n">
         <v>0.2105696461538427</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="BA53" t="n">
         <v>3.469168210591955</v>
       </c>
     </row>
@@ -8139,21 +8461,27 @@
         <v>0.585</v>
       </c>
       <c r="AT54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU54" t="n">
         <v>109.2225954198473</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
+        <v>9.155614698186209</v>
+      </c>
+      <c r="AW54" t="n">
         <v>0.5568335588633289</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AX54" t="n">
         <v>17.18961723916043</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AY54" t="n">
         <v>-1.09799079624996</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AZ54" t="n">
         <v>0.2230482700063978</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="BA54" t="n">
         <v>3.834114387266885</v>
       </c>
     </row>
@@ -8280,21 +8608,27 @@
         <v>0.585</v>
       </c>
       <c r="AT55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU55" t="n">
         <v>48.06573001322752</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
+        <v>20.80484369476556</v>
+      </c>
+      <c r="AW55" t="n">
         <v>0.6501619620546044</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AX55" t="n">
         <v>34.16916319918331</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AY55" t="n">
         <v>-1.013558134662488</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AZ55" t="n">
         <v>0.2700331914670088</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="BA55" t="n">
         <v>9.226808188432537</v>
       </c>
     </row>
@@ -8421,21 +8755,27 @@
         <v>0.788</v>
       </c>
       <c r="AT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU56" t="n">
         <v>84.28579136690648</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
+        <v>11.86439592940258</v>
+      </c>
+      <c r="AW56" t="n">
         <v>0.5164166123070233</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AX56" t="n">
         <v>31.13148059335148</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AY56" t="n">
         <v>-1.029758709416929</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AZ56" t="n">
         <v>0.1811914954031918</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="BA56" t="n">
         <v>5.640759522824799</v>
       </c>
     </row>
@@ -8562,21 +8902,27 @@
         <v>0.536</v>
       </c>
       <c r="AT57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU57" t="n">
         <v>70.80198674418605</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
+        <v>14.12389744956014</v>
+      </c>
+      <c r="AW57" t="n">
         <v>0.5656565656565657</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AX57" t="n">
         <v>42.28261169430561</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AY57" t="n">
         <v>-1.071407723597514</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AZ57" t="n">
         <v>0.1485071659290358</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="BA57" t="n">
         <v>6.279270830799232</v>
       </c>
     </row>
@@ -8703,21 +9049,27 @@
         <v>0.788</v>
       </c>
       <c r="AT58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU58" t="n">
         <v>87.00776041666667</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
+        <v>11.4932276754528</v>
+      </c>
+      <c r="AW58" t="n">
         <v>0.5489781536293165</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AX58" t="n">
         <v>30.4083735401035</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AY58" t="n">
         <v>-1.076020463092165</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AZ58" t="n">
         <v>0.181805467668072</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="BA58" t="n">
         <v>5.528408572483942</v>
       </c>
     </row>
@@ -8844,21 +9196,27 @@
         <v>0.536</v>
       </c>
       <c r="AT59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU59" t="n">
         <v>76.72765957446808</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
+        <v>13.03310964450114</v>
+      </c>
+      <c r="AW59" t="n">
         <v>0.5607476635514019</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AX59" t="n">
         <v>41.39388452825128</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AY59" t="n">
         <v>-1.131721301339614</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AZ59" t="n">
         <v>0.1468960643433882</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="BA59" t="n">
         <v>6.080598725084783</v>
       </c>
     </row>
@@ -8985,21 +9343,27 @@
         <v>0.585</v>
       </c>
       <c r="AT60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU60" t="n">
         <v>93.55598173611111</v>
       </c>
-      <c r="AU60" t="n">
+      <c r="AV60" t="n">
+        <v>10.68878741308762</v>
+      </c>
+      <c r="AW60" t="n">
         <v>0.7698454981353223</v>
       </c>
-      <c r="AV60" t="n">
+      <c r="AX60" t="n">
         <v>28.16106955669685</v>
       </c>
-      <c r="AW60" t="n">
+      <c r="AY60" t="n">
         <v>-1.148906986345209</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AZ60" t="n">
         <v>0.1640718941643498</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="BA60" t="n">
         <v>4.620440023861259</v>
       </c>
     </row>
@@ -9126,21 +9490,27 @@
         <v>0.585</v>
       </c>
       <c r="AT61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU61" t="n">
         <v>68.17344376893939</v>
       </c>
-      <c r="AU61" t="n">
+      <c r="AV61" t="n">
+        <v>14.66846831721315</v>
+      </c>
+      <c r="AW61" t="n">
         <v>0.7409224730127575</v>
       </c>
-      <c r="AV61" t="n">
+      <c r="AX61" t="n">
         <v>28.34964144442967</v>
       </c>
-      <c r="AW61" t="n">
+      <c r="AY61" t="n">
         <v>-0.9802187884414533</v>
       </c>
-      <c r="AX61" t="n">
+      <c r="AZ61" t="n">
         <v>0.2324436326842925</v>
       </c>
-      <c r="AY61" t="n">
+      <c r="BA61" t="n">
         <v>6.589693642640406</v>
       </c>
     </row>
@@ -9213,7 +9583,7 @@
         <v>0.2556666666666667</v>
       </c>
       <c r="T62" t="n">
-        <v>25.52</v>
+        <v>35.52</v>
       </c>
       <c r="U62" t="n">
         <v>17.36</v>
@@ -9230,7 +9600,7 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="n">
-        <v>680.2507836990595</v>
+        <v>488.7387387387387</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
@@ -9267,21 +9637,27 @@
         <v>0.788</v>
       </c>
       <c r="AT62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU62" t="n">
         <v>60.43922811059907</v>
       </c>
-      <c r="AU62" t="n">
-        <v>0.3197492163009404</v>
-      </c>
       <c r="AV62" t="n">
+        <v>16.54554552169459</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0.5112612612612614</v>
+      </c>
+      <c r="AX62" t="n">
         <v>35.750550975415</v>
       </c>
-      <c r="AW62" t="n">
+      <c r="AY62" t="n">
         <v>-1.059967417806882</v>
       </c>
-      <c r="AX62" t="n">
+      <c r="AZ62" t="n">
         <v>0.2271852849396293</v>
       </c>
-      <c r="AY62" t="n">
+      <c r="BA62" t="n">
         <v>8.1219991100984</v>
       </c>
     </row>
@@ -9354,7 +9730,7 @@
         <v>0.201</v>
       </c>
       <c r="T63" t="n">
-        <v>25.15</v>
+        <v>35.15</v>
       </c>
       <c r="U63" t="n">
         <v>18.2</v>
@@ -9371,7 +9747,7 @@
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="n">
-        <v>723.6580516898608</v>
+        <v>517.7809388335704</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
@@ -9408,21 +9784,27 @@
         <v>0.788</v>
       </c>
       <c r="AT63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU63" t="n">
         <v>71.22549450549451</v>
       </c>
-      <c r="AU63" t="n">
-        <v>0.2763419483101391</v>
-      </c>
       <c r="AV63" t="n">
+        <v>14.03991656278157</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0.4822190611664296</v>
+      </c>
+      <c r="AX63" t="n">
         <v>31.74524498440573</v>
       </c>
-      <c r="AW63" t="n">
+      <c r="AY63" t="n">
         <v>-1.07072599241777</v>
       </c>
-      <c r="AX63" t="n">
+      <c r="AZ63" t="n">
         <v>0.2097736888129386</v>
       </c>
-      <c r="AY63" t="n">
+      <c r="BA63" t="n">
         <v>6.659317142649229</v>
       </c>
     </row>
@@ -9495,7 +9877,7 @@
         <v>0.201</v>
       </c>
       <c r="T64" t="n">
-        <v>25.15</v>
+        <v>35.15</v>
       </c>
       <c r="U64" t="n">
         <v>18.2</v>
@@ -9512,7 +9894,7 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="n">
-        <v>723.6580516898608</v>
+        <v>517.7809388335704</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
@@ -9549,21 +9931,27 @@
         <v>0.788</v>
       </c>
       <c r="AT64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU64" t="n">
         <v>71.22549450549451</v>
       </c>
-      <c r="AU64" t="n">
-        <v>0.2763419483101391</v>
-      </c>
       <c r="AV64" t="n">
+        <v>14.03991656278157</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0.4822190611664296</v>
+      </c>
+      <c r="AX64" t="n">
         <v>32.75482157518042</v>
       </c>
-      <c r="AW64" t="n">
+      <c r="AY64" t="n">
         <v>-1.07072599241777</v>
       </c>
-      <c r="AX64" t="n">
+      <c r="AZ64" t="n">
         <v>0.2051731480905204</v>
       </c>
-      <c r="AY64" t="n">
+      <c r="BA64" t="n">
         <v>6.720409857723063</v>
       </c>
     </row>
@@ -9690,21 +10078,27 @@
         <v>0.536</v>
       </c>
       <c r="AT65" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU65" t="n">
         <v>70.78017943396226</v>
       </c>
-      <c r="AU65" t="n">
+      <c r="AV65" t="n">
+        <v>14.12824900978102</v>
+      </c>
+      <c r="AW65" t="n">
         <v>0.547008547008547</v>
       </c>
-      <c r="AV65" t="n">
+      <c r="AX65" t="n">
         <v>37.77978443238764</v>
       </c>
-      <c r="AW65" t="n">
+      <c r="AY65" t="n">
         <v>-1.072717162486702</v>
       </c>
-      <c r="AX65" t="n">
+      <c r="AZ65" t="n">
         <v>0.1711270057226029</v>
       </c>
-      <c r="AY65" t="n">
+      <c r="BA65" t="n">
         <v>6.465141386759904</v>
       </c>
     </row>
@@ -9831,21 +10225,27 @@
         <v>0.536</v>
       </c>
       <c r="AT66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU66" t="n">
         <v>73.034885</v>
       </c>
-      <c r="AU66" t="n">
+      <c r="AV66" t="n">
+        <v>13.69208700746226</v>
+      </c>
+      <c r="AW66" t="n">
         <v>0.5416666666666667</v>
       </c>
-      <c r="AV66" t="n">
+      <c r="AX66" t="n">
         <v>46.78990518799996</v>
       </c>
-      <c r="AW66" t="n">
+      <c r="AY66" t="n">
         <v>-1.186907968195777</v>
       </c>
-      <c r="AX66" t="n">
+      <c r="AZ66" t="n">
         <v>0.1264668813853405</v>
       </c>
-      <c r="AY66" t="n">
+      <c r="BA66" t="n">
         <v>5.917373389442116</v>
       </c>
     </row>
@@ -9972,21 +10372,27 @@
         <v>0.585</v>
       </c>
       <c r="AT67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU67" t="n">
         <v>85.05351446969696</v>
       </c>
-      <c r="AU67" t="n">
+      <c r="AV67" t="n">
+        <v>11.75730369561956</v>
+      </c>
+      <c r="AW67" t="n">
         <v>0.7659574468085105</v>
       </c>
-      <c r="AV67" t="n">
+      <c r="AX67" t="n">
         <v>29.55848025895564</v>
       </c>
-      <c r="AW67" t="n">
+      <c r="AY67" t="n">
         <v>-1.05716724908219</v>
       </c>
-      <c r="AX67" t="n">
+      <c r="AZ67" t="n">
         <v>0.1735620252135451</v>
       </c>
-      <c r="AY67" t="n">
+      <c r="BA67" t="n">
         <v>5.130229695978934</v>
       </c>
     </row>
@@ -10113,21 +10519,27 @@
         <v>0.585</v>
       </c>
       <c r="AT68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU68" t="n">
         <v>95.80497285285286</v>
       </c>
-      <c r="AU68" t="n">
+      <c r="AV68" t="n">
+        <v>10.43787154489259</v>
+      </c>
+      <c r="AW68" t="n">
         <v>0.7672955974842768</v>
       </c>
-      <c r="AV68" t="n">
+      <c r="AX68" t="n">
         <v>27.95108301698842</v>
       </c>
-      <c r="AW68" t="n">
+      <c r="AY68" t="n">
         <v>-1.062612342442872</v>
       </c>
-      <c r="AX68" t="n">
+      <c r="AZ68" t="n">
         <v>0.1651892043876882</v>
       </c>
-      <c r="AY68" t="n">
+      <c r="BA68" t="n">
         <v>4.61721716535054</v>
       </c>
     </row>
@@ -10254,21 +10666,27 @@
         <v>0.585</v>
       </c>
       <c r="AT69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU69" t="n">
         <v>102.9321114369501</v>
       </c>
-      <c r="AU69" t="n">
+      <c r="AV69" t="n">
+        <v>9.715141232797292</v>
+      </c>
+      <c r="AW69" t="n">
         <v>0.5605670103092784</v>
       </c>
-      <c r="AV69" t="n">
+      <c r="AX69" t="n">
         <v>24.10341074609785</v>
       </c>
-      <c r="AW69" t="n">
+      <c r="AY69" t="n">
         <v>-1.162202419950019</v>
       </c>
-      <c r="AX69" t="n">
+      <c r="AZ69" t="n">
         <v>0.1729739026459769</v>
       </c>
-      <c r="AY69" t="n">
+      <c r="BA69" t="n">
         <v>4.169261023831525</v>
       </c>
     </row>
@@ -10395,21 +10813,27 @@
         <v>0.788</v>
       </c>
       <c r="AT70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU70" t="n">
         <v>78.68020076150917</v>
       </c>
-      <c r="AU70" t="n">
+      <c r="AV70" t="n">
+        <v>12.70967778833129</v>
+      </c>
+      <c r="AW70" t="n">
         <v>0.5284035259549461</v>
       </c>
-      <c r="AV70" t="n">
+      <c r="AX70" t="n">
         <v>33.07869485466203</v>
       </c>
-      <c r="AW70" t="n">
+      <c r="AY70" t="n">
         <v>-0.9735100220183867</v>
       </c>
-      <c r="AX70" t="n">
+      <c r="AZ70" t="n">
         <v>0.1653302877966243</v>
       </c>
-      <c r="AY70" t="n">
+      <c r="BA70" t="n">
         <v>5.468910140257988</v>
       </c>
     </row>
@@ -10536,21 +10960,27 @@
         <v>0.788</v>
       </c>
       <c r="AT71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU71" t="n">
         <v>74.43121248499399</v>
       </c>
-      <c r="AU71" t="n">
+      <c r="AV71" t="n">
+        <v>13.4352238343774</v>
+      </c>
+      <c r="AW71" t="n">
         <v>0.5137186223000584</v>
       </c>
-      <c r="AV71" t="n">
+      <c r="AX71" t="n">
         <v>28.43772466129882</v>
       </c>
-      <c r="AW71" t="n">
+      <c r="AY71" t="n">
         <v>-1.151540486656524</v>
       </c>
-      <c r="AX71" t="n">
+      <c r="AZ71" t="n">
         <v>0.224534879706159</v>
       </c>
-      <c r="AY71" t="n">
+      <c r="BA71" t="n">
         <v>6.385261085941602</v>
       </c>
     </row>
@@ -10677,21 +11107,27 @@
         <v>0.585</v>
       </c>
       <c r="AT72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU72" t="n">
         <v>93.83754512635377</v>
       </c>
-      <c r="AU72" t="n">
+      <c r="AV72" t="n">
+        <v>10.65671526949563</v>
+      </c>
+      <c r="AW72" t="n">
         <v>0.5512958963282937</v>
       </c>
-      <c r="AV72" t="n">
+      <c r="AX72" t="n">
         <v>27.25954615592946</v>
       </c>
-      <c r="AW72" t="n">
+      <c r="AY72" t="n">
         <v>-1.081507885923864</v>
       </c>
-      <c r="AX72" t="n">
+      <c r="AZ72" t="n">
         <v>0.1704181532420173</v>
       </c>
-      <c r="AY72" t="n">
+      <c r="BA72" t="n">
         <v>4.64552151410903</v>
       </c>
     </row>
@@ -10818,21 +11254,27 @@
         <v>0.585</v>
       </c>
       <c r="AT73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU73" t="n">
         <v>80.69806507082153</v>
       </c>
-      <c r="AU73" t="n">
+      <c r="AV73" t="n">
+        <v>12.39187084749044</v>
+      </c>
+      <c r="AW73" t="n">
         <v>0.7437386569872959</v>
       </c>
-      <c r="AV73" t="n">
+      <c r="AX73" t="n">
         <v>30.02082045458015</v>
       </c>
-      <c r="AW73" t="n">
+      <c r="AY73" t="n">
         <v>-1.008164398010397</v>
       </c>
-      <c r="AX73" t="n">
+      <c r="AZ73" t="n">
         <v>0.1771344004138958</v>
       </c>
-      <c r="AY73" t="n">
+      <c r="BA73" t="n">
         <v>5.317720031155273</v>
       </c>
     </row>
@@ -10959,21 +11401,27 @@
         <v>0.585</v>
       </c>
       <c r="AT74" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU74" t="n">
         <v>58.14073602661597</v>
       </c>
-      <c r="AU74" t="n">
+      <c r="AV74" t="n">
+        <v>17.19964466122711</v>
+      </c>
+      <c r="AW74" t="n">
         <v>0.7434146341463415</v>
       </c>
-      <c r="AV74" t="n">
+      <c r="AX74" t="n">
         <v>26.46707679984683</v>
       </c>
-      <c r="AW74" t="n">
+      <c r="AY74" t="n">
         <v>-0.9019527661726316</v>
       </c>
-      <c r="AX74" t="n">
+      <c r="AZ74" t="n">
         <v>0.2890653446677475</v>
       </c>
-      <c r="AY74" t="n">
+      <c r="BA74" t="n">
         <v>7.650714677495467</v>
       </c>
     </row>
@@ -11100,21 +11548,27 @@
         <v>0.788</v>
       </c>
       <c r="AT75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU75" t="n">
         <v>58.797049689441</v>
       </c>
-      <c r="AU75" t="n">
+      <c r="AV75" t="n">
+        <v>17.00765608617917</v>
+      </c>
+      <c r="AW75" t="n">
         <v>0.449886104783599</v>
       </c>
-      <c r="AV75" t="n">
+      <c r="AX75" t="n">
         <v>30.22124201621856</v>
       </c>
-      <c r="AW75" t="n">
+      <c r="AY75" t="n">
         <v>-1.064321440481539</v>
       </c>
-      <c r="AX75" t="n">
+      <c r="AZ75" t="n">
         <v>0.2678379030470969</v>
       </c>
-      <c r="AY75" t="n">
+      <c r="BA75" t="n">
         <v>8.094394089102797</v>
       </c>
     </row>
@@ -11241,21 +11695,27 @@
         <v>0.585</v>
       </c>
       <c r="AT76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU76" t="n">
         <v>67.24956401960785</v>
       </c>
-      <c r="AU76" t="n">
+      <c r="AV76" t="n">
+        <v>14.86998487764815</v>
+      </c>
+      <c r="AW76" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="AV76" t="n">
+      <c r="AX76" t="n">
         <v>32.73336164766602</v>
       </c>
-      <c r="AW76" t="n">
+      <c r="AY76" t="n">
         <v>-1.036430349351861</v>
       </c>
-      <c r="AX76" t="n">
+      <c r="AZ76" t="n">
         <v>0.2020516390549202</v>
       </c>
-      <c r="AY76" t="n">
+      <c r="BA76" t="n">
         <v>6.613829372688381</v>
       </c>
     </row>
@@ -11382,21 +11842,27 @@
         <v>0.585</v>
       </c>
       <c r="AT77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU77" t="n">
         <v>67.63895368951613</v>
       </c>
-      <c r="AU77" t="n">
+      <c r="AV77" t="n">
+        <v>14.78438008651511</v>
+      </c>
+      <c r="AW77" t="n">
         <v>0.7311653116531165</v>
       </c>
-      <c r="AV77" t="n">
+      <c r="AX77" t="n">
         <v>27.85958429127932</v>
       </c>
-      <c r="AW77" t="n">
+      <c r="AY77" t="n">
         <v>-0.9447135609596995</v>
       </c>
-      <c r="AX77" t="n">
+      <c r="AZ77" t="n">
         <v>0.2290004233178914</v>
       </c>
-      <c r="AY77" t="n">
+      <c r="BA77" t="n">
         <v>6.379856596163442</v>
       </c>
     </row>
@@ -11523,21 +11989,27 @@
         <v>0.585</v>
       </c>
       <c r="AT78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU78" t="n">
         <v>91.96880891173952</v>
       </c>
-      <c r="AU78" t="n">
+      <c r="AV78" t="n">
+        <v>10.87325161468252</v>
+      </c>
+      <c r="AW78" t="n">
         <v>0.5427115987460815</v>
       </c>
-      <c r="AV78" t="n">
+      <c r="AX78" t="n">
         <v>21.8162096187406</v>
       </c>
-      <c r="AW78" t="n">
+      <c r="AY78" t="n">
         <v>-1.136069687512091</v>
       </c>
-      <c r="AX78" t="n">
+      <c r="AZ78" t="n">
         <v>0.2143935207599353</v>
       </c>
-      <c r="AY78" t="n">
+      <c r="BA78" t="n">
         <v>4.677253989798563</v>
       </c>
     </row>
@@ -11664,21 +12136,27 @@
         <v>0.585</v>
       </c>
       <c r="AT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU79" t="n">
         <v>72.98086995867769</v>
       </c>
-      <c r="AU79" t="n">
+      <c r="AV79" t="n">
+        <v>13.70222087741908</v>
+      </c>
+      <c r="AW79" t="n">
         <v>0.7195828505214369</v>
       </c>
-      <c r="AV79" t="n">
+      <c r="AX79" t="n">
         <v>18.28478648070588</v>
       </c>
-      <c r="AW79" t="n">
+      <c r="AY79" t="n">
         <v>-0.7957323640055816</v>
       </c>
-      <c r="AX79" t="n">
+      <c r="AZ79" t="n">
         <v>0.3250436485054538</v>
       </c>
-      <c r="AY79" t="n">
+      <c r="BA79" t="n">
         <v>5.943353709831833</v>
       </c>
     </row>
@@ -11805,21 +12283,27 @@
         <v>0.585</v>
       </c>
       <c r="AT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU80" t="n">
         <v>63.13908010101009</v>
       </c>
-      <c r="AU80" t="n">
+      <c r="AV80" t="n">
+        <v>15.83805146353411</v>
+      </c>
+      <c r="AW80" t="n">
         <v>0.7093933463796477</v>
       </c>
-      <c r="AV80" t="n">
+      <c r="AX80" t="n">
         <v>22.12908955486301</v>
       </c>
-      <c r="AW80" t="n">
+      <c r="AY80" t="n">
         <v>-1.083830924468203</v>
       </c>
-      <c r="AX80" t="n">
+      <c r="AZ80" t="n">
         <v>0.2998648154876037</v>
       </c>
-      <c r="AY80" t="n">
+      <c r="BA80" t="n">
         <v>6.635735356277657</v>
       </c>
     </row>
@@ -11946,21 +12430,27 @@
         <v>0.585</v>
       </c>
       <c r="AT81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU81" t="n">
         <v>60.47368048048047</v>
       </c>
-      <c r="AU81" t="n">
+      <c r="AV81" t="n">
+        <v>16.53611938375038</v>
+      </c>
+      <c r="AW81" t="n">
         <v>0.7073813708260106</v>
       </c>
-      <c r="AV81" t="n">
+      <c r="AX81" t="n">
         <v>23.88772942228289</v>
       </c>
-      <c r="AW81" t="n">
+      <c r="AY81" t="n">
         <v>-0.852490835998494</v>
       </c>
-      <c r="AX81" t="n">
+      <c r="AZ81" t="n">
         <v>0.2994186256562353</v>
       </c>
-      <c r="AY81" t="n">
+      <c r="BA81" t="n">
         <v>7.152431113667959</v>
       </c>
     </row>
@@ -12087,21 +12577,27 @@
         <v>0.788</v>
       </c>
       <c r="AT82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU82" t="n">
         <v>82.68561093247588</v>
       </c>
-      <c r="AU82" t="n">
+      <c r="AV82" t="n">
+        <v>12.0940026774022</v>
+      </c>
+      <c r="AW82" t="n">
         <v>0.4902683876254866</v>
       </c>
-      <c r="AV82" t="n">
+      <c r="AX82" t="n">
         <v>29.22142888916803</v>
       </c>
-      <c r="AW82" t="n">
+      <c r="AY82" t="n">
         <v>-1.073512489772441</v>
       </c>
-      <c r="AX82" t="n">
+      <c r="AZ82" t="n">
         <v>0.1986099449474032</v>
       </c>
-      <c r="AY82" t="n">
+      <c r="BA82" t="n">
         <v>5.80366638296212</v>
       </c>
     </row>
@@ -12228,21 +12724,27 @@
         <v>0.788</v>
       </c>
       <c r="AT83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU83" t="n">
         <v>106.3460708782743</v>
       </c>
-      <c r="AU83" t="n">
+      <c r="AV83" t="n">
+        <v>9.403262309000761</v>
+      </c>
+      <c r="AW83" t="n">
         <v>0.5595520868680013</v>
       </c>
-      <c r="AV83" t="n">
+      <c r="AX83" t="n">
         <v>26.31625012037236</v>
       </c>
-      <c r="AW83" t="n">
+      <c r="AY83" t="n">
         <v>-1.045162407612312</v>
       </c>
-      <c r="AX83" t="n">
+      <c r="AZ83" t="n">
         <v>0.1574768288150041</v>
       </c>
-      <c r="AY83" t="n">
+      <c r="BA83" t="n">
         <v>4.144199615258708</v>
       </c>
     </row>
@@ -12369,21 +12871,27 @@
         <v>0.788</v>
       </c>
       <c r="AT84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU84" t="n">
         <v>96.34761279018835</v>
       </c>
-      <c r="AU84" t="n">
+      <c r="AV84" t="n">
+        <v>10.37908434926823</v>
+      </c>
+      <c r="AW84" t="n">
         <v>0.4989025460930642</v>
       </c>
-      <c r="AV84" t="n">
+      <c r="AX84" t="n">
         <v>30.20416467837983</v>
       </c>
-      <c r="AW84" t="n">
+      <c r="AY84" t="n">
         <v>-1.011763599487811</v>
       </c>
-      <c r="AX84" t="n">
+      <c r="AZ84" t="n">
         <v>0.1625698637855855</v>
       </c>
-      <c r="AY84" t="n">
+      <c r="BA84" t="n">
         <v>4.910286937521602</v>
       </c>
     </row>
@@ -12510,21 +13018,27 @@
         <v>0.788</v>
       </c>
       <c r="AT85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU85" t="n">
         <v>75.91252181500872</v>
       </c>
-      <c r="AU85" t="n">
+      <c r="AV85" t="n">
+        <v>13.1730573045235</v>
+      </c>
+      <c r="AW85" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AV85" t="n">
+      <c r="AX85" t="n">
         <v>27.98331631734705</v>
       </c>
-      <c r="AW85" t="n">
+      <c r="AY85" t="n">
         <v>-1.056436243301099</v>
       </c>
-      <c r="AX85" t="n">
+      <c r="AZ85" t="n">
         <v>0.2261410104794487</v>
       </c>
-      <c r="AY85" t="n">
+      <c r="BA85" t="n">
         <v>6.328175428570905</v>
       </c>
     </row>
@@ -12651,21 +13165,27 @@
         <v>0.788</v>
       </c>
       <c r="AT86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU86" t="n">
         <v>74.01554341226473</v>
       </c>
-      <c r="AU86" t="n">
+      <c r="AV86" t="n">
+        <v>13.51067564862728</v>
+      </c>
+      <c r="AW86" t="n">
         <v>0.4900928792569659</v>
       </c>
-      <c r="AV86" t="n">
+      <c r="AX86" t="n">
         <v>30.59860950966031</v>
       </c>
-      <c r="AW86" t="n">
+      <c r="AY86" t="n">
         <v>-1.139184969499528</v>
       </c>
-      <c r="AX86" t="n">
+      <c r="AZ86" t="n">
         <v>0.2131678007547578</v>
       </c>
-      <c r="AY86" t="n">
+      <c r="BA86" t="n">
         <v>6.522638295327906</v>
       </c>
     </row>
@@ -12792,21 +13312,27 @@
         <v>0.585</v>
       </c>
       <c r="AT87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU87" t="n">
         <v>60.21125734463277</v>
       </c>
-      <c r="AU87" t="n">
+      <c r="AV87" t="n">
+        <v>16.60818996481461</v>
+      </c>
+      <c r="AW87" t="n">
         <v>0.7318181818181819</v>
       </c>
-      <c r="AV87" t="n">
+      <c r="AX87" t="n">
         <v>27.00689943428555</v>
       </c>
-      <c r="AW87" t="n">
+      <c r="AY87" t="n">
         <v>-0.9994064701242487</v>
       </c>
-      <c r="AX87" t="n">
+      <c r="AZ87" t="n">
         <v>0.2723142473493239</v>
       </c>
-      <c r="AY87" t="n">
+      <c r="BA87" t="n">
         <v>7.354363492686352</v>
       </c>
     </row>
@@ -12933,21 +13459,27 @@
         <v>0.585</v>
       </c>
       <c r="AT88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU88" t="n">
         <v>101.6063559322034</v>
       </c>
-      <c r="AU88" t="n">
+      <c r="AV88" t="n">
+        <v>9.841903991392504</v>
+      </c>
+      <c r="AW88" t="n">
         <v>0.5961209355390759</v>
       </c>
-      <c r="AV88" t="n">
+      <c r="AX88" t="n">
         <v>20.09981608868212</v>
       </c>
-      <c r="AW88" t="n">
+      <c r="AY88" t="n">
         <v>-0.9530514877786842</v>
       </c>
-      <c r="AX88" t="n">
+      <c r="AZ88" t="n">
         <v>0.2165437559626953</v>
       </c>
-      <c r="AY88" t="n">
+      <c r="BA88" t="n">
         <v>4.352489670002637</v>
       </c>
     </row>
@@ -13094,21 +13626,27 @@
         <v>0.717</v>
       </c>
       <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="n">
         <v>34.15994277539342</v>
       </c>
-      <c r="AU89" t="n">
+      <c r="AV89" t="n">
+        <v>29.27405372354237</v>
+      </c>
+      <c r="AW89" t="n">
         <v>0.5212328767123288</v>
       </c>
-      <c r="AV89" t="n">
+      <c r="AX89" t="n">
         <v>59.38716473519461</v>
       </c>
-      <c r="AW89" t="n">
+      <c r="AY89" t="n">
         <v>-0.921325744894543</v>
       </c>
-      <c r="AX89" t="n">
+      <c r="AZ89" t="n">
         <v>0.2273110803333757</v>
       </c>
-      <c r="AY89" t="n">
+      <c r="BA89" t="n">
         <v>13.49936057389324</v>
       </c>
     </row>
@@ -13255,21 +13793,27 @@
         <v>0.717</v>
       </c>
       <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="n">
         <v>33.18294478527607</v>
       </c>
-      <c r="AU90" t="n">
+      <c r="AV90" t="n">
+        <v>30.13596311210209</v>
+      </c>
+      <c r="AW90" t="n">
         <v>0.5018337408312958</v>
       </c>
-      <c r="AV90" t="n">
+      <c r="AX90" t="n">
         <v>55.07549417735655</v>
       </c>
-      <c r="AW90" t="n">
+      <c r="AY90" t="n">
         <v>-0.9396264176117411</v>
       </c>
-      <c r="AX90" t="n">
+      <c r="AZ90" t="n">
         <v>0.2562349769016561</v>
       </c>
-      <c r="AY90" t="n">
+      <c r="BA90" t="n">
         <v>14.11226797838226</v>
       </c>
     </row>
@@ -13416,21 +13960,27 @@
         <v>0.717</v>
       </c>
       <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="n">
         <v>37.93648208469055</v>
       </c>
-      <c r="AU91" t="n">
+      <c r="AV91" t="n">
+        <v>26.35985059889238</v>
+      </c>
+      <c r="AW91" t="n">
         <v>0.5147523709167544</v>
       </c>
-      <c r="AV91" t="n">
+      <c r="AX91" t="n">
         <v>45.17757835768303</v>
       </c>
-      <c r="AW91" t="n">
+      <c r="AY91" t="n">
         <v>-0.9000000000000001</v>
       </c>
-      <c r="AX91" t="n">
+      <c r="AZ91" t="n">
         <v>0.2747689268163115</v>
       </c>
-      <c r="AY91" t="n">
+      <c r="BA91" t="n">
         <v>12.41339472150039</v>
       </c>
     </row>
@@ -13577,21 +14127,27 @@
         <v>0.717</v>
       </c>
       <c r="AT92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU92" t="n">
         <v>40.56470588235294</v>
       </c>
-      <c r="AU92" t="n">
+      <c r="AV92" t="n">
+        <v>24.65197215777262</v>
+      </c>
+      <c r="AW92" t="n">
         <v>0.5620483820295319</v>
       </c>
-      <c r="AV92" t="n">
+      <c r="AX92" t="n">
         <v>43.38637434690112</v>
       </c>
-      <c r="AW92" t="n">
+      <c r="AY92" t="n">
         <v>-0.9772876892692561</v>
       </c>
-      <c r="AX92" t="n">
+      <c r="AZ92" t="n">
         <v>0.2638257036105743</v>
       </c>
-      <c r="AY92" t="n">
+      <c r="BA92" t="n">
         <v>11.44644073918296</v>
       </c>
     </row>
@@ -13738,21 +14294,27 @@
         <v>0.717</v>
       </c>
       <c r="AT93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU93" t="n">
         <v>35.25954751131221</v>
       </c>
-      <c r="AU93" t="n">
+      <c r="AV93" t="n">
+        <v>28.36111267959899</v>
+      </c>
+      <c r="AW93" t="n">
         <v>0.4891354600092463</v>
       </c>
-      <c r="AV93" t="n">
+      <c r="AX93" t="n">
         <v>61.02294354014969</v>
       </c>
-      <c r="AW93" t="n">
+      <c r="AY93" t="n">
         <v>-0.8726919339164237</v>
       </c>
-      <c r="AX93" t="n">
+      <c r="AZ93" t="n">
         <v>0.2205905999210828</v>
       </c>
-      <c r="AY93" t="n">
+      <c r="BA93" t="n">
         <v>13.46108772447198</v>
       </c>
     </row>
@@ -13899,21 +14461,27 @@
         <v>0.717</v>
       </c>
       <c r="AT94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU94" t="n">
         <v>33.15173383317713</v>
       </c>
-      <c r="AU94" t="n">
+      <c r="AV94" t="n">
+        <v>30.16433484390593</v>
+      </c>
+      <c r="AW94" t="n">
         <v>0.4981185324553152</v>
       </c>
-      <c r="AV94" t="n">
+      <c r="AX94" t="n">
         <v>50.18888849181604</v>
       </c>
-      <c r="AW94" t="n">
+      <c r="AY94" t="n">
         <v>-0.8030209617755858</v>
       </c>
-      <c r="AX94" t="n">
+      <c r="AZ94" t="n">
         <v>0.2899244513121407</v>
       </c>
-      <c r="AY94" t="n">
+      <c r="BA94" t="n">
         <v>14.55098595795598</v>
       </c>
     </row>
@@ -14060,21 +14628,27 @@
         <v>0.523</v>
       </c>
       <c r="AT95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU95" t="n">
         <v>30.50483754512636</v>
       </c>
-      <c r="AU95" t="n">
+      <c r="AV95" t="n">
+        <v>32.78168580706853</v>
+      </c>
+      <c r="AW95" t="n">
         <v>0.5650125628140704</v>
       </c>
-      <c r="AV95" t="n">
+      <c r="AX95" t="n">
         <v>44.53537356895627</v>
       </c>
-      <c r="AW95" t="n">
+      <c r="AY95" t="n">
         <v>-0.9410150891632374</v>
       </c>
-      <c r="AX95" t="n">
+      <c r="AZ95" t="n">
         <v>0.3639814907180162</v>
       </c>
-      <c r="AY95" t="n">
+      <c r="BA95" t="n">
         <v>16.21005166131244</v>
       </c>
     </row>
@@ -14221,21 +14795,27 @@
         <v>0.717</v>
       </c>
       <c r="AT96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU96" t="n">
         <v>40.07197898423818</v>
       </c>
-      <c r="AU96" t="n">
+      <c r="AV96" t="n">
+        <v>24.95509394216187</v>
+      </c>
+      <c r="AW96" t="n">
         <v>0.5391444713478613</v>
       </c>
-      <c r="AV96" t="n">
+      <c r="AX96" t="n">
         <v>41.91201493351629</v>
       </c>
-      <c r="AW96" t="n">
+      <c r="AY96" t="n">
         <v>-0.8697027197975964</v>
       </c>
-      <c r="AX96" t="n">
+      <c r="AZ96" t="n">
         <v>0.2754165199655664</v>
       </c>
-      <c r="AY96" t="n">
+      <c r="BA96" t="n">
         <v>11.5432612977339</v>
       </c>
     </row>
@@ -14382,21 +14962,27 @@
         <v>0.717</v>
       </c>
       <c r="AT97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU97" t="n">
         <v>25.14212910532276</v>
       </c>
-      <c r="AU97" t="n">
+      <c r="AV97" t="n">
+        <v>39.77387896668994</v>
+      </c>
+      <c r="AW97" t="n">
         <v>0.5298189563365282</v>
       </c>
-      <c r="AV97" t="n">
+      <c r="AX97" t="n">
         <v>70.70612613426273</v>
       </c>
-      <c r="AW97" t="n">
+      <c r="AY97" t="n">
         <v>-0.8926196808510639</v>
       </c>
-      <c r="AX97" t="n">
+      <c r="AZ97" t="n">
         <v>0.2635851161810385</v>
       </c>
-      <c r="AY97" t="n">
+      <c r="BA97" t="n">
         <v>18.63708247181081</v>
       </c>
     </row>
@@ -14543,21 +15129,27 @@
         <v>0.717</v>
       </c>
       <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="n">
         <v>34.10823136818687</v>
       </c>
-      <c r="AU98" t="n">
+      <c r="AV98" t="n">
+        <v>29.31843604569632</v>
+      </c>
+      <c r="AW98" t="n">
         <v>0.5177038626609443</v>
       </c>
-      <c r="AV98" t="n">
+      <c r="AX98" t="n">
         <v>56.15700798713841</v>
       </c>
-      <c r="AW98" t="n">
+      <c r="AY98" t="n">
         <v>-0.9120214909335124</v>
       </c>
-      <c r="AX98" t="n">
+      <c r="AZ98" t="n">
         <v>0.2379812101557392</v>
       </c>
-      <c r="AY98" t="n">
+      <c r="BA98" t="n">
         <v>13.36431271950471</v>
       </c>
     </row>
@@ -14704,21 +15296,27 @@
         <v>0.717</v>
       </c>
       <c r="AT99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU99" t="n">
         <v>43.40028169014084</v>
       </c>
-      <c r="AU99" t="n">
+      <c r="AV99" t="n">
+        <v>23.04132510336143</v>
+      </c>
+      <c r="AW99" t="n">
         <v>0.5321560358460727</v>
       </c>
-      <c r="AV99" t="n">
+      <c r="AX99" t="n">
         <v>55.79246449666994</v>
       </c>
-      <c r="AW99" t="n">
+      <c r="AY99" t="n">
         <v>-0.9579330904272938</v>
       </c>
-      <c r="AX99" t="n">
+      <c r="AZ99" t="n">
         <v>0.1937192235493845</v>
       </c>
-      <c r="AY99" t="n">
+      <c r="BA99" t="n">
         <v>10.8080729022015</v>
       </c>
     </row>
@@ -14865,21 +15463,27 @@
         <v>0.717</v>
       </c>
       <c r="AT100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU100" t="n">
         <v>35.8758865248227</v>
       </c>
-      <c r="AU100" t="n">
+      <c r="AV100" t="n">
+        <v>27.87387565483839</v>
+      </c>
+      <c r="AW100" t="n">
         <v>0.535966149506347</v>
       </c>
-      <c r="AV100" t="n">
+      <c r="AX100" t="n">
         <v>65.93475017680478</v>
       </c>
-      <c r="AW100" t="n">
+      <c r="AY100" t="n">
         <v>-0.8845169545745361</v>
       </c>
-      <c r="AX100" t="n">
+      <c r="AZ100" t="n">
         <v>0.1937567807703534</v>
       </c>
-      <c r="AY100" t="n">
+      <c r="BA100" t="n">
         <v>12.77530493515518</v>
       </c>
     </row>
@@ -15026,21 +15630,27 @@
         <v>0.523</v>
       </c>
       <c r="AT101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU101" t="n">
         <v>31.9693215339233</v>
       </c>
-      <c r="AU101" t="n">
+      <c r="AV101" t="n">
+        <v>31.279988189267</v>
+      </c>
+      <c r="AW101" t="n">
         <v>0.5531634446397189</v>
       </c>
-      <c r="AV101" t="n">
+      <c r="AX101" t="n">
         <v>62.55686848770559</v>
       </c>
-      <c r="AW101" t="n">
+      <c r="AY101" t="n">
         <v>-0.8345370978332239</v>
       </c>
-      <c r="AX101" t="n">
+      <c r="AZ101" t="n">
         <v>0.2390186769233919</v>
       </c>
-      <c r="AY101" t="n">
+      <c r="BA101" t="n">
         <v>14.95225993840202</v>
       </c>
     </row>
@@ -15187,21 +15797,27 @@
         <v>0.717</v>
       </c>
       <c r="AT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU102" t="n">
         <v>32.25160202360878</v>
       </c>
-      <c r="AU102" t="n">
+      <c r="AV102" t="n">
+        <v>31.00621169974693</v>
+      </c>
+      <c r="AW102" t="n">
         <v>0.5488779003423355</v>
       </c>
-      <c r="AV102" t="n">
+      <c r="AX102" t="n">
         <v>48.18483993222593</v>
       </c>
-      <c r="AW102" t="n">
+      <c r="AY102" t="n">
         <v>-0.8655913978494624</v>
       </c>
-      <c r="AX102" t="n">
+      <c r="AZ102" t="n">
         <v>0.3022826134073608</v>
       </c>
-      <c r="AY102" t="n">
+      <c r="BA102" t="n">
         <v>14.56543934132861</v>
       </c>
     </row>
@@ -15348,21 +15964,27 @@
         <v>0.717</v>
       </c>
       <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" t="n">
         <v>35.23089668615984</v>
       </c>
-      <c r="AU103" t="n">
+      <c r="AV103" t="n">
+        <v>28.38417678971087</v>
+      </c>
+      <c r="AW103" t="n">
         <v>0.4877683474787819</v>
       </c>
-      <c r="AV103" t="n">
+      <c r="AX103" t="n">
         <v>48.50036505453044</v>
       </c>
-      <c r="AW103" t="n">
+      <c r="AY103" t="n">
         <v>-0.8713188220230473</v>
       </c>
-      <c r="AX103" t="n">
+      <c r="AZ103" t="n">
         <v>0.2697981424651091</v>
       </c>
-      <c r="AY103" t="n">
+      <c r="BA103" t="n">
         <v>13.085308400592</v>
       </c>
     </row>
@@ -15509,21 +16131,27 @@
         <v>0.717</v>
       </c>
       <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="n">
         <v>34.03149664929263</v>
       </c>
-      <c r="AU104" t="n">
+      <c r="AV104" t="n">
+        <v>29.38454368626147</v>
+      </c>
+      <c r="AW104" t="n">
         <v>0.5196709585121603</v>
       </c>
-      <c r="AV104" t="n">
+      <c r="AX104" t="n">
         <v>42.08566962870098</v>
       </c>
-      <c r="AW104" t="n">
+      <c r="AY104" t="n">
         <v>-0.873405299313052</v>
       </c>
-      <c r="AX104" t="n">
+      <c r="AZ104" t="n">
         <v>0.3273385634947573</v>
       </c>
-      <c r="AY104" t="n">
+      <c r="BA104" t="n">
         <v>13.77626263997392</v>
       </c>
     </row>
@@ -15670,21 +16298,27 @@
         <v>0.717</v>
       </c>
       <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU105" t="n">
         <v>34.42013201320133</v>
       </c>
-      <c r="AU105" t="n">
+      <c r="AV105" t="n">
+        <v>29.05276480684226</v>
+      </c>
+      <c r="AW105" t="n">
         <v>0.5026672137874436</v>
       </c>
-      <c r="AV105" t="n">
+      <c r="AX105" t="n">
         <v>51.94526295590641</v>
       </c>
-      <c r="AW105" t="n">
+      <c r="AY105" t="n">
         <v>-0.7809629835791817</v>
       </c>
-      <c r="AX105" t="n">
+      <c r="AZ105" t="n">
         <v>0.2627407067212578</v>
       </c>
-      <c r="AY105" t="n">
+      <c r="BA105" t="n">
         <v>13.64813509985642</v>
       </c>
     </row>
@@ -15831,21 +16465,27 @@
         <v>0.717</v>
       </c>
       <c r="AT106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU106" t="n">
         <v>37.13388601036269</v>
       </c>
-      <c r="AU106" t="n">
+      <c r="AV106" t="n">
+        <v>26.92958123803518</v>
+      </c>
+      <c r="AW106" t="n">
         <v>0.5488546049555867</v>
       </c>
-      <c r="AV106" t="n">
+      <c r="AX106" t="n">
         <v>55.62393534386633</v>
       </c>
-      <c r="AW106" t="n">
+      <c r="AY106" t="n">
         <v>-0.9106683804627249</v>
       </c>
-      <c r="AX106" t="n">
+      <c r="AZ106" t="n">
         <v>0.2253565398386968</v>
       </c>
-      <c r="AY106" t="n">
+      <c r="BA106" t="n">
         <v>12.53521760130511</v>
       </c>
     </row>
@@ -15992,21 +16632,27 @@
         <v>0.717</v>
       </c>
       <c r="AT107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU107" t="n">
         <v>34.93205417607223</v>
       </c>
-      <c r="AU107" t="n">
+      <c r="AV107" t="n">
+        <v>28.62700243620314</v>
+      </c>
+      <c r="AW107" t="n">
         <v>0.4978747520544063</v>
       </c>
-      <c r="AV107" t="n">
+      <c r="AX107" t="n">
         <v>58.95157666997726</v>
       </c>
-      <c r="AW107" t="n">
+      <c r="AY107" t="n">
         <v>-0.840602950609365</v>
       </c>
-      <c r="AX107" t="n">
+      <c r="AZ107" t="n">
         <v>0.2310070069738794</v>
       </c>
-      <c r="AY107" t="n">
+      <c r="BA107" t="n">
         <v>13.61822728292262</v>
       </c>
     </row>
@@ -16153,21 +16799,27 @@
         <v>0.717</v>
       </c>
       <c r="AT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU108" t="n">
         <v>38.12042253521127</v>
       </c>
-      <c r="AU108" t="n">
+      <c r="AV108" t="n">
+        <v>26.23265781160518</v>
+      </c>
+      <c r="AW108" t="n">
         <v>0.5200386286817963</v>
       </c>
-      <c r="AV108" t="n">
+      <c r="AX108" t="n">
         <v>61.68991897543837</v>
       </c>
-      <c r="AW108" t="n">
+      <c r="AY108" t="n">
         <v>-0.9048231511254019</v>
       </c>
-      <c r="AX108" t="n">
+      <c r="AZ108" t="n">
         <v>0.2004180823301927</v>
       </c>
-      <c r="AY108" t="n">
+      <c r="BA108" t="n">
         <v>12.36377526016233</v>
       </c>
     </row>
@@ -16314,21 +16966,27 @@
         <v>0.717</v>
       </c>
       <c r="AT109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU109" t="n">
         <v>34.02602230483271</v>
       </c>
-      <c r="AU109" t="n">
+      <c r="AV109" t="n">
+        <v>29.38927127717688</v>
+      </c>
+      <c r="AW109" t="n">
         <v>0.5066483264557542</v>
       </c>
-      <c r="AV109" t="n">
+      <c r="AX109" t="n">
         <v>42.51564615776595</v>
       </c>
-      <c r="AW109" t="n">
+      <c r="AY109" t="n">
         <v>-0.8401015228426396</v>
       </c>
-      <c r="AX109" t="n">
+      <c r="AZ109" t="n">
         <v>0.3164054433208752</v>
       </c>
-      <c r="AY109" t="n">
+      <c r="BA109" t="n">
         <v>13.4521818706214</v>
       </c>
     </row>
@@ -16475,21 +17133,27 @@
         <v>0.523</v>
       </c>
       <c r="AT110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU110" t="n">
         <v>36.02815442561206</v>
       </c>
-      <c r="AU110" t="n">
+      <c r="AV110" t="n">
+        <v>27.75607066036971</v>
+      </c>
+      <c r="AW110" t="n">
         <v>0.5085608514576585</v>
       </c>
-      <c r="AV110" t="n">
+      <c r="AX110" t="n">
         <v>43.63977691743113</v>
       </c>
-      <c r="AW110" t="n">
+      <c r="AY110" t="n">
         <v>-0.9122807017543859</v>
       </c>
-      <c r="AX110" t="n">
+      <c r="AZ110" t="n">
         <v>0.3143298872640892</v>
       </c>
-      <c r="AY110" t="n">
+      <c r="BA110" t="n">
         <v>13.71728615868613</v>
       </c>
     </row>
@@ -16636,21 +17300,27 @@
         <v>0.717</v>
       </c>
       <c r="AT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" t="n">
         <v>35.10835322195704</v>
       </c>
-      <c r="AU111" t="n">
+      <c r="AV111" t="n">
+        <v>28.48324994561671</v>
+      </c>
+      <c r="AW111" t="n">
         <v>0.5398132894014278</v>
       </c>
-      <c r="AV111" t="n">
+      <c r="AX111" t="n">
         <v>48.27107341587141</v>
       </c>
-      <c r="AW111" t="n">
+      <c r="AY111" t="n">
         <v>-0.9649181423321083</v>
       </c>
-      <c r="AX111" t="n">
+      <c r="AZ111" t="n">
         <v>0.2727743536270423</v>
       </c>
-      <c r="AY111" t="n">
+      <c r="BA111" t="n">
         <v>13.16711084989783</v>
       </c>
     </row>
@@ -16797,21 +17467,27 @@
         <v>0.717</v>
       </c>
       <c r="AT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" t="n">
         <v>32.21244286439817</v>
       </c>
-      <c r="AU112" t="n">
+      <c r="AV112" t="n">
+        <v>31.04390450018368</v>
+      </c>
+      <c r="AW112" t="n">
         <v>0.5466267556988257</v>
       </c>
-      <c r="AV112" t="n">
+      <c r="AX112" t="n">
         <v>55.68533253151493</v>
       </c>
-      <c r="AW112" t="n">
+      <c r="AY112" t="n">
         <v>-0.9372869802317655</v>
       </c>
-      <c r="AX112" t="n">
+      <c r="AZ112" t="n">
         <v>0.2677287744794695</v>
       </c>
-      <c r="AY112" t="n">
+      <c r="BA112" t="n">
         <v>14.90856583514423</v>
       </c>
     </row>
@@ -16958,21 +17634,27 @@
         <v>0.523</v>
       </c>
       <c r="AT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" t="n">
         <v>38.78301343570058</v>
       </c>
-      <c r="AU113" t="n">
+      <c r="AV113" t="n">
+        <v>25.78448427319675</v>
+      </c>
+      <c r="AW113" t="n">
         <v>0.5035731300619343</v>
       </c>
-      <c r="AV113" t="n">
+      <c r="AX113" t="n">
         <v>46.55285938373989</v>
       </c>
-      <c r="AW113" t="n">
+      <c r="AY113" t="n">
         <v>-0.8688741721854304</v>
       </c>
-      <c r="AX113" t="n">
+      <c r="AZ113" t="n">
         <v>0.2699350840327465</v>
       </c>
-      <c r="AY113" t="n">
+      <c r="BA113" t="n">
         <v>12.56625000971446</v>
       </c>
     </row>
@@ -17119,21 +17801,27 @@
         <v>0.523</v>
       </c>
       <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="n">
         <v>35.49061855670104</v>
       </c>
-      <c r="AU114" t="n">
+      <c r="AV114" t="n">
+        <v>28.17646016516634</v>
+      </c>
+      <c r="AW114" t="n">
         <v>0.4870438921205711</v>
       </c>
-      <c r="AV114" t="n">
+      <c r="AX114" t="n">
         <v>28.78285344011537</v>
       </c>
-      <c r="AW114" t="n">
+      <c r="AY114" t="n">
         <v>-0.821639344262295</v>
       </c>
-      <c r="AX114" t="n">
+      <c r="AZ114" t="n">
         <v>0.4709552277566549</v>
       </c>
-      <c r="AY114" t="n">
+      <c r="BA114" t="n">
         <v>13.55543529737596</v>
       </c>
     </row>
@@ -17280,21 +17968,27 @@
         <v>0.523</v>
       </c>
       <c r="AT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU115" t="n">
         <v>34.75611814345991</v>
       </c>
-      <c r="AU115" t="n">
+      <c r="AV115" t="n">
+        <v>28.77191278589812</v>
+      </c>
+      <c r="AW115" t="n">
         <v>0.5466524973432518</v>
       </c>
-      <c r="AV115" t="n">
+      <c r="AX115" t="n">
         <v>40.26096003557048</v>
       </c>
-      <c r="AW115" t="n">
+      <c r="AY115" t="n">
         <v>-1.043353636689359</v>
       </c>
-      <c r="AX115" t="n">
+      <c r="AZ115" t="n">
         <v>0.3439129986152255</v>
       </c>
-      <c r="AY115" t="n">
+      <c r="BA115" t="n">
         <v>13.8462674929608</v>
       </c>
     </row>
@@ -17441,21 +18135,27 @@
         <v>0.523</v>
       </c>
       <c r="AT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" t="n">
         <v>34.20469107551487</v>
       </c>
-      <c r="AU116" t="n">
+      <c r="AV116" t="n">
+        <v>29.23575593161375</v>
+      </c>
+      <c r="AW116" t="n">
         <v>0.5594758064516129</v>
       </c>
-      <c r="AV116" t="n">
+      <c r="AX116" t="n">
         <v>40.26096003557048</v>
       </c>
-      <c r="AW116" t="n">
+      <c r="AY116" t="n">
         <v>-1.023550087873462</v>
       </c>
-      <c r="AX116" t="n">
+      <c r="AZ116" t="n">
         <v>0.3494573532195661</v>
       </c>
-      <c r="AY116" t="n">
+      <c r="BA116" t="n">
         <v>14.06948853210919</v>
       </c>
     </row>
@@ -17602,21 +18302,27 @@
         <v>0.523</v>
       </c>
       <c r="AT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU117" t="n">
         <v>43.41372646184341</v>
       </c>
-      <c r="AU117" t="n">
+      <c r="AV117" t="n">
+        <v>23.03418944878888</v>
+      </c>
+      <c r="AW117" t="n">
         <v>0.5943718592964824</v>
       </c>
-      <c r="AV117" t="n">
+      <c r="AX117" t="n">
         <v>38.62830546324884</v>
       </c>
-      <c r="AW117" t="n">
+      <c r="AY117" t="n">
         <v>-0.9992862241256246</v>
       </c>
-      <c r="AX117" t="n">
+      <c r="AZ117" t="n">
         <v>0.2941786834792475</v>
       </c>
-      <c r="AY117" t="n">
+      <c r="BA117" t="n">
         <v>11.36362404621276</v>
       </c>
     </row>
@@ -17763,21 +18469,27 @@
         <v>0.523</v>
       </c>
       <c r="AT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU118" t="n">
         <v>43.41372646184341</v>
       </c>
-      <c r="AU118" t="n">
+      <c r="AV118" t="n">
+        <v>23.03418944878888</v>
+      </c>
+      <c r="AW118" t="n">
         <v>0.5943718592964824</v>
       </c>
-      <c r="AV118" t="n">
+      <c r="AX118" t="n">
         <v>47.60443554531614</v>
       </c>
-      <c r="AW118" t="n">
+      <c r="AY118" t="n">
         <v>-0.9220733427362482</v>
       </c>
-      <c r="AX118" t="n">
+      <c r="AZ118" t="n">
         <v>0.2356234081045346</v>
       </c>
-      <c r="AY118" t="n">
+      <c r="BA118" t="n">
         <v>11.21671934408004</v>
       </c>
     </row>
@@ -17924,21 +18636,27 @@
         <v>0.523</v>
       </c>
       <c r="AT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU119" t="n">
         <v>38.38884093711468</v>
       </c>
-      <c r="AU119" t="n">
+      <c r="AV119" t="n">
+        <v>26.04923659034443</v>
+      </c>
+      <c r="AW119" t="n">
         <v>0.5616216216216217</v>
       </c>
-      <c r="AV119" t="n">
+      <c r="AX119" t="n">
         <v>47.60443554531614</v>
       </c>
-      <c r="AW119" t="n">
+      <c r="AY119" t="n">
         <v>-0.9540313754104341</v>
       </c>
-      <c r="AX119" t="n">
+      <c r="AZ119" t="n">
         <v>0.2664652002443708</v>
       </c>
-      <c r="AY119" t="n">
+      <c r="BA119" t="n">
         <v>12.68492545010291</v>
       </c>
     </row>
@@ -18085,21 +18803,27 @@
         <v>0.523</v>
       </c>
       <c r="AT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU120" t="n">
         <v>28.00729765590447</v>
       </c>
-      <c r="AU120" t="n">
+      <c r="AV120" t="n">
+        <v>35.70497990509202</v>
+      </c>
+      <c r="AW120" t="n">
         <v>0.5872581234027018</v>
       </c>
-      <c r="AV120" t="n">
+      <c r="AX120" t="n">
         <v>38.09610849251812</v>
       </c>
-      <c r="AW120" t="n">
+      <c r="AY120" t="n">
         <v>-0.8568159529257928</v>
       </c>
-      <c r="AX120" t="n">
+      <c r="AZ120" t="n">
         <v>0.4458705469717965</v>
       </c>
-      <c r="AY120" t="n">
+      <c r="BA120" t="n">
         <v>16.98593273105596</v>
       </c>
     </row>
@@ -18246,21 +18970,27 @@
         <v>0.523</v>
       </c>
       <c r="AT121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU121" t="n">
         <v>28.00729765590447</v>
       </c>
-      <c r="AU121" t="n">
+      <c r="AV121" t="n">
+        <v>35.70497990509202</v>
+      </c>
+      <c r="AW121" t="n">
         <v>0.5872581234027018</v>
       </c>
-      <c r="AV121" t="n">
+      <c r="AX121" t="n">
         <v>35.84967061566433</v>
       </c>
-      <c r="AW121" t="n">
+      <c r="AY121" t="n">
         <v>-0.8646491519787163</v>
       </c>
-      <c r="AX121" t="n">
+      <c r="AZ121" t="n">
         <v>0.4809162989997219</v>
       </c>
-      <c r="AY121" t="n">
+      <c r="BA121" t="n">
         <v>17.24069091284437</v>
       </c>
     </row>
@@ -18407,21 +19137,27 @@
         <v>0.523</v>
       </c>
       <c r="AT122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU122" t="n">
         <v>37.72970873786407</v>
       </c>
-      <c r="AU122" t="n">
+      <c r="AV122" t="n">
+        <v>26.50431274059741</v>
+      </c>
+      <c r="AW122" t="n">
         <v>0.5840064620355412</v>
       </c>
-      <c r="AV122" t="n">
+      <c r="AX122" t="n">
         <v>46.88581586268426</v>
       </c>
-      <c r="AW122" t="n">
+      <c r="AY122" t="n">
         <v>-0.8040981061782054</v>
       </c>
-      <c r="AX122" t="n">
+      <c r="AZ122" t="n">
         <v>0.2754411937467637</v>
       </c>
-      <c r="AY122" t="n">
+      <c r="BA122" t="n">
         <v>12.9142850910087</v>
       </c>
     </row>
@@ -18568,21 +19304,27 @@
         <v>0.523</v>
       </c>
       <c r="AT123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU123" t="n">
         <v>34.93055141579732</v>
       </c>
-      <c r="AU123" t="n">
+      <c r="AV123" t="n">
+        <v>28.62823400914738</v>
+      </c>
+      <c r="AW123" t="n">
         <v>0.5502680965147453</v>
       </c>
-      <c r="AV123" t="n">
+      <c r="AX123" t="n">
         <v>51.2080861390158</v>
       </c>
-      <c r="AW123" t="n">
+      <c r="AY123" t="n">
         <v>-0.9652323580034423</v>
       </c>
-      <c r="AX123" t="n">
+      <c r="AZ123" t="n">
         <v>0.2712645733328085</v>
       </c>
-      <c r="AY123" t="n">
+      <c r="BA123" t="n">
         <v>13.89093963768983</v>
       </c>
     </row>
@@ -18729,21 +19471,27 @@
         <v>0.523</v>
       </c>
       <c r="AT124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU124" t="n">
         <v>31.18076158940397</v>
       </c>
-      <c r="AU124" t="n">
+      <c r="AV124" t="n">
+        <v>32.07105756967225</v>
+      </c>
+      <c r="AW124" t="n">
         <v>0.5213187509906483</v>
       </c>
-      <c r="AV124" t="n">
+      <c r="AX124" t="n">
         <v>44.75623909743305</v>
       </c>
-      <c r="AW124" t="n">
+      <c r="AY124" t="n">
         <v>-0.9461077844311376</v>
       </c>
-      <c r="AX124" t="n">
+      <c r="AZ124" t="n">
         <v>0.3551411071187895</v>
       </c>
-      <c r="AY124" t="n">
+      <c r="BA124" t="n">
         <v>15.89478030353562</v>
       </c>
     </row>
@@ -18890,21 +19638,27 @@
         <v>0.523</v>
       </c>
       <c r="AT125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU125" t="n">
         <v>41.06741071428572</v>
       </c>
-      <c r="AU125" t="n">
+      <c r="AV125" t="n">
+        <v>24.35020817253862</v>
+      </c>
+      <c r="AW125" t="n">
         <v>0.5998809169395655</v>
       </c>
-      <c r="AV125" t="n">
+      <c r="AX125" t="n">
         <v>38.4857211629195</v>
       </c>
-      <c r="AW125" t="n">
+      <c r="AY125" t="n">
         <v>-0.9985683607730851</v>
       </c>
-      <c r="AX125" t="n">
+      <c r="AZ125" t="n">
         <v>0.307205325190028</v>
       </c>
-      <c r="AY125" t="n">
+      <c r="BA125" t="n">
         <v>11.82301848502743</v>
       </c>
     </row>
@@ -19051,21 +19805,27 @@
         <v>0.523</v>
       </c>
       <c r="AT126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU126" t="n">
         <v>37.32312049433573</v>
       </c>
-      <c r="AU126" t="n">
+      <c r="AV126" t="n">
+        <v>26.79304374219629</v>
+      </c>
+      <c r="AW126" t="n">
         <v>0.5242528172464478</v>
       </c>
-      <c r="AV126" t="n">
+      <c r="AX126" t="n">
         <v>38.02881287743782</v>
       </c>
-      <c r="AW126" t="n">
+      <c r="AY126" t="n">
         <v>-0.8554932365555923</v>
       </c>
-      <c r="AX126" t="n">
+      <c r="AZ126" t="n">
         <v>0.3403595277379776</v>
       </c>
-      <c r="AY126" t="n">
+      <c r="BA126" t="n">
         <v>12.94346879140066</v>
       </c>
     </row>
@@ -19212,21 +19972,27 @@
         <v>0.523</v>
       </c>
       <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="n">
         <v>36.17970168612192</v>
       </c>
-      <c r="AU127" t="n">
+      <c r="AV127" t="n">
+        <v>27.63980777607096</v>
+      </c>
+      <c r="AW127" t="n">
         <v>0.5462036492054149</v>
       </c>
-      <c r="AV127" t="n">
+      <c r="AX127" t="n">
         <v>42.69161633319679</v>
       </c>
-      <c r="AW127" t="n">
+      <c r="AY127" t="n">
         <v>-0.8341742347796839</v>
       </c>
-      <c r="AX127" t="n">
+      <c r="AZ127" t="n">
         <v>0.3160063990834164</v>
       </c>
-      <c r="AY127" t="n">
+      <c r="BA127" t="n">
         <v>13.49082394850428</v>
       </c>
     </row>
@@ -19373,21 +20139,27 @@
         <v>0.523</v>
       </c>
       <c r="AT128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU128" t="n">
         <v>32.91402805611222</v>
       </c>
-      <c r="AU128" t="n">
+      <c r="AV128" t="n">
+        <v>30.38218228091646</v>
+      </c>
+      <c r="AW128" t="n">
         <v>0.5709372312983663</v>
       </c>
-      <c r="AV128" t="n">
+      <c r="AX128" t="n">
         <v>42.92451945516472</v>
       </c>
-      <c r="AW128" t="n">
+      <c r="AY128" t="n">
         <v>-0.8899897505978819</v>
       </c>
-      <c r="AX128" t="n">
+      <c r="AZ128" t="n">
         <v>0.3483273407058165</v>
       </c>
-      <c r="AY128" t="n">
+      <c r="BA128" t="n">
         <v>14.95178371289261</v>
       </c>
     </row>
@@ -19534,21 +20306,27 @@
         <v>0.523</v>
       </c>
       <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="n">
         <v>31.10285451197053</v>
       </c>
-      <c r="AU129" t="n">
+      <c r="AV129" t="n">
+        <v>32.1513898222792</v>
+      </c>
+      <c r="AW129" t="n">
         <v>0.5543701272055807</v>
       </c>
-      <c r="AV129" t="n">
+      <c r="AX129" t="n">
         <v>40.16479905872414</v>
       </c>
-      <c r="AW129" t="n">
+      <c r="AY129" t="n">
         <v>-0.9594183293878932</v>
       </c>
-      <c r="AX129" t="n">
+      <c r="AZ129" t="n">
         <v>0.3335399262952408</v>
       </c>
-      <c r="AY129" t="n">
+      <c r="BA129" t="n">
         <v>13.39656411771</v>
       </c>
     </row>
@@ -19695,21 +20473,27 @@
         <v>0.717</v>
       </c>
       <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="n">
         <v>30.39869888475836</v>
       </c>
-      <c r="AU130" t="n">
+      <c r="AV130" t="n">
+        <v>32.89614479195329</v>
+      </c>
+      <c r="AW130" t="n">
         <v>0.5485314685314685</v>
       </c>
-      <c r="AV130" t="n">
+      <c r="AX130" t="n">
         <v>54.14554217891045</v>
       </c>
-      <c r="AW130" t="n">
+      <c r="AY130" t="n">
         <v>-0.8095535435529191</v>
       </c>
-      <c r="AX130" t="n">
+      <c r="AZ130" t="n">
         <v>0.2816077793273518</v>
       </c>
-      <c r="AY130" t="n">
+      <c r="BA130" t="n">
         <v>15.24780589347843</v>
       </c>
     </row>
@@ -19856,21 +20640,27 @@
         <v>0.717</v>
       </c>
       <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="n">
         <v>37.48323197219809</v>
       </c>
-      <c r="AU131" t="n">
+      <c r="AV131" t="n">
+        <v>26.67859593168796</v>
+      </c>
+      <c r="AW131" t="n">
         <v>0.5674558436677941</v>
       </c>
-      <c r="AV131" t="n">
+      <c r="AX131" t="n">
         <v>54.14554217891045</v>
       </c>
-      <c r="AW131" t="n">
+      <c r="AY131" t="n">
         <v>-0.8061192631907587</v>
       </c>
-      <c r="AX131" t="n">
+      <c r="AZ131" t="n">
         <v>0.2283823895902871</v>
       </c>
-      <c r="AY131" t="n">
+      <c r="BA131" t="n">
         <v>12.36588830848125</v>
       </c>
     </row>
@@ -20017,21 +20807,27 @@
         <v>0.523</v>
       </c>
       <c r="AT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU132" t="n">
         <v>32.09768</v>
       </c>
-      <c r="AU132" t="n">
+      <c r="AV132" t="n">
+        <v>31.1548996687611</v>
+      </c>
+      <c r="AW132" t="n">
         <v>0.491869918699187</v>
       </c>
-      <c r="AV132" t="n">
+      <c r="AX132" t="n">
         <v>34.63030631687734</v>
       </c>
-      <c r="AW132" t="n">
+      <c r="AY132" t="n">
         <v>-0.9432647644326476</v>
       </c>
-      <c r="AX132" t="n">
+      <c r="AZ132" t="n">
         <v>0.4425021074703185</v>
       </c>
-      <c r="AY132" t="n">
+      <c r="BA132" t="n">
         <v>15.32398352756091</v>
       </c>
     </row>
@@ -20178,21 +20974,27 @@
         <v>0.523</v>
       </c>
       <c r="AT133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU133" t="n">
         <v>32.09768</v>
       </c>
-      <c r="AU133" t="n">
+      <c r="AV133" t="n">
+        <v>31.1548996687611</v>
+      </c>
+      <c r="AW133" t="n">
         <v>0.491869918699187</v>
       </c>
-      <c r="AV133" t="n">
+      <c r="AX133" t="n">
         <v>44.89996935838486</v>
       </c>
-      <c r="AW133" t="n">
+      <c r="AY133" t="n">
         <v>-0.9047947568126941</v>
       </c>
-      <c r="AX133" t="n">
+      <c r="AZ133" t="n">
         <v>0.3424239972728017</v>
       </c>
-      <c r="AY133" t="n">
+      <c r="BA133" t="n">
         <v>15.37482698512445</v>
       </c>
     </row>
@@ -20339,21 +21141,27 @@
         <v>0.523</v>
       </c>
       <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="n">
         <v>39.16065382370111</v>
       </c>
-      <c r="AU134" t="n">
+      <c r="AV134" t="n">
+        <v>25.53583513957503</v>
+      </c>
+      <c r="AW134" t="n">
         <v>0.5946521533364885</v>
       </c>
-      <c r="AV134" t="n">
+      <c r="AX134" t="n">
         <v>43.93419906095097</v>
       </c>
-      <c r="AW134" t="n">
+      <c r="AY134" t="n">
         <v>-0.925575101488498</v>
       </c>
-      <c r="AX134" t="n">
+      <c r="AZ134" t="n">
         <v>0.2877727947098655</v>
       </c>
-      <c r="AY134" t="n">
+      <c r="BA134" t="n">
         <v>12.64306724710941</v>
       </c>
     </row>
@@ -20500,21 +21308,27 @@
         <v>0.717</v>
       </c>
       <c r="AT135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU135" t="n">
         <v>32.11846846846846</v>
       </c>
-      <c r="AU135" t="n">
+      <c r="AV135" t="n">
+        <v>31.13473486389072</v>
+      </c>
+      <c r="AW135" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AV135" t="n">
+      <c r="AX135" t="n">
         <v>62.73974732172039</v>
       </c>
-      <c r="AW135" t="n">
+      <c r="AY135" t="n">
         <v>-0.8729547641963427</v>
       </c>
-      <c r="AX135" t="n">
+      <c r="AZ135" t="n">
         <v>0.2286543990281047</v>
       </c>
-      <c r="AY135" t="n">
+      <c r="BA135" t="n">
         <v>14.34571921902312</v>
       </c>
     </row>
@@ -20661,21 +21475,27 @@
         <v>0.523</v>
       </c>
       <c r="AT136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU136" t="n">
         <v>38.09801840056618</v>
       </c>
-      <c r="AU136" t="n">
+      <c r="AV136" t="n">
+        <v>26.24808433567083</v>
+      </c>
+      <c r="AW136" t="n">
         <v>0.5716883904213398</v>
       </c>
-      <c r="AV136" t="n">
+      <c r="AX136" t="n">
         <v>56.82593529734338</v>
       </c>
-      <c r="AW136" t="n">
+      <c r="AY136" t="n">
         <v>-0.8111718275652702</v>
       </c>
-      <c r="AX136" t="n">
+      <c r="AZ136" t="n">
         <v>0.212522899192218</v>
       </c>
-      <c r="AY136" t="n">
+      <c r="BA136" t="n">
         <v>12.07681251870081</v>
       </c>
     </row>
@@ -20822,21 +21642,27 @@
         <v>0.717</v>
       </c>
       <c r="AT137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU137" t="n">
         <v>37.71034928848641</v>
       </c>
-      <c r="AU137" t="n">
+      <c r="AV137" t="n">
+        <v>26.5179193210315</v>
+      </c>
+      <c r="AW137" t="n">
         <v>0.5222496909765142</v>
       </c>
-      <c r="AV137" t="n">
+      <c r="AX137" t="n">
         <v>51.97156457320585</v>
       </c>
-      <c r="AW137" t="n">
+      <c r="AY137" t="n">
         <v>-0.9191253037139883</v>
       </c>
-      <c r="AX137" t="n">
+      <c r="AZ137" t="n">
         <v>0.2487492359828174</v>
       </c>
-      <c r="AY137" t="n">
+      <c r="BA137" t="n">
         <v>12.92788698041661</v>
       </c>
     </row>
@@ -20983,21 +21809,27 @@
         <v>0.523</v>
       </c>
       <c r="AT138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU138" t="n">
         <v>39.72764811490126</v>
       </c>
-      <c r="AU138" t="n">
+      <c r="AV138" t="n">
+        <v>25.17138686659165</v>
+      </c>
+      <c r="AW138" t="n">
         <v>0.5884236453201971</v>
       </c>
-      <c r="AV138" t="n">
+      <c r="AX138" t="n">
         <v>34.71279366258031</v>
       </c>
-      <c r="AW138" t="n">
+      <c r="AY138" t="n">
         <v>-0.983991462113127</v>
       </c>
-      <c r="AX138" t="n">
+      <c r="AZ138" t="n">
         <v>0.3634267201648407</v>
       </c>
-      <c r="AY138" t="n">
+      <c r="BA138" t="n">
         <v>12.61555674855043</v>
       </c>
     </row>
@@ -21144,21 +21976,27 @@
         <v>0.717</v>
       </c>
       <c r="AT139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU139" t="n">
         <v>33.31036454610436</v>
       </c>
-      <c r="AU139" t="n">
+      <c r="AV139" t="n">
+        <v>30.02068616258809</v>
+      </c>
+      <c r="AW139" t="n">
         <v>0.5165860400829302</v>
       </c>
-      <c r="AV139" t="n">
+      <c r="AX139" t="n">
         <v>16.82978356315537</v>
       </c>
-      <c r="AW139" t="n">
+      <c r="AY139" t="n">
         <v>-0.8676616915422886</v>
       </c>
-      <c r="AX139" t="n">
+      <c r="AZ139" t="n">
         <v>0.887896060770315</v>
       </c>
-      <c r="AY139" t="n">
+      <c r="BA139" t="n">
         <v>14.94309852934265</v>
       </c>
     </row>
@@ -21305,21 +22143,27 @@
         <v>0.717</v>
       </c>
       <c r="AT140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU140" t="n">
         <v>34.7460815047022</v>
       </c>
-      <c r="AU140" t="n">
+      <c r="AV140" t="n">
+        <v>28.78022374594009</v>
+      </c>
+      <c r="AW140" t="n">
         <v>0.5231689088191331</v>
       </c>
-      <c r="AV140" t="n">
+      <c r="AX140" t="n">
         <v>48.86662529556703</v>
       </c>
-      <c r="AW140" t="n">
+      <c r="AY140" t="n">
         <v>-0.9794520547945206</v>
       </c>
-      <c r="AX140" t="n">
+      <c r="AZ140" t="n">
         <v>0.2763025421902743</v>
       </c>
-      <c r="AY140" t="n">
+      <c r="BA140" t="n">
         <v>13.50197279742473</v>
       </c>
     </row>
@@ -21466,21 +22310,27 @@
         <v>0.717</v>
       </c>
       <c r="AT141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU141" t="n">
         <v>31.98261633011413</v>
       </c>
-      <c r="AU141" t="n">
+      <c r="AV141" t="n">
+        <v>31.26698546730281</v>
+      </c>
+      <c r="AW141" t="n">
         <v>0.4660103141115798</v>
       </c>
-      <c r="AV141" t="n">
+      <c r="AX141" t="n">
         <v>48.48989580379418</v>
       </c>
-      <c r="AW141" t="n">
+      <c r="AY141" t="n">
         <v>-0.8755935422602089</v>
       </c>
-      <c r="AX141" t="n">
+      <c r="AZ141" t="n">
         <v>0.3071371534917146</v>
       </c>
-      <c r="AY141" t="n">
+      <c r="BA141" t="n">
         <v>14.89304857028718</v>
       </c>
     </row>
@@ -21627,21 +22477,27 @@
         <v>0.717</v>
       </c>
       <c r="AT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" t="n">
         <v>38.49102196752626</v>
       </c>
-      <c r="AU142" t="n">
+      <c r="AV142" t="n">
+        <v>25.98008441666398</v>
+      </c>
+      <c r="AW142" t="n">
         <v>0.526886579304112</v>
       </c>
-      <c r="AV142" t="n">
+      <c r="AX142" t="n">
         <v>52.45513538310598</v>
       </c>
-      <c r="AW142" t="n">
+      <c r="AY142" t="n">
         <v>-0.8558154437680231</v>
       </c>
-      <c r="AX142" t="n">
+      <c r="AZ142" t="n">
         <v>0.2351665444744986</v>
       </c>
-      <c r="AY142" t="n">
+      <c r="BA142" t="n">
         <v>12.33569292798704</v>
       </c>
     </row>
@@ -21788,21 +22644,27 @@
         <v>0.717</v>
       </c>
       <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="n">
         <v>35.47107516650809</v>
       </c>
-      <c r="AU143" t="n">
+      <c r="AV143" t="n">
+        <v>28.19198446356099</v>
+      </c>
+      <c r="AW143" t="n">
         <v>0.5007125890736343</v>
       </c>
-      <c r="AV143" t="n">
+      <c r="AX143" t="n">
         <v>50.12173210626537</v>
       </c>
-      <c r="AW143" t="n">
+      <c r="AY143" t="n">
         <v>-0.910299003322259</v>
       </c>
-      <c r="AX143" t="n">
+      <c r="AZ143" t="n">
         <v>0.2634069568539765</v>
       </c>
-      <c r="AY143" t="n">
+      <c r="BA143" t="n">
         <v>13.20241292636161</v>
       </c>
     </row>
@@ -21949,21 +22811,27 @@
         <v>0.717</v>
       </c>
       <c r="AT144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU144" t="n">
         <v>32.22464912280702</v>
       </c>
-      <c r="AU144" t="n">
+      <c r="AV144" t="n">
+        <v>31.03214549176423</v>
+      </c>
+      <c r="AW144" t="n">
         <v>0.474896361123906</v>
       </c>
-      <c r="AV144" t="n">
+      <c r="AX144" t="n">
         <v>51.64905585832408</v>
       </c>
-      <c r="AW144" t="n">
+      <c r="AY144" t="n">
         <v>-0.8479307025986524</v>
       </c>
-      <c r="AX144" t="n">
+      <c r="AZ144" t="n">
         <v>0.2850083474322018</v>
       </c>
-      <c r="AY144" t="n">
+      <c r="BA144" t="n">
         <v>14.72041205661443</v>
       </c>
     </row>
@@ -22110,21 +22978,27 @@
         <v>0.717</v>
       </c>
       <c r="AT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" t="n">
         <v>33.99637952559301</v>
       </c>
-      <c r="AU145" t="n">
+      <c r="AV145" t="n">
+        <v>29.41489693769256</v>
+      </c>
+      <c r="AW145" t="n">
         <v>0.5288235294117647</v>
       </c>
-      <c r="AV145" t="n">
+      <c r="AX145" t="n">
         <v>40.84573233660999</v>
       </c>
-      <c r="AW145" t="n">
+      <c r="AY145" t="n">
         <v>-0.9031939413895291</v>
       </c>
-      <c r="AX145" t="n">
+      <c r="AZ145" t="n">
         <v>0.3306302943724049</v>
       </c>
-      <c r="AY145" t="n">
+      <c r="BA145" t="n">
         <v>13.50483650630982</v>
       </c>
     </row>
@@ -22271,21 +23145,27 @@
         <v>0.523</v>
       </c>
       <c r="AT146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU146" t="n">
         <v>33.4044665012407</v>
       </c>
-      <c r="AU146" t="n">
+      <c r="AV146" t="n">
+        <v>29.93611647600654</v>
+      </c>
+      <c r="AW146" t="n">
         <v>0.4903035413153457</v>
       </c>
-      <c r="AV146" t="n">
+      <c r="AX146" t="n">
         <v>37.41961875184389</v>
       </c>
-      <c r="AW146" t="n">
+      <c r="AY146" t="n">
         <v>-0.8867924528301887</v>
       </c>
-      <c r="AX146" t="n">
+      <c r="AZ146" t="n">
         <v>0.3753925003975221</v>
       </c>
-      <c r="AY146" t="n">
+      <c r="BA146" t="n">
         <v>14.04704424717668</v>
       </c>
     </row>
@@ -22432,21 +23312,27 @@
         <v>0.717</v>
       </c>
       <c r="AT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" t="n">
         <v>37.73743016759776</v>
       </c>
-      <c r="AU147" t="n">
+      <c r="AV147" t="n">
+        <v>26.49888971132494</v>
+      </c>
+      <c r="AW147" t="n">
         <v>0.4713526284701713</v>
       </c>
-      <c r="AV147" t="n">
+      <c r="AX147" t="n">
         <v>44.98594091218243</v>
       </c>
-      <c r="AW147" t="n">
+      <c r="AY147" t="n">
         <v>-0.9927797833935018</v>
       </c>
-      <c r="AX147" t="n">
+      <c r="AZ147" t="n">
         <v>0.275498874631122</v>
       </c>
-      <c r="AY147" t="n">
+      <c r="BA147" t="n">
         <v>12.39357609552841</v>
       </c>
     </row>
@@ -22593,21 +23479,27 @@
         <v>0.717</v>
       </c>
       <c r="AT148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU148" t="n">
         <v>37.00026553372279</v>
       </c>
-      <c r="AU148" t="n">
+      <c r="AV148" t="n">
+        <v>27.02683306660542</v>
+      </c>
+      <c r="AW148" t="n">
         <v>0.5766636690647482</v>
       </c>
-      <c r="AV148" t="n">
+      <c r="AX148" t="n">
         <v>62.3287590104805</v>
       </c>
-      <c r="AW148" t="n">
+      <c r="AY148" t="n">
         <v>-0.8752424046541692</v>
       </c>
-      <c r="AX148" t="n">
+      <c r="AZ148" t="n">
         <v>0.204352754630459</v>
       </c>
-      <c r="AY148" t="n">
+      <c r="BA148" t="n">
         <v>12.73705359648974</v>
       </c>
     </row>
@@ -22754,21 +23646,27 @@
         <v>0.717</v>
       </c>
       <c r="AT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU149" t="n">
         <v>45.65359911406424</v>
       </c>
-      <c r="AU149" t="n">
+      <c r="AV149" t="n">
+        <v>21.90407808815967</v>
+      </c>
+      <c r="AW149" t="n">
         <v>0.5908473040326235</v>
       </c>
-      <c r="AV149" t="n">
+      <c r="AX149" t="n">
         <v>63.04106431069755</v>
       </c>
-      <c r="AW149" t="n">
+      <c r="AY149" t="n">
         <v>-0.9457209457209457</v>
       </c>
-      <c r="AX149" t="n">
+      <c r="AZ149" t="n">
         <v>0.1613708822578354</v>
       </c>
-      <c r="AY149" t="n">
+      <c r="BA149" t="n">
         <v>10.17299216629021</v>
       </c>
     </row>
@@ -22915,21 +23813,27 @@
         <v>0.717</v>
       </c>
       <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="n">
         <v>31.62051282051283</v>
       </c>
-      <c r="AU150" t="n">
+      <c r="AV150" t="n">
+        <v>31.62504054492377</v>
+      </c>
+      <c r="AW150" t="n">
         <v>0.4886769964243147</v>
       </c>
-      <c r="AV150" t="n">
+      <c r="AX150" t="n">
         <v>55.56667726163774</v>
       </c>
-      <c r="AW150" t="n">
+      <c r="AY150" t="n">
         <v>-0.8900032351989647</v>
       </c>
-      <c r="AX150" t="n">
+      <c r="AZ150" t="n">
         <v>0.2776338886342699</v>
       </c>
-      <c r="AY150" t="n">
+      <c r="BA150" t="n">
         <v>15.42719268663395</v>
       </c>
     </row>
@@ -23076,21 +23980,27 @@
         <v>0.717</v>
       </c>
       <c r="AT151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU151" t="n">
         <v>38.07644376899696</v>
       </c>
-      <c r="AU151" t="n">
+      <c r="AV151" t="n">
+        <v>26.26295685770506</v>
+      </c>
+      <c r="AW151" t="n">
         <v>0.5359661495063469</v>
       </c>
-      <c r="AV151" t="n">
+      <c r="AX151" t="n">
         <v>61.70799806962501</v>
       </c>
-      <c r="AW151" t="n">
+      <c r="AY151" t="n">
         <v>-0.9144542772861356</v>
       </c>
-      <c r="AX151" t="n">
+      <c r="AZ151" t="n">
         <v>0.1992943083149607</v>
       </c>
-      <c r="AY151" t="n">
+      <c r="BA151" t="n">
         <v>12.29805279278685</v>
       </c>
     </row>
@@ -23237,21 +24147,27 @@
         <v>0.717</v>
       </c>
       <c r="AT152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU152" t="n">
         <v>34.4926213592233</v>
       </c>
-      <c r="AU152" t="n">
+      <c r="AV152" t="n">
+        <v>28.99170780862095</v>
+      </c>
+      <c r="AW152" t="n">
         <v>0.4950980392156862</v>
       </c>
-      <c r="AV152" t="n">
+      <c r="AX152" t="n">
         <v>47.27323855607655</v>
       </c>
-      <c r="AW152" t="n">
+      <c r="AY152" t="n">
         <v>-0.870988867059594</v>
       </c>
-      <c r="AX152" t="n">
+      <c r="AZ152" t="n">
         <v>0.2929222953305048</v>
       </c>
-      <c r="AY152" t="n">
+      <c r="BA152" t="n">
         <v>13.84738554555246</v>
       </c>
     </row>
@@ -23398,21 +24314,27 @@
         <v>0.717</v>
       </c>
       <c r="AT153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU153" t="n">
         <v>36.54322709163347</v>
       </c>
-      <c r="AU153" t="n">
+      <c r="AV153" t="n">
+        <v>27.36485197359455</v>
+      </c>
+      <c r="AW153" t="n">
         <v>0.5332403533240354</v>
       </c>
-      <c r="AV153" t="n">
+      <c r="AX153" t="n">
         <v>46.60021045219221</v>
       </c>
-      <c r="AW153" t="n">
+      <c r="AY153" t="n">
         <v>-0.9734422880490295</v>
       </c>
-      <c r="AX153" t="n">
+      <c r="AZ153" t="n">
         <v>0.278928268195533</v>
       </c>
-      <c r="AY153" t="n">
+      <c r="BA153" t="n">
         <v>12.99811599897735</v>
       </c>
     </row>
@@ -23559,21 +24481,27 @@
         <v>0.523</v>
       </c>
       <c r="AT154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU154" t="n">
         <v>36.84074074074074</v>
       </c>
-      <c r="AU154" t="n">
+      <c r="AV154" t="n">
+        <v>27.14386247109681</v>
+      </c>
+      <c r="AW154" t="n">
         <v>0.5225263157894737</v>
       </c>
-      <c r="AV154" t="n">
+      <c r="AX154" t="n">
         <v>36.4008599384631</v>
       </c>
-      <c r="AW154" t="n">
+      <c r="AY154" t="n">
         <v>-0.8216748768472907</v>
       </c>
-      <c r="AX154" t="n">
+      <c r="AZ154" t="n">
         <v>0.3594130595075935</v>
       </c>
-      <c r="AY154" t="n">
+      <c r="BA154" t="n">
         <v>13.08294443919041</v>
       </c>
     </row>
@@ -23720,21 +24648,27 @@
         <v>0.717</v>
       </c>
       <c r="AT155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU155" t="n">
         <v>36.31700201207244</v>
       </c>
-      <c r="AU155" t="n">
+      <c r="AV155" t="n">
+        <v>27.53531251471643</v>
+      </c>
+      <c r="AW155" t="n">
         <v>0.5096201282683769</v>
       </c>
-      <c r="AV155" t="n">
+      <c r="AX155" t="n">
         <v>55.60819532627404</v>
       </c>
-      <c r="AW155" t="n">
+      <c r="AY155" t="n">
         <v>-0.8612735542560104</v>
       </c>
-      <c r="AX155" t="n">
+      <c r="AZ155" t="n">
         <v>0.2320891755316213</v>
       </c>
-      <c r="AY155" t="n">
+      <c r="BA155" t="n">
         <v>12.9060602060763</v>
       </c>
     </row>
@@ -23881,21 +24815,27 @@
         <v>0.523</v>
       </c>
       <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="n">
         <v>33.07568366592757</v>
       </c>
-      <c r="AU156" t="n">
+      <c r="AV156" t="n">
+        <v>30.23369101301859</v>
+      </c>
+      <c r="AW156" t="n">
         <v>0.5494505494505494</v>
       </c>
-      <c r="AV156" t="n">
+      <c r="AX156" t="n">
         <v>43.12164298019695</v>
       </c>
-      <c r="AW156" t="n">
+      <c r="AY156" t="n">
         <v>-1.018099547511312</v>
       </c>
-      <c r="AX156" t="n">
+      <c r="AZ156" t="n">
         <v>0.3462797777914783</v>
       </c>
-      <c r="AY156" t="n">
+      <c r="BA156" t="n">
         <v>14.93215294918606</v>
       </c>
     </row>
@@ -24042,21 +24982,27 @@
         <v>0.523</v>
       </c>
       <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="n">
         <v>32.22326111744584</v>
       </c>
-      <c r="AU157" t="n">
+      <c r="AV157" t="n">
+        <v>31.03348219024904</v>
+      </c>
+      <c r="AW157" t="n">
         <v>0.4868344060854301</v>
       </c>
-      <c r="AV157" t="n">
+      <c r="AX157" t="n">
         <v>43.12164298019695</v>
       </c>
-      <c r="AW157" t="n">
+      <c r="AY157" t="n">
         <v>-1.04876299749014</v>
       </c>
-      <c r="AX157" t="n">
+      <c r="AZ157" t="n">
         <v>0.3554401383644461</v>
       </c>
-      <c r="AY157" t="n">
+      <c r="BA157" t="n">
         <v>15.32716274738345</v>
       </c>
     </row>
@@ -24203,21 +25149,27 @@
         <v>0.523</v>
       </c>
       <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="n">
         <v>36.82448866777225</v>
       </c>
-      <c r="AU158" t="n">
+      <c r="AV158" t="n">
+        <v>27.15584210881852</v>
+      </c>
+      <c r="AW158" t="n">
         <v>0.5639913232104121</v>
       </c>
-      <c r="AV158" t="n">
+      <c r="AX158" t="n">
         <v>40.64145553340282</v>
       </c>
-      <c r="AW158" t="n">
+      <c r="AY158" t="n">
         <v>-0.8695652173913042</v>
       </c>
-      <c r="AX158" t="n">
+      <c r="AZ158" t="n">
         <v>0.3274162961093018</v>
       </c>
-      <c r="AY158" t="n">
+      <c r="BA158" t="n">
         <v>13.30667483923764</v>
       </c>
     </row>
@@ -24362,19 +25314,25 @@
         <v>0.523</v>
       </c>
       <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="n">
         <v>36.82448866777225</v>
       </c>
-      <c r="AU159" t="n">
+      <c r="AV159" t="n">
+        <v>27.15584210881852</v>
+      </c>
+      <c r="AW159" t="n">
         <v>0.5639913232104121</v>
       </c>
-      <c r="AV159" t="n">
+      <c r="AX159" t="n">
         <v>39.86388713858987</v>
       </c>
-      <c r="AW159" t="inlineStr"/>
-      <c r="AX159" t="n">
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="n">
         <v>0.3352256061133059</v>
       </c>
-      <c r="AY159" t="n">
+      <c r="BA159" t="n">
         <v>13.36339572806621</v>
       </c>
     </row>
@@ -24519,19 +25477,25 @@
         <v>0.717</v>
       </c>
       <c r="AT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" t="n">
         <v>37.93288288288289</v>
       </c>
-      <c r="AU160" t="n">
+      <c r="AV160" t="n">
+        <v>26.36235171177162</v>
+      </c>
+      <c r="AW160" t="n">
         <v>0.5806799784133837</v>
       </c>
-      <c r="AV160" t="n">
+      <c r="AX160" t="n">
         <v>50.48954256485062</v>
       </c>
-      <c r="AW160" t="inlineStr"/>
-      <c r="AX160" t="n">
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="n">
         <v>0.2434472726667247</v>
       </c>
-      <c r="AY160" t="n">
+      <c r="BA160" t="n">
         <v>12.29154143560339</v>
       </c>
     </row>
@@ -24678,21 +25642,27 @@
         <v>0.717</v>
       </c>
       <c r="AT161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU161" t="n">
         <v>39.81607142857143</v>
       </c>
-      <c r="AU161" t="n">
+      <c r="AV161" t="n">
+        <v>25.11548638830336</v>
+      </c>
+      <c r="AW161" t="n">
         <v>0.5831663326653306</v>
       </c>
-      <c r="AV161" t="n">
+      <c r="AX161" t="n">
         <v>53.08725031617568</v>
       </c>
-      <c r="AW161" t="n">
+      <c r="AY161" t="n">
         <v>-0.9148648648648647</v>
       </c>
-      <c r="AX161" t="n">
+      <c r="AZ161" t="n">
         <v>0.2193729066609965</v>
       </c>
-      <c r="AY161" t="n">
+      <c r="BA161" t="n">
         <v>11.64590440849937</v>
       </c>
     </row>
@@ -24839,21 +25809,27 @@
         <v>0.717</v>
       </c>
       <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="n">
         <v>38.9956570155902</v>
       </c>
-      <c r="AU162" t="n">
+      <c r="AV162" t="n">
+        <v>25.64388130709547</v>
+      </c>
+      <c r="AW162" t="n">
         <v>0.5505505505505506</v>
       </c>
-      <c r="AV162" t="n">
+      <c r="AX162" t="n">
         <v>45.2001414226272</v>
       </c>
-      <c r="AW162" t="n">
+      <c r="AY162" t="n">
         <v>-0.875</v>
       </c>
-      <c r="AX162" t="n">
+      <c r="AZ162" t="n">
         <v>0.2693134402703707</v>
       </c>
-      <c r="AY162" t="n">
+      <c r="BA162" t="n">
         <v>12.17300558723502</v>
       </c>
     </row>
@@ -25000,21 +25976,27 @@
         <v>0.717</v>
       </c>
       <c r="AT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU163" t="n">
         <v>35.01108280254777</v>
       </c>
-      <c r="AU163" t="n">
+      <c r="AV163" t="n">
+        <v>28.56238424957338</v>
+      </c>
+      <c r="AW163" t="n">
         <v>0.5213414634146342</v>
       </c>
-      <c r="AV163" t="n">
+      <c r="AX163" t="n">
         <v>48.16685335643782</v>
       </c>
-      <c r="AW163" t="n">
+      <c r="AY163" t="n">
         <v>-0.9019350606756315</v>
       </c>
-      <c r="AX163" t="n">
+      <c r="AZ163" t="n">
         <v>0.2786500146224659</v>
       </c>
-      <c r="AY163" t="n">
+      <c r="BA163" t="n">
         <v>13.42169439208957</v>
       </c>
     </row>
@@ -25161,21 +26143,27 @@
         <v>0.523</v>
       </c>
       <c r="AT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU164" t="n">
         <v>35.7625352112676</v>
       </c>
-      <c r="AU164" t="n">
+      <c r="AV164" t="n">
+        <v>27.96222342998023</v>
+      </c>
+      <c r="AW164" t="n">
         <v>0.5279255319148936</v>
       </c>
-      <c r="AV164" t="n">
+      <c r="AX164" t="n">
         <v>42.61425540516829</v>
       </c>
-      <c r="AW164" t="n">
+      <c r="AY164" t="n">
         <v>-0.8602257636122178</v>
       </c>
-      <c r="AX164" t="n">
+      <c r="AZ164" t="n">
         <v>0.3302696303234725</v>
       </c>
-      <c r="AY164" t="n">
+      <c r="BA164" t="n">
         <v>14.07419437917497</v>
       </c>
     </row>
@@ -25322,21 +26310,27 @@
         <v>0.523</v>
       </c>
       <c r="AT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" t="n">
         <v>36.05222437137331</v>
       </c>
-      <c r="AU165" t="n">
+      <c r="AV165" t="n">
+        <v>27.73753956757337</v>
+      </c>
+      <c r="AW165" t="n">
         <v>0.5409884581237053</v>
       </c>
-      <c r="AV165" t="n">
+      <c r="AX165" t="n">
         <v>42.46993249100026</v>
       </c>
-      <c r="AW165" t="n">
+      <c r="AY165" t="n">
         <v>-0.8340425531914893</v>
       </c>
-      <c r="AX165" t="n">
+      <c r="AZ165" t="n">
         <v>0.3140509103601919</v>
       </c>
-      <c r="AY165" t="n">
+      <c r="BA165" t="n">
         <v>13.33772096173453</v>
       </c>
     </row>
@@ -25483,21 +26477,27 @@
         <v>0.523</v>
       </c>
       <c r="AT166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU166" t="n">
         <v>29.2687074829932</v>
       </c>
-      <c r="AU166" t="n">
+      <c r="AV166" t="n">
+        <v>34.16618245206275</v>
+      </c>
+      <c r="AW166" t="n">
         <v>0.5394736842105263</v>
       </c>
-      <c r="AV166" t="n">
+      <c r="AX166" t="n">
         <v>38.40701417106357</v>
       </c>
-      <c r="AW166" t="n">
+      <c r="AY166" t="n">
         <v>-0.9123961218836566</v>
       </c>
-      <c r="AX166" t="n">
+      <c r="AZ166" t="n">
         <v>0.4419867263324095</v>
       </c>
-      <c r="AY166" t="n">
+      <c r="BA166" t="n">
         <v>16.97539046167085</v>
       </c>
     </row>
@@ -25644,21 +26644,27 @@
         <v>0.523</v>
       </c>
       <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="n">
         <v>40.31574858757062</v>
       </c>
-      <c r="AU167" t="n">
+      <c r="AV167" t="n">
+        <v>24.80420270078529</v>
+      </c>
+      <c r="AW167" t="n">
         <v>0.6319209773849753</v>
       </c>
-      <c r="AV167" t="n">
+      <c r="AX167" t="n">
         <v>41.27967137504851</v>
       </c>
-      <c r="AW167" t="n">
+      <c r="AY167" t="n">
         <v>-0.9287135278514589</v>
       </c>
-      <c r="AX167" t="n">
+      <c r="AZ167" t="n">
         <v>0.2822534280040117</v>
       </c>
-      <c r="AY167" t="n">
+      <c r="BA167" t="n">
         <v>11.65132875248652</v>
       </c>
     </row>
@@ -25805,21 +26811,27 @@
         <v>0.523</v>
       </c>
       <c r="AT168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU168" t="n">
         <v>32.95561719833564</v>
       </c>
-      <c r="AU168" t="n">
+      <c r="AV168" t="n">
+        <v>30.34384074744329</v>
+      </c>
+      <c r="AW168" t="n">
         <v>0.4881079162229322</v>
       </c>
-      <c r="AV168" t="n">
+      <c r="AX168" t="n">
         <v>40.6374878617617</v>
       </c>
-      <c r="AW168" t="n">
+      <c r="AY168" t="n">
         <v>-0.794580970384373</v>
       </c>
-      <c r="AX168" t="n">
+      <c r="AZ168" t="n">
         <v>0.3720589980627997</v>
       </c>
-      <c r="AY168" t="n">
+      <c r="BA168" t="n">
         <v>15.11954301763624</v>
       </c>
     </row>
@@ -25966,21 +26978,27 @@
         <v>0.523</v>
       </c>
       <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="n">
         <v>37.79894273127753</v>
       </c>
-      <c r="AU169" t="n">
+      <c r="AV169" t="n">
+        <v>26.45576642471877</v>
+      </c>
+      <c r="AW169" t="n">
         <v>0.554552590266876</v>
       </c>
-      <c r="AV169" t="n">
+      <c r="AX169" t="n">
         <v>38.08684472600527</v>
       </c>
-      <c r="AW169" t="n">
+      <c r="AY169" t="n">
         <v>-0.8666886109282422</v>
       </c>
-      <c r="AX169" t="n">
+      <c r="AZ169" t="n">
         <v>0.3370510290002701</v>
       </c>
-      <c r="AY169" t="n">
+      <c r="BA169" t="n">
         <v>12.83721020627359</v>
       </c>
     </row>
@@ -26127,21 +27145,27 @@
         <v>0.523</v>
       </c>
       <c r="AT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU170" t="n">
         <v>31.78387096774194</v>
       </c>
-      <c r="AU170" t="n">
+      <c r="AV170" t="n">
+        <v>31.46249873135085</v>
+      </c>
+      <c r="AW170" t="n">
         <v>0.5653791130185981</v>
       </c>
-      <c r="AV170" t="n">
+      <c r="AX170" t="n">
         <v>43.33108356621307</v>
       </c>
-      <c r="AW170" t="n">
+      <c r="AY170" t="n">
         <v>-0.8734652114597544</v>
       </c>
-      <c r="AX170" t="n">
+      <c r="AZ170" t="n">
         <v>0.3618600999053327</v>
       </c>
-      <c r="AY170" t="n">
+      <c r="BA170" t="n">
         <v>15.67979022827618</v>
       </c>
     </row>
@@ -26288,21 +27312,27 @@
         <v>0.523</v>
       </c>
       <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="n">
         <v>41.63273092369477</v>
       </c>
-      <c r="AU171" t="n">
+      <c r="AV171" t="n">
+        <v>24.01956292112612</v>
+      </c>
+      <c r="AW171" t="n">
         <v>0.6081825334382376</v>
       </c>
-      <c r="AV171" t="n">
+      <c r="AX171" t="n">
         <v>45.59782712484886</v>
       </c>
-      <c r="AW171" t="n">
+      <c r="AY171" t="n">
         <v>-0.9163306451612903</v>
       </c>
-      <c r="AX171" t="n">
+      <c r="AZ171" t="n">
         <v>0.254785183807967</v>
       </c>
-      <c r="AY171" t="n">
+      <c r="BA171" t="n">
         <v>11.61765076524852</v>
       </c>
     </row>
@@ -26449,21 +27479,27 @@
         <v>0.717</v>
       </c>
       <c r="AT172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU172" t="n">
         <v>32.12362911266202</v>
       </c>
-      <c r="AU172" t="n">
+      <c r="AV172" t="n">
+        <v>31.12973308504035</v>
+      </c>
+      <c r="AW172" t="n">
         <v>0.5760777683854608</v>
       </c>
-      <c r="AV172" t="n">
+      <c r="AX172" t="n">
         <v>46.08862851636469</v>
       </c>
-      <c r="AW172" t="n">
+      <c r="AY172" t="n">
         <v>-0.8450749123366273</v>
       </c>
-      <c r="AX172" t="n">
+      <c r="AZ172" t="n">
         <v>0.3188696860136649</v>
       </c>
-      <c r="AY172" t="n">
+      <c r="BA172" t="n">
         <v>14.69626650381366</v>
       </c>
     </row>
@@ -26610,21 +27646,27 @@
         <v>0.523</v>
       </c>
       <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU173" t="n">
         <v>39.07777777777778</v>
       </c>
-      <c r="AU173" t="n">
+      <c r="AV173" t="n">
+        <v>25.58999147000285</v>
+      </c>
+      <c r="AW173" t="n">
         <v>0.5766246362754607</v>
       </c>
-      <c r="AV173" t="n">
+      <c r="AX173" t="n">
         <v>31.20218338168698</v>
       </c>
-      <c r="AW173" t="n">
+      <c r="AY173" t="n">
         <v>-0.8522613065326633</v>
       </c>
-      <c r="AX173" t="n">
+      <c r="AZ173" t="n">
         <v>0.399707243754127</v>
       </c>
-      <c r="AY173" t="n">
+      <c r="BA173" t="n">
         <v>12.47173871860493</v>
       </c>
     </row>
@@ -26771,21 +27813,27 @@
         <v>0.523</v>
       </c>
       <c r="AT174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU174" t="n">
         <v>34.49588744588745</v>
       </c>
-      <c r="AU174" t="n">
+      <c r="AV174" t="n">
+        <v>28.98896286024434</v>
+      </c>
+      <c r="AW174" t="n">
         <v>0.5402985074626866</v>
       </c>
-      <c r="AV174" t="n">
+      <c r="AX174" t="n">
         <v>37.47652040214079</v>
       </c>
-      <c r="AW174" t="n">
+      <c r="AY174" t="n">
         <v>-0.9190476190476191</v>
       </c>
-      <c r="AX174" t="n">
+      <c r="AZ174" t="n">
         <v>0.3801718619146223</v>
       </c>
-      <c r="AY174" t="n">
+      <c r="BA174" t="n">
         <v>14.2475185393632</v>
       </c>
     </row>
@@ -26932,21 +27980,27 @@
         <v>0.523</v>
       </c>
       <c r="AT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU175" t="n">
         <v>43.50616113744076</v>
       </c>
-      <c r="AU175" t="n">
+      <c r="AV175" t="n">
+        <v>22.98525022331641</v>
+      </c>
+      <c r="AW175" t="n">
         <v>0.6444219750589821</v>
       </c>
-      <c r="AV175" t="n">
+      <c r="AX175" t="n">
         <v>45.90057484261069</v>
       </c>
-      <c r="AW175" t="n">
+      <c r="AY175" t="n">
         <v>-0.8253346392425727</v>
       </c>
-      <c r="AX175" t="n">
+      <c r="AZ175" t="n">
         <v>0.2470312536106503</v>
       </c>
-      <c r="AY175" t="n">
+      <c r="BA175" t="n">
         <v>11.3388765448196</v>
       </c>
     </row>
@@ -27093,21 +28147,27 @@
         <v>0.717</v>
       </c>
       <c r="AT176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU176" t="n">
         <v>41.68621562952244</v>
       </c>
-      <c r="AU176" t="n">
+      <c r="AV176" t="n">
+        <v>23.98874507792436</v>
+      </c>
+      <c r="AW176" t="n">
         <v>0.5922100914724108</v>
       </c>
-      <c r="AV176" t="n">
+      <c r="AX176" t="n">
         <v>47.40155652187085</v>
       </c>
-      <c r="AW176" t="n">
+      <c r="AY176" t="n">
         <v>-0.8593242365172189</v>
       </c>
-      <c r="AX176" t="n">
+      <c r="AZ176" t="n">
         <v>0.2303895675632164</v>
       </c>
-      <c r="AY176" t="n">
+      <c r="BA176" t="n">
         <v>10.92082410889718</v>
       </c>
     </row>
@@ -27254,21 +28314,27 @@
         <v>0.523</v>
       </c>
       <c r="AT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU177" t="n">
         <v>35.96792650918635</v>
       </c>
-      <c r="AU177" t="n">
+      <c r="AV177" t="n">
+        <v>27.80254791013867</v>
+      </c>
+      <c r="AW177" t="n">
         <v>0.5765725716825961</v>
       </c>
-      <c r="AV177" t="n">
+      <c r="AX177" t="n">
         <v>44.74207179927146</v>
       </c>
-      <c r="AW177" t="n">
+      <c r="AY177" t="n">
         <v>-1.011280931586608</v>
       </c>
-      <c r="AX177" t="n">
+      <c r="AZ177" t="n">
         <v>0.2939442645614514</v>
       </c>
-      <c r="AY177" t="n">
+      <c r="BA177" t="n">
         <v>13.1516753899925</v>
       </c>
     </row>
@@ -27415,21 +28481,27 @@
         <v>0.717</v>
       </c>
       <c r="AT178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU178" t="n">
         <v>34.36061538461539</v>
       </c>
-      <c r="AU178" t="n">
+      <c r="AV178" t="n">
+        <v>29.10308761372591</v>
+      </c>
+      <c r="AW178" t="n">
         <v>0.5083207261724659</v>
       </c>
-      <c r="AV178" t="n">
+      <c r="AX178" t="n">
         <v>44.0343228797727</v>
       </c>
-      <c r="AW178" t="n">
+      <c r="AY178" t="n">
         <v>-0.8638230647709321</v>
       </c>
-      <c r="AX178" t="n">
+      <c r="AZ178" t="n">
         <v>0.3054467120359153</v>
       </c>
-      <c r="AY178" t="n">
+      <c r="BA178" t="n">
         <v>13.45013914035445</v>
       </c>
     </row>
@@ -27576,21 +28648,27 @@
         <v>0.717</v>
       </c>
       <c r="AT179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU179" t="n">
         <v>35.34196357878068</v>
       </c>
-      <c r="AU179" t="n">
+      <c r="AV179" t="n">
+        <v>28.29497568155495</v>
+      </c>
+      <c r="AW179" t="n">
         <v>0.5822031094938803</v>
       </c>
-      <c r="AV179" t="n">
+      <c r="AX179" t="n">
         <v>54.20072825178515</v>
       </c>
-      <c r="AW179" t="n">
+      <c r="AY179" t="n">
         <v>-0.8194444444444445</v>
       </c>
-      <c r="AX179" t="n">
+      <c r="AZ179" t="n">
         <v>0.2464363334952325</v>
       </c>
-      <c r="AY179" t="n">
+      <c r="BA179" t="n">
         <v>13.35702874314139</v>
       </c>
     </row>
@@ -27737,21 +28815,27 @@
         <v>0.523</v>
       </c>
       <c r="AT180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU180" t="n">
         <v>38.64987714987715</v>
       </c>
-      <c r="AU180" t="n">
+      <c r="AV180" t="n">
+        <v>25.87330345507136</v>
+      </c>
+      <c r="AW180" t="n">
         <v>0.5340583858042358</v>
       </c>
-      <c r="AV180" t="n">
+      <c r="AX180" t="n">
         <v>39.38800376216415</v>
       </c>
-      <c r="AW180" t="n">
+      <c r="AY180" t="n">
         <v>-0.8907371167645139</v>
       </c>
-      <c r="AX180" t="n">
+      <c r="AZ180" t="n">
         <v>0.3280651598232026</v>
       </c>
-      <c r="AY180" t="n">
+      <c r="BA180" t="n">
         <v>12.92183174935129</v>
       </c>
     </row>
@@ -27898,21 +28982,27 @@
         <v>0.717</v>
       </c>
       <c r="AT181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU181" t="n">
         <v>30.17824074074074</v>
       </c>
-      <c r="AU181" t="n">
+      <c r="AV181" t="n">
+        <v>33.13645777402777</v>
+      </c>
+      <c r="AW181" t="n">
         <v>0.4705882352941176</v>
       </c>
-      <c r="AV181" t="n">
+      <c r="AX181" t="n">
         <v>42.7829066706362</v>
       </c>
-      <c r="AW181" t="n">
+      <c r="AY181" t="n">
         <v>-0.9359058207979072</v>
       </c>
-      <c r="AX181" t="n">
+      <c r="AZ181" t="n">
         <v>0.3562090494563998</v>
       </c>
-      <c r="AY181" t="n">
+      <c r="BA181" t="n">
         <v>15.23965851812918</v>
       </c>
     </row>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA181"/>
+  <dimension ref="A1:BC181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,6 +691,16 @@
       <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Carea</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -840,6 +850,12 @@
       <c r="BA2" t="n">
         <v>6.267862957094129</v>
       </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -987,6 +1003,12 @@
       <c r="BA3" t="n">
         <v>4.931398966307422</v>
       </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1134,6 +1156,12 @@
       <c r="BA4" t="n">
         <v>6.201410491775166</v>
       </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1281,6 +1309,12 @@
       <c r="BA5" t="n">
         <v>6.803966990152447</v>
       </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1428,6 +1462,12 @@
       <c r="BA6" t="n">
         <v>5.814010355624786</v>
       </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1575,6 +1615,12 @@
       <c r="BA7" t="n">
         <v>6.393667365779264</v>
       </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1722,6 +1768,12 @@
       <c r="BA8" t="n">
         <v>6.582919875238116</v>
       </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1869,6 +1921,12 @@
       <c r="BA9" t="n">
         <v>7.04653963916366</v>
       </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -2016,6 +2074,12 @@
       <c r="BA10" t="n">
         <v>5.385976820401974</v>
       </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -2163,6 +2227,12 @@
       <c r="BA11" t="n">
         <v>6.156964889603419</v>
       </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -2310,6 +2380,12 @@
       <c r="BA12" t="n">
         <v>7.04539122144526</v>
       </c>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2457,6 +2533,12 @@
       <c r="BA13" t="n">
         <v>6.298227944361334</v>
       </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2604,6 +2686,12 @@
       <c r="BA14" t="n">
         <v>5.933547349313596</v>
       </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2751,6 +2839,12 @@
       <c r="BA15" t="n">
         <v>6.737742901484933</v>
       </c>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2898,6 +2992,12 @@
       <c r="BA16" t="n">
         <v>7.585479688556592</v>
       </c>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -3045,6 +3145,12 @@
       <c r="BA17" t="n">
         <v>5.793309073325802</v>
       </c>
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -3192,6 +3298,12 @@
       <c r="BA18" t="n">
         <v>6.418104834646514</v>
       </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -3339,6 +3451,12 @@
       <c r="BA19" t="n">
         <v>4.811120672929789</v>
       </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -3486,6 +3604,12 @@
       <c r="BA20" t="n">
         <v>6.816510648324604</v>
       </c>
+      <c r="BB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -3633,6 +3757,12 @@
       <c r="BA21" t="n">
         <v>6.269341168086865</v>
       </c>
+      <c r="BB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3780,6 +3910,12 @@
       <c r="BA22" t="n">
         <v>7.209869586996444</v>
       </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -3927,6 +4063,12 @@
       <c r="BA23" t="n">
         <v>5.8814772925756</v>
       </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -4074,6 +4216,12 @@
       <c r="BA24" t="n">
         <v>6.450269324889292</v>
       </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -4221,6 +4369,12 @@
       <c r="BA25" t="n">
         <v>5.922628309595306</v>
       </c>
+      <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -4368,6 +4522,12 @@
       <c r="BA26" t="n">
         <v>5.819873982352418</v>
       </c>
+      <c r="BB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -4515,6 +4675,12 @@
       <c r="BA27" t="n">
         <v>4.353630630525455</v>
       </c>
+      <c r="BB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -4662,6 +4828,12 @@
       <c r="BA28" t="n">
         <v>6.180318961158282</v>
       </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -4809,6 +4981,12 @@
       <c r="BA29" t="n">
         <v>4.77039521233669</v>
       </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -4956,6 +5134,12 @@
       <c r="BA30" t="n">
         <v>6.003256549989229</v>
       </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -5103,6 +5287,12 @@
       <c r="BA31" t="n">
         <v>5.871422404388254</v>
       </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -5250,6 +5440,12 @@
       <c r="BA32" t="n">
         <v>4.248872527334292</v>
       </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -5397,6 +5593,12 @@
       <c r="BA33" t="n">
         <v>4.707179999838402</v>
       </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -5544,6 +5746,12 @@
       <c r="BA34" t="n">
         <v>5.538752547725021</v>
       </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -5691,6 +5899,12 @@
       <c r="BA35" t="n">
         <v>5.72708070874746</v>
       </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -5838,6 +6052,12 @@
       <c r="BA36" t="n">
         <v>6.421580057406096</v>
       </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -5985,6 +6205,12 @@
       <c r="BA37" t="n">
         <v>5.382476778431748</v>
       </c>
+      <c r="BB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -6132,6 +6358,12 @@
       <c r="BA38" t="n">
         <v>7.926449640071605</v>
       </c>
+      <c r="BB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -6279,6 +6511,12 @@
       <c r="BA39" t="n">
         <v>3.990234824028318</v>
       </c>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -6426,6 +6664,12 @@
       <c r="BA40" t="n">
         <v>6.701960533465813</v>
       </c>
+      <c r="BB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -6573,6 +6817,12 @@
       <c r="BA41" t="n">
         <v>6.406993482654983</v>
       </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -6720,6 +6970,12 @@
       <c r="BA42" t="n">
         <v>6.406993482654983</v>
       </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -6867,6 +7123,12 @@
       <c r="BA43" t="n">
         <v>6.406993482654983</v>
       </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -7014,6 +7276,12 @@
       <c r="BA44" t="n">
         <v>6.406993482654983</v>
       </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -7161,6 +7429,12 @@
       <c r="BA45" t="n">
         <v>7.270477607848516</v>
       </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -7308,6 +7582,12 @@
       <c r="BA46" t="n">
         <v>4.981358951370535</v>
       </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -7455,6 +7735,12 @@
       <c r="BA47" t="n">
         <v>4.941560931653564</v>
       </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -7602,6 +7888,12 @@
       <c r="BA48" t="n">
         <v>5.627608137299266</v>
       </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -7749,6 +8041,12 @@
       <c r="BA49" t="n">
         <v>7.860992204916545</v>
       </c>
+      <c r="BB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -7896,6 +8194,12 @@
       <c r="BA50" t="n">
         <v>6.085878779925097</v>
       </c>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -8043,6 +8347,12 @@
       <c r="BA51" t="n">
         <v>7.600880368696366</v>
       </c>
+      <c r="BB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -8190,6 +8500,12 @@
       <c r="BA52" t="n">
         <v>8.029662939995131</v>
       </c>
+      <c r="BB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -8337,6 +8653,12 @@
       <c r="BA53" t="n">
         <v>3.469168210591955</v>
       </c>
+      <c r="BB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -8484,6 +8806,12 @@
       <c r="BA54" t="n">
         <v>3.834114387266885</v>
       </c>
+      <c r="BB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -8631,6 +8959,12 @@
       <c r="BA55" t="n">
         <v>9.226808188432537</v>
       </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -8778,6 +9112,12 @@
       <c r="BA56" t="n">
         <v>5.640759522824799</v>
       </c>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -8925,6 +9265,12 @@
       <c r="BA57" t="n">
         <v>6.279270830799232</v>
       </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -9072,6 +9418,12 @@
       <c r="BA58" t="n">
         <v>5.528408572483942</v>
       </c>
+      <c r="BB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -9219,6 +9571,12 @@
       <c r="BA59" t="n">
         <v>6.080598725084783</v>
       </c>
+      <c r="BB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -9366,6 +9724,12 @@
       <c r="BA60" t="n">
         <v>4.620440023861259</v>
       </c>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -9513,6 +9877,12 @@
       <c r="BA61" t="n">
         <v>6.589693642640406</v>
       </c>
+      <c r="BB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -9660,6 +10030,12 @@
       <c r="BA62" t="n">
         <v>8.1219991100984</v>
       </c>
+      <c r="BB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -9807,6 +10183,12 @@
       <c r="BA63" t="n">
         <v>6.659317142649229</v>
       </c>
+      <c r="BB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -9954,6 +10336,12 @@
       <c r="BA64" t="n">
         <v>6.720409857723063</v>
       </c>
+      <c r="BB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -10101,6 +10489,12 @@
       <c r="BA65" t="n">
         <v>6.465141386759904</v>
       </c>
+      <c r="BB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -10248,6 +10642,12 @@
       <c r="BA66" t="n">
         <v>5.917373389442116</v>
       </c>
+      <c r="BB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -10395,6 +10795,12 @@
       <c r="BA67" t="n">
         <v>5.130229695978934</v>
       </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -10542,6 +10948,12 @@
       <c r="BA68" t="n">
         <v>4.61721716535054</v>
       </c>
+      <c r="BB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -10689,6 +11101,12 @@
       <c r="BA69" t="n">
         <v>4.169261023831525</v>
       </c>
+      <c r="BB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -10836,6 +11254,12 @@
       <c r="BA70" t="n">
         <v>5.468910140257988</v>
       </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -10983,6 +11407,12 @@
       <c r="BA71" t="n">
         <v>6.385261085941602</v>
       </c>
+      <c r="BB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -11130,6 +11560,12 @@
       <c r="BA72" t="n">
         <v>4.64552151410903</v>
       </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -11277,6 +11713,12 @@
       <c r="BA73" t="n">
         <v>5.317720031155273</v>
       </c>
+      <c r="BB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -11424,6 +11866,12 @@
       <c r="BA74" t="n">
         <v>7.650714677495467</v>
       </c>
+      <c r="BB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -11571,6 +12019,12 @@
       <c r="BA75" t="n">
         <v>8.094394089102797</v>
       </c>
+      <c r="BB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -11718,6 +12172,12 @@
       <c r="BA76" t="n">
         <v>6.613829372688381</v>
       </c>
+      <c r="BB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -11865,6 +12325,12 @@
       <c r="BA77" t="n">
         <v>6.379856596163442</v>
       </c>
+      <c r="BB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -12012,6 +12478,12 @@
       <c r="BA78" t="n">
         <v>4.677253989798563</v>
       </c>
+      <c r="BB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -12159,6 +12631,12 @@
       <c r="BA79" t="n">
         <v>5.943353709831833</v>
       </c>
+      <c r="BB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -12306,6 +12784,12 @@
       <c r="BA80" t="n">
         <v>6.635735356277657</v>
       </c>
+      <c r="BB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -12453,6 +12937,12 @@
       <c r="BA81" t="n">
         <v>7.152431113667959</v>
       </c>
+      <c r="BB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -12600,6 +13090,12 @@
       <c r="BA82" t="n">
         <v>5.80366638296212</v>
       </c>
+      <c r="BB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -12747,6 +13243,12 @@
       <c r="BA83" t="n">
         <v>4.144199615258708</v>
       </c>
+      <c r="BB83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -12894,6 +13396,12 @@
       <c r="BA84" t="n">
         <v>4.910286937521602</v>
       </c>
+      <c r="BB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -13041,6 +13549,12 @@
       <c r="BA85" t="n">
         <v>6.328175428570905</v>
       </c>
+      <c r="BB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -13188,6 +13702,12 @@
       <c r="BA86" t="n">
         <v>6.522638295327906</v>
       </c>
+      <c r="BB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -13335,6 +13855,12 @@
       <c r="BA87" t="n">
         <v>7.354363492686352</v>
       </c>
+      <c r="BB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -13482,6 +14008,12 @@
       <c r="BA88" t="n">
         <v>4.352489670002637</v>
       </c>
+      <c r="BB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -13649,6 +14181,12 @@
       <c r="BA89" t="n">
         <v>13.49936057389324</v>
       </c>
+      <c r="BB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -13816,6 +14354,12 @@
       <c r="BA90" t="n">
         <v>14.11226797838226</v>
       </c>
+      <c r="BB90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -13983,6 +14527,12 @@
       <c r="BA91" t="n">
         <v>12.41339472150039</v>
       </c>
+      <c r="BB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -14150,6 +14700,12 @@
       <c r="BA92" t="n">
         <v>11.44644073918296</v>
       </c>
+      <c r="BB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -14317,6 +14873,12 @@
       <c r="BA93" t="n">
         <v>13.46108772447198</v>
       </c>
+      <c r="BB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -14484,6 +15046,12 @@
       <c r="BA94" t="n">
         <v>14.55098595795598</v>
       </c>
+      <c r="BB94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -14651,6 +15219,12 @@
       <c r="BA95" t="n">
         <v>16.21005166131244</v>
       </c>
+      <c r="BB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -14818,6 +15392,12 @@
       <c r="BA96" t="n">
         <v>11.5432612977339</v>
       </c>
+      <c r="BB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -14985,6 +15565,12 @@
       <c r="BA97" t="n">
         <v>18.63708247181081</v>
       </c>
+      <c r="BB97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -15152,6 +15738,12 @@
       <c r="BA98" t="n">
         <v>13.36431271950471</v>
       </c>
+      <c r="BB98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -15319,6 +15911,12 @@
       <c r="BA99" t="n">
         <v>10.8080729022015</v>
       </c>
+      <c r="BB99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -15486,6 +16084,12 @@
       <c r="BA100" t="n">
         <v>12.77530493515518</v>
       </c>
+      <c r="BB100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -15653,6 +16257,12 @@
       <c r="BA101" t="n">
         <v>14.95225993840202</v>
       </c>
+      <c r="BB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -15820,6 +16430,12 @@
       <c r="BA102" t="n">
         <v>14.56543934132861</v>
       </c>
+      <c r="BB102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -15987,6 +16603,12 @@
       <c r="BA103" t="n">
         <v>13.085308400592</v>
       </c>
+      <c r="BB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -16154,6 +16776,12 @@
       <c r="BA104" t="n">
         <v>13.77626263997392</v>
       </c>
+      <c r="BB104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -16321,6 +16949,12 @@
       <c r="BA105" t="n">
         <v>13.64813509985642</v>
       </c>
+      <c r="BB105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -16488,6 +17122,12 @@
       <c r="BA106" t="n">
         <v>12.53521760130511</v>
       </c>
+      <c r="BB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -16655,6 +17295,12 @@
       <c r="BA107" t="n">
         <v>13.61822728292262</v>
       </c>
+      <c r="BB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -16822,6 +17468,12 @@
       <c r="BA108" t="n">
         <v>12.36377526016233</v>
       </c>
+      <c r="BB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -16989,6 +17641,12 @@
       <c r="BA109" t="n">
         <v>13.4521818706214</v>
       </c>
+      <c r="BB109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -17156,6 +17814,12 @@
       <c r="BA110" t="n">
         <v>13.71728615868613</v>
       </c>
+      <c r="BB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -17323,6 +17987,12 @@
       <c r="BA111" t="n">
         <v>13.16711084989783</v>
       </c>
+      <c r="BB111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -17490,6 +18160,12 @@
       <c r="BA112" t="n">
         <v>14.90856583514423</v>
       </c>
+      <c r="BB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -17657,6 +18333,12 @@
       <c r="BA113" t="n">
         <v>12.56625000971446</v>
       </c>
+      <c r="BB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -17824,6 +18506,12 @@
       <c r="BA114" t="n">
         <v>13.55543529737596</v>
       </c>
+      <c r="BB114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -17991,6 +18679,12 @@
       <c r="BA115" t="n">
         <v>13.8462674929608</v>
       </c>
+      <c r="BB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -18158,6 +18852,12 @@
       <c r="BA116" t="n">
         <v>14.06948853210919</v>
       </c>
+      <c r="BB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -18325,6 +19025,12 @@
       <c r="BA117" t="n">
         <v>11.36362404621276</v>
       </c>
+      <c r="BB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -18492,6 +19198,12 @@
       <c r="BA118" t="n">
         <v>11.21671934408004</v>
       </c>
+      <c r="BB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -18659,6 +19371,12 @@
       <c r="BA119" t="n">
         <v>12.68492545010291</v>
       </c>
+      <c r="BB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -18826,6 +19544,12 @@
       <c r="BA120" t="n">
         <v>16.98593273105596</v>
       </c>
+      <c r="BB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -18993,6 +19717,12 @@
       <c r="BA121" t="n">
         <v>17.24069091284437</v>
       </c>
+      <c r="BB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -19160,6 +19890,12 @@
       <c r="BA122" t="n">
         <v>12.9142850910087</v>
       </c>
+      <c r="BB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -19327,6 +20063,12 @@
       <c r="BA123" t="n">
         <v>13.89093963768983</v>
       </c>
+      <c r="BB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -19494,6 +20236,12 @@
       <c r="BA124" t="n">
         <v>15.89478030353562</v>
       </c>
+      <c r="BB124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -19661,6 +20409,12 @@
       <c r="BA125" t="n">
         <v>11.82301848502743</v>
       </c>
+      <c r="BB125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -19828,6 +20582,12 @@
       <c r="BA126" t="n">
         <v>12.94346879140066</v>
       </c>
+      <c r="BB126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -19995,6 +20755,12 @@
       <c r="BA127" t="n">
         <v>13.49082394850428</v>
       </c>
+      <c r="BB127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -20162,6 +20928,12 @@
       <c r="BA128" t="n">
         <v>14.95178371289261</v>
       </c>
+      <c r="BB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -20329,6 +21101,12 @@
       <c r="BA129" t="n">
         <v>13.39656411771</v>
       </c>
+      <c r="BB129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -20496,6 +21274,12 @@
       <c r="BA130" t="n">
         <v>15.24780589347843</v>
       </c>
+      <c r="BB130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -20663,6 +21447,12 @@
       <c r="BA131" t="n">
         <v>12.36588830848125</v>
       </c>
+      <c r="BB131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -20830,6 +21620,12 @@
       <c r="BA132" t="n">
         <v>15.32398352756091</v>
       </c>
+      <c r="BB132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -20997,6 +21793,12 @@
       <c r="BA133" t="n">
         <v>15.37482698512445</v>
       </c>
+      <c r="BB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -21164,6 +21966,12 @@
       <c r="BA134" t="n">
         <v>12.64306724710941</v>
       </c>
+      <c r="BB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -21331,6 +22139,12 @@
       <c r="BA135" t="n">
         <v>14.34571921902312</v>
       </c>
+      <c r="BB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -21498,6 +22312,12 @@
       <c r="BA136" t="n">
         <v>12.07681251870081</v>
       </c>
+      <c r="BB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -21665,6 +22485,12 @@
       <c r="BA137" t="n">
         <v>12.92788698041661</v>
       </c>
+      <c r="BB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -21832,6 +22658,12 @@
       <c r="BA138" t="n">
         <v>12.61555674855043</v>
       </c>
+      <c r="BB138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -21999,6 +22831,12 @@
       <c r="BA139" t="n">
         <v>14.94309852934265</v>
       </c>
+      <c r="BB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -22166,6 +23004,12 @@
       <c r="BA140" t="n">
         <v>13.50197279742473</v>
       </c>
+      <c r="BB140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -22333,6 +23177,12 @@
       <c r="BA141" t="n">
         <v>14.89304857028718</v>
       </c>
+      <c r="BB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -22500,6 +23350,12 @@
       <c r="BA142" t="n">
         <v>12.33569292798704</v>
       </c>
+      <c r="BB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -22667,6 +23523,12 @@
       <c r="BA143" t="n">
         <v>13.20241292636161</v>
       </c>
+      <c r="BB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -22834,6 +23696,12 @@
       <c r="BA144" t="n">
         <v>14.72041205661443</v>
       </c>
+      <c r="BB144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -23001,6 +23869,12 @@
       <c r="BA145" t="n">
         <v>13.50483650630982</v>
       </c>
+      <c r="BB145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -23168,6 +24042,12 @@
       <c r="BA146" t="n">
         <v>14.04704424717668</v>
       </c>
+      <c r="BB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -23335,6 +24215,12 @@
       <c r="BA147" t="n">
         <v>12.39357609552841</v>
       </c>
+      <c r="BB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -23502,6 +24388,12 @@
       <c r="BA148" t="n">
         <v>12.73705359648974</v>
       </c>
+      <c r="BB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -23669,6 +24561,12 @@
       <c r="BA149" t="n">
         <v>10.17299216629021</v>
       </c>
+      <c r="BB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -23836,6 +24734,12 @@
       <c r="BA150" t="n">
         <v>15.42719268663395</v>
       </c>
+      <c r="BB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -24003,6 +24907,12 @@
       <c r="BA151" t="n">
         <v>12.29805279278685</v>
       </c>
+      <c r="BB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -24170,6 +25080,12 @@
       <c r="BA152" t="n">
         <v>13.84738554555246</v>
       </c>
+      <c r="BB152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -24337,6 +25253,12 @@
       <c r="BA153" t="n">
         <v>12.99811599897735</v>
       </c>
+      <c r="BB153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -24504,6 +25426,12 @@
       <c r="BA154" t="n">
         <v>13.08294443919041</v>
       </c>
+      <c r="BB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -24671,6 +25599,12 @@
       <c r="BA155" t="n">
         <v>12.9060602060763</v>
       </c>
+      <c r="BB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -24838,6 +25772,12 @@
       <c r="BA156" t="n">
         <v>14.93215294918606</v>
       </c>
+      <c r="BB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -25005,6 +25945,12 @@
       <c r="BA157" t="n">
         <v>15.32716274738345</v>
       </c>
+      <c r="BB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -25172,6 +26118,12 @@
       <c r="BA158" t="n">
         <v>13.30667483923764</v>
       </c>
+      <c r="BB158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -25335,6 +26287,12 @@
       <c r="BA159" t="n">
         <v>13.36339572806621</v>
       </c>
+      <c r="BB159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -25498,6 +26456,12 @@
       <c r="BA160" t="n">
         <v>12.29154143560339</v>
       </c>
+      <c r="BB160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -25665,6 +26629,12 @@
       <c r="BA161" t="n">
         <v>11.64590440849937</v>
       </c>
+      <c r="BB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -25832,6 +26802,12 @@
       <c r="BA162" t="n">
         <v>12.17300558723502</v>
       </c>
+      <c r="BB162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -25999,6 +26975,12 @@
       <c r="BA163" t="n">
         <v>13.42169439208957</v>
       </c>
+      <c r="BB163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -26166,6 +27148,12 @@
       <c r="BA164" t="n">
         <v>14.07419437917497</v>
       </c>
+      <c r="BB164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -26333,6 +27321,12 @@
       <c r="BA165" t="n">
         <v>13.33772096173453</v>
       </c>
+      <c r="BB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -26500,6 +27494,12 @@
       <c r="BA166" t="n">
         <v>16.97539046167085</v>
       </c>
+      <c r="BB166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -26667,6 +27667,12 @@
       <c r="BA167" t="n">
         <v>11.65132875248652</v>
       </c>
+      <c r="BB167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -26834,6 +27840,12 @@
       <c r="BA168" t="n">
         <v>15.11954301763624</v>
       </c>
+      <c r="BB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -27001,6 +28013,12 @@
       <c r="BA169" t="n">
         <v>12.83721020627359</v>
       </c>
+      <c r="BB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -27168,6 +28186,12 @@
       <c r="BA170" t="n">
         <v>15.67979022827618</v>
       </c>
+      <c r="BB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -27335,6 +28359,12 @@
       <c r="BA171" t="n">
         <v>11.61765076524852</v>
       </c>
+      <c r="BB171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -27502,6 +28532,12 @@
       <c r="BA172" t="n">
         <v>14.69626650381366</v>
       </c>
+      <c r="BB172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -27669,6 +28705,12 @@
       <c r="BA173" t="n">
         <v>12.47173871860493</v>
       </c>
+      <c r="BB173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -27836,6 +28878,12 @@
       <c r="BA174" t="n">
         <v>14.2475185393632</v>
       </c>
+      <c r="BB174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -28003,6 +29051,12 @@
       <c r="BA175" t="n">
         <v>11.3388765448196</v>
       </c>
+      <c r="BB175" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -28170,6 +29224,12 @@
       <c r="BA176" t="n">
         <v>10.92082410889718</v>
       </c>
+      <c r="BB176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -28337,6 +29397,12 @@
       <c r="BA177" t="n">
         <v>13.1516753899925</v>
       </c>
+      <c r="BB177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -28504,6 +29570,12 @@
       <c r="BA178" t="n">
         <v>13.45013914035445</v>
       </c>
+      <c r="BB178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -28671,6 +29743,12 @@
       <c r="BA179" t="n">
         <v>13.35702874314139</v>
       </c>
+      <c r="BB179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -28838,6 +29916,12 @@
       <c r="BA180" t="n">
         <v>12.92183174935129</v>
       </c>
+      <c r="BB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -29004,6 +30088,12 @@
       </c>
       <c r="BA181" t="n">
         <v>15.23965851812918</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -2903,7 +2903,7 @@
         <v>42.28</v>
       </c>
       <c r="P16" t="n">
-        <v>-28.2</v>
+        <v>-31.00109077040427</v>
       </c>
       <c r="Q16" t="n">
         <v>15.5</v>
@@ -2945,16 +2945,16 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
-        <v>19.32430148930667</v>
+        <v>22.27086816317477</v>
       </c>
       <c r="AM16" t="n">
-        <v>324.3159602666282</v>
+        <v>384.1537123992449</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.7066443400185419</v>
+        <v>0.8370233963843873</v>
       </c>
       <c r="AO16" t="n">
-        <v>84.14763727184936</v>
+        <v>46.74904218896397</v>
       </c>
       <c r="AP16" t="n">
         <v>2000</v>
@@ -2984,7 +2984,7 @@
         <v>32.32547486872957</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.9202190103021481</v>
+        <v>-1.011623867625123</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.2346594974817987</v>
@@ -3515,7 +3515,7 @@
         <v>47.75</v>
       </c>
       <c r="P20" t="n">
-        <v>-26.37</v>
+        <v>-32.60541078255443</v>
       </c>
       <c r="Q20" t="n">
         <v>15.9</v>
@@ -3557,16 +3557,16 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>17.40841612040325</v>
+        <v>23.9661945893428</v>
       </c>
       <c r="AM20" t="n">
-        <v>285.4088909524788</v>
+        <v>418.5817548299786</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.6218706511290104</v>
+        <v>0.9120378400201408</v>
       </c>
       <c r="AO20" t="n">
-        <v>108.4645555931928</v>
+        <v>25.23151566975534</v>
       </c>
       <c r="AP20" t="n">
         <v>2000</v>
@@ -3596,7 +3596,7 @@
         <v>30.75436275117814</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.9251081452731393</v>
+        <v>-1.14385783446787</v>
       </c>
       <c r="AZ20" t="n">
         <v>0.2216436966512492</v>
@@ -8549,7 +8549,7 @@
         <v>-32.30627681984863</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0253654953216571</v>
+        <v>0.02436191095400565</v>
       </c>
       <c r="L53" t="n">
         <v>2.212395175186674</v>
@@ -8641,15 +8641,11 @@
       <c r="AW53" t="n">
         <v>0.5561426684280054</v>
       </c>
-      <c r="AX53" t="n">
-        <v>16.47515809594595</v>
-      </c>
+      <c r="AX53" t="inlineStr"/>
       <c r="AY53" t="n">
         <v>-1.059704205037399</v>
       </c>
-      <c r="AZ53" t="n">
-        <v>0.2105696461538427</v>
-      </c>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
         <v>3.469168210591955</v>
       </c>
@@ -22707,7 +22703,7 @@
         <v>-30.32987330795573</v>
       </c>
       <c r="K139" t="n">
-        <v>0.02957614146330922</v>
+        <v>0.0117556</v>
       </c>
       <c r="L139" t="n">
         <v>2.373333643299183</v>
@@ -22820,13 +22816,13 @@
         <v>0.5165860400829302</v>
       </c>
       <c r="AX139" t="n">
-        <v>16.82978356315537</v>
+        <v>42.34237805477897</v>
       </c>
       <c r="AY139" t="n">
         <v>-0.8676616915422886</v>
       </c>
       <c r="AZ139" t="n">
-        <v>0.887896060770315</v>
+        <v>0.3529111782529205</v>
       </c>
       <c r="BA139" t="n">
         <v>14.94309852934265</v>

--- a/data_for_R.xlsx
+++ b/data_for_R.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC181"/>
+  <dimension ref="A1:BB181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,15 +690,10 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>Carea</t>
+          <t>N</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -845,15 +840,12 @@
         <v>-1.069204566063425</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1583411527786951</v>
+        <v>1.583411527786951</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.267862957094129</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -998,15 +990,12 @@
         <v>-1.162714378482783</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1927929018543231</v>
+        <v>1.927929018543231</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.931398966307422</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1151,15 +1140,12 @@
         <v>-1.083217188451016</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1459443363957555</v>
+        <v>1.459443363957554</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.201410491775166</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1304,15 +1290,12 @@
         <v>-1.173469655199274</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2308390026071944</v>
+        <v>2.308390026071943</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.803966990152447</v>
+        <v>1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1457,15 +1440,12 @@
         <v>-1.152717050430573</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1972952651382424</v>
+        <v>1.972952651382424</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.814010355624786</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1610,15 +1590,12 @@
         <v>-0.9757692279498354</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2411024955423218</v>
+        <v>2.411024955423218</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.393667365779264</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1763,15 +1740,12 @@
         <v>-1.066817746219274</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2212734935521185</v>
+        <v>2.212734935521185</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.582919875238116</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1916,15 +1890,12 @@
         <v>-1.120257664680253</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2491330280495736</v>
+        <v>2.491330280495736</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.04653963916366</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2069,15 +2040,12 @@
         <v>-1.176763154946914</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1922442143630735</v>
+        <v>1.922442143630735</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.385976820401974</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2222,15 +2190,12 @@
         <v>-1.083133704760353</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1541538771183675</v>
+        <v>1.541538771183675</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.156964889603419</v>
+        <v>1</v>
       </c>
       <c r="BB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2375,15 +2340,12 @@
         <v>-0.9693632665794485</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1704503359635594</v>
+        <v>1.704503359635594</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.04539122144526</v>
+        <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2528,15 +2490,12 @@
         <v>-1.01178671221848</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1893086604314295</v>
+        <v>1.893086604314296</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.298227944361334</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2681,15 +2640,12 @@
         <v>-0.9086318732906992</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2420263723581012</v>
+        <v>2.420263723581012</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.933547349313596</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2834,15 +2790,12 @@
         <v>-0.9710658232898745</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2262696828216982</v>
+        <v>2.262696828216981</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.737742901484933</v>
+        <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2987,15 +2940,12 @@
         <v>-1.011623867625123</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2346594974817987</v>
+        <v>2.346594974817986</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.585479688556592</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3140,15 +3090,12 @@
         <v>-1.137930339273472</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2040293659175826</v>
+        <v>2.040293659175827</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.793309073325802</v>
+        <v>1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3293,15 +3240,12 @@
         <v>-0.9983195512068304</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.2199748552043699</v>
+        <v>2.199748552043698</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.418104834646514</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3446,15 +3390,12 @@
         <v>-1.159881181147376</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.1804095984933663</v>
+        <v>1.804095984933663</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.811120672929789</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3599,15 +3540,12 @@
         <v>-1.14385783446787</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.2216436966512492</v>
+        <v>2.216436966512492</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.816510648324604</v>
+        <v>1</v>
       </c>
       <c r="BB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3752,15 +3690,12 @@
         <v>-0.8250529055541557</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.2731252805030631</v>
+        <v>2.731252805030631</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.269341168086865</v>
+        <v>1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3905,15 +3840,12 @@
         <v>-0.9307778716019919</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.1359691165823957</v>
+        <v>1.359691165823957</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.209869586996444</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4058,15 +3990,12 @@
         <v>-1.076624094600751</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.1532285064088778</v>
+        <v>1.532285064088778</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.8814772925756</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4211,15 +4140,12 @@
         <v>-0.9531215121310557</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.2083919474390169</v>
+        <v>2.083919474390169</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.450269324889292</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4364,15 +4290,12 @@
         <v>-1.127672428671739</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.1924962019984864</v>
+        <v>1.924962019984864</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.922628309595306</v>
+        <v>1</v>
       </c>
       <c r="BB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4517,15 +4440,12 @@
         <v>-1.093730835683608</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.1993680458705612</v>
+        <v>1.993680458705612</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.819873982352418</v>
+        <v>1</v>
       </c>
       <c r="BB26" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4670,15 +4590,12 @@
         <v>-0.9251981278059437</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.2247906864753312</v>
+        <v>2.247906864753312</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.353630630525455</v>
+        <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4823,15 +4740,12 @@
         <v>-1.110646754176239</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.1941969337398241</v>
+        <v>1.941969337398241</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.180318961158282</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4976,15 +4890,12 @@
         <v>-0.8721981465115956</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.2299853817964811</v>
+        <v>2.299853817964811</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.77039521233669</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5129,15 +5040,12 @@
         <v>-1.026018023099852</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.2056480718564838</v>
+        <v>2.056480718564837</v>
       </c>
       <c r="BA30" t="n">
-        <v>6.003256549989229</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5282,15 +5190,12 @@
         <v>-1.081725628636109</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.136631885562437</v>
+        <v>1.36631885562437</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.871422404388254</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5435,15 +5340,12 @@
         <v>-0.9757257325131097</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.2060536274187499</v>
+        <v>2.060536274187499</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.248872527334292</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5588,15 +5490,12 @@
         <v>-1.108000186694067</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.2140487849336566</v>
+        <v>2.140487849336566</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.707179999838402</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5741,15 +5640,12 @@
         <v>-1.1317622997201</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.1262484116656832</v>
+        <v>1.262484116656831</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.538752547725021</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5894,15 +5790,12 @@
         <v>-1.097985206987246</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.236853606683806</v>
+        <v>2.36853606683806</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.72708070874746</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6047,15 +5940,12 @@
         <v>-1.041003254864917</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.1404492354378129</v>
+        <v>1.404492354378129</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.421580057406096</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6200,15 +6090,12 @@
         <v>-1.128326182974303</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.165736668134432</v>
+        <v>1.65736668134432</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.382476778431748</v>
+        <v>1</v>
       </c>
       <c r="BB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6353,15 +6240,12 @@
         <v>-1.052221717593601</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.25370946862891</v>
+        <v>2.5370946862891</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.926449640071605</v>
+        <v>1</v>
       </c>
       <c r="BB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6506,15 +6390,12 @@
         <v>-1.018263130425242</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.1790085898974969</v>
+        <v>1.790085898974969</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.990234824028318</v>
+        <v>1</v>
       </c>
       <c r="BB39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6659,15 +6540,12 @@
         <v>-1.134852638614013</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.1636334848571583</v>
+        <v>1.636334848571583</v>
       </c>
       <c r="BA40" t="n">
-        <v>6.701960533465813</v>
+        <v>1</v>
       </c>
       <c r="BB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6812,15 +6690,12 @@
         <v>-1.046794083447492</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.1962293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.406993482654983</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6965,15 +6840,12 @@
         <v>-1.055363556422817</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.1962293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BA42" t="n">
-        <v>6.406993482654983</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7118,15 +6990,12 @@
         <v>-1.027478472194354</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.1962293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BA43" t="n">
-        <v>6.406993482654983</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7271,15 +7140,12 @@
         <v>-1.035889819888641</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.1962293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BA44" t="n">
-        <v>6.406993482654983</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7424,15 +7290,12 @@
         <v>-1.016944806660762</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.2080347916779913</v>
+        <v>2.080347916779913</v>
       </c>
       <c r="BA45" t="n">
-        <v>7.270477607848516</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7577,15 +7440,12 @@
         <v>-1.168428613749502</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.1803572361821152</v>
+        <v>1.803572361821152</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.981358951370535</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7730,15 +7590,12 @@
         <v>-1.006406074511895</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.1563233988308393</v>
+        <v>1.563233988308393</v>
       </c>
       <c r="BA47" t="n">
-        <v>4.941560931653564</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7883,15 +7740,12 @@
         <v>-1.002974473340656</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.1727182447385554</v>
+        <v>1.727182447385554</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.627608137299266</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8036,15 +7890,12 @@
         <v>-1.033343565098957</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.2118768969038876</v>
+        <v>2.118768969038876</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.860992204916545</v>
+        <v>1</v>
       </c>
       <c r="BB49" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8189,15 +8040,12 @@
         <v>-1.094831536193773</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.1305405133948935</v>
+        <v>1.305405133948935</v>
       </c>
       <c r="BA50" t="n">
-        <v>6.085878779925097</v>
+        <v>1</v>
       </c>
       <c r="BB50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8342,15 +8190,12 @@
         <v>-1.034130614924995</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.2749705279828398</v>
+        <v>2.749705279828397</v>
       </c>
       <c r="BA51" t="n">
-        <v>7.600880368696366</v>
+        <v>1</v>
       </c>
       <c r="BB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8495,15 +8340,12 @@
         <v>-0.9330413776996519</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0.2554237568151246</v>
+        <v>2.554237568151246</v>
       </c>
       <c r="BA52" t="n">
-        <v>8.029662939995131</v>
+        <v>1</v>
       </c>
       <c r="BB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8548,9 +8390,7 @@
       <c r="J53" t="n">
         <v>-32.30627681984863</v>
       </c>
-      <c r="K53" t="n">
-        <v>0.02436191095400565</v>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>2.212395175186674</v>
       </c>
@@ -8647,12 +8487,9 @@
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
-        <v>3.469168210591955</v>
+        <v>1</v>
       </c>
       <c r="BB53" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8797,15 +8634,12 @@
         <v>-1.09799079624996</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0.2230482700063978</v>
+        <v>2.230482700063977</v>
       </c>
       <c r="BA54" t="n">
-        <v>3.834114387266885</v>
+        <v>1</v>
       </c>
       <c r="BB54" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8950,15 +8784,12 @@
         <v>-1.013558134662488</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0.2700331914670088</v>
+        <v>2.700331914670088</v>
       </c>
       <c r="BA55" t="n">
-        <v>9.226808188432537</v>
+        <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9103,15 +8934,12 @@
         <v>-1.029758709416929</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0.1811914954031918</v>
+        <v>1.811914954031917</v>
       </c>
       <c r="BA56" t="n">
-        <v>5.640759522824799</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9256,15 +9084,12 @@
         <v>-1.071407723597514</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.1485071659290358</v>
+        <v>1.485071659290358</v>
       </c>
       <c r="BA57" t="n">
-        <v>6.279270830799232</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9409,15 +9234,12 @@
         <v>-1.076020463092165</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0.181805467668072</v>
+        <v>1.818054676680719</v>
       </c>
       <c r="BA58" t="n">
-        <v>5.528408572483942</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9562,15 +9384,12 @@
         <v>-1.131721301339614</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.1468960643433882</v>
+        <v>1.468960643433882</v>
       </c>
       <c r="BA59" t="n">
-        <v>6.080598725084783</v>
+        <v>1</v>
       </c>
       <c r="BB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9715,15 +9534,12 @@
         <v>-1.148906986345209</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.1640718941643498</v>
+        <v>1.640718941643499</v>
       </c>
       <c r="BA60" t="n">
-        <v>4.620440023861259</v>
+        <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9868,15 +9684,12 @@
         <v>-0.9802187884414533</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0.2324436326842925</v>
+        <v>2.324436326842925</v>
       </c>
       <c r="BA61" t="n">
-        <v>6.589693642640406</v>
+        <v>1</v>
       </c>
       <c r="BB61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10021,15 +9834,12 @@
         <v>-1.059967417806882</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0.2271852849396293</v>
+        <v>2.271852849396293</v>
       </c>
       <c r="BA62" t="n">
-        <v>8.1219991100984</v>
+        <v>1</v>
       </c>
       <c r="BB62" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10174,15 +9984,12 @@
         <v>-1.07072599241777</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0.2097736888129386</v>
+        <v>2.097736888129386</v>
       </c>
       <c r="BA63" t="n">
-        <v>6.659317142649229</v>
+        <v>1</v>
       </c>
       <c r="BB63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10327,15 +10134,12 @@
         <v>-1.07072599241777</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0.2051731480905204</v>
+        <v>2.051731480905203</v>
       </c>
       <c r="BA64" t="n">
-        <v>6.720409857723063</v>
+        <v>1</v>
       </c>
       <c r="BB64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10480,15 +10284,12 @@
         <v>-1.072717162486702</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0.1711270057226029</v>
+        <v>1.71127005722603</v>
       </c>
       <c r="BA65" t="n">
-        <v>6.465141386759904</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10633,15 +10434,12 @@
         <v>-1.186907968195777</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0.1264668813853405</v>
+        <v>1.264668813853404</v>
       </c>
       <c r="BA66" t="n">
-        <v>5.917373389442116</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC66" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10786,15 +10584,12 @@
         <v>-1.05716724908219</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0.1735620252135451</v>
+        <v>1.735620252135451</v>
       </c>
       <c r="BA67" t="n">
-        <v>5.130229695978934</v>
+        <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10939,15 +10734,12 @@
         <v>-1.062612342442872</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0.1651892043876882</v>
+        <v>1.651892043876882</v>
       </c>
       <c r="BA68" t="n">
-        <v>4.61721716535054</v>
+        <v>0</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11092,15 +10884,12 @@
         <v>-1.162202419950019</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0.1729739026459769</v>
+        <v>1.72973902645977</v>
       </c>
       <c r="BA69" t="n">
-        <v>4.169261023831525</v>
+        <v>0</v>
       </c>
       <c r="BB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11245,15 +11034,12 @@
         <v>-0.9735100220183867</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0.1653302877966243</v>
+        <v>1.653302877966243</v>
       </c>
       <c r="BA70" t="n">
-        <v>5.468910140257988</v>
+        <v>0</v>
       </c>
       <c r="BB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11398,15 +11184,12 @@
         <v>-1.151540486656524</v>
       </c>
       <c r="AZ71" t="n">
-        <v>0.224534879706159</v>
+        <v>2.24534879706159</v>
       </c>
       <c r="BA71" t="n">
-        <v>6.385261085941602</v>
+        <v>0</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11551,15 +11334,12 @@
         <v>-1.081507885923864</v>
       </c>
       <c r="AZ72" t="n">
-        <v>0.1704181532420173</v>
+        <v>1.704181532420173</v>
       </c>
       <c r="BA72" t="n">
-        <v>4.64552151410903</v>
+        <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11704,15 +11484,12 @@
         <v>-1.008164398010397</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0.1771344004138958</v>
+        <v>1.771344004138958</v>
       </c>
       <c r="BA73" t="n">
-        <v>5.317720031155273</v>
+        <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC73" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11857,15 +11634,12 @@
         <v>-0.9019527661726316</v>
       </c>
       <c r="AZ74" t="n">
-        <v>0.2890653446677475</v>
+        <v>2.890653446677475</v>
       </c>
       <c r="BA74" t="n">
-        <v>7.650714677495467</v>
+        <v>0</v>
       </c>
       <c r="BB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC74" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12010,15 +11784,12 @@
         <v>-1.064321440481539</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0.2678379030470969</v>
+        <v>2.678379030470969</v>
       </c>
       <c r="BA75" t="n">
-        <v>8.094394089102797</v>
+        <v>0</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC75" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12163,15 +11934,12 @@
         <v>-1.036430349351861</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0.2020516390549202</v>
+        <v>2.020516390549202</v>
       </c>
       <c r="BA76" t="n">
-        <v>6.613829372688381</v>
+        <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12316,15 +12084,12 @@
         <v>-0.9447135609596995</v>
       </c>
       <c r="AZ77" t="n">
-        <v>0.2290004233178914</v>
+        <v>2.290004233178915</v>
       </c>
       <c r="BA77" t="n">
-        <v>6.379856596163442</v>
+        <v>0</v>
       </c>
       <c r="BB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12469,15 +12234,12 @@
         <v>-1.136069687512091</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0.2143935207599353</v>
+        <v>2.143935207599353</v>
       </c>
       <c r="BA78" t="n">
-        <v>4.677253989798563</v>
+        <v>0</v>
       </c>
       <c r="BB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12622,15 +12384,12 @@
         <v>-0.7957323640055816</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0.3250436485054538</v>
+        <v>3.250436485054538</v>
       </c>
       <c r="BA79" t="n">
-        <v>5.943353709831833</v>
+        <v>1</v>
       </c>
       <c r="BB79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12775,15 +12534,12 @@
         <v>-1.083830924468203</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0.2998648154876037</v>
+        <v>2.998648154876038</v>
       </c>
       <c r="BA80" t="n">
-        <v>6.635735356277657</v>
+        <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12928,15 +12684,12 @@
         <v>-0.852490835998494</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0.2994186256562353</v>
+        <v>2.994186256562354</v>
       </c>
       <c r="BA81" t="n">
-        <v>7.152431113667959</v>
+        <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13081,15 +12834,12 @@
         <v>-1.073512489772441</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0.1986099449474032</v>
+        <v>1.986099449474032</v>
       </c>
       <c r="BA82" t="n">
-        <v>5.80366638296212</v>
+        <v>1</v>
       </c>
       <c r="BB82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13234,15 +12984,12 @@
         <v>-1.045162407612312</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0.1574768288150041</v>
+        <v>1.574768288150041</v>
       </c>
       <c r="BA83" t="n">
-        <v>4.144199615258708</v>
+        <v>1</v>
       </c>
       <c r="BB83" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13387,15 +13134,12 @@
         <v>-1.011763599487811</v>
       </c>
       <c r="AZ84" t="n">
-        <v>0.1625698637855855</v>
+        <v>1.625698637855855</v>
       </c>
       <c r="BA84" t="n">
-        <v>4.910286937521602</v>
+        <v>1</v>
       </c>
       <c r="BB84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13540,15 +13284,12 @@
         <v>-1.056436243301099</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0.2261410104794487</v>
+        <v>2.261410104794487</v>
       </c>
       <c r="BA85" t="n">
-        <v>6.328175428570905</v>
+        <v>1</v>
       </c>
       <c r="BB85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13693,15 +13434,12 @@
         <v>-1.139184969499528</v>
       </c>
       <c r="AZ86" t="n">
-        <v>0.2131678007547578</v>
+        <v>2.131678007547578</v>
       </c>
       <c r="BA86" t="n">
-        <v>6.522638295327906</v>
+        <v>1</v>
       </c>
       <c r="BB86" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13846,15 +13584,12 @@
         <v>-0.9994064701242487</v>
       </c>
       <c r="AZ87" t="n">
-        <v>0.2723142473493239</v>
+        <v>2.723142473493239</v>
       </c>
       <c r="BA87" t="n">
-        <v>7.354363492686352</v>
+        <v>1</v>
       </c>
       <c r="BB87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13999,15 +13734,12 @@
         <v>-0.9530514877786842</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0.2165437559626953</v>
+        <v>2.165437559626953</v>
       </c>
       <c r="BA88" t="n">
-        <v>4.352489670002637</v>
+        <v>1</v>
       </c>
       <c r="BB88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14172,15 +13904,12 @@
         <v>-0.921325744894543</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0.2273110803333757</v>
+        <v>2.273110803333757</v>
       </c>
       <c r="BA89" t="n">
-        <v>13.49936057389324</v>
+        <v>0</v>
       </c>
       <c r="BB89" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14345,15 +14074,12 @@
         <v>-0.9396264176117411</v>
       </c>
       <c r="AZ90" t="n">
-        <v>0.2562349769016561</v>
+        <v>2.562349769016562</v>
       </c>
       <c r="BA90" t="n">
-        <v>14.11226797838226</v>
+        <v>0</v>
       </c>
       <c r="BB90" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC90" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14518,15 +14244,12 @@
         <v>-0.9000000000000001</v>
       </c>
       <c r="AZ91" t="n">
-        <v>0.2747689268163115</v>
+        <v>2.747689268163116</v>
       </c>
       <c r="BA91" t="n">
-        <v>12.41339472150039</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14691,15 +14414,12 @@
         <v>-0.9772876892692561</v>
       </c>
       <c r="AZ92" t="n">
-        <v>0.2638257036105743</v>
+        <v>2.638257036105744</v>
       </c>
       <c r="BA92" t="n">
-        <v>11.44644073918296</v>
+        <v>0</v>
       </c>
       <c r="BB92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14864,15 +14584,12 @@
         <v>-0.8726919339164237</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0.2205905999210828</v>
+        <v>2.205905999210828</v>
       </c>
       <c r="BA93" t="n">
-        <v>13.46108772447198</v>
+        <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15037,15 +14754,12 @@
         <v>-0.8030209617755858</v>
       </c>
       <c r="AZ94" t="n">
-        <v>0.2899244513121407</v>
+        <v>2.899244513121407</v>
       </c>
       <c r="BA94" t="n">
-        <v>14.55098595795598</v>
+        <v>1</v>
       </c>
       <c r="BB94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15210,15 +14924,12 @@
         <v>-0.9410150891632374</v>
       </c>
       <c r="AZ95" t="n">
-        <v>0.3639814907180162</v>
+        <v>3.639814907180162</v>
       </c>
       <c r="BA95" t="n">
-        <v>16.21005166131244</v>
+        <v>0</v>
       </c>
       <c r="BB95" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15383,15 +15094,12 @@
         <v>-0.8697027197975964</v>
       </c>
       <c r="AZ96" t="n">
-        <v>0.2754165199655664</v>
+        <v>2.754165199655663</v>
       </c>
       <c r="BA96" t="n">
-        <v>11.5432612977339</v>
+        <v>1</v>
       </c>
       <c r="BB96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC96" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15556,15 +15264,12 @@
         <v>-0.8926196808510639</v>
       </c>
       <c r="AZ97" t="n">
-        <v>0.2635851161810385</v>
+        <v>2.635851161810386</v>
       </c>
       <c r="BA97" t="n">
-        <v>18.63708247181081</v>
+        <v>0</v>
       </c>
       <c r="BB97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15729,15 +15434,12 @@
         <v>-0.9120214909335124</v>
       </c>
       <c r="AZ98" t="n">
-        <v>0.2379812101557392</v>
+        <v>2.379812101557392</v>
       </c>
       <c r="BA98" t="n">
-        <v>13.36431271950471</v>
+        <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC98" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15902,15 +15604,12 @@
         <v>-0.9579330904272938</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0.1937192235493845</v>
+        <v>1.937192235493844</v>
       </c>
       <c r="BA99" t="n">
-        <v>10.8080729022015</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16075,15 +15774,12 @@
         <v>-0.8845169545745361</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0.1937567807703534</v>
+        <v>1.937567807703533</v>
       </c>
       <c r="BA100" t="n">
-        <v>12.77530493515518</v>
+        <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC100" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16248,15 +15944,12 @@
         <v>-0.8345370978332239</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0.2390186769233919</v>
+        <v>2.390186769233919</v>
       </c>
       <c r="BA101" t="n">
-        <v>14.95225993840202</v>
+        <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16421,15 +16114,12 @@
         <v>-0.8655913978494624</v>
       </c>
       <c r="AZ102" t="n">
-        <v>0.3022826134073608</v>
+        <v>3.022826134073608</v>
       </c>
       <c r="BA102" t="n">
-        <v>14.56543934132861</v>
+        <v>1</v>
       </c>
       <c r="BB102" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16594,15 +16284,12 @@
         <v>-0.8713188220230473</v>
       </c>
       <c r="AZ103" t="n">
-        <v>0.2697981424651091</v>
+        <v>2.697981424651091</v>
       </c>
       <c r="BA103" t="n">
-        <v>13.085308400592</v>
+        <v>1</v>
       </c>
       <c r="BB103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC103" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16767,15 +16454,12 @@
         <v>-0.873405299313052</v>
       </c>
       <c r="AZ104" t="n">
-        <v>0.3273385634947573</v>
+        <v>3.273385634947574</v>
       </c>
       <c r="BA104" t="n">
-        <v>13.77626263997392</v>
+        <v>1</v>
       </c>
       <c r="BB104" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16940,15 +16624,12 @@
         <v>-0.7809629835791817</v>
       </c>
       <c r="AZ105" t="n">
-        <v>0.2627407067212578</v>
+        <v>2.627407067212578</v>
       </c>
       <c r="BA105" t="n">
-        <v>13.64813509985642</v>
+        <v>1</v>
       </c>
       <c r="BB105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17113,15 +16794,12 @@
         <v>-0.9106683804627249</v>
       </c>
       <c r="AZ106" t="n">
-        <v>0.2253565398386968</v>
+        <v>2.253565398386967</v>
       </c>
       <c r="BA106" t="n">
-        <v>12.53521760130511</v>
+        <v>0</v>
       </c>
       <c r="BB106" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC106" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17286,15 +16964,12 @@
         <v>-0.840602950609365</v>
       </c>
       <c r="AZ107" t="n">
-        <v>0.2310070069738794</v>
+        <v>2.310070069738794</v>
       </c>
       <c r="BA107" t="n">
-        <v>13.61822728292262</v>
+        <v>0</v>
       </c>
       <c r="BB107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC107" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17459,15 +17134,12 @@
         <v>-0.9048231511254019</v>
       </c>
       <c r="AZ108" t="n">
-        <v>0.2004180823301927</v>
+        <v>2.004180823301927</v>
       </c>
       <c r="BA108" t="n">
-        <v>12.36377526016233</v>
+        <v>0</v>
       </c>
       <c r="BB108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC108" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17632,15 +17304,12 @@
         <v>-0.8401015228426396</v>
       </c>
       <c r="AZ109" t="n">
-        <v>0.3164054433208752</v>
+        <v>3.164054433208753</v>
       </c>
       <c r="BA109" t="n">
-        <v>13.4521818706214</v>
+        <v>1</v>
       </c>
       <c r="BB109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC109" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17805,15 +17474,12 @@
         <v>-0.9122807017543859</v>
       </c>
       <c r="AZ110" t="n">
-        <v>0.3143298872640892</v>
+        <v>3.143298872640891</v>
       </c>
       <c r="BA110" t="n">
-        <v>13.71728615868613</v>
+        <v>0</v>
       </c>
       <c r="BB110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17978,15 +17644,12 @@
         <v>-0.9649181423321083</v>
       </c>
       <c r="AZ111" t="n">
-        <v>0.2727743536270423</v>
+        <v>2.727743536270423</v>
       </c>
       <c r="BA111" t="n">
-        <v>13.16711084989783</v>
+        <v>1</v>
       </c>
       <c r="BB111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18151,15 +17814,12 @@
         <v>-0.9372869802317655</v>
       </c>
       <c r="AZ112" t="n">
-        <v>0.2677287744794695</v>
+        <v>2.677287744794695</v>
       </c>
       <c r="BA112" t="n">
-        <v>14.90856583514423</v>
+        <v>0</v>
       </c>
       <c r="BB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC112" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18324,15 +17984,12 @@
         <v>-0.8688741721854304</v>
       </c>
       <c r="AZ113" t="n">
-        <v>0.2699350840327465</v>
+        <v>2.699350840327465</v>
       </c>
       <c r="BA113" t="n">
-        <v>12.56625000971446</v>
+        <v>0</v>
       </c>
       <c r="BB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC113" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18497,15 +18154,12 @@
         <v>-0.821639344262295</v>
       </c>
       <c r="AZ114" t="n">
-        <v>0.4709552277566549</v>
+        <v>4.70955227756655</v>
       </c>
       <c r="BA114" t="n">
-        <v>13.55543529737596</v>
+        <v>1</v>
       </c>
       <c r="BB114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18670,15 +18324,12 @@
         <v>-1.043353636689359</v>
       </c>
       <c r="AZ115" t="n">
-        <v>0.3439129986152255</v>
+        <v>3.439129986152254</v>
       </c>
       <c r="BA115" t="n">
-        <v>13.8462674929608</v>
+        <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC115" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18843,15 +18494,12 @@
         <v>-1.023550087873462</v>
       </c>
       <c r="AZ116" t="n">
-        <v>0.3494573532195661</v>
+        <v>3.494573532195661</v>
       </c>
       <c r="BA116" t="n">
-        <v>14.06948853210919</v>
+        <v>0</v>
       </c>
       <c r="BB116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC116" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19016,15 +18664,12 @@
         <v>-0.9992862241256246</v>
       </c>
       <c r="AZ117" t="n">
-        <v>0.2941786834792475</v>
+        <v>2.941786834792475</v>
       </c>
       <c r="BA117" t="n">
-        <v>11.36362404621276</v>
+        <v>0</v>
       </c>
       <c r="BB117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19189,15 +18834,12 @@
         <v>-0.9220733427362482</v>
       </c>
       <c r="AZ118" t="n">
-        <v>0.2356234081045346</v>
+        <v>2.356234081045346</v>
       </c>
       <c r="BA118" t="n">
-        <v>11.21671934408004</v>
+        <v>0</v>
       </c>
       <c r="BB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC118" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19362,15 +19004,12 @@
         <v>-0.9540313754104341</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0.2664652002443708</v>
+        <v>2.664652002443708</v>
       </c>
       <c r="BA119" t="n">
-        <v>12.68492545010291</v>
+        <v>0</v>
       </c>
       <c r="BB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC119" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19535,15 +19174,12 @@
         <v>-0.8568159529257928</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0.4458705469717965</v>
+        <v>4.458705469717965</v>
       </c>
       <c r="BA120" t="n">
-        <v>16.98593273105596</v>
+        <v>1</v>
       </c>
       <c r="BB120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19708,15 +19344,12 @@
         <v>-0.8646491519787163</v>
       </c>
       <c r="AZ121" t="n">
-        <v>0.4809162989997219</v>
+        <v>4.809162989997219</v>
       </c>
       <c r="BA121" t="n">
-        <v>17.24069091284437</v>
+        <v>0</v>
       </c>
       <c r="BB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC121" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19881,15 +19514,12 @@
         <v>-0.8040981061782054</v>
       </c>
       <c r="AZ122" t="n">
-        <v>0.2754411937467637</v>
+        <v>2.754411937467637</v>
       </c>
       <c r="BA122" t="n">
-        <v>12.9142850910087</v>
+        <v>0</v>
       </c>
       <c r="BB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20054,15 +19684,12 @@
         <v>-0.9652323580034423</v>
       </c>
       <c r="AZ123" t="n">
-        <v>0.2712645733328085</v>
+        <v>2.712645733328085</v>
       </c>
       <c r="BA123" t="n">
-        <v>13.89093963768983</v>
+        <v>0</v>
       </c>
       <c r="BB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC123" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20227,15 +19854,12 @@
         <v>-0.9461077844311376</v>
       </c>
       <c r="AZ124" t="n">
-        <v>0.3551411071187895</v>
+        <v>3.551411071187895</v>
       </c>
       <c r="BA124" t="n">
-        <v>15.89478030353562</v>
+        <v>1</v>
       </c>
       <c r="BB124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20400,15 +20024,12 @@
         <v>-0.9985683607730851</v>
       </c>
       <c r="AZ125" t="n">
-        <v>0.307205325190028</v>
+        <v>3.07205325190028</v>
       </c>
       <c r="BA125" t="n">
-        <v>11.82301848502743</v>
+        <v>1</v>
       </c>
       <c r="BB125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20573,15 +20194,12 @@
         <v>-0.8554932365555923</v>
       </c>
       <c r="AZ126" t="n">
-        <v>0.3403595277379776</v>
+        <v>3.403595277379776</v>
       </c>
       <c r="BA126" t="n">
-        <v>12.94346879140066</v>
+        <v>1</v>
       </c>
       <c r="BB126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20746,15 +20364,12 @@
         <v>-0.8341742347796839</v>
       </c>
       <c r="AZ127" t="n">
-        <v>0.3160063990834164</v>
+        <v>3.160063990834163</v>
       </c>
       <c r="BA127" t="n">
-        <v>13.49082394850428</v>
+        <v>1</v>
       </c>
       <c r="BB127" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20919,15 +20534,12 @@
         <v>-0.8899897505978819</v>
       </c>
       <c r="AZ128" t="n">
-        <v>0.3483273407058165</v>
+        <v>3.483273407058165</v>
       </c>
       <c r="BA128" t="n">
-        <v>14.95178371289261</v>
+        <v>0</v>
       </c>
       <c r="BB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC128" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21092,15 +20704,12 @@
         <v>-0.9594183293878932</v>
       </c>
       <c r="AZ129" t="n">
-        <v>0.3335399262952408</v>
+        <v>3.335399262952408</v>
       </c>
       <c r="BA129" t="n">
-        <v>13.39656411771</v>
+        <v>1</v>
       </c>
       <c r="BB129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC129" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21265,15 +20874,12 @@
         <v>-0.8095535435529191</v>
       </c>
       <c r="AZ130" t="n">
-        <v>0.2816077793273518</v>
+        <v>2.816077793273518</v>
       </c>
       <c r="BA130" t="n">
-        <v>15.24780589347843</v>
+        <v>1</v>
       </c>
       <c r="BB130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21438,15 +21044,12 @@
         <v>-0.8061192631907587</v>
       </c>
       <c r="AZ131" t="n">
-        <v>0.2283823895902871</v>
+        <v>2.283823895902871</v>
       </c>
       <c r="BA131" t="n">
-        <v>12.36588830848125</v>
+        <v>1</v>
       </c>
       <c r="BB131" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC131" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21611,15 +21214,12 @@
         <v>-0.9432647644326476</v>
       </c>
       <c r="AZ132" t="n">
-        <v>0.4425021074703185</v>
+        <v>4.425021074703185</v>
       </c>
       <c r="BA132" t="n">
-        <v>15.32398352756091</v>
+        <v>1</v>
       </c>
       <c r="BB132" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC132" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21784,15 +21384,12 @@
         <v>-0.9047947568126941</v>
       </c>
       <c r="AZ133" t="n">
-        <v>0.3424239972728017</v>
+        <v>3.424239972728016</v>
       </c>
       <c r="BA133" t="n">
-        <v>15.37482698512445</v>
+        <v>0</v>
       </c>
       <c r="BB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21957,15 +21554,12 @@
         <v>-0.925575101488498</v>
       </c>
       <c r="AZ134" t="n">
-        <v>0.2877727947098655</v>
+        <v>2.877727947098654</v>
       </c>
       <c r="BA134" t="n">
-        <v>12.64306724710941</v>
+        <v>0</v>
       </c>
       <c r="BB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC134" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22130,15 +21724,12 @@
         <v>-0.8729547641963427</v>
       </c>
       <c r="AZ135" t="n">
-        <v>0.2286543990281047</v>
+        <v>2.286543990281047</v>
       </c>
       <c r="BA135" t="n">
-        <v>14.34571921902312</v>
+        <v>0</v>
       </c>
       <c r="BB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC135" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22303,15 +21894,12 @@
         <v>-0.8111718275652702</v>
       </c>
       <c r="AZ136" t="n">
-        <v>0.212522899192218</v>
+        <v>2.12522899192218</v>
       </c>
       <c r="BA136" t="n">
-        <v>12.07681251870081</v>
+        <v>0</v>
       </c>
       <c r="BB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC136" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22476,15 +22064,12 @@
         <v>-0.9191253037139883</v>
       </c>
       <c r="AZ137" t="n">
-        <v>0.2487492359828174</v>
+        <v>2.487492359828174</v>
       </c>
       <c r="BA137" t="n">
-        <v>12.92788698041661</v>
+        <v>0</v>
       </c>
       <c r="BB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22649,15 +22234,12 @@
         <v>-0.983991462113127</v>
       </c>
       <c r="AZ138" t="n">
-        <v>0.3634267201648407</v>
+        <v>3.634267201648408</v>
       </c>
       <c r="BA138" t="n">
-        <v>12.61555674855043</v>
+        <v>1</v>
       </c>
       <c r="BB138" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22822,15 +22404,12 @@
         <v>-0.8676616915422886</v>
       </c>
       <c r="AZ139" t="n">
-        <v>0.3529111782529205</v>
+        <v>3.529111782529205</v>
       </c>
       <c r="BA139" t="n">
-        <v>14.94309852934265</v>
+        <v>0</v>
       </c>
       <c r="BB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22995,15 +22574,12 @@
         <v>-0.9794520547945206</v>
       </c>
       <c r="AZ140" t="n">
-        <v>0.2763025421902743</v>
+        <v>2.763025421902743</v>
       </c>
       <c r="BA140" t="n">
-        <v>13.50197279742473</v>
+        <v>1</v>
       </c>
       <c r="BB140" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23168,15 +22744,12 @@
         <v>-0.8755935422602089</v>
       </c>
       <c r="AZ141" t="n">
-        <v>0.3071371534917146</v>
+        <v>3.071371534917147</v>
       </c>
       <c r="BA141" t="n">
-        <v>14.89304857028718</v>
+        <v>0</v>
       </c>
       <c r="BB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23341,15 +22914,12 @@
         <v>-0.8558154437680231</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0.2351665444744986</v>
+        <v>2.351665444744986</v>
       </c>
       <c r="BA142" t="n">
-        <v>12.33569292798704</v>
+        <v>0</v>
       </c>
       <c r="BB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23514,15 +23084,12 @@
         <v>-0.910299003322259</v>
       </c>
       <c r="AZ143" t="n">
-        <v>0.2634069568539765</v>
+        <v>2.634069568539765</v>
       </c>
       <c r="BA143" t="n">
-        <v>13.20241292636161</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23687,15 +23254,12 @@
         <v>-0.8479307025986524</v>
       </c>
       <c r="AZ144" t="n">
-        <v>0.2850083474322018</v>
+        <v>2.850083474322018</v>
       </c>
       <c r="BA144" t="n">
-        <v>14.72041205661443</v>
+        <v>1</v>
       </c>
       <c r="BB144" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23860,15 +23424,12 @@
         <v>-0.9031939413895291</v>
       </c>
       <c r="AZ145" t="n">
-        <v>0.3306302943724049</v>
+        <v>3.306302943724048</v>
       </c>
       <c r="BA145" t="n">
-        <v>13.50483650630982</v>
+        <v>1</v>
       </c>
       <c r="BB145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24033,15 +23594,12 @@
         <v>-0.8867924528301887</v>
       </c>
       <c r="AZ146" t="n">
-        <v>0.3753925003975221</v>
+        <v>3.753925003975221</v>
       </c>
       <c r="BA146" t="n">
-        <v>14.04704424717668</v>
+        <v>0</v>
       </c>
       <c r="BB146" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24206,15 +23764,12 @@
         <v>-0.9927797833935018</v>
       </c>
       <c r="AZ147" t="n">
-        <v>0.275498874631122</v>
+        <v>2.754988746311219</v>
       </c>
       <c r="BA147" t="n">
-        <v>12.39357609552841</v>
+        <v>0</v>
       </c>
       <c r="BB147" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24379,15 +23934,12 @@
         <v>-0.8752424046541692</v>
       </c>
       <c r="AZ148" t="n">
-        <v>0.204352754630459</v>
+        <v>2.043527546304591</v>
       </c>
       <c r="BA148" t="n">
-        <v>12.73705359648974</v>
+        <v>0</v>
       </c>
       <c r="BB148" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24552,15 +24104,12 @@
         <v>-0.9457209457209457</v>
       </c>
       <c r="AZ149" t="n">
-        <v>0.1613708822578354</v>
+        <v>1.613708822578354</v>
       </c>
       <c r="BA149" t="n">
-        <v>10.17299216629021</v>
+        <v>0</v>
       </c>
       <c r="BB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24725,15 +24274,12 @@
         <v>-0.8900032351989647</v>
       </c>
       <c r="AZ150" t="n">
-        <v>0.2776338886342699</v>
+        <v>2.776338886342698</v>
       </c>
       <c r="BA150" t="n">
-        <v>15.42719268663395</v>
+        <v>0</v>
       </c>
       <c r="BB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24898,15 +24444,12 @@
         <v>-0.9144542772861356</v>
       </c>
       <c r="AZ151" t="n">
-        <v>0.1992943083149607</v>
+        <v>1.992943083149608</v>
       </c>
       <c r="BA151" t="n">
-        <v>12.29805279278685</v>
+        <v>0</v>
       </c>
       <c r="BB151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25071,15 +24614,12 @@
         <v>-0.870988867059594</v>
       </c>
       <c r="AZ152" t="n">
-        <v>0.2929222953305048</v>
+        <v>2.929222953305048</v>
       </c>
       <c r="BA152" t="n">
-        <v>13.84738554555246</v>
+        <v>1</v>
       </c>
       <c r="BB152" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25244,15 +24784,12 @@
         <v>-0.9734422880490295</v>
       </c>
       <c r="AZ153" t="n">
-        <v>0.278928268195533</v>
+        <v>2.78928268195533</v>
       </c>
       <c r="BA153" t="n">
-        <v>12.99811599897735</v>
+        <v>1</v>
       </c>
       <c r="BB153" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25417,15 +24954,12 @@
         <v>-0.8216748768472907</v>
       </c>
       <c r="AZ154" t="n">
-        <v>0.3594130595075935</v>
+        <v>3.594130595075935</v>
       </c>
       <c r="BA154" t="n">
-        <v>13.08294443919041</v>
+        <v>0</v>
       </c>
       <c r="BB154" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC154" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25590,15 +25124,12 @@
         <v>-0.8612735542560104</v>
       </c>
       <c r="AZ155" t="n">
-        <v>0.2320891755316213</v>
+        <v>2.320891755316213</v>
       </c>
       <c r="BA155" t="n">
-        <v>12.9060602060763</v>
+        <v>0</v>
       </c>
       <c r="BB155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25763,15 +25294,12 @@
         <v>-1.018099547511312</v>
       </c>
       <c r="AZ156" t="n">
-        <v>0.3462797777914783</v>
+        <v>3.462797777914784</v>
       </c>
       <c r="BA156" t="n">
-        <v>14.93215294918606</v>
+        <v>0</v>
       </c>
       <c r="BB156" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC156" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25936,15 +25464,12 @@
         <v>-1.04876299749014</v>
       </c>
       <c r="AZ157" t="n">
-        <v>0.3554401383644461</v>
+        <v>3.554401383644462</v>
       </c>
       <c r="BA157" t="n">
-        <v>15.32716274738345</v>
+        <v>0</v>
       </c>
       <c r="BB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC157" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26109,15 +25634,12 @@
         <v>-0.8695652173913042</v>
       </c>
       <c r="AZ158" t="n">
-        <v>0.3274162961093018</v>
+        <v>3.274162961093018</v>
       </c>
       <c r="BA158" t="n">
-        <v>13.30667483923764</v>
+        <v>1</v>
       </c>
       <c r="BB158" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26278,15 +25800,12 @@
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="n">
-        <v>0.3352256061133059</v>
+        <v>3.352256061133059</v>
       </c>
       <c r="BA159" t="n">
-        <v>13.36339572806621</v>
+        <v>1</v>
       </c>
       <c r="BB159" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26447,15 +25966,12 @@
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="n">
-        <v>0.2434472726667247</v>
+        <v>2.434472726667246</v>
       </c>
       <c r="BA160" t="n">
-        <v>12.29154143560339</v>
+        <v>1</v>
       </c>
       <c r="BB160" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC160" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26620,15 +26136,12 @@
         <v>-0.9148648648648647</v>
       </c>
       <c r="AZ161" t="n">
-        <v>0.2193729066609965</v>
+        <v>2.193729066609965</v>
       </c>
       <c r="BA161" t="n">
-        <v>11.64590440849937</v>
+        <v>0</v>
       </c>
       <c r="BB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26793,15 +26306,12 @@
         <v>-0.875</v>
       </c>
       <c r="AZ162" t="n">
-        <v>0.2693134402703707</v>
+        <v>2.693134402703707</v>
       </c>
       <c r="BA162" t="n">
-        <v>12.17300558723502</v>
+        <v>1</v>
       </c>
       <c r="BB162" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26966,15 +26476,12 @@
         <v>-0.9019350606756315</v>
       </c>
       <c r="AZ163" t="n">
-        <v>0.2786500146224659</v>
+        <v>2.786500146224659</v>
       </c>
       <c r="BA163" t="n">
-        <v>13.42169439208957</v>
+        <v>1</v>
       </c>
       <c r="BB163" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27139,15 +26646,12 @@
         <v>-0.8602257636122178</v>
       </c>
       <c r="AZ164" t="n">
-        <v>0.3302696303234725</v>
+        <v>3.302696303234725</v>
       </c>
       <c r="BA164" t="n">
-        <v>14.07419437917497</v>
+        <v>1</v>
       </c>
       <c r="BB164" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27312,15 +26816,12 @@
         <v>-0.8340425531914893</v>
       </c>
       <c r="AZ165" t="n">
-        <v>0.3140509103601919</v>
+        <v>3.140509103601919</v>
       </c>
       <c r="BA165" t="n">
-        <v>13.33772096173453</v>
+        <v>0</v>
       </c>
       <c r="BB165" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC165" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27485,15 +26986,12 @@
         <v>-0.9123961218836566</v>
       </c>
       <c r="AZ166" t="n">
-        <v>0.4419867263324095</v>
+        <v>4.419867263324095</v>
       </c>
       <c r="BA166" t="n">
-        <v>16.97539046167085</v>
+        <v>1</v>
       </c>
       <c r="BB166" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27658,15 +27156,12 @@
         <v>-0.9287135278514589</v>
       </c>
       <c r="AZ167" t="n">
-        <v>0.2822534280040117</v>
+        <v>2.822534280040117</v>
       </c>
       <c r="BA167" t="n">
-        <v>11.65132875248652</v>
+        <v>1</v>
       </c>
       <c r="BB167" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27831,15 +27326,12 @@
         <v>-0.794580970384373</v>
       </c>
       <c r="AZ168" t="n">
-        <v>0.3720589980627997</v>
+        <v>3.720589980627997</v>
       </c>
       <c r="BA168" t="n">
-        <v>15.11954301763624</v>
+        <v>0</v>
       </c>
       <c r="BB168" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28004,15 +27496,12 @@
         <v>-0.8666886109282422</v>
       </c>
       <c r="AZ169" t="n">
-        <v>0.3370510290002701</v>
+        <v>3.370510290002701</v>
       </c>
       <c r="BA169" t="n">
-        <v>12.83721020627359</v>
+        <v>0</v>
       </c>
       <c r="BB169" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28177,15 +27666,12 @@
         <v>-0.8734652114597544</v>
       </c>
       <c r="AZ170" t="n">
-        <v>0.3618600999053327</v>
+        <v>3.618600999053328</v>
       </c>
       <c r="BA170" t="n">
-        <v>15.67979022827618</v>
+        <v>0</v>
       </c>
       <c r="BB170" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28350,15 +27836,12 @@
         <v>-0.9163306451612903</v>
       </c>
       <c r="AZ171" t="n">
-        <v>0.254785183807967</v>
+        <v>2.547851838079669</v>
       </c>
       <c r="BA171" t="n">
-        <v>11.61765076524852</v>
+        <v>0</v>
       </c>
       <c r="BB171" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28523,15 +28006,12 @@
         <v>-0.8450749123366273</v>
       </c>
       <c r="AZ172" t="n">
-        <v>0.3188696860136649</v>
+        <v>3.18869686013665</v>
       </c>
       <c r="BA172" t="n">
-        <v>14.69626650381366</v>
+        <v>1</v>
       </c>
       <c r="BB172" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28696,15 +28176,12 @@
         <v>-0.8522613065326633</v>
       </c>
       <c r="AZ173" t="n">
-        <v>0.399707243754127</v>
+        <v>3.99707243754127</v>
       </c>
       <c r="BA173" t="n">
-        <v>12.47173871860493</v>
+        <v>1</v>
       </c>
       <c r="BB173" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28869,15 +28346,12 @@
         <v>-0.9190476190476191</v>
       </c>
       <c r="AZ174" t="n">
-        <v>0.3801718619146223</v>
+        <v>3.801718619146223</v>
       </c>
       <c r="BA174" t="n">
-        <v>14.2475185393632</v>
+        <v>0</v>
       </c>
       <c r="BB174" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29042,15 +28516,12 @@
         <v>-0.8253346392425727</v>
       </c>
       <c r="AZ175" t="n">
-        <v>0.2470312536106503</v>
+        <v>2.470312536106503</v>
       </c>
       <c r="BA175" t="n">
-        <v>11.3388765448196</v>
+        <v>1</v>
       </c>
       <c r="BB175" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC175" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29215,15 +28686,12 @@
         <v>-0.8593242365172189</v>
       </c>
       <c r="AZ176" t="n">
-        <v>0.2303895675632164</v>
+        <v>2.303895675632163</v>
       </c>
       <c r="BA176" t="n">
-        <v>10.92082410889718</v>
+        <v>1</v>
       </c>
       <c r="BB176" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC176" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29388,15 +28856,12 @@
         <v>-1.011280931586608</v>
       </c>
       <c r="AZ177" t="n">
-        <v>0.2939442645614514</v>
+        <v>2.939442645614514</v>
       </c>
       <c r="BA177" t="n">
-        <v>13.1516753899925</v>
+        <v>1</v>
       </c>
       <c r="BB177" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC177" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29561,15 +29026,12 @@
         <v>-0.8638230647709321</v>
       </c>
       <c r="AZ178" t="n">
-        <v>0.3054467120359153</v>
+        <v>3.054467120359153</v>
       </c>
       <c r="BA178" t="n">
-        <v>13.45013914035445</v>
+        <v>1</v>
       </c>
       <c r="BB178" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC178" t="n">
         <v>1</v>
       </c>
     </row>
@@ -29734,15 +29196,12 @@
         <v>-0.8194444444444445</v>
       </c>
       <c r="AZ179" t="n">
-        <v>0.2464363334952325</v>
+        <v>2.464363334952325</v>
       </c>
       <c r="BA179" t="n">
-        <v>13.35702874314139</v>
+        <v>1</v>
       </c>
       <c r="BB179" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29907,15 +29366,12 @@
         <v>-0.8907371167645139</v>
       </c>
       <c r="AZ180" t="n">
-        <v>0.3280651598232026</v>
+        <v>3.280651598232026</v>
       </c>
       <c r="BA180" t="n">
-        <v>12.92183174935129</v>
+        <v>0</v>
       </c>
       <c r="BB180" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30080,15 +29536,12 @@
         <v>-0.9359058207979072</v>
       </c>
       <c r="AZ181" t="n">
-        <v>0.3562090494563998</v>
+        <v>3.562090494563997</v>
       </c>
       <c r="BA181" t="n">
-        <v>15.23965851812918</v>
+        <v>1</v>
       </c>
       <c r="BB181" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC181" t="n">
         <v>1</v>
       </c>
     </row>
